--- a/datasets/AU_attributes/aposteriori_unimodal_attitudes.politics.xlsx
+++ b/datasets/AU_attributes/aposteriori_unimodal_attitudes.politics.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T21"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,85 +441,80 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>toany</t>
+          <t>annotatorMinority</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>annotatorMinority</t>
+          <t>annotatorPolitics</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>bert</t>
+          <t>traditionalism</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>annotatorPolitics</t>
+          <t>annotatorRace</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>traditionalism</t>
+          <t>annotatorAge</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>annotatorRace</t>
+          <t>annotatorGender</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>annotatorAge</t>
+          <t>freeSpeech</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>annotatorGender</t>
+          <t>harmHateSpeech</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>freeSpeech</t>
+          <t>intent</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>harmHateSpeech</t>
+          <t>lingPurism</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>intent</t>
+          <t>racism</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>lingPurism</t>
+          <t>racist</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>racism</t>
+          <t>annotator_count</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>racist</t>
+          <t>scores</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>scores</t>
+          <t>HIST</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>HIST</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>DFU</t>
         </is>
@@ -527,1962 +522,1549 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>32</v>
+        <v>131</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>"My Grammy never stops talking. She will talk to you for an hour straight with only the ""mhmm"" responses n give no fucks."</t>
+          <t>Exactly, not only that but BLM has been talking about white privilege for awhile now, yet it's the white privilege which is attracting them to our woman and our own woman to whites. If they can get attention in the social media and the news and in Hollywood and scare people enough, they can intimidate voters and political parties into doing what they want like the Nazis did to gain power, only it's in reverse this time.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[2, 1, 3, 3, 1, 1]</t>
+          <t>[5, 5, 1, 5, 5, 5]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[2, 1, 4, 3, 1, 1]</t>
+          <t>['{}', 'black; female', nan, '{}', '{}', '{}']</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>['Black american', '{}', '{}', '{}', '{}', '{}']</t>
+          <t>['center', 'far left', 'far right', 'center', 'left', 'far left']</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[0.374459445476532, 0.1750366985797882, 0.18394684791564941, 0.039672426879405975, 0.24010665714740753, -0.18678389489650726, 0.19001220166683197, 0.3435990512371063, -0.26791414618492126, 0.010608158074319363, 0.06268418580293655, -0.000760797644034028, -0.4113321900367737, 0.4967348873615265, 0.09519940614700317, -0.0876065269112587, -0.2074437290430069, 0.24990028142929077, -0.3806615471839905, -0.1424223929643631, -0.2143644243478775, 0.006524036638438702, 0.029219821095466614, -0.12881208956241608, -0.26125961542129517, 0.11023221909999847, 0.16716699302196503, -0.35560137033462524, -0.357138991355896, 0.09226297587156296, -0.23845915496349335, -0.10166221112012863, 0.07002048939466476, -0.0692884624004364, -0.23911932110786438, 0.12836073338985443, -0.11286277323961258, 0.26746314764022827, -0.05616606026887894, -0.10514776408672333, -0.24127979576587677, 0.11944998055696487, -0.05923069640994072, -0.2905561327934265, -0.12452563643455505, 0.13190853595733643, -3.6059072017669678, -0.22051353752613068, 0.3595612645149231, -0.3121044635772705, 0.04468162730336189, -0.07324021309614182, -0.2951444089412689, -0.02807294949889183, 0.4720187187194824, -0.08338020741939545, -0.18610720336437225, -0.05113591253757477, 0.15134596824645996, 0.013157995417714119, 0.4705774784088135, 0.30244719982147217, -0.4010734558105469, 0.18961545825004578, 0.18982580304145813, 0.1333325356245041, 0.05556662753224373, 0.0884428545832634, -0.030535271391272545, 0.5122504830360413, -0.07323753833770752, -0.4613927900791168, 0.1515742540359497, -0.28069135546684265, 0.3184241056442261, 0.040312204509973526, -0.15713152289390564, 0.3140885531902313, 0.38081094622612, 0.30001750588417053, -0.08931241184473038, 0.08183065056800842, 0.24704119563102722, -0.12832021713256836, -0.25474756956100464, 0.2871052920818329, 0.02904762700200081, 0.32498881220817566, -0.16476960480213165, -0.036211028695106506, -0.14563775062561035, 0.04754561558365822, -0.05541514232754707, -0.3049798607826233, 0.2544020116329193, -0.24328738451004028, 0.011884515173733234, 0.11887948960065842, 0.08222956955432892, 0.34866049885749817, -0.027707327157258987, -0.28925031423568726, -0.15045562386512756, -0.41152238845825195, -0.05915018171072006, -0.08456501364707947, -0.18489687144756317, 0.07824774086475372, 0.29140540957450867, -2.2818188667297363, 0.3803642988204956, 0.2042611688375473, 0.04440711811184883, -0.4398238956928253, -0.20757442712783813, 0.15043096244335175, 0.6717333793640137, 0.06993140280246735, 0.031407345086336136, 0.07724212855100632, -0.17574244737625122, 0.19261620938777924, 0.4222624599933624, -0.2320183664560318, 0.12748955190181732, 0.21086610853672028, 0.1485329121351242, 0.01621044985949993, 0.014066098257899284, 0.4731455445289612, -0.06770536303520203, 0.3079717755317688, -0.04935760423541069, 0.17484784126281738, -0.3551827669143677, 0.21839264035224915, 0.08796367049217224, -0.4100631773471832, 0.3108788728713989, 0.03890848904848099, -0.5255451202392578, -0.13472025096416473, -3.3146674633026123, 0.3697202801704407, 0.055447131395339966, -0.0037222388200461864, -0.07165849208831787, 0.0990825742483139, -0.06924103945493698, 0.587361752986908, 0.21092402935028076, 0.18656806647777557, -0.123125821352005, -0.20987863838672638, -0.32784315943717957, -0.4956643879413605, -0.14388267695903778, -0.11271463334560394, 0.17613843083381653, 0.3506719768047333, 0.021973762661218643, -0.008772152476012707, -0.2556697130203247, -0.0977216511964798, -0.30087921023368835, -0.01767190545797348, 0.2689434885978699, 0.4307289123535156, -0.27483752369880676, -0.3927803337574005, 0.004309022333472967, 0.16602367162704468, 0.362601637840271, 0.0172750074416399, -0.13864006102085114, -0.1427268534898758, 0.3575350046157837, 0.21612469851970673, -0.04041435196995735, -0.15477202832698822, -0.3233354985713959, 0.09644865989685059, 0.06565061211585999, 0.08502967655658722, 0.39692971110343933, -0.22852030396461487, 0.6510151624679565, 0.14154525101184845, -0.19787609577178955, 0.2140522003173828, -0.3688008189201355, -0.20756682753562927, 0.3603973984718323, 0.23897463083267212, 0.058256883174180984, -0.20196814835071564, 0.34559065103530884, -0.2921854555606842, 0.21103215217590332, 0.37539243698120117, -0.1870337873697281, -0.037064552307128906, 0.057919684797525406, -0.5333690047264099, -0.5083895921707153, 4.311912536621094, 0.12228608131408691, -0.11483906209468842, 0.2746317684650421, 0.2398640215396881, -0.13819581270217896, 0.13399085402488708, -0.024220822378993034, -0.19454771280288696, -0.24475257098674774, -0.09682749211788177, 0.4837818145751953, -0.2674146890640259, -0.15504509210586548, -0.15695850551128387, 0.06397472321987152, 0.2878458499908447, -0.384248286485672, -0.15237493813037872, -0.29205843806266785, -0.08192729949951172, -0.2287660837173462, -0.104098379611969, -0.034730877727270126, -1.718609094619751, 0.022981077432632446, -0.35199618339538574, -0.2875485122203827, 0.2838161289691925, 0.3107942044734955, 0.37518101930618286, 0.2541871964931488, 0.2903200387954712, 0.16617779433727264, -0.10201786458492279, 0.16352824866771698, 0.3816727101802826, -0.05675933510065079, 0.3466907739639282, -0.23182974755764008, 0.5694490075111389, 0.07846513390541077, -0.37294530868530273, -0.21335168182849884, 0.1682850569486618, 0.07231450825929642, 0.1463288962841034, -0.06650856882333755, 0.050707072019577026, 0.19631311297416687, 0.43572336435317993, -0.09797587245702744, 0.18727174401283264, -0.24183230102062225, -0.37450116872787476, -0.578693151473999, -0.25923871994018555, 0.327412486076355, 0.0919896736741066, -0.31991398334503174, 0.32365795969963074, -0.012237221002578735, 0.10256332159042358, -0.10610664635896683, -0.028225500136613846, 0.3259163200855255, -0.01715601049363613, -0.041627682745456696, -3.680157423019409, 0.16894753277301788, -0.23407773673534393, 0.2579424977302551, 0.06528361141681671, 0.015561515465378761, -0.3989129960536957, -0.06131698191165924, 0.31241175532341003, -0.32179489731788635, -0.00334224128164351, 0.4968445301055908, -0.14125210046768188, -0.043597374111413956, -0.6860787868499756, 0.6449692845344543, 0.13810813426971436, 0.011914094910025597, -0.1732405573129654, 0.045405711978673935, 0.300489217042923, 0.16657060384750366, -0.6737754940986633, 0.34178322553634644, -0.2265983521938324, 0.17883968353271484, 0.1405872106552124, -0.43962690234184265, -0.05204681679606438, 0.42278629541397095, 0.38466745615005493, -0.10466285049915314, 0.17478376626968384, -0.2407846450805664, -0.2858499586582184, -3.539674997329712, -0.00937762949615717, -0.23713935911655426, -0.32798850536346436, 0.20727697014808655, -0.22387300431728363, 0.43116888403892517, -0.25914788246154785, -0.32494479417800903, 0.5872281789779663, -0.013003730215132236, -0.02773366868495941, 0.05854588374495506, -0.04666011780500412, 0.16009917855262756, 0.20312350988388062, 0.12961886823177338, -0.45314547419548035, -0.003273717826232314, 0.19182853400707245, 0.1710662990808487, -0.10973960906267166, -0.06733844429254532, 0.11904026567935944, 0.2055414319038391, 0.42537760734558105, -0.3242322504520416, 0.09598182886838913, -0.11403288692235947, -0.3041570484638214, 0.14949581027030945, 0.005701543763279915, -0.031877551227808, -0.33098843693733215, -0.16967058181762695, -0.2967384159564972, 0.457346111536026, 0.3861444890499115, 0.23464392125606537, 0.1292579472064972, 0.18763363361358643, 0.1062106341123581, -0.04862634092569351, 0.20113924145698547, 0.04376479238271713, 0.16488641500473022, 0.34646493196487427, -0.33900386095046997, -0.21941253542900085, 0.24874168634414673, -0.02949400804936886, -0.2217002660036087, 1.1669795513153076, 0.13703973591327667, 0.16453272104263306, -0.29779744148254395, 0.05222185328602791, -0.061855725944042206, 0.2188786417245865, -0.03892575949430466, 0.42702922224998474, -0.5424349904060364, 0.028287053108215332, 0.07944748550653458, -0.08390429615974426, -0.36012205481529236, 0.2804468274116516, -0.436423659324646, 0.07934676855802536, 0.2892024517059326, -0.0479363314807415, 0.1097915917634964, 0.02148277498781681, -1.3970370292663574, -0.05157838016748428, 0.1435825377702713, -0.013383714482188225, 0.42591869831085205, -0.3042648732662201, 0.08795911818742752, -0.09856180846691132, 0.06922043114900589, 0.2549750804901123, 0.26222240924835205, -0.5666810870170593, 0.012982198968529701, -0.0675036832690239, 0.23452255129814148, -0.17242513597011566, 0.043402645736932755, -0.0943569466471672, 0.2352752685546875, -0.10766300559043884, -0.10121749341487885, 0.05024624988436699, 0.1024518758058548, 0.23516333103179932, -0.2768627107143402, -0.007964515127241611, 0.09398466348648071, 0.07768107950687408, -0.32668647170066833, 0.03138161823153496, -0.08831733465194702, -0.013380272313952446, -0.0017225088085979223, -0.7499580383300781, 0.5630412101745605, -0.02239716611802578, -0.04065028578042984, -0.33566319942474365, 0.2522500455379486, -0.39962050318717957, 0.0012006753822788596, 0.8683096170425415, 0.13952666521072388, -0.0876629501581192, 0.5180781483650208, -0.11984933167695999, -0.07002843916416168, 0.3468650281429291, 0.40181735157966614, -0.13189290463924408, 0.25656983256340027, -0.35588589310646057, -0.034204594790935516, -0.05571020394563675, 0.050858207046985626, 0.0049147638492286205, 0.19747452437877655, 0.04837818816304207, 0.04795697703957558, -0.02859179861843586, -0.4536491930484772, -0.16672244668006897, 0.05587249621748924, 0.03496914729475975, -0.01825787127017975, 0.24648432433605194, -0.019770855084061623, 0.19383206963539124, 0.12663429975509644, 0.01253268402069807, 0.7225856184959412, -0.35331910848617554, 0.400357186794281, 0.05473543703556061, -0.06359334290027618, -0.1518317013978958, 0.3479182720184326, 0.1213783323764801, -0.09937246888875961, 0.13398301601409912, -0.22766412794589996, -0.05062442645430565, 0.26133695244789124, -0.22284603118896484, 0.4336373805999756, 0.05794310197234154, 0.30943766236305237, 0.17069947719573975, -0.10836618393659592, -1.5931181907653809, -0.021246811375021935, 0.3882538080215454, -0.12047675997018814, 0.09839469194412231, -0.09310296177864075, 0.06806930154561996, 0.6036596894264221, 0.214784637093544, -0.17421852052211761, -0.08954451233148575, 0.17892207205295563, -0.03654976934194565, 0.1864905059337616, 0.21502774953842163, -0.2189197689294815, 0.5117000937461853, -0.16307997703552246, 0.033012766391038895, 0.2017831653356552, 0.4645363688468933, 0.2033025026321411, 0.2252442091703415, 0.45459243655204773, 0.16612128913402557, -0.3545790910720825, -0.04315242916345596, 0.4174840748310089, -0.11096592992544174, 0.012004814110696316, 0.2871250808238983, 0.033453043550252914, -0.4859505295753479, -0.6261860728263855, 0.3887459635734558, 0.266737699508667, -0.14137351512908936, 0.2770659029483795, 0.30014368891716003, 0.5396667122840881, -0.10695845633745193, 0.48787152767181396, 0.268391877412796, 0.4386051595211029, 0.4825739860534668, 0.10256476700305939, -0.044591695070266724, 0.1298976093530655, 0.18995366990566254, -0.20107851922512054, -0.24550756812095642, -0.014320878311991692, -0.16078782081604004, -0.15227892994880676, 0.023585064336657524, -0.2904135584831238, 0.13629598915576935, 0.12530484795570374, 0.10928233712911606, -0.3018477261066437, 0.13995297253131866, 0.13183218240737915, -0.246071457862854, 0.1542661041021347, -0.46964147686958313, -0.8171577453613281, 0.1317613571882248, -0.32596468925476074, 0.10400737076997757, 0.27599528431892395, 0.510492205619812, 0.08240900188684464, -0.33941060304641724, -0.06413038820028305, -0.36631137132644653, 0.7528637051582336, -0.17497102916240692, 0.36309048533439636, 0.21554234623908997, -0.12735214829444885, -0.1284901648759842, -0.05070694163441658, 0.07176421582698822, 0.31739190220832825, 0.10220450907945633, 0.03306322172284126, -0.14218440651893616, -0.07735901325941086, 0.026845036074519157, -0.13854433596134186, -0.27617982029914856, -0.4042271375656128, 0.31099697947502136, -0.20753860473632812, 0.365892231464386, -0.10041636973619461, 0.15044249594211578, 0.12386003881692886, 0.0014521628618240356, 0.00957469642162323, -0.4047219157218933, 0.03701168671250343, 0.49152129888534546, 0.4902339279651642, 0.31180697679519653, 0.41550204157829285, 0.240350604057312, -0.02769569680094719, -0.1831773966550827, -0.3065933287143707, 0.28877028822898865, -0.16655313968658447, -0.05317500978708267, -0.12539872527122498, -0.10850895941257477, -0.025243740528821945, 0.4933210611343384, 0.05347415432333946, 2.329782247543335, 0.27046138048171997, -0.22747895121574402, -0.28816965222358704, 0.21768179535865784, 0.033637069165706635, -0.06638029962778091, -0.11225639283657074, 0.2167978435754776, 0.5648358464241028, -0.29122114181518555, 0.4946313798427582, -0.09825503081083298, -0.18823042511940002, 0.3721804618835449, 0.2856598496437073, 0.12321890145540237, -0.40636762976646423, -0.475726455450058, 0.11537891626358032, -0.17849421501159668, 0.3763706684112549, -0.09335991740226746, -0.27502623200416565, -0.15418438613414764, -0.09991303086280823, 0.3429725468158722, 0.20221200585365295, 0.17916204035282135, 0.48178377747535706, -0.3843262791633606, -0.2624666690826416, 0.1528664529323578, 0.05923907831311226, -0.15622155368328094, -0.10846392810344696, 0.1807306855916977, 0.17606008052825928, 0.12983426451683044, 0.0900924876332283, 0.19773419201374054, -0.38333243131637573, 0.27361375093460083, 0.004918897058814764, -0.23784588277339935, 0.3789252042770386, 0.2097049504518509, -0.07447627931833267, 0.23144155740737915, -0.03467613458633423, 0.1045026108622551, 0.30157312750816345, 0.1964416354894638, -0.2923423647880554, 0.37499985098838806, -0.14688529074192047, -0.2338453084230423, -0.017687641084194183, -0.3760054111480713, 0.22711895406246185, -0.18665675818920135, 0.12372544407844543, 0.150115966796875, -0.04342172294855118, -0.04704989865422249, -0.3055206835269928, -0.3441869914531708, -0.39578622579574585, 0.1469247192144394, -0.7554191946983337, -0.3127509355545044, 0.10395009815692902, 0.3225424885749817, 0.014672321267426014, 0.330570250749588, 0.3381301462650299, 0.30255234241485596, -0.5416148900985718, -0.31596294045448303, -2.711977481842041, 0.07095973938703537, -0.0905270203948021, 0.22577914595603943, 0.21061719954013824, 0.04730971157550812, 0.5108411312103271, -0.16401661932468414, 0.1256723403930664, -0.03154776990413666, 0.22958548367023468, 0.3406836688518524, 0.07050041109323502, -0.042908042669296265, 0.11359372735023499, 0.037512071430683136, -0.07241295278072357, -0.3395543694496155, -0.06771083921194077, -0.3636418282985687, 0.43877583742141724, 0.11942507326602936, 0.10500074177980423, 0.0037583683151751757, -0.4169212877750397, 0.13851623237133026, 0.03774570673704147, -0.1193988025188446, 0.01232972927391529, -0.19324098527431488, -0.44179123640060425, 0.5584561228752136, -0.29835212230682373, -0.0007251134957186878, -0.3158634901046753, -0.08006684482097626, -0.050744909793138504, 0.04942862689495087, -0.39696115255355835, -0.09511993080377579, 0.03147241845726967, 0.7087212800979614, -0.13511161506175995, 0.13368278741836548, -0.2751483619213104, 0.10269676893949509, 0.4282105267047882, 0.08048487454652786, 0.06944726407527924, 0.00920814834535122, 0.057845376431941986, 0.11064432561397552, 0.26933804154396057, 0.31569236516952515, -0.10611653327941895, 0.08740713447332382, 0.20370079576969147, -0.028394779190421104, 0.1075722873210907, -0.3432503044605255, -0.2805697023868561, 0.23374556005001068, 0.07069651037454605, -0.07555210590362549, 0.2745231091976166, -0.05706378072500229, -0.317635715007782, 0.2772144377231598, -0.2878321409225464, -0.2311398833990097, -0.17369556427001953, 0.16698013246059418, 0.26070594787597656, -0.05873989686369896, 0.12037192285060883, -0.01898067258298397, 0.5473326444625854, -0.01430446095764637, 0.2799437642097473, -0.5426046848297119, -0.1274389922618866, -0.14539390802383423, 0.4122866988182068, -0.41744542121887207, 0.1683962047100067, -6.979092121124268, 0.2202601134777069, -0.2882018983364105, -0.4080060124397278, -0.03679599240422249, -0.7038924694061279, -0.20673508942127228, -0.019551491364836693, 0.2289578765630722, -0.2518870532512665, 0.43546491861343384, 0.030797049403190613, -0.034553926438093185, -0.24181683361530304, 0.365812748670578, 0.3573201596736908]</t>
+          <t>['high', 'medium', 'medium', 'high', 'medium', 'high']</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>[-0.5, -0.5, 0.5, 0.5, -1.0, -1.0]</t>
+          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[5, 3, 3, 4, 4, 4]</t>
+          <t>[35.0, 40.0, 35.0, 40.0, 45.0, 25.0]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
+          <t>['man', 'woman', 'man', 'woman', 'woman', 'man']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>[30.0, 30.0, 35.0, 35.0, 40.0, 30.0]</t>
+          <t>[1, 1, 5, 1, 2, 1]</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>['man', 'woman', 'man', 'woman', 'man', 'man']</t>
+          <t>[4, 5, 1, 5, 3, 4]</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1, 3]</t>
+          <t>[5, 5, 1, 5, 5, 5]</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>[5, 4, 4, 5, 5, 5]</t>
+          <t>[4, 4, 5, 5, 3, 5]</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>[2, 1, 4, 2, 1, 1]</t>
+          <t>[1, 1, 5, 1, 2, 1]</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 5, 3, 4]</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>[5, 1, 3, 1, 1, 1]</t>
-        </is>
+          <t>[5, 5, 2, 5, 5, 5]</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>6</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>[1, 1, 4, 1, 1, 1]</t>
+          <t>[5, 5, 1, 5, 5, 5]</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>[2, 1, 3, 3, 1, 1]</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>[0.5        0.16666667 0.33333333 0.         0.        ]</t>
-        </is>
-      </c>
-      <c r="T2" t="n">
-        <v>0.3333333333333333</v>
+          <t>[0.16666667 0.         0.         0.         0.83333333]</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>53</v>
+        <v>172</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>#feminists disagree, for a generation that grew up with the whisper song, get low, Buble butt &amp; bitches aint shit... We've come along way</t>
+          <t>I always hated visiting Nig York, but if I'm ever forced to I'll be sure to pack all my Confederate clothes and flags and to dance around Central Park! ( I may need a little protection)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[1, 1, 3, 3, 1, 1]</t>
+          <t>[5, 5, 3, 5, 5, 5]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[1, 1, 4, 3, 3, 1]</t>
+          <t>['{}', '{}', nan, 'none', '{}', '{}']</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['Black american', '{}', '{}', '{}', 'Jewish', nan]</t>
+          <t>['left', 'center', 'far right', 'left', 'left', 'left']</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[0.32393571734428406, -0.15556733310222626, 0.3630802035331726, -0.35930976271629333, -0.533163845539093, -0.07320702821016312, 0.7095556855201721, 0.4875403344631195, 0.01808616705238819, -0.3436216413974762, 0.22299548983573914, 0.32796791195869446, -0.16725896298885345, 0.8240855932235718, 0.11069746315479279, 0.5498968362808228, -0.21373455226421356, 0.13822831213474274, 0.34016239643096924, -0.0059905587695539, 0.0636095330119133, -0.07424671202898026, 0.528918445110321, -0.13900743424892426, 0.14118066430091858, 0.11341707408428192, 0.2075546681880951, -0.5705676078796387, -0.34785592555999756, 0.5999587178230286, -0.19912369549274445, 0.6221951246261597, -0.41572046279907227, -0.007507155183702707, 0.613330602645874, -0.15714296698570251, 0.07549737393856049, 0.1184234768152237, 0.747262716293335, 0.09921678900718689, -0.4792092740535736, -0.1454397588968277, 0.2419825941324234, -0.0016867411322891712, -0.17950814962387085, -0.047736186534166336, -3.7543795108795166, 0.10501015186309814, -0.2774803340435028, -0.4131146967411041, 0.1417028307914734, -0.525246262550354, -0.191148042678833, 0.6320850253105164, 0.11507308483123779, 0.24292057752609253, -0.18838009238243103, 0.21966731548309326, -0.02379021793603897, 0.10434465110301971, 0.4613264799118042, 0.032340966165065765, -0.1904124766588211, 0.029813522472977638, -0.2742066979408264, 0.1311160773038864, -0.023515526205301285, 0.37277188897132874, -0.5047023892402649, 0.5611194372177124, -0.7014790773391724, -0.2712181508541107, 0.5932232141494751, -0.47084784507751465, -0.14199350774288177, -0.02320273034274578, -0.13114199042320251, 0.607715368270874, -0.2151101529598236, -0.06941649317741394, -0.24082894623279572, 0.569916307926178, 0.3430994153022766, 0.48591187596321106, -0.09349603950977325, 0.4755690097808838, 0.38198161125183105, -0.29464471340179443, -0.026059862226247787, 0.7042309045791626, -0.34979066252708435, -0.33763042092323303, -0.42559394240379333, 0.21512216329574585, 0.6037312746047974, 0.09690988808870316, 0.40431666374206543, 0.0269053652882576, 0.2235316038131714, 0.8029205203056335, 0.2641580402851105, 0.09942984580993652, 0.3054206967353821, -0.7809670567512512, -0.305697500705719, -0.03992222622036934, -0.02525651641190052, -0.13396970927715302, 0.30586621165275574, -1.8801636695861816, 0.659387469291687, 0.23433229327201843, -0.2707289457321167, -0.5109279751777649, 0.3155577778816223, 0.03375978022813797, 0.4616550803184509, -0.18807189166545868, 0.16983728110790253, 0.4410032033920288, -0.5677628517150879, 0.41008153557777405, 0.01227322407066822, -0.07598179578781128, 0.1425870656967163, 0.46356746554374695, 0.05551186203956604, 0.312666654586792, -0.10480628907680511, 0.456798791885376, 0.28332430124282837, 0.45153406262397766, -0.10746275633573532, -0.6452776193618774, -0.1839161217212677, -0.05622035637497902, 0.6687511205673218, -0.28459152579307556, 0.1713891327381134, 0.02477124333381653, -0.41581103205680847, -0.07031985372304916, -2.440474271774292, -0.05480945110321045, 0.8810675144195557, 0.06649888306856155, -0.6159719824790955, -0.024733316153287888, -0.4005666971206665, 0.15769347548484802, 0.0658922791481018, -0.07814408838748932, 0.33590924739837646, -0.24397233128547668, -0.5179211497306824, -0.49004891514778137, -0.4149114191532135, -0.08791396766901016, 0.2924540340900421, 0.8908694982528687, -0.1981913447380066, 0.04666455090045929, 0.33367037773132324, 0.0773748904466629, -0.15783853828907013, -0.31737959384918213, 0.07281080633401871, 0.32806575298309326, -0.29622626304626465, -0.11997966468334198, 0.29297778010368347, -0.2478523999452591, 0.6286811828613281, 0.042165063321590424, 0.47500479221343994, 0.5506865978240967, -0.019522955641150475, 0.2026786357164383, -0.2698037624359131, -0.19097022712230682, -0.3790413737297058, 0.5401566028594971, 0.20906628668308258, -0.06183266639709473, 0.7471281290054321, -0.3565988838672638, 0.6702805757522583, -0.16816264390945435, 0.1538073867559433, 0.135809063911438, -0.5248678922653198, -0.7753051519393921, 0.5309966802597046, 0.4525168538093567, 0.665465772151947, -0.15265478193759918, 0.3232894539833069, -0.5686280131340027, 0.04390852525830269, -0.08109626173973083, 0.26709261536598206, -0.3084076941013336, 0.45194366574287415, -0.18111194670200348, -0.7727661728858948, 4.057440280914307, -0.11729499697685242, -0.04433749243617058, -0.22196179628372192, 0.1176871582865715, -0.38325822353363037, 0.2613684833049774, -0.5153442621231079, -0.06803102046251297, -0.13814249634742737, 0.029727650806307793, 0.6183047890663147, -0.2509740889072418, 0.05459257587790489, 0.18238338828086853, -0.05105939134955406, 0.20201127231121063, -0.006154966540634632, -0.3368772566318512, -0.18642593920230865, -0.13544820249080658, 0.0135321244597435, -0.31687459349632263, 0.03536392003297806, -1.3669240474700928, 0.09580792486667633, 0.14791250228881836, -0.5430815815925598, 0.622039794921875, -0.11900664120912552, 0.21138069033622742, -0.07327622175216675, 0.020516084507107735, -0.0958254411816597, 0.002726656850427389, 0.24501071870326996, 0.3893662691116333, 0.44914278388023376, 0.6836077570915222, -0.3846379816532135, 0.32992836833000183, 0.2910626530647278, -0.7862752079963684, 0.12652969360351562, 0.21852189302444458, 0.21364127099514008, 0.2261354625225067, -0.07601885497570038, -0.02510022185742855, 0.3024349808692932, 0.37239328026771545, 0.08817476779222488, -0.2653259038925171, 0.05226941034197807, -0.6847356557846069, -0.1983335018157959, -0.1974741369485855, 0.020627640187740326, 0.17632628977298737, -0.1330854743719101, -0.41040876507759094, -0.24849185347557068, 0.086868517100811, 0.05912748724222183, -0.021747570484876633, 0.12659023702144623, 0.3461133539676666, -0.22097298502922058, -2.4566423892974854, -0.12726232409477234, -0.05043306574225426, 0.4640611708164215, 0.04478050395846367, -0.30292466282844543, -0.6991070508956909, 0.19461393356323242, 0.3987315893173218, -0.20877613127231598, 0.30880221724510193, 0.16106009483337402, 0.09674220532178879, 0.4219985902309418, -0.3049343228340149, 0.36891970038414, 0.25038132071495056, -0.3761475682258606, -0.3812183439731598, -0.21588778495788574, -0.0618310384452343, 0.1397741436958313, 0.04392927512526512, 0.17941026389598846, 0.22984027862548828, -0.31094038486480713, 0.27158668637275696, -0.35958853363990784, -0.004790614824742079, -0.23394766449928284, 0.3008359372615814, -0.25444480776786804, -0.0987449437379837, 0.028716707602143288, -0.09009326249361038, -3.993335485458374, 0.09088645875453949, -0.1108061894774437, -0.3516658842563629, -0.07520872354507446, -0.2522505223751068, 0.4368753731250763, -0.07628834247589111, -0.5604135990142822, 0.007057906128466129, 0.06786128133535385, 0.51548832654953, 0.31925511360168457, 0.1674242913722992, 0.34449511766433716, -0.13570553064346313, 0.4461438059806824, -0.39007729291915894, 0.016474315896630287, -0.10790281742811203, 0.1791716068983078, 0.030481085181236267, 0.18174192309379578, 0.10666105151176453, 0.14427906274795532, 0.055115632712841034, -0.6459688544273376, -0.13616643846035004, -0.24983495473861694, 0.04163770377635956, 0.20747493207454681, -0.07165877521038055, -0.08125587552785873, -0.3186638355255127, -0.3998492360115051, -0.2688020169734955, 0.04418035224080086, -0.15519294142723083, -0.10552214831113815, -0.28903383016586304, 0.17172197997570038, 0.12735900282859802, -0.3634292483329773, -0.012133619748055935, 0.6343435645103455, -0.432367742061615, 0.03574493154883385, -0.5045153498649597, 0.370784729719162, 0.4802180230617523, -0.15776169300079346, 0.026752572506666183, 1.1183022260665894, -0.48845112323760986, 0.1963912397623062, -0.3121773600578308, 0.42050865292549133, 0.22120912373065948, 0.10435614734888077, -0.23064905405044556, 0.7847875356674194, 0.07862216234207153, 0.4620213806629181, -0.05327131971716881, -0.4341462254524231, -0.3798539340496063, 0.3306262791156769, -0.5713021159172058, -0.02744627185165882, -0.15244725346565247, -0.03293447196483612, 0.6246495246887207, -0.7215827107429504, -1.4487853050231934, 0.003989059943705797, 0.10988453030586243, -0.34315401315689087, 0.23115558922290802, -0.025535138323903084, 0.159192755818367, 0.1531120389699936, 0.1968093365430832, 0.04106644168496132, 0.1773548424243927, -0.8481621742248535, -0.3558847904205322, 0.1258399337530136, -0.09646838903427124, -0.632138729095459, 0.12412825226783752, -0.1890324503183365, 0.2447243183851242, 0.10685184597969055, 0.1330590844154358, 0.5092692375183105, 0.22258593142032623, 0.6747917532920837, -0.5660988092422485, 0.3039347529411316, -0.08003172278404236, 0.38344088196754456, -0.028868917375802994, -0.05340007320046425, -0.28235578536987305, -0.2659631669521332, -0.06331106275320053, -0.5471086502075195, 0.6820501685142517, 0.31696271896362305, -0.24500161409378052, -0.06581655889749527, 0.043642472475767136, 0.07127316296100616, 0.10249802470207214, 0.9137537479400635, -0.3602257966995239, -0.17708416283130646, 0.44301193952560425, 0.30143964290618896, -0.31197717785835266, 0.5871953368186951, 0.34027576446533203, -0.04039318114519119, 0.1152513325214386, -0.43199965357780457, -0.10110676288604736, 0.08896113932132721, 0.07792741060256958, -0.7214783430099487, -0.09525638073682785, -0.2026224434375763, -0.727576732635498, -0.2998898923397064, -0.5359319448471069, -0.5327183604240417, -0.2412116974592209, -0.13496007025241852, 0.5873335003852844, 0.05554533004760742, -0.14870095252990723, 0.4249933660030365, 0.31152600049972534, -0.45324569940567017, 0.39501240849494934, -0.4342898726463318, 0.7457199692726135, -0.010604077018797398, 0.3747882843017578, -0.46931740641593933, 0.5135130286216736, 0.10471155494451523, 0.009686989709734917, -0.04975394904613495, -0.5207942724227905, 0.4860057234764099, 0.29392313957214355, -0.3791087567806244, 0.34581783413887024, -0.2633545994758606, -0.18253357708454132, -0.17994095385074615, -0.011110249906778336, -1.6375147104263306, 0.4634670913219452, 0.15709710121154785, -0.06849870830774307, 0.3947395086288452, -0.3407348692417145, -0.6669765114784241, -0.07002145797014236, 0.17223456501960754, 0.269832968711853, -0.04725981503725052, -0.0988766998052597, -0.23078498244285583, 0.15351960062980652, 0.21470531821250916, -0.5436458587646484, 0.2150679975748062, -0.2170228511095047, -0.1009216457605362, 0.015850679948925972, -0.13956144452095032, 0.2337704747915268, 0.5153816342353821, -0.2727539539337158, -0.17273332178592682, -0.2721787989139557, -0.20449957251548767, 0.7570866942405701, 0.12968070805072784, 0.40441226959228516, -0.17931221425533295, -0.20986224710941315, -0.5836969017982483, 0.05097479000687599, 0.4085310101509094, 0.10300694406032562, 0.28029224276542664, 0.02415657415986061, 0.6508205533027649, 0.9181411266326904, -0.29366806149482727, 0.4195311367511749, 0.39692699909210205, 0.2595403790473938, 0.46993058919906616, 0.09164342284202576, -0.5261561870574951, 0.4019002318382263, 0.3237345516681671, -0.08163416385650635, -0.3236372172832489, -0.1996389627456665, -0.3672976493835449, -0.5974564552307129, -0.3479005694389343, -0.20870156586170197, -0.19312578439712524, -0.025629378855228424, -0.2615281343460083, -0.3435174226760864, -0.04641227796673775, 0.13598766922950745, -0.5998694896697998, 0.3121601343154907, -0.9978627562522888, -0.7619092464447021, -0.23540250957012177, -0.24686060845851898, -0.1868327409029007, 0.2653399407863617, 0.6625364422798157, 0.3688371181488037, -0.4260512590408325, 0.17685003578662872, -0.31227967143058777, 0.7056297063827515, -0.3088134229183197, -0.014156656339764595, 0.20580542087554932, -0.5693032145500183, -0.009456775151193142, -0.31874051690101624, -0.14235106110572815, 0.596713662147522, -0.17852917313575745, 0.1584501564502716, -0.29163891077041626, 0.11694902181625366, -0.06875988095998764, -0.16335268318653107, -0.3931238353252411, -0.5426549315452576, -0.05027201771736145, -0.22962239384651184, -0.14907540380954742, -0.2507132291793823, 0.019738242030143738, -0.09793735295534134, -0.25940659642219543, -0.40193960070610046, -0.4763522446155548, 0.1464942991733551, 0.2223222702741623, 0.0022990049328655005, 0.009507662616670132, 0.2543555200099945, 0.18467237055301666, -0.05677872151136398, -0.9535579085350037, -0.20018544793128967, 0.27682745456695557, 0.17787086963653564, 0.049126628786325455, 0.18002410233020782, -0.15462444722652435, -0.17149955034255981, 0.586154043674469, -0.7500867247581482, 1.77558171749115, 0.1465636044740677, 0.009727912954986095, -0.22184810042381287, 0.7537790536880493, -0.18969696760177612, 0.16765940189361572, -0.059569645673036575, -0.28966331481933594, 0.0677570104598999, -0.1620911806821823, 0.10376016050577164, -0.05535568669438362, 0.22270634770393372, 0.4847261607646942, 0.3490801453590393, 0.2828138768672943, -0.5447971820831299, -0.6300061345100403, -0.08004054427146912, -0.2972820997238159, -0.02094842679798603, 0.4754985272884369, -0.10598306357860565, 0.1534435749053955, 0.20541951060295105, 0.47557151317596436, -0.10875825583934784, 0.2953401505947113, 0.8797112703323364, -0.33831506967544556, 0.05464169383049011, 0.2600986361503601, 0.6119256019592285, -0.6796594262123108, 0.011595051735639572, 0.10431384295225143, 0.03258899226784706, 0.050856444984674454, 0.08325756341218948, 0.02215973660349846, 0.19253304600715637, 0.8901114463806152, 0.22618776559829712, 0.2528277337551117, 0.45043638348579407, -0.13601887226104736, 0.0292794369161129, 0.8513936996459961, 0.14040648937225342, -0.14490611851215363, 0.010116985999047756, -0.19701363146305084, 0.061704911291599274, 0.42023301124572754, -0.3428954780101776, -0.20528624951839447, 0.1638452112674713, -0.13424213230609894, 0.34129399061203003, -0.2606331408023834, 0.14638645946979523, 0.5501741766929626, -0.1189604327082634, 0.015027545392513275, -0.06556399911642075, -0.37987926602363586, -0.03352268412709236, 0.3213319778442383, -0.35713136196136475, -0.10310758650302887, 0.35835951566696167, 0.04059000313282013, 0.13779929280281067, 0.8949403166770935, 0.2858949303627014, 0.8871415257453918, -0.09914203733205795, -0.45734545588493347, -1.8423880338668823, 0.23735491931438446, 0.1578005850315094, -0.20233434438705444, -0.2532413899898529, -0.06472756713628769, -0.027171771973371506, -0.23668187856674194, 0.08565469831228256, -0.4669637978076935, 0.31227681040763855, 0.9225685000419617, 0.4510655701160431, -0.020788127556443214, 0.29431211948394775, -0.292755126953125, 0.2605326175689697, -0.07471813261508942, -0.25414130091667175, -0.1626966893672943, 0.0027296599000692368, 0.17841137945652008, -0.22985851764678955, -0.1571456789970398, 0.2034115046262741, 0.4614422619342804, 0.026103775948286057, -0.2575453519821167, 0.3847912847995758, -0.1605215221643448, 0.2279544174671173, -0.16089698672294617, -0.02512528747320175, -0.47932618856430054, 0.022280169650912285, 0.2054150402545929, -0.4166054427623749, 0.47019079327583313, 0.14775343239307404, -0.21279600262641907, 0.22581607103347778, 0.7003654837608337, 0.07935052365064621, -0.05651966854929924, 0.3556041419506073, -0.3603334128856659, 0.12804058194160461, -0.25300025939941406, 0.4081861078739166, -0.22168266773223877, 0.5153877139091492, 0.15452001988887787, 0.31615471839904785, -0.02139895036816597, 0.5885279774665833, -0.05205361917614937, -0.38730549812316895, -0.06391958892345428, -0.0012270492734387517, -0.5536316633224487, -0.8508360981941223, -0.0642378106713295, -0.3445153832435608, -0.16407977044582367, 0.7523255348205566, -0.3685630261898041, -0.05895017087459564, -0.20366358757019043, -0.024587038904428482, -0.11328320950269699, -0.04102402180433273, -0.036754362285137177, 0.5535851716995239, 0.3472888469696045, -0.1886654496192932, -0.11008208245038986, 0.051363274455070496, -0.05242481455206871, -0.08637294173240662, -0.163528710603714, -0.0942215695977211, 0.2603762447834015, -0.25700220465660095, 0.05002135410904884, 0.09901794046163559, -5.821940898895264, -0.20742659270763397, -0.2372940331697464, -0.248107448220253, -0.276915967464447, -0.05574037879705429, -0.07013726234436035, -0.2149561047554016, -0.19004139304161072, -0.36891406774520874, 0.22544042766094208, -0.05350186303257942, -0.172159805893898, -0.4437611699104309, 0.4114968180656433, 0.22266869246959686]</t>
+          <t>['high', 'high', 'medium', 'low', 'high', 'high']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>[-0.5, -0.5, 0.5, 0.5, -0.5, -1.0]</t>
+          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[5, 3, 3, 4, 4, 5]</t>
+          <t>[40.0, 35.0, 35.0, 50.0, 35.0, 35.0]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
+          <t>['woman', 'man', 'man', 'man', 'woman', 'woman']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>[30.0, 30.0, 35.0, 35.0, 30.0, 45.0]</t>
+          <t>[1, 1, 5, 1, 1, 1]</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>['man', 'woman', 'man', 'woman', 'man', 'woman']</t>
+          <t>[4, 4, 1, 2, 5, 5]</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1, 1]</t>
+          <t>[5, 5, 5, 5, 5, 5]</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>[5, 4, 4, 5, 4, 5]</t>
+          <t>[2, 4, 5, 5, 4, 4]</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>[1, 1, 4, 4, 1, 1]</t>
+          <t>[1, 1, 5, 3, 1, 1]</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 5, 3, 3]</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>[5, 1, 3, 1, 2, 1]</t>
-        </is>
+          <t>[5, 5, 5, 5, 5, 5]</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>6</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 3, 1, 1]</t>
+          <t>[5, 5, 3, 5, 5, 5]</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>[1, 1, 3, 3, 1, 1]</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>[0.66666667 0.         0.33333333 0.         0.        ]</t>
-        </is>
-      </c>
-      <c r="T3" t="n">
-        <v>0.5</v>
+          <t>[0.         0.         0.16666667 0.         0.83333333]</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>99</v>
+        <v>216</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>British native youth have completely given in to nigger culture, music and customs and constantly encourage miscegenation. In fact they are already starting to talk like the blacks. They need guidance thats for sure</t>
+          <t xml:space="preserve">I mean, I dont care if all the gays are infected to the nines. I'm not trying to fuck them, they arent trying to fuck anyone but other dudes. Just making doctors rich raw dogging their twink boys.Who cares what they got or do, its an insular culture anyway.
+</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[5, 5, 3, 5, 5, 5]</t>
+          <t>[2, 5, 3, 3, 5, 4]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 5, 5, 5]</t>
+          <t>['NONE', 'immigrant, black,', '{}', '{}', '{}', '{}']</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>['{}', 'black; female', nan, 'none', '{}', '{}']</t>
+          <t>['far right', 'center', 'right', 'right', 'left', 'left']</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[0.13886664807796478, 0.14132989943027496, -0.06325411051511765, -0.13822850584983826, -0.644498884677887, -0.6872404217720032, 0.8542863130569458, 0.9888802766799927, 0.0541636198759079, -0.813217043876648, 0.36997267603874207, -0.05499548465013504, -0.21643124520778656, 0.8660178184509277, 0.31288349628448486, 0.38769927620887756, 0.04568934068083763, 0.6423038244247437, 0.25001147389411926, 0.3267013728618622, -0.17402322590351105, -0.4070992171764374, 0.5963816046714783, 0.23545387387275696, 0.2897907793521881, -0.2399098426103592, 0.14220581948757172, -0.537743866443634, -0.6759033799171448, 0.1604032814502716, -0.06067637354135513, 0.5398139357566833, -0.562498927116394, -0.15656720101833344, 0.47650080919265747, -0.2777695953845978, -0.0614202655851841, 0.2336057424545288, 0.4385203421115875, 0.17961467802524567, -0.45062217116355896, -0.02320375107228756, 0.04665117338299751, -0.24995073676109314, -0.4277699887752533, -0.30027151107788086, -4.140355587005615, -0.14895135164260864, -0.09561141580343246, -0.42119285464286804, -0.05288420990109444, -0.6523289084434509, -0.3049623668193817, 0.47609201073646545, 0.4097725450992584, 0.15992988646030426, -1.0016992092132568, 0.022030197083950043, -0.3145330548286438, 0.23185791075229645, 0.9870610237121582, 0.10680828988552094, -0.570120096206665, -0.5527721643447876, 0.03880121186375618, -0.014579882845282555, -0.006738119293004274, 0.3709973692893982, -0.6255950927734375, 0.26360592246055603, -1.0722641944885254, -0.4095596671104431, 0.660210371017456, -0.023314889520406723, -0.12388910353183746, 0.14770850539207458, -0.14550094306468964, 0.2540445029735565, -0.4028489887714386, -0.3271527886390686, -0.2516002953052521, 0.70660799741745, -0.1700434684753418, -0.23461608588695526, -0.4071064591407776, 1.0640347003936768, -0.15713638067245483, -0.5545867681503296, -0.24982815980911255, 0.6469117999076843, 0.28263431787490845, -0.014477699063718319, 0.4358951449394226, 0.244290292263031, 0.6453913450241089, 0.4275790750980377, 0.5845153331756592, -0.3291417360305786, -0.1727364957332611, 0.6245794296264648, 0.5915027856826782, -0.39852839708328247, 0.09427814185619354, -0.36092203855514526, 0.09250375628471375, -0.4089904725551605, 0.02373252436518669, 0.07051849365234375, 0.41601085662841797, -1.1897965669631958, 0.5877987742424011, 0.2741785943508148, -0.03323209285736084, -0.21333706378936768, -0.4868086874485016, -0.22491444647312164, 0.49272018671035767, -0.34606918692588806, 0.6326391696929932, 0.3682684302330017, -0.08707302063703537, 0.04935753345489502, -0.5778021216392517, 0.15953029692173004, -0.35800787806510925, 0.6278204917907715, -0.6012130379676819, 0.22662122547626495, 0.09648708254098892, 0.5741996169090271, 0.48799610137939453, 0.5442620515823364, -0.09816765785217285, -0.8036298155784607, -0.10175012797117233, 0.037977542728185654, 0.6292494535446167, -0.29356512427330017, 0.5277921557426453, -0.4541569948196411, -0.6490952968597412, -0.6904963254928589, -1.5646812915802002, 0.26094794273376465, 0.6596558094024658, -0.043691761791706085, -0.7653311491012573, -0.02342149056494236, -0.34033894538879395, -0.18027952313423157, -0.02618503011763096, -0.34021246433258057, 0.3543790876865387, -0.4749726355075836, -0.31115442514419556, -0.5119867920875549, -1.1554510593414307, -0.2587759494781494, -0.17305335402488708, 1.295196294784546, -0.09904565662145615, -0.08435412496328354, 0.31500717997550964, 0.16500119864940643, -0.7024117708206177, 0.38249534368515015, 0.4508873522281647, 0.7210216522216797, -0.04601845145225525, 0.2960168719291687, 0.2632293105125427, 0.8467848300933838, 0.8657616972923279, -0.5845382213592529, 0.4124178886413574, 0.28138652443885803, -0.11278484761714935, 0.6407594680786133, -0.12173020094633102, 0.24063052237033844, -0.6234552264213562, 0.8281975388526917, -0.2843845784664154, 0.24220941960811615, 0.6928572058677673, -0.8101029992103577, 0.2128162980079651, -0.04242168366909027, 0.212309792637825, 0.3310375213623047, -0.24067671597003937, -0.9119172692298889, 0.4758189022541046, 0.12361396849155426, 1.3072673082351685, -0.026490600779652596, 0.9744155406951904, -0.6263149380683899, -0.1537189930677414, 0.16873863339424133, -0.29918840527534485, 0.02272099442780018, 0.1078290268778801, 0.3301086723804474, -0.7780734300613403, 3.4673166275024414, 0.15466301143169403, 0.5107031464576721, 0.34910017251968384, 0.6080694794654846, -0.2701472043991089, -0.45191797614097595, -0.2989249527454376, -0.05006086826324463, -0.08664827048778534, 0.2156345397233963, 0.5721468329429626, -0.5213420987129211, -0.6764107942581177, -0.22671382129192352, -0.039879560470581055, 0.35621169209480286, -0.10304220765829086, 0.34047091007232666, -0.7406339645385742, -0.6285298466682434, -0.4862336218357086, -0.5983181595802307, 0.04168291762471199, -1.5776227712631226, 0.02290879189968109, -0.4134904742240906, -0.05036913976073265, 0.3575870096683502, -0.31818491220474243, 0.37129756808280945, -0.09702834486961365, -0.3104749917984009, -0.07769240438938141, 0.06866079568862915, 0.4318602681159973, 0.49244314432144165, -0.23582226037979126, -0.15726450085639954, -0.4753766655921936, 0.5847371816635132, 0.2280733287334442, -0.6242688894271851, 0.18099737167358398, -0.41444724798202515, 0.48308074474334717, 0.1749504804611206, 0.13499340415000916, -0.33780723810195923, 0.3909884989261627, 0.09421208500862122, -0.09431911259889603, -0.024935832247138023, -0.6266997456550598, -0.8919131755828857, -0.25040188431739807, 0.14880244433879852, -0.37800100445747375, 0.057467587292194366, -1.2305216789245605, -0.7363048195838928, -0.0016023896168917418, 0.12656031548976898, -0.6190370321273804, -0.07008577883243561, 0.9072130918502808, -0.1347019523382187, -0.44887015223503113, -0.9681255221366882, 0.23957525193691254, 0.10982447862625122, 0.1465683877468109, 0.25763964653015137, -0.6462825536727905, -0.33086276054382324, 0.32468801736831665, 0.4901005029678345, -0.8220627903938293, 0.7361792922019958, -0.09487096965312958, 0.1762285828590393, 0.1619262844324112, -0.2139665186405182, 0.2704787254333496, -0.49310141801834106, -0.0033421488478779793, 0.08083876222372055, -0.2162553071975708, 0.05167650803923607, -0.11723209917545319, -0.07069145143032074, -0.2042214423418045, 0.2533933222293854, 0.0994507446885109, -0.0733269527554512, -0.6624124646186829, 0.6491514444351196, 0.12694533169269562, 0.3899034559726715, -0.11219144612550735, -0.2508496344089508, -0.23625700175762177, -0.49325868487358093, -3.8021111488342285, 0.09113830327987671, -0.6417968273162842, -0.37478604912757874, -0.08368033915758133, -0.17855148017406464, 0.5312224626541138, -0.19828873872756958, -0.4857719838619232, -0.19788414239883423, 0.0183588694781065, -0.20688410103321075, -0.5670155882835388, 0.4467075765132904, 0.9372946619987488, 0.3122096359729767, 0.6320870518684387, -0.5077260136604309, 0.035845015197992325, 0.23017680644989014, -0.22677543759346008, -0.22761034965515137, 0.30438342690467834, -0.08964084088802338, 1.108680248260498, 0.34033849835395813, -1.0595481395721436, -0.2871771454811096, -0.4291631579399109, 0.06013011187314987, -0.2583267092704773, -0.017083657905459404, -0.04210696369409561, -0.28036728501319885, -0.012590866535902023, -0.4929748773574829, -0.07212719321250916, -0.21272119879722595, 0.6263495683670044, -0.39582809805870056, 0.2873351275920868, 0.41852229833602905, -0.4031490981578827, 0.3511832058429718, 1.0119150876998901, 0.26381954550743103, -0.04040698707103729, 0.04556620493531227, -0.16067364811897278, 0.5495065450668335, -0.03502311557531357, 0.2520202100276947, 0.26887279748916626, -0.000642058381345123, -0.31573018431663513, -0.0035249069333076477, 0.6861832737922668, 0.4944040775299072, -0.034801773726940155, -0.2864372432231903, 0.5429103970527649, -0.5600049495697021, -0.43937546014785767, -0.2632264494895935, 0.06947539001703262, -0.8008300065994263, -0.011746382340788841, -0.508030116558075, 0.4695853590965271, -0.1291397213935852, -0.23118703067302704, 0.17902132868766785, -0.6973118782043457, -1.8965421915054321, 0.0845925360918045, -0.20246121287345886, -0.298078715801239, 0.5060622096061707, 0.11384493112564087, 0.16445931792259216, -0.09824458509683609, -0.029597274959087372, -0.6010406613349915, 0.5628977417945862, -0.4875984191894531, -0.227606862783432, -0.17980238795280457, 0.3463689684867859, -0.7690153121948242, -0.3095651865005493, 0.4077751934528351, 0.23324640095233917, -0.003935612738132477, 0.18991045653820038, 0.07457569986581802, -0.060913342982530594, 0.7873605489730835, -0.4215131402015686, 0.24287176132202148, -0.10817377269268036, 0.024988234043121338, -0.19491101801395416, -0.6423704624176025, 0.35774412751197815, 0.21319976449012756, -0.33496469259262085, -0.25403091311454773, 0.9501655101776123, -0.015095635317265987, 0.053491849452257156, 0.24464963376522064, -0.6268536448478699, -0.27816006541252136, 0.4612947404384613, 0.5626453161239624, -0.3595963418483734, 0.1437111794948578, 0.6735683679580688, 0.4039076864719391, 0.06179552897810936, 0.8291913866996765, 0.16408409178256989, -0.10918935388326645, -0.22884616255760193, -0.9067028164863586, -0.11197949945926666, 0.3213755488395691, 0.2650403380393982, -0.8990569710731506, -0.10144118219614029, 0.05037521943449974, -0.3063933253288269, -0.9049686193466187, -0.29579609632492065, 0.03429870679974556, -0.33788585662841797, 0.024565190076828003, -0.0588841550052166, 0.32756271958351135, 0.13876928389072418, 0.7541008591651917, -0.34596848487854004, -0.1043066680431366, 0.603671669960022, -0.39396172761917114, 0.7902078628540039, -0.26966893672943115, -0.14796805381774902, -0.26838013529777527, 0.2862977683544159, -0.0029028216376900673, 0.04296661168336868, -0.13785463571548462, -0.8744632601737976, 0.5376803278923035, -0.22012513875961304, -0.12364229559898376, 0.1443062722682953, -0.19028615951538086, -0.8899868726730347, 0.5408160090446472, 0.2412070333957672, -2.220205545425415, 0.9430559873580933, 0.9987841248512268, 0.1952478438615799, 0.12746545672416687, 0.015215016901493073, -0.8063203692436218, 1.074387788772583, -0.14419451355934143, 0.0653451606631279, -0.6223251223564148, -0.2651470899581909, 0.03178975358605385, 0.05547410249710083, 0.21340009570121765, 0.23687811195850372, 0.09789930284023285, -1.0026015043258667, -0.5778250098228455, -0.14119015634059906, -0.44746577739715576, -0.23462945222854614, 0.22857485711574554, 0.3885977566242218, 0.40265023708343506, -0.4120875298976898, -0.20537102222442627, 0.4931635856628418, 0.05822426453232765, 0.7357998490333557, -0.473725825548172, -0.1845991164445877, -0.5192478895187378, -0.1958080232143402, 0.5465899109840393, -0.08715856820344925, 0.3426954448223114, -0.12252262234687805, 1.1507515907287598, 0.34071558713912964, 0.04912898689508438, 0.6114797592163086, 0.5830556750297546, 0.8065363764762878, 0.3434081971645355, 0.3736730217933655, -0.5492110848426819, 0.8325181603431702, 0.38546088337898254, -0.6717626452445984, -0.3886786103248596, -0.06377825886011124, -0.6779078245162964, -0.5906392931938171, 0.058762721717357635, -0.018678413704037666, 0.018488340079784393, 0.9580772519111633, -1.1104929447174072, -0.3029276430606842, -0.084125816822052, -0.16333147883415222, -0.45223215222358704, -0.16037964820861816, -0.1594119518995285, -0.5694189667701721, -0.4076392948627472, -1.0863393545150757, -0.32133910059928894, 0.3734413981437683, 0.941669225692749, 0.2895268499851227, -0.6864404678344727, 1.232069969177246, -0.48827728629112244, 0.7745417356491089, 0.5025655031204224, -0.2797163426876068, 0.29641398787498474, -0.6374520659446716, -0.21099138259887695, -0.9972916841506958, -0.31834906339645386, 0.5602218508720398, -0.07171838730573654, 0.6274253129959106, -0.3981660008430481, 0.20571547746658325, -0.002682539401575923, -0.3344925045967102, -0.7435295581817627, -0.3387802243232727, -0.18765784800052643, 0.21842464804649353, -0.19067613780498505, -0.08910372108221054, 0.029561936855316162, -0.12187851965427399, 0.1041504368185997, -0.34636569023132324, -0.46337565779685974, 0.2095383256673813, 0.26276373863220215, -0.3170337378978729, -0.0817507654428482, 0.2904002070426941, 0.3139607310295105, 0.42707422375679016, -0.1945846527814865, 0.01916714943945408, 0.37838059663772583, -0.31459540128707886, -0.09700152277946472, -0.1063355952501297, 0.3113466501235962, -0.4762876033782959, 0.25117748975753784, -0.5361388325691223, 1.5003676414489746, 0.307449609041214, 0.21389858424663544, -0.7977626919746399, 1.0472291707992554, -0.15802575647830963, 0.13447634875774384, 0.2501779794692993, -0.5335609912872314, 0.4581928253173828, -0.6557689905166626, -0.0034146211110055447, -0.45174890756607056, 0.21018868684768677, 0.6945035457611084, 0.10558579862117767, -0.038453031331300735, -0.26084280014038086, -0.018899768590927124, 0.11520379036664963, -0.3206545412540436, 0.4773276746273041, 0.3329438269138336, 0.168910950422287, 0.13816598057746887, 0.576270341873169, 0.3922492265701294, 0.4418308734893799, 0.37552589178085327, 0.8442570567131042, -0.7076574563980103, -0.34877610206604004, 0.6262446045875549, 0.8279503583908081, -0.7253714799880981, -0.08570989221334457, 0.2041003406047821, -0.02193366549909115, -0.04004295915365219, 0.7472792863845825, 0.44892817735671997, -0.6440631151199341, 0.9410282969474792, 0.13201852142810822, 0.1488572210073471, 1.0960453748703003, -0.17874133586883545, -0.7270236611366272, 0.7996461391448975, 0.8456637263298035, 0.07554009556770325, 0.26855939626693726, -0.8988398313522339, 0.15157490968704224, 0.38075244426727295, -0.14780639111995697, -0.6993314623832703, 0.05711967125535011, -0.10378319770097733, -0.007619092240929604, -0.13912829756736755, 0.1908092349767685, 0.26146745681762695, -0.38001662492752075, -0.1736908107995987, 0.1660013645887375, -0.5676197409629822, 0.45711585879325867, 0.1031007170677185, -0.24580127000808716, 0.4960379898548126, 0.14154325425624847, 0.04018820822238922, 0.13754138350486755, 0.691220760345459, 0.6843429803848267, 0.41612741351127625, 0.0547160767018795, -0.6683252453804016, -0.815663754940033, 0.4493359923362732, -0.007585574872791767, 0.09835848212242126, -0.05016542598605156, 0.901289165019989, 0.21942566335201263, 0.025925062596797943, -0.07748226821422577, 0.03531067445874214, -0.3361316919326782, 0.5186361074447632, 0.13559621572494507, -0.10842910408973694, -0.006747240666300058, 0.2529773712158203, 0.4293636083602905, -0.48978573083877563, -0.5743353366851807, -0.5758499503135681, 0.2874925136566162, 0.7549723982810974, -0.12841536104679108, -0.814142107963562, -0.24609880149364471, 0.9579582214355469, -0.06173258647322655, -0.6375352144241333, 0.41084417700767517, 0.34333866834640503, -0.09857789427042007, 0.0005226050852797925, -0.18326523900032043, -0.3007417321205139, 0.4783698618412018, 0.1587304025888443, -0.7924976944923401, 0.5121681094169617, 0.2302936166524887, -0.5287771224975586, -0.5431392788887024, 0.9841803908348083, -0.3114013075828552, 0.044350236654281616, 0.027952266857028008, -0.4605143368244171, 0.31203892827033997, -0.04131997376680374, 0.8258940577507019, 0.06745880097150803, 0.6448147296905518, -0.019342023879289627, 0.5850331783294678, -0.49341821670532227, 0.8897557258605957, 0.19257424771785736, 0.8582530617713928, 0.30379563570022583, 0.20701222121715546, -0.6153269410133362, 0.19260849058628082, 0.2355082780122757, -0.7040315270423889, -0.1438945084810257, 0.2733692228794098, 0.04189247637987137, -0.0073656123131513596, -0.08391092717647552, 0.5272378921508789, -0.3274035155773163, -0.2793577313423157, 0.4040865898132324, 0.7921896576881409, 0.31406620144844055, -0.24816858768463135, -0.3533494174480438, 0.21724505722522736, -0.15122950077056885, 0.3635408282279968, -0.2498130202293396, -0.4590494632720947, 1.0630794763565063, -0.9595275521278381, 0.43594005703926086, -0.03386729955673218, -2.502354383468628, -0.3335168659687042, -0.5619158148765564, -0.10245729237794876, -0.35600754618644714, -0.6249331831932068, -0.3742627799510956, -0.6359171271324158, -0.006877074483782053, -0.7068288326263428, 0.1650209128856659, 0.02465871348977089, -0.37371379137039185, -0.7325643301010132, 1.172458291053772, 0.09364122897386551]</t>
+          <t>['medium', 'medium', 'medium', 'low', 'high', 'high']</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>[-1.0, -1.0, 1.0, -0.5, -1.0, -0.5]</t>
+          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 2, 1, 3]</t>
+          <t>[45.0, 35.0, 45.0, 35.0, 40.0, 25.0]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
+          <t>['man', 'woman', 'man', 'man', 'man', 'man']</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>[25.0, 40.0, 35.0, 50.0, 25.0, 45.0]</t>
+          <t>[5, 1, 4, 2, 2, 1]</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>['man', 'woman', 'man', 'man', 'man', 'woman']</t>
+          <t>[4, 4, 3, 2, 4, 3]</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>[1, 1, 5, 1, 1, 1]</t>
+          <t>[2, 5, 3, 2, 5, 5]</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>[4, 5, 1, 2, 5, 4]</t>
+          <t>[3, 4, 4, 2, 3, 5]</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>[5, 5, 3, 5, 5, 4]</t>
+          <t>[2, 1, 3, 3, 2, 2]</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>[3, 4, 5, 5, 5, 4]</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>[1, 1, 5, 3, 1, 1]</t>
-        </is>
+          <t>[4, 1, 1, 3, 1, 2]</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>6</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 5, 5, 5]</t>
+          <t>[2, 5, 3, 3, 5, 4]</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>[5, 5, 3, 5, 5, 5]</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>[0.         0.         0.16666667 0.         0.83333333]</t>
-        </is>
-      </c>
-      <c r="T4" t="n">
-        <v>0.2</v>
+          <t>[0.         0.16666667 0.33333333 0.16666667 0.33333333]</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>131</v>
+        <v>250</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Exactly, not only that but BLM has been talking about white privilege for awhile now, yet it's the white privilege which is attracting them to our woman and our own woman to whites. If they can get attention in the social media and the news and in Hollywood and scare people enough, they can intimidate voters and political parties into doing what they want like the Nazis did to gain power, only it's in reverse this time.</t>
+          <t>I'm too broke to buy anything angry... Hot heads ain't sexy. Calling names ain't sexy.. How would a queen address problems? Not wit anger</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[5, 5, 1, 5, 5, 5]</t>
+          <t>[1, 1, 1, 3, 1, 1]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[5, 5, 4, 5, 5, 5]</t>
+          <t>[nan, '{}', '{}', '{}', 'bisexual', '{}']</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>['{}', 'black; female', nan, '{}', '{}', '{}']</t>
+          <t>['left', 'left', 'right', 'center', 'left', 'far left']</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[0.1108744814991951, 0.056330613791942596, 0.043380774557590485, -0.0368364155292511, -0.6887669563293457, -0.586030125617981, 0.46640464663505554, 0.4143576920032501, 0.04589206352829933, -0.3633045256137848, 0.633968710899353, 0.004187117330729961, 0.030616769567131996, 0.6289759278297424, -0.18105536699295044, 0.56756991147995, -0.44447848200798035, 0.18800683319568634, 0.35285499691963196, 0.028971951454877853, -0.24503149092197418, 0.18928183615207672, 0.8924008011817932, 0.23233945667743683, -0.01296771876513958, -0.051038410514593124, 0.2570476830005646, -0.6500557065010071, -0.3278382420539856, 0.6798247694969177, 0.16758203506469727, 0.02166249044239521, -0.9625610709190369, -0.26748228073120117, 0.1391981691122055, -0.30224645137786865, -0.10261527448892593, 0.321621298789978, 0.23828652501106262, 0.05733873322606087, -0.5674081444740295, -0.14170604944229126, -0.3050674796104431, 0.2661287486553192, -0.41932541131973267, -0.2812703549861908, -4.411975383758545, 0.2364066243171692, -0.015654869377613068, -0.23024152219295502, 0.007835108786821365, -0.8112707138061523, -0.020137932151556015, 0.31320440769195557, 0.8194195628166199, 0.39966821670532227, -0.5921730995178223, 0.1951269954442978, -0.3049418032169342, -0.45454591512680054, 0.18720759451389313, -0.029515868052840233, -0.06349053978919983, -0.5387840867042542, 0.08101274073123932, 0.18027494847774506, 0.10719895362854004, 0.15058645606040955, -0.47950536012649536, 0.07419908791780472, -0.5326067805290222, -0.7010601162910461, 0.1327449381351471, 0.07983025908470154, 0.049090687185525894, -0.3535424470901489, -0.12499407678842545, 0.44689732789993286, -0.006045932415872812, -0.25776466727256775, -0.1028643250465393, 0.705938994884491, -0.01977531425654888, -0.2101774960756302, -0.07521208375692368, 0.3755967319011688, -0.06190692260861397, -0.06540577113628387, 0.11269872635602951, 0.3145444095134735, -0.2277744859457016, 0.3179461359977722, 0.4212074875831604, 0.552117109298706, 0.5622216463088989, 0.08785629272460938, 0.8142260313034058, -0.7900168895721436, -0.09657488763332367, 0.9414086937904358, 0.6947139501571655, -0.44300055503845215, 0.17562782764434814, -0.7582553029060364, 0.20558999478816986, -0.27121269702911377, 0.07622372359037399, -0.0622125081717968, 0.3743933439254761, -1.465059757232666, 0.47466766834259033, 0.471171498298645, -0.2283792346715927, -0.2509661316871643, -0.6072933673858643, -0.14732226729393005, 0.29375365376472473, -0.364289253950119, 0.7493733763694763, 0.4657273292541504, 0.2725849747657776, 0.3838970959186554, -0.43888992071151733, -0.4062831699848175, -0.004353881347924471, -0.2626389265060425, -0.0557844415307045, 0.41062116622924805, -0.3940805196762085, 0.4087601602077484, 0.5090437531471252, 0.3494042754173279, -0.003752073273062706, -0.14280448853969574, 0.06332896649837494, -0.07167242467403412, 0.5558503270149231, -0.20614871382713318, -0.296438992023468, -0.23853246867656708, -0.36733219027519226, -0.48125818371772766, -2.275724411010742, 0.2385370135307312, 1.089111089706421, 0.4358890652656555, -0.09876753389835358, 0.23105722665786743, 0.022378286346793175, -0.13237670063972473, 0.12808789312839508, -0.06461244821548462, 0.06694852560758591, -0.3212900757789612, -0.38108664751052856, -0.024338675662875175, -0.41459017992019653, -0.08455027639865875, 0.08542018383741379, 0.7083004713058472, 0.09891802072525024, -0.45362889766693115, 0.09271354973316193, 0.11623555421829224, -0.35317400097846985, 0.4080652594566345, 0.5120157599449158, 0.8263442516326904, -0.5685637593269348, 0.10933134704828262, -0.25737464427948, 0.5325361490249634, 0.46487322449684143, -0.39535006880760193, 0.31480905413627625, 0.18831349909305573, -0.4707135558128357, 0.46763911843299866, 0.17536261677742004, 0.38457250595092773, -0.8971589803695679, 0.4695582985877991, 0.02749638818204403, 0.07509751617908478, 0.4979918897151947, -0.2609197199344635, 0.2533476948738098, -0.3619326651096344, -0.32655036449432373, 0.2620289623737335, -0.45465296506881714, -0.4142025411128998, 0.43300285935401917, -0.05442415922880173, 0.6893777847290039, 0.11084859818220139, 0.23052412271499634, 0.05436517670750618, -0.5452813506126404, 0.07248638570308685, -0.30956530570983887, -0.3526724874973297, -0.249139666557312, -0.3810148537158966, -0.5367735624313354, 3.8961403369903564, 0.32347962260246277, 0.2895418405532837, 0.16390740871429443, 0.31394633650779724, -0.33614009618759155, -0.35098832845687866, -0.3916410505771637, 0.14790278673171997, -0.23045878112316132, 0.24803009629249573, 0.2347719520330429, -0.24289175868034363, -0.0007998031214810908, -0.1087762638926506, 0.2900017201900482, 0.34609705209732056, -0.16995051503181458, 0.2101689577102661, -0.261895090341568, -0.22926586866378784, -0.0569792240858078, 0.04647119715809822, 0.050213515758514404, -1.471197485923767, 0.2919922471046448, 0.2950341999530792, -0.3459010422229767, 0.04695509001612663, -0.1507202386856079, 0.008657286874949932, -0.16169454157352448, -0.2953847646713257, 0.07334662228822708, 0.03955419361591339, 0.1741788685321808, 0.5079758167266846, 0.04155522584915161, 0.011022276245057583, 0.11302399635314941, 0.7066981792449951, 0.03879992291331291, -0.6475798487663269, 0.17039263248443604, -0.18113404512405396, 0.33460676670074463, 0.563170850276947, 0.01459746714681387, -0.5325775742530823, 0.2953178584575653, 0.40237241983413696, -0.11809217929840088, -0.018090227618813515, 0.2058829814195633, -0.6380741596221924, -0.2933630645275116, -0.13046510517597198, -0.5389412641525269, 0.11373139172792435, -0.8456617593765259, -0.21780452132225037, -0.1603015512228012, -0.12991546094417572, -0.3961525559425354, -0.1620926707983017, 0.284774512052536, -0.03418191149830818, -0.5881626009941101, -1.9834190607070923, 0.10829614847898483, -0.06554979830980301, -0.08152636885643005, 0.3372652232646942, -0.5504985451698303, -0.21544477343559265, 0.17509929835796356, -0.030618103221058846, -0.1677548587322235, 0.24059398472309113, 0.03155619651079178, -0.006870467681437731, 0.27390334010124207, -0.3283816874027252, 0.10539671778678894, 0.2774301767349243, -0.12368293851613998, 0.08023649454116821, -0.3429165184497833, -0.13610467314720154, 0.26050248742103577, -0.09740400314331055, -0.0590660534799099, 0.0231684111058712, 0.0937417522072792, 0.09090722352266312, -0.6306176781654358, 0.10082513839006424, 0.36134064197540283, -0.006664206273853779, 0.003151617245748639, -0.018875200301408768, -0.0003945203498005867, 0.17982128262519836, -4.162956237792969, -0.007359060924500227, -0.5377955436706543, -0.06569523364305496, -0.048684898763895035, -0.05822747200727463, 0.5835570096969604, -0.33782508969306946, -0.6397446393966675, -0.04600031301379204, 0.41890689730644226, -0.09892220050096512, -0.09283757954835892, 0.2887151837348938, 0.4550030529499054, 0.20351754128932953, 0.8300009965896606, -0.44780123233795166, 0.3465662896633148, 0.6314317584037781, -0.21769265830516815, -0.42534682154655457, 0.15403300523757935, -0.06409496814012527, 0.4170515835285187, 0.1843925565481186, -0.9014331102371216, -0.6783928275108337, 0.3148942291736603, 0.101080521941185, 0.046612806618213654, -0.2487199753522873, 0.13252845406532288, -0.017296506091952324, -0.22850292921066284, -0.4828316569328308, -0.02563159167766571, -0.5027076601982117, -0.08317861706018448, -0.39770567417144775, -0.12019281834363937, 0.4552111327648163, -0.08343743532896042, 0.37935060262680054, 0.8074355125427246, -0.48638716340065, 0.2762908935546875, -0.3531534671783447, 0.04624170809984207, 0.2758244276046753, 0.31741899251937866, 0.552129864692688, 1.2618672847747803, -0.25331440567970276, -0.4489273726940155, -0.09277772903442383, 0.4124803841114044, -0.2147534042596817, 0.038381025195121765, 0.286187082529068, 0.6079062819480896, -0.4259226620197296, 0.16162864863872528, -0.27394789457321167, 0.11273189634084702, -0.8365704417228699, 0.5092911124229431, -0.4148992896080017, -0.03291887417435646, -0.04598742350935936, -0.0985490009188652, 0.3436257839202881, -1.0096572637557983, -1.6023023128509521, 0.2800414264202118, -0.2375950664281845, -0.033885858952999115, -0.03468259796500206, 0.1196514368057251, 0.5898922085762024, 0.18112905323505402, 0.12434588372707367, -0.29114341735839844, 0.04948347806930542, -0.3171156942844391, -0.6771730780601501, 0.034541405737400055, 0.6587205529212952, -0.27664366364479065, 0.048381976783275604, 0.25544700026512146, 0.0821245089173317, 0.5594784617424011, 0.3327162265777588, 0.18459154665470123, -0.3916473090648651, 0.3874443769454956, -0.5288774371147156, 0.421538770198822, 0.1289551705121994, -0.13686737418174744, 0.08518528938293457, -0.4233495891094208, -0.258539080619812, -0.008746876381337643, -0.3751493990421295, -0.21610493957996368, 0.8535037636756897, 0.12510836124420166, 0.07773131877183914, -0.06329768896102905, 0.16174352169036865, 0.08439019322395325, -0.06617353856563568, 0.877878725528717, -0.438030868768692, 0.14288398623466492, 0.6412883996963501, 0.3636501133441925, -0.45985791087150574, 0.541509747505188, 0.35605207085609436, -0.03132091090083122, 0.08199170976877213, -0.48981142044067383, -0.20234760642051697, 0.10916338115930557, 0.49424418807029724, -0.654547393321991, 0.23408427834510803, -0.31483182311058044, -0.0003416533872950822, -0.743898868560791, -0.03358932211995125, -0.3320833742618561, -0.26389116048812866, 0.000571821816265583, 0.2711428999900818, 0.35380828380584717, 0.18336346745491028, 0.8458436131477356, 0.08762303739786148, -0.3753221929073334, 0.11654806137084961, -0.6260966062545776, 0.5594015717506409, 0.2653970420360565, 0.3657940924167633, -0.2886694669723511, 0.31973016262054443, -0.06327468901872635, 0.2484709769487381, 0.1332343965768814, -0.5933648943901062, 0.9134273529052734, 0.002122812671586871, -0.12643690407276154, 0.22948984801769257, 0.09269339591264725, -0.5720077157020569, 0.15528202056884766, 0.35632821917533875, -2.162750005722046, 0.36654195189476013, 1.0417519807815552, 0.7230980396270752, 0.15865901112556458, 0.01762823387980461, -0.38437142968177795, 0.6942869424819946, -0.15920564532279968, -0.3175148367881775, -0.5275948643684387, -0.25337663292884827, -0.019943322986364365, -0.28208744525909424, 0.3017590343952179, -0.39884132146835327, -0.10832494497299194, -0.3664981722831726, 0.12963497638702393, 0.046548712998628616, -0.5517195463180542, -0.10592024773359299, 0.32869085669517517, 0.31959962844848633, 0.08576451987028122, -0.41252264380455017, -0.44485288858413696, 0.4695587754249573, 0.1321214884519577, 0.81955885887146, -0.1661635935306549, -0.17770041525363922, -0.7279148697853088, -0.2921713888645172, 0.2859593629837036, -0.09924022108316422, 0.2642454206943512, -0.3855542838573456, 0.6731321811676025, 0.9602990746498108, -0.1416298896074295, 0.5806688070297241, 0.602950930595398, 0.27292197942733765, 0.8326802253723145, 0.46718329191207886, -0.34340032935142517, 0.4670521914958954, -0.16269801557064056, -0.16978402435779572, -0.23218220472335815, 0.13151879608631134, -0.4012428820133209, -0.42997652292251587, -0.27950718998908997, -0.4726773202419281, -0.7029002904891968, 0.841943621635437, -0.44460660219192505, -0.19689302146434784, 0.34254851937294006, -0.0529353953897953, -0.696681797504425, -0.07606053352355957, -0.26162347197532654, -0.4840572476387024, -0.30819788575172424, -0.5890718698501587, -0.13527131080627441, 0.74410080909729, 0.5351388454437256, 0.3929828703403473, -0.8567354679107666, 0.6925881505012512, -0.05953278765082359, 0.9045844674110413, -0.30891141295433044, -0.3323407769203186, 0.03978266939520836, -0.371690571308136, -0.34441637992858887, -0.2903265058994293, 0.36631709337234497, 0.32220110297203064, -0.03628962114453316, 0.2641904056072235, -0.65496426820755, 0.001413058489561081, -0.14718730747699738, -0.1182553768157959, -0.6096611022949219, -0.3808045983314514, 0.3902694284915924, 0.013897157274186611, 0.022926276549696922, -0.3822667896747589, -0.1432589590549469, -0.4372309446334839, -0.32206395268440247, -0.11189451813697815, -0.2444453239440918, 0.235103577375412, 0.19640973210334778, -0.19487059116363525, 0.009393811225891113, 0.30524206161499023, 0.19409893453121185, -0.12367640435695648, -0.22029626369476318, 0.043421078473329544, 0.268425315618515, -0.3782844841480255, 0.09154202789068222, 0.19899292290210724, 0.15479141473770142, -0.34044694900512695, 0.44687116146087646, -0.6717712879180908, 1.2995387315750122, -0.18844354152679443, -0.14026185870170593, -0.9658604860305786, 0.5315178632736206, -0.17054621875286102, 0.3177822530269623, 0.4125414490699768, -0.25087207555770874, 0.3311322331428528, -0.6746060252189636, 0.06728634983301163, 0.16989408433437347, 0.2724369764328003, 0.4426826238632202, 0.22533667087554932, -0.06812106817960739, -0.4988769292831421, -0.2416248470544815, -0.24004344642162323, -0.29828599095344543, 0.3988034427165985, -0.0019626026041805744, 0.003867240622639656, -0.17353114485740662, 0.48029157519340515, -0.0174881462007761, -0.13535793125629425, 0.4504123032093048, 0.9043319225311279, 0.010808500461280346, 0.13630074262619019, 0.3956044018268585, 0.5362134575843811, -0.7223476767539978, 0.213048055768013, 0.24854569137096405, -0.1572645753622055, -0.23272205889225006, 0.4017229974269867, 0.0012482323218137026, -0.051057104021310806, 0.6037190556526184, -0.24055875837802887, -0.0542689673602581, 0.5951301455497742, -0.24304449558258057, -0.20833852887153625, 0.6027721762657166, 0.29788994789123535, 0.11914800107479095, 0.7118335962295532, -0.5666064620018005, 0.35186511278152466, 0.3945617973804474, -0.19812913239002228, -0.40639927983283997, 0.09456495940685272, -0.03859317675232887, 0.3637678921222687, -0.2426193654537201, 0.2943999767303467, 0.16560153663158417, -0.29370930790901184, -0.030180856585502625, 0.18689388036727905, -0.3224271833896637, 0.2679217755794525, 0.171902596950531, -0.08529239147901535, 0.3251214325428009, 0.049829624593257904, -0.030838357284665108, 0.10350698977708817, 0.9789140820503235, 0.4193251430988312, 0.6753358840942383, 0.22614234685897827, -0.19103069603443146, -1.3597426414489746, 0.3167490065097809, -0.41678735613822937, 0.09607363492250443, 0.21864785254001617, 0.4705243408679962, 0.5451952815055847, 0.10584452748298645, -0.01661158911883831, -0.01962624117732048, -0.0008057264494709671, 0.3619295656681061, 0.004990465007722378, 0.07274209707975388, 0.20023629069328308, 0.04967810958623886, 0.38319826126098633, -0.20598731935024261, -0.38265642523765564, -0.5610111951828003, 0.23125985264778137, 0.09795954078435898, -0.30904337763786316, -0.592821478843689, -0.5630902647972107, -0.13758477568626404, 0.31965121626853943, -0.3337225615978241, 0.33261433243751526, 0.0009387285099364817, -0.06750937551259995, 0.0983065739274025, -0.29814761877059937, -0.41589224338531494, 0.4233097732067108, 0.40357542037963867, -0.28873685002326965, -0.09578586369752884, -0.15218323469161987, -0.24794460833072662, -0.1409931778907776, 1.0688999891281128, -0.185180202126503, 0.08469430357217789, 0.48689332604408264, -0.6869418025016785, 0.4700569808483124, -0.17085975408554077, 0.2240189015865326, -0.018809795379638672, 0.1824861317873001, 0.05867845565080643, -0.0011252908734604716, 0.21801547706127167, 0.5232343673706055, -0.25270819664001465, 0.29514139890670776, 0.241784930229187, 0.23613406717777252, -0.15709558129310608, 0.005206935573369265, -0.4502829611301422, -0.5090432167053223, -0.5221863389015198, 0.127210795879364, -0.011362986639142036, 0.2792245149612427, 0.7388638854026794, 0.25896134972572327, -0.7407834529876709, -0.2345595508813858, -0.0020283882040530443, 0.5615165829658508, 0.16522890329360962, 0.3238469064235687, -0.2095261514186859, 0.3365901708602905, -0.2463793158531189, 0.4434559941291809, -0.2203047275543213, -0.4976585805416107, 0.585705041885376, -0.019523855298757553, 0.015464793890714645, -0.20567622780799866, -4.147169589996338, -0.14626672863960266, -0.37199077010154724, -0.21222007274627686, 0.11972176283597946, -0.11131401360034943, -0.7781128883361816, -0.2693723738193512, 0.05288831144571304, -0.2509262263774872, -0.06963491439819336, 0.3868856132030487, -0.07187007367610931, -0.3921681046485901, 0.7610272765159607, 0.38399559259414673]</t>
+          <t>['medium', 'high', 'high', 'high', 'medium', 'low']</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>[0.0, -1.0, 1.0, 0.0, -0.5, -1.0]</t>
+          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[4, 3, 3, 5, 3, 4]</t>
+          <t>[30.0, 30.0, 35.0, 30.0, 40.0, 30.0]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
+          <t>['man', 'man', 'man', 'man', 'woman', 'man']</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>[35.0, 40.0, 35.0, 40.0, 45.0, 25.0]</t>
+          <t>[1, 1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>['man', 'woman', 'man', 'woman', 'woman', 'man']</t>
+          <t>[3, 3, 5, 4, 5, 5]</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>[1, 1, 5, 1, 2, 1]</t>
+          <t>[1, 1, 1, 3, 1, 1]</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>[4, 5, 1, 5, 3, 4]</t>
+          <t>[5, 3, 5, 4, 5, 5]</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>[5, 5, 1, 5, 5, 5]</t>
+          <t>[1, 1, 1, 3, 1, 1]</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>[4, 4, 5, 5, 3, 5]</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>[1, 1, 5, 1, 2, 1]</t>
-        </is>
+          <t>[1, 1, 1, 3, 1, 1]</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>6</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>[5, 5, 2, 5, 5, 5]</t>
+          <t>[1, 1, 1, 3, 1, 1]</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>[5, 5, 1, 5, 5, 5]</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>[0.16666667 0.         0.         0.         0.83333333]</t>
-        </is>
-      </c>
-      <c r="T5" t="n">
+          <t>[0.83333333 0.         0.16666667 0.         0.        ]</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
         <v>0.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>172</v>
+        <v>251</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>I always hated visiting Nig York, but if I'm ever forced to I'll be sure to pack all my Confederate clothes and flags and to dance around Central Park! ( I may need a little protection)</t>
+          <t>I've been to Italy a few times, and only saw two niggers in Venice.... some old dudes who were missing nearly all their teeth.. . I just don't go back to Venice.. problem solved.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[5, 5, 3, 5, 5, 5]</t>
+          <t>[5, 5, 5, 3, 5, 5]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 5, 5, 5]</t>
+          <t>['{}', '{}', '{}', '{}', '{}', '{}']</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>['{}', '{}', nan, 'none', '{}', '{}']</t>
+          <t>['left', 'center', 'center', 'right', 'center', 'left']</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[0.18953466415405273, -0.12954939901828766, 0.12362214922904968, -0.2832106351852417, -0.012347601354122162, -0.3506954610347748, 0.48293477296829224, 0.5608935356140137, 0.08732230216264725, 0.2200043946504593, -0.13303859531879425, -0.09407863765954971, 0.2469187080860138, 0.24836522340774536, 0.2214251309633255, 0.07983452081680298, -0.43563175201416016, 0.5737276673316956, 0.15947705507278442, 0.1634404957294464, 0.11980665475130081, -0.14355529844760895, -0.08332802355289459, -0.24451564252376556, 0.1547774225473404, -0.17118701338768005, -0.07827331870794296, 0.08675416558980942, 0.26089945435523987, 0.08755478262901306, -0.14912258088588715, 0.3123522996902466, 0.4108164608478546, 0.2471110224723816, 0.4899941384792328, -0.15151964128017426, 0.13769754767417908, -0.23253847658634186, 0.3117489516735077, -0.014786536805331707, -0.3044322729110718, 0.07990158349275589, 0.2570172846317291, 0.2247253954410553, 0.511442244052887, -0.22667518258094788, -3.4119958877563477, -0.23858892917633057, -0.15090565383434296, -0.2360733449459076, 0.5664359927177429, -0.015808578580617905, 0.10301943123340607, 0.1732967346906662, 0.3253426253795624, 0.26150384545326233, -0.31547755002975464, 0.11090890318155289, 0.14305458962917328, 0.22266541421413422, 0.09104356914758682, 0.3708895742893219, -0.10524266958236694, 0.041340362280607224, -0.08455180376768112, 0.23370154201984406, 0.07417488843202591, 0.37103432416915894, -0.05238677188754082, 0.49055778980255127, -0.07754170149564743, 0.012947238981723785, 0.20721255242824554, 0.12470173090696335, -0.1231141984462738, -0.10273982584476471, -0.1465768963098526, 0.04535790532827377, -0.18380264937877655, 0.11336015164852142, -0.08033537119626999, 0.33833611011505127, 0.4796937108039856, -0.09905190765857697, 0.4715518653392792, 0.26153120398521423, -0.5715172290802002, -0.24645809829235077, 0.5872121453285217, 0.18375976383686066, -0.407003253698349, -0.08847513794898987, -0.7673766016960144, 0.36854493618011475, 0.5339222550392151, -0.14497250318527222, -0.3447905480861664, 0.029644468799233437, -0.0186544731259346, 0.3525669574737549, 0.14227618277072906, 0.3810250163078308, 0.16369444131851196, -0.5954182744026184, -0.0719691663980484, -0.044370975345373154, 0.5176187753677368, -0.4106487035751343, 0.45970258116722107, -2.023466110229492, 0.12676411867141724, 0.2794957458972931, -0.2789470851421356, -0.7380471229553223, 0.03256852179765701, 0.20321615040302277, 0.6289880871772766, -0.03206442669034004, -0.013396377675235271, 0.26550841331481934, -0.4473975896835327, 0.2871883511543274, 0.14922551810741425, -0.5213819742202759, 0.6550262570381165, 0.051819730550050735, 0.4404484033584595, -0.3266807198524475, -0.022229919210076332, 0.34033912420272827, 0.2870990037918091, 0.3563705086708069, -0.2884742319583893, -0.531906247138977, -0.30390939116477966, 0.5634857416152954, 0.015033716335892677, -0.11025913804769516, -0.23308081924915314, -0.23613937199115753, -0.3184332251548767, 0.12576061487197876, -3.2444021701812744, 0.20553691685199738, 0.6770379543304443, 0.5927380323410034, -0.24509121477603912, 0.10018900781869888, -0.28275641798973083, 0.09154196083545685, 0.14064738154411316, -0.20427335798740387, -0.4011048674583435, 0.17905652523040771, -0.2709961533546448, -0.46242624521255493, 0.361895352602005, 0.00919704232364893, -0.13281290233135223, 0.3102405071258545, 0.43445101380348206, 0.045253001153469086, -0.1433006376028061, 0.10540038347244263, -0.24149376153945923, 0.43553048372268677, 0.5769399404525757, 0.16844040155410767, 0.09659241139888763, -0.28263697028160095, 0.22650347650051117, 0.05178459733724594, 0.4779789447784424, 0.1880759447813034, 0.15491776168346405, 0.08363448828458786, 0.42319416999816895, 0.3495617210865021, -0.2969740927219391, -0.020783182233572006, -0.47746121883392334, 0.022549958899617195, 0.11758114397525787, 0.2855798602104187, 0.4584800899028778, 0.050249338150024414, 0.42458072304725647, -0.04323910176753998, -0.3754667043685913, 0.565227210521698, -0.18798455595970154, -0.15003719925880432, 0.27872881293296814, 0.15817132592201233, 0.6861234903335571, 0.014832697808742523, 0.30662956833839417, -0.38035133481025696, 0.00433669239282608, 0.1050715446472168, -0.050474222749471664, -0.006936382502317429, 0.42740243673324585, 0.298155814409256, -0.3527820110321045, 3.96579909324646, -0.1257067769765854, 0.1630493551492691, 0.03865627944469452, 0.21863460540771484, -0.33276885747909546, -0.08516747504472733, -0.3338213264942169, -0.026297569274902344, -0.5095548033714294, -0.17486631870269775, 0.29011160135269165, 0.1987965852022171, -0.11754123121500015, 0.20745857059955597, -0.026609817519783974, 0.4055173397064209, -0.6792902946472168, 0.2637365758419037, -0.09839151054620743, -0.0658607929944992, -0.19378632307052612, 0.038156908005476, 0.601410984992981, -1.8661062717437744, -0.2708955407142639, -0.17345036566257477, -0.6481391191482544, 0.33217743039131165, -0.18684892356395721, 0.2500835955142975, -0.005669105798006058, -0.22897066175937653, -0.06640903651714325, 0.27621182799339294, 0.050373371690511703, 0.2813678979873657, 0.1919534057378769, 0.34681838750839233, -0.2983148694038391, 0.5988423824310303, 0.05781414732336998, 0.06754641234874725, 0.4407851994037628, -0.020996449515223503, 0.327778697013855, 0.11607814580202103, 0.3019161820411682, -0.41050758957862854, 0.41418027877807617, 0.24526531994342804, 0.0866447314620018, -0.07494121044874191, -0.4494825303554535, -0.15188683569431305, -0.3554558753967285, 0.05684719234704971, -0.15959268808364868, 0.4641048014163971, -0.8341992497444153, 0.3189395070075989, 0.11177489906549454, -0.2913726270198822, 0.04060695692896843, -0.028070423752069473, -0.050384826958179474, -0.2836168706417084, -0.5499386787414551, -3.320336103439331, -0.2815144658088684, -0.21428106725215912, -0.08295558393001556, 0.19688470661640167, 0.06231993809342384, 0.003980754874646664, 0.17238838970661163, 0.12295561283826828, -0.5753601789474487, 0.39639854431152344, -0.24600958824157715, -0.2247198224067688, 0.1982877254486084, -0.31186822056770325, 0.16976794600486755, 0.416408509016037, -0.04943222925066948, -0.36096644401550293, -0.02000303566455841, -0.07003476470708847, 0.07896791398525238, -0.15329022705554962, 0.5449593663215637, 0.11731007695198059, -0.39693641662597656, -0.17526371777057648, -0.3639944791793823, -0.08368100970983505, -0.16960042715072632, 0.3218437731266022, -0.1506977081298828, -0.35041943192481995, -0.05125286057591438, -0.4428589940071106, -2.8461713790893555, -0.03173539415001869, -0.3240760862827301, -0.08104892075061798, -0.06764805316925049, 0.5170959234237671, 0.5960897207260132, -0.11438897997140884, -0.3048948049545288, -0.2571578025817871, 0.4663500487804413, -0.10422563552856445, 0.3252648711204529, -0.3002443313598633, 0.16478630900382996, 0.09416299313306808, 0.22714892029762268, 0.08287826180458069, 0.2614622712135315, 0.14073191583156586, -0.23945187032222748, 0.6147001385688782, 0.018067384138703346, -0.1780426949262619, 0.07525818049907684, 0.4900432825088501, -0.3485482335090637, 0.030909700319170952, -0.5049957633018494, -0.06500603258609772, 0.41892656683921814, -0.01105338241904974, -0.10044440627098083, -0.29050058126449585, -0.31595802307128906, -0.19323168694972992, 0.43009793758392334, -0.1994861364364624, 0.33214515447616577, -0.14694197475910187, 0.22273384034633636, 0.4409550130367279, 0.16928063333034515, 0.11943361163139343, 0.6346120238304138, -0.22336293756961823, -0.12381097674369812, 0.12914083898067474, 0.0917297825217247, 0.5052368640899658, 0.02465861104428768, 0.18569906055927277, 1.1331011056900024, 0.01146983727812767, 0.18191006779670715, 0.06608652323484421, 0.25748446583747864, 0.03808378428220749, -0.03611423075199127, 0.3264113962650299, 0.7578557133674622, -0.3154306411743164, 0.17952826619148254, -0.3411088287830353, -0.14195242524147034, -0.1697012037038803, 0.3638163208961487, -0.8567026257514954, -0.2506199777126312, -0.14049361646175385, -0.2767319083213806, -0.08886158466339111, -0.40777587890625, -1.273618459701538, 0.06868896633386612, 0.5323069095611572, -0.5416176915168762, 0.2239087074995041, 0.1975836306810379, 0.35389992594718933, 0.08345858752727509, -0.06336789578199387, -0.27493390440940857, 0.5872051119804382, -0.7021631598472595, -0.3023829460144043, -0.31105536222457886, 0.24217498302459717, -0.8245153427124023, 0.17775680124759674, 0.09330292791128159, 0.3288348913192749, 0.15954647958278656, 0.5410256385803223, -0.06689563393592834, 0.12096904218196869, 0.4397873282432556, -0.8399028778076172, 0.31958574056625366, -0.279251366853714, -0.27192842960357666, 0.3164294958114624, 0.17096664011478424, -0.21444165706634521, -0.054346416145563126, 0.15808238089084625, -0.2666836678981781, 0.6428825259208679, 0.25018998980522156, -0.004722029436379671, -0.3745221793651581, -0.2705639898777008, -0.3252834379673004, -0.012762133032083511, 0.9299941658973694, -0.17070262134075165, 0.03503269702196121, 0.7375450730323792, 0.14805632829666138, -0.02622140757739544, 0.018077297136187553, -0.12647458910942078, -0.25054553151130676, -0.40831276774406433, -0.4910616874694824, -0.44602087140083313, -0.005834557581692934, -0.12042378634214401, 0.38111722469329834, -0.28872421383857727, 0.03289012238383293, 0.1469353288412094, -0.5033267736434937, -0.2795037627220154, -0.20366553962230682, -0.41702619194984436, -0.5306599140167236, -0.10647419095039368, 0.24370764195919037, 0.08166685700416565, 0.06876646727323532, -0.06969036161899567, -0.3691222369670868, 0.0077437590807676315, -0.6273783445358276, 0.43941617012023926, -0.0699857622385025, 0.08999156951904297, -0.2166459560394287, 0.8204482197761536, -0.25825849175453186, 0.09213143587112427, 0.37586623430252075, -0.8088434934616089, 0.16270393133163452, 0.22639459371566772, 0.04849689453840256, 0.40321171283721924, -0.017038144171237946, 0.23709847033023834, 0.14763040840625763, -0.13404768705368042, -1.7651481628417969, 0.5506430864334106, 0.4871740937232971, 0.20703865587711334, 0.16855275630950928, -0.6028946042060852, -0.06651566177606583, 0.2982349395751953, -0.18579961359500885, -0.08289315551519394, -0.26787006855010986, 0.3461763858795166, -0.0988774299621582, 0.05522364005446434, 0.18331357836723328, 0.09581492841243744, 0.07985636591911316, -0.6802030801773071, 0.029714519158005714, -0.2896302044391632, -0.10489330440759659, 0.20097114145755768, 0.18859291076660156, -0.2628791332244873, 0.15546007454395294, -0.3977111876010895, -0.1272943615913391, 0.6107766032218933, -0.15157897770404816, 0.8759635090827942, 0.17092609405517578, -0.35260048508644104, -1.0259214639663696, -0.1458306610584259, 0.17922845482826233, 0.15839605033397675, 0.3486660420894623, -0.061603713780641556, 0.17542555928230286, 0.39341139793395996, -0.610471248626709, 0.16289007663726807, 0.5009344816207886, 0.28897470235824585, 0.39206209778785706, 0.26259931921958923, 0.06102991849184036, 0.5853742361068726, 0.35950928926467896, -0.8231483697891235, -0.037595637142658234, -0.37363943457603455, -0.006944881286472082, -0.1695394665002823, -0.44473159313201904, -0.5153519511222839, -0.014215939678251743, 0.015143207274377346, -0.3861336410045624, -0.20921817421913147, 0.03766912594437599, -0.17166246473789215, -0.3460163176059723, 0.011731536127626896, -0.5013523101806641, -0.5408381223678589, -0.32114753127098083, -0.38589540123939514, -0.3363487422466278, 0.3197103440761566, 0.38422223925590515, 0.5129035115242004, -0.3262856602668762, 0.27652111649513245, -0.2926426827907562, 0.03740639239549637, -0.4338953495025635, 0.2670336961746216, 0.5929874777793884, -0.15763871371746063, 0.3661041259765625, -0.2876189649105072, 0.08790995925664902, 0.23904414474964142, -0.4185607433319092, 0.24513204395771027, -0.548856258392334, -0.15514984726905823, 0.1587066501379013, -0.2806679904460907, -0.4915028214454651, -0.4969082772731781, 0.27248939871788025, 0.21152988076210022, -0.18009598553180695, -0.03274380788207054, 0.25325146317481995, -0.06715511530637741, -0.01765604130923748, -0.3011521100997925, -0.348734050989151, 0.4276728630065918, 0.567051887512207, 0.035414814949035645, -0.033936794847249985, 0.39295434951782227, 0.2862843871116638, -0.11190750449895859, -0.5445308089256287, -0.3720764219760895, 0.3232634961605072, -0.0009052504901774228, -0.35755494236946106, 0.267628014087677, 0.20252513885498047, -0.47921234369277954, 0.58466637134552, -0.6309748291969299, 1.583558201789856, 0.052852217108011246, 0.17205582559108734, -0.43515393137931824, 0.6153824329376221, 0.00855983980000019, -0.41268348693847656, -0.057967618107795715, -0.40801218152046204, 0.7291703820228577, -0.41948720812797546, 0.3662143647670746, -0.4246722459793091, -0.08404210209846497, 0.7934908866882324, 0.15338335931301117, 0.026515958830714226, -0.47236230969429016, -0.4605250060558319, -0.01923634670674801, -0.2778598964214325, 0.31402090191841125, 0.44036275148391724, -0.3441648483276367, 0.30036669969558716, 0.1980140656232834, 0.11512745171785355, -0.22600023448467255, 0.3611380457878113, 0.3891128897666931, -0.049429479986429214, 0.10537370294332504, -0.19024981558322906, 0.6359582543373108, -0.6493231654167175, 0.38252565264701843, 0.35645344853401184, -0.14907988905906677, -0.24741603434085846, -0.06216438114643097, 0.04255540296435356, -0.17749549448490143, 0.4859490692615509, -0.056558433920145035, -0.09963681548833847, 0.2883847951889038, -0.10599005967378616, -0.27182066440582275, 0.5573864579200745, 0.0813189372420311, -0.21554522216320038, -0.06346600502729416, 0.13984426856040955, 0.06767681241035461, 0.10241123288869858, -0.12128055095672607, 0.07827557623386383, -0.3988453149795532, -0.45441552996635437, 0.5746878385543823, -0.6084668040275574, 0.2842324674129486, -0.013178255409002304, -0.019992824643850327, -0.12412739545106888, -0.0772612988948822, -0.14514535665512085, -0.11022640019655228, 0.03353080898523331, -0.554133951663971, -0.21696321666240692, 0.5966172218322754, -0.07962106168270111, -0.3506455719470978, 0.6413316130638123, 0.4605424106121063, 0.5322234034538269, -0.447333425283432, 0.0018571619875729084, -2.7813000679016113, -0.06723301857709885, 0.11515448242425919, 0.13278229534626007, -0.03402676060795784, 0.27800098061561584, 0.530665934085846, -0.014131966046988964, 0.27621304988861084, -0.1602630764245987, 0.36397069692611694, 0.4305591285228729, 0.5602949857711792, -0.2311272919178009, 0.08811100572347641, 0.029517199844121933, 0.10777647793292999, -0.4413858950138092, 0.08908498287200928, -0.15761762857437134, 0.1226329356431961, 0.014177154749631882, 0.03595047444105148, -0.11839596927165985, -0.4832229018211365, 0.2568952143192291, -0.07216787338256836, -0.041986819356679916, -0.09229068458080292, 0.23257729411125183, -0.2875365614891052, 0.35637128353118896, -0.49378541111946106, 0.13651582598686218, 0.0746263638138771, 0.26622912287712097, -0.4912823438644409, 0.042083580046892166, 0.3100489377975464, -0.01571623794734478, 0.048015888780355453, 0.3091544210910797, -0.015920262783765793, 0.3430970311164856, 0.557468056678772, 0.2457537204027176, 0.5540631413459778, -0.2110106199979782, 0.32089781761169434, -0.06476767361164093, -0.10954828560352325, -0.10861057788133621, 0.0931183397769928, 0.13314415514469147, 0.16315647959709167, 0.13179698586463928, 0.06933259218931198, 0.16593092679977417, 0.07836219668388367, -0.48574140667915344, -0.06598905473947525, 0.3468623757362366, -0.10092335194349289, -0.0021658337209373713, 0.26309964060783386, -0.2918263375759125, -0.1812460869550705, 0.11045219749212265, -0.2850523889064789, -0.6351697444915771, -0.6068411469459534, 0.11957966536283493, 0.30340251326560974, 0.2780187427997589, 0.23608966171741486, -0.31165826320648193, 0.8706942796707153, 0.9179645776748657, 0.12474776059389114, 0.10258949548006058, 0.004233906976878643, 0.10181385278701782, 0.2847824990749359, 0.11404620110988617, 0.24978652596473694, -7.5015974044799805, -0.13952632248401642, 0.07953639328479767, -0.23202061653137207, -0.30644795298576355, -0.6874006986618042, -0.3848969638347626, -0.3922750949859619, -0.07900048792362213, -0.399050235748291, 0.5449746251106262, 0.051275257021188736, -0.14747510850429535, -0.17919480800628662, 0.1925240308046341, 0.6543784141540527]</t>
+          <t>['high', 'high', 'high', 'high', 'high', 'high']</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>[-0.5, 0.0, 1.0, -0.5, -0.5, -0.5]</t>
+          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[4, 4, 3, 2, 5, 5]</t>
+          <t>[40.0, 45.0, 40.0, 40.0, 35.0, 35.0]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
+          <t>['woman', 'man', 'woman', 'man', 'woman', 'woman']</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>[40.0, 35.0, 35.0, 50.0, 35.0, 35.0]</t>
+          <t>[1, 1, 1, 5, 3, 1]</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>['woman', 'man', 'man', 'man', 'woman', 'woman']</t>
+          <t>[4, 5, 5, 1, 4, 5]</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>[1, 1, 5, 1, 1, 1]</t>
+          <t>[5, 5, 5, 3, 5, 5]</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>[4, 4, 1, 2, 5, 5]</t>
+          <t>[2, 4, 5, 5, 3, 4]</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 5, 5, 5]</t>
+          <t>[1, 1, 1, 3, 5, 1]</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>[2, 4, 5, 5, 4, 4]</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>[1, 1, 5, 3, 1, 1]</t>
-        </is>
+          <t>[5, 5, 5, 3, 5, 5]</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>6</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 5, 5, 5]</t>
+          <t>[5, 5, 5, 3, 5, 5]</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>[5, 5, 3, 5, 5, 5]</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
           <t>[0.         0.         0.16666667 0.         0.83333333]</t>
         </is>
       </c>
-      <c r="T6" t="n">
+      <c r="S6" t="n">
         <v>0.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>216</v>
+        <v>328</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">I mean, I dont care if all the gays are infected to the nines. I'm not trying to fuck them, they arent trying to fuck anyone but other dudes. Just making doctors rich raw dogging their twink boys.Who cares what they got or do, its an insular culture anyway.
-</t>
+          <t>Our economy is in the fucking dark and all black people care about is black lives matter</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[2, 5, 3, 3, 5, 4]</t>
+          <t>[5, 4, 1, 4, 5, 5]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[4, 5, 4, 3, 5, 5]</t>
+          <t>[nan, '{}', '{}', '{}', '{}', 'bisexual']</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>['NONE', 'immigrant, black,', '{}', '{}', '{}', '{}']</t>
+          <t>['left', 'left', 'right', 'center', 'far left', 'left']</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[0.03162346035242081, 0.2916378676891327, -0.08129120618104935, -0.1355944275856018, -0.6339654326438904, -0.40261128544807434, 1.0576157569885254, 0.8723669052124023, 0.3278671205043793, -0.2887972593307495, 0.7507408261299133, -0.053960397839546204, -0.5244370698928833, 0.22167466580867767, 0.7075574994087219, 0.38742029666900635, -0.2163691371679306, 0.3874398469924927, 0.06687367707490921, 0.17613357305526733, -0.31283941864967346, -0.685192346572876, 0.1273922175168991, -0.11083315312862396, 0.14657297730445862, 0.3612074553966522, 0.5653220415115356, -0.4104512929916382, -0.34480997920036316, 0.409758061170578, -0.2767021954059601, 0.23438945412635803, -1.2112584114074707, -0.4463362693786621, 0.477976530790329, -0.1398356854915619, -0.21451997756958008, 0.45743900537490845, 0.34278517961502075, -0.08664330095052719, -0.2936602830886841, -0.5054985880851746, -0.6046721935272217, -0.21651028096675873, 0.13916949927806854, -0.2580583989620209, -4.152390956878662, 0.4047583341598511, -0.03271223604679108, -0.4926501512527466, 0.340203195810318, -0.8679124712944031, -0.3536781668663025, 0.7646378874778748, 0.2725053131580353, 0.6220437288284302, -0.1854400634765625, 0.27252089977264404, -0.11330282688140869, 0.3254898190498352, 0.22557540237903595, 0.3398028612136841, -0.09537907689809799, 0.22916226089000702, 0.12772150337696075, 0.43655073642730713, -0.5276766419410706, 0.6776153445243835, -0.6637458205223083, 0.05986293777823448, -0.8174158334732056, -0.298711359500885, 0.9646116495132446, 0.021430913358926773, 0.43944689631462097, -0.15212097764015198, -0.18795038759708405, 0.12068025022745132, -0.5189422965049744, 0.5318782925605774, 0.09019794315099716, 1.0414769649505615, -0.11759013682603836, 0.34477972984313965, 0.008966260589659214, 0.48310330510139465, 0.2459014654159546, 0.000653889263048768, 0.20402562618255615, 0.057466961443424225, -0.2993861436843872, 0.11428206413984299, 0.5482475757598877, -0.05171232298016548, 0.38067826628685, 0.07202218472957611, 0.49655428528785706, 0.022195113822817802, 0.396646112203598, 0.4891708493232727, 0.5918349027633667, 0.14497826993465424, 0.14658859372138977, -0.8864210844039917, -0.3943009674549103, -0.3859744369983673, 0.09818284958600998, -0.5869826674461365, 0.05777541175484657, -1.613875389099121, 0.6565560698509216, -0.09961767494678497, -0.3640945851802826, -0.2618887722492218, -0.4363120198249817, 0.29901331663131714, 0.42253977060317993, -0.680112898349762, 0.4608747065067291, 0.21933284401893616, 0.06784617155790329, 0.05494588240981102, -0.05837966874241829, -0.250410258769989, -0.307657390832901, 0.08542292565107346, 0.4445756673812866, 0.36633235216140747, 0.23198530077934265, 0.4119616448879242, 0.30737656354904175, 0.571276843547821, -0.23225657641887665, -0.3929581940174103, 0.15443910658359528, -0.24171099066734314, 0.012515868060290813, -0.2567460834980011, -0.149830624461174, -0.32782426476478577, -0.5478636622428894, -0.766400933265686, -2.291105031967163, 0.1727130115032196, 0.40283653140068054, -0.06987108290195465, -0.07577259093523026, -0.5702873468399048, -0.3220115005970001, 0.08742348849773407, 0.2897500991821289, 0.12635229527950287, 0.4005694091320038, 0.03905089199542999, -0.2015279084444046, 0.07710196822881699, -0.310420423746109, -0.48914697766304016, 0.529222846031189, 0.6142507195472717, 0.0985177531838417, -0.04295686259865761, 0.10951122641563416, 0.22856317460536957, 0.04477729648351669, 0.19924069941043854, 0.05556416139006615, 0.4079797863960266, -0.32486847043037415, -0.3665468990802765, 0.18829163908958435, 0.026010049507021904, 0.7552726864814758, -0.12973448634147644, 0.5381236672401428, -0.18126602470874786, 0.6724468469619751, 0.6289281249046326, 0.0814952477812767, 0.22264261543750763, -0.8162114024162292, 0.5928858518600464, 0.3372948169708252, 0.12611980736255646, 0.7488950490951538, -0.3415221571922302, 0.9002389311790466, -0.10295701771974564, -0.6080870628356934, 0.4800710082054138, -0.67823725938797, -0.7104496359825134, 0.6848040819168091, 0.3893868327140808, 0.7524284720420837, -0.49863409996032715, 0.30362895131111145, -0.6360498666763306, -0.016636202111840248, -0.03777701035141945, -0.368662565946579, -0.4292182922363281, 0.17994417250156403, -0.047203388065099716, -0.7522571682929993, 3.6840951442718506, 0.07551208138465881, -0.3419222831726074, -0.18736177682876587, 0.4005468487739563, -0.15721391141414642, -0.4646240472793579, -0.14116863906383514, -0.544162929058075, -0.39411821961402893, 0.2866460382938385, 0.22208049893379211, -0.3198656439781189, -0.3161543905735016, -0.19054313004016876, 0.6625582575798035, 0.022686075419187546, -0.21946923434734344, 0.2002706378698349, -0.1056799441576004, -0.11942531913518906, -0.18018929660320282, -0.2385411411523819, 0.12728461623191833, -2.074162006378174, 0.14061187207698822, -0.2585657238960266, -0.024917514994740486, 0.3718380331993103, -0.17547477781772614, 0.4812304377555847, -0.05467956140637398, -0.09271559864282608, -0.10499775409698486, -0.15371286869049072, -0.2645532190799713, 0.8825575113296509, -0.4752761423587799, -0.1641717404127121, -0.21884466707706451, 0.5995067954063416, 0.4279713034629822, -0.9744900465011597, 0.022818459197878838, 0.11202806979417801, -0.3426836431026459, 0.21622207760810852, -0.07229804247617722, -0.27776429057121277, 0.4885690212249756, 0.39358919858932495, 0.1379392445087433, 0.03089764527976513, -0.10685867816209793, -1.0867934226989746, -0.5705129504203796, 0.24459944665431976, -0.06659457832574844, 0.2740868628025055, -0.6262964010238647, -0.4494022727012634, 0.39181914925575256, 0.22116197645664215, -0.8436005115509033, -0.15494513511657715, 0.4656033515930176, 0.11031526327133179, -0.10281524807214737, -2.1626431941986084, 0.136419415473938, -0.03697802126407623, 0.19536380469799042, 0.5327426791191101, -0.5734347701072693, -0.4014192819595337, 0.14229273796081543, 0.32414326071739197, -1.0255790948867798, 0.1047305017709732, -0.0893465057015419, 0.15878750383853912, 0.11043509840965271, -0.3871058225631714, 0.22782008349895477, -0.1272561401128769, -0.08467058837413788, -0.144761860370636, -0.34765246510505676, 0.39824870228767395, -0.10488017648458481, 0.10848457366228104, 0.08436967432498932, -0.15396511554718018, -0.20493726432323456, 0.008698745630681515, -0.35983729362487793, 0.008070792071521282, 0.04385047033429146, 0.5488082766532898, -0.23004542291164398, -0.31070181727409363, 0.1345546543598175, -0.2023065984249115, -3.4716129302978516, -0.0902012288570404, -0.21014362573623657, -0.30954182147979736, 0.14225520193576813, -0.20300208032131195, 0.8788809776306152, -0.2614476978778839, -0.4990038275718689, 0.29121163487434387, 0.2549493610858917, -0.14528849720954895, 0.005197358317673206, -0.0756659135222435, 0.9716208577156067, 0.349403440952301, 0.6197189092636108, -0.6055514216423035, 0.5481987595558167, 0.24354518949985504, 0.4668482542037964, 0.525001585483551, 0.221421480178833, -0.47521767020225525, 1.0149667263031006, 0.2421831637620926, -0.9206185936927795, -0.13369764387607574, 0.14650066196918488, 0.607887327671051, 0.16464921832084656, 0.2175251841545105, 0.5691898465156555, -0.3141505718231201, -0.17235417664051056, -0.45058950781822205, 0.3352995216846466, 0.05337637662887573, 0.15103371441364288, 0.020604047924280167, 0.13495473563671112, 0.25797852873802185, -0.31691449880599976, -0.3672538995742798, 0.6725305318832397, -0.06486690789461136, -0.07818151265382767, -0.2716698944568634, 0.2557845711708069, 0.3286843001842499, 0.05856569483876228, 0.3626294732093811, 0.8795822262763977, 0.4293292164802551, -0.1335458755493164, -0.432040810585022, -0.011531071737408638, 0.11671468615531921, -0.3926435112953186, -0.3099226951599121, 0.654900312423706, -0.5432937741279602, 0.24153535068035126, 0.1534767597913742, 0.18366371095180511, -0.26353776454925537, 0.22721438109874725, -0.6220851540565491, 0.22568973898887634, 0.3381824493408203, -0.013459893874824047, 0.07324470579624176, -0.46413514018058777, -1.7567542791366577, 0.12392064929008484, -0.3049074709415436, -0.29406362771987915, 0.4171111285686493, -0.3407987654209137, 0.4280080199241638, -0.4548780024051666, -0.021668365225195885, -0.6212848424911499, 0.3015971779823303, -0.8225098848342896, -0.3761279881000519, 0.42747002840042114, 0.23171374201774597, -1.0038518905639648, -0.33991530537605286, 0.26518651843070984, 0.3735462725162506, 0.03845975548028946, 0.7366487979888916, -0.3851306438446045, -0.043672606348991394, 0.380986750125885, -0.32612431049346924, 0.4871065020561218, -0.4280685484409332, 0.5502877235412598, -0.2108376920223236, -0.27246320247650146, -0.1696454882621765, -0.1712731420993805, -0.0027382755652070045, 0.16441373527050018, 1.0781959295272827, 0.2010343223810196, 0.061532147228717804, -0.615516722202301, -0.22201485931873322, -0.08661749213933945, 0.34888508915901184, 0.8297410011291504, -0.47479575872421265, -0.3492421507835388, 0.6579763293266296, 0.42080673575401306, -0.0345076285302639, 0.873876690864563, 0.148498073220253, -0.5090097784996033, -0.38284510374069214, -0.4417203962802887, 0.5504167675971985, -0.3559165894985199, -0.11691935360431671, -0.5004832148551941, -0.2406294345855713, 0.09361225366592407, -0.3229018747806549, -0.39191240072250366, -0.10081758350133896, -0.05015810579061508, -0.36773237586021423, 0.05966277793049812, 0.17976464331150055, -0.06690867245197296, 0.3017362952232361, 0.9203867316246033, 0.013833114877343178, -0.06104772537946701, -0.31672435998916626, -0.8115331530570984, 0.5940654873847961, -0.17117571830749512, 0.2732599377632141, 0.04534987360239029, 0.787509560585022, -1.1434592008590698, 0.039819516241550446, -0.16128084063529968, -1.278127670288086, 0.32652536034584045, 0.5281636118888855, -0.34171682596206665, -0.20285829901695251, 0.07469018548727036, -0.5643680095672607, -0.06376976519823074, 0.059951797127723694, -2.084012746810913, 0.5108001828193665, 0.6417270302772522, 0.2082120031118393, 0.5286903977394104, -0.3866058886051178, -0.7292677760124207, 0.26125583052635193, 0.017737651243805885, 0.10783872753381729, -0.656389057636261, -0.12806643545627594, 0.11174386739730835, 0.10022930800914764, 0.22334244847297668, 0.1525033712387085, -0.09822270274162292, -0.6374445557594299, -0.5180403590202332, -0.1372334212064743, -0.17779839038848877, 0.19783708453178406, 0.19474096596240997, 0.12491445988416672, 0.09861510992050171, -0.21528056263923645, -0.26413196325302124, 0.8207747340202332, 0.2681827247142792, 0.10307414829730988, -0.4440036118030548, -0.15173953771591187, -0.8674488663673401, -0.07463257759809494, -0.07291723787784576, 0.15629160404205322, 0.42874565720558167, 0.0360267348587513, 1.1007695198059082, 0.8400364518165588, -0.22979606688022614, 0.5427291989326477, 0.4855043590068817, 0.3150266706943512, 0.2549593150615692, 0.03734690696001053, -0.5519983768463135, 1.0648972988128662, 0.3695361614227295, -0.6903159618377686, -0.5756056904792786, -0.08112186193466187, -0.5294415950775146, -0.4710378348827362, -0.034821800887584686, -0.2612575590610504, -0.3623181879520416, 0.15088240802288055, -0.9194978475570679, 0.20750652253627777, -0.4548499584197998, -0.13196943700313568, -0.6818135380744934, -0.048021990805864334, -0.4246494174003601, -0.9860365390777588, -0.08498594909906387, -0.6968238949775696, -0.22380931675434113, 0.25639721751213074, 0.6565604209899902, 0.20921824872493744, -0.6485985517501831, 0.7526859045028687, 0.22962409257888794, 0.9910159707069397, 0.08158313482999802, -0.06325164437294006, 0.3647784888744354, -0.18477527797222137, -0.14609065651893616, -0.3648098111152649, 0.15804055333137512, 0.16027390956878662, 0.33060240745544434, 0.32412558794021606, -0.11540832370519638, -0.06716346740722656, 0.10539401322603226, -0.787543773651123, -1.0042264461517334, -0.1962897628545761, -0.002588920295238495, 0.26731085777282715, -0.21501900255680084, -0.013117928057909012, 0.29426369071006775, -0.22734016180038452, -0.15966100990772247, -0.05858184024691582, -0.6673073172569275, -0.15683580935001373, 0.25961828231811523, -0.1658429056406021, 0.42790526151657104, 0.34861359000205994, 0.18444988131523132, 0.22249403595924377, -0.44245728850364685, -0.17700690031051636, 0.31656837463378906, -0.10118291527032852, -0.47805365920066833, -0.48439279198646545, -0.35316768288612366, -0.30166545510292053, 0.6095967292785645, -0.4962719976902008, 1.1401288509368896, -0.03612276166677475, 0.17075946927070618, -0.7503501772880554, 0.7654518485069275, -0.17424368858337402, 0.4932510256767273, 0.6218554377555847, -0.38308972120285034, 0.7189727425575256, -0.6327261328697205, 0.2542937994003296, -0.32759636640548706, -0.004089306108653545, 1.1042797565460205, -0.31670093536376953, -0.09208649396896362, -0.39600393176078796, -0.5840178728103638, -0.041073501110076904, 0.0033410442993044853, 0.3601943850517273, 0.8213513493537903, -0.2178429365158081, 0.5573360919952393, 0.4992762506008148, 0.4536724388599396, 0.16190218925476074, 0.556321918964386, 0.6827682256698608, -0.3604658842086792, -0.1777479350566864, 0.0963314026594162, -0.050357189029455185, -1.1405088901519775, -0.027566678822040558, 0.1654103398323059, 0.0925077423453331, -0.2336675226688385, 0.33007198572158813, 0.38843050599098206, -0.12691456079483032, 0.6094261407852173, -0.11796893179416656, -0.3655281662940979, 0.2827186584472656, -0.3500381112098694, -0.4044727087020874, 1.0034884214401245, 0.7022695541381836, 0.44706758856773376, -0.11178859323263168, -0.4898187816143036, -0.000922340783290565, 0.36438265442848206, -0.42067816853523254, -0.33031395077705383, -0.1086675301194191, 0.025024909526109695, 0.32252734899520874, -0.2463851422071457, 0.9208357334136963, -0.24363985657691956, -0.33365747332572937, 0.07362976670265198, 0.632227897644043, -0.3741901218891144, -0.2815866768360138, 0.4103255867958069, -0.5934826731681824, 0.13311032950878143, 0.6365718841552734, 0.04118524119257927, 0.16732533276081085, 0.7092669010162354, 0.45631012320518494, 0.059856489300727844, 0.13643278181552887, -0.12341345101594925, -1.869421124458313, 0.78108811378479, 0.07128635793924332, 0.14462760090827942, -0.08763507753610611, 0.6056867241859436, 0.3771549463272095, -0.3615497946739197, 0.4278433322906494, -0.4156019985675812, 0.6044084429740906, 0.5329890847206116, 0.29432353377342224, -0.02586185373365879, 0.46747416257858276, 0.16124986112117767, 0.4001419246196747, -0.23735901713371277, -0.009024271741509438, -0.6276984810829163, 0.5480588674545288, 0.40914106369018555, -0.237317755818367, -0.6834548711776733, -0.5029794573783875, 0.6517370343208313, 0.20061205327510834, -0.03141656517982483, 0.3492780923843384, 0.39744964241981506, 0.06305336952209473, 0.2200542390346527, 0.4249112010002136, -0.45564183592796326, 0.20820306241512299, -0.2974744737148285, -0.7290053367614746, 0.1667044311761856, 0.05886487290263176, -0.06351745128631592, -0.13384626805782318, 0.5571627020835876, 0.08769822865724564, -0.06883016973733902, 0.2925160825252533, -0.6842144727706909, 0.4922679364681244, 0.01922772265970707, 0.8266743421554565, -0.20815154910087585, 0.01906672492623329, 0.20811805129051208, 0.34411928057670593, -0.3097880780696869, 0.06305758655071259, 0.1406562626361847, 0.19906781613826752, 0.0008142589940689504, -0.07477542012929916, -0.9312046766281128, 0.15869438648223877, 0.17051075398921967, -0.20906619727611542, -0.1540295034646988, 0.4084375500679016, -0.31716394424438477, 0.1447151154279709, 0.828787088394165, 0.22189173102378845, -0.29735496640205383, -0.16822704672813416, 0.026098359376192093, 0.6301441192626953, 0.1870841085910797, -0.3563863933086395, -0.2619963586330414, 0.2442842572927475, -0.46134939789772034, 0.4367152154445648, -0.291891872882843, -0.05752560496330261, 0.402913898229599, -0.18714100122451782, 0.2902128994464874, 0.6053564548492432, -4.46500825881958, -0.10231557488441467, -0.3388936519622803, -0.6449106931686401, -0.09987743198871613, -0.3968251943588257, -0.1916573941707611, -0.27554622292518616, 0.07636361569166183, -0.2032131850719452, 0.013392109423875809, 0.36296260356903076, -0.30075421929359436, -0.6095419526100159, 0.743807852268219, 0.5400926470756531]</t>
+          <t>['medium', 'high', 'low', 'high', 'low', 'medium']</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>[1.0, 0.0, 0.5, 0.5, -0.5, -0.5]</t>
+          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 2, 4, 4]</t>
+          <t>[30.0, 30.0, 40.0, 30.0, 30.0, 40.0]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
+          <t>['man', 'man', 'man', 'man', 'nonBinary', 'woman']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>[45.0, 35.0, 45.0, 35.0, 40.0, 25.0]</t>
+          <t>[1, 1, 5, 2, 1, 1]</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>['man', 'woman', 'man', 'man', 'man', 'man']</t>
+          <t>[3, 3, 2, 4, 3, 5]</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>[5, 1, 4, 2, 2, 1]</t>
+          <t>[5, 4, 3, 4, 5, 5]</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>[4, 4, 3, 2, 4, 3]</t>
+          <t>[5, 3, 5, 4, 3, 5]</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>[2, 5, 3, 2, 5, 5]</t>
+          <t>[1, 1, 4, 3, 1, 1]</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>[3, 4, 4, 2, 3, 5]</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>[2, 1, 3, 3, 2, 2]</t>
-        </is>
+          <t>[5, 1, 1, 4, 5, 5]</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>6</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>[4, 1, 1, 3, 1, 2]</t>
+          <t>[5, 4, 1, 4, 5, 5]</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>[2, 5, 3, 3, 5, 4]</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>[0.         0.16666667 0.33333333 0.16666667 0.33333333]</t>
-        </is>
-      </c>
-      <c r="T7" t="n">
-        <v>0.5</v>
+          <t>[0.16666667 0.         0.         0.33333333 0.5       ]</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>250</v>
+        <v>343</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>I'm too broke to buy anything angry... Hot heads ain't sexy. Calling names ain't sexy.. How would a queen address problems? Not wit anger</t>
+          <t>Rick the dick is a complete prick! Whenever he appears or picks up the camera to say somethingI want to hit my head against the wall. Why do the husbands always think they can get involved in the wives channels?! Bore off mate, go to work!</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 3, 1, 1]</t>
+          <t>[5, 5, 4, 5, 1, 5]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 3, 1, 3]</t>
+          <t>[nan, '{}', '{}', '{}', '{}', '{}']</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>[nan, '{}', '{}', '{}', 'bisexual', '{}']</t>
+          <t>['left', 'left', 'right', 'right', 'center', 'far left']</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>[0.05658324062824249, 0.1919056475162506, -0.11798959970474243, -0.3706163465976715, -0.4131578803062439, -0.14645102620124817, 0.23752586543560028, -0.016051821410655975, 0.2564968168735504, -0.39846134185791016, 0.16055026650428772, 0.2956118583679199, -0.11692455410957336, 0.2135411649942398, 0.21581587195396423, 0.10598955303430557, 0.2720598578453064, 0.5262373089790344, -0.00699204346165061, -0.0934164747595787, -0.15844234824180603, -0.17860886454582214, 0.2358720302581787, -0.116275355219841, 0.3718523383140564, -0.08219517767429352, 0.11486028134822845, 0.006406588479876518, -0.25861918926239014, 0.3937673270702362, 0.01622401736676693, 0.18233336508274078, -0.22212094068527222, -0.10729286819696426, 0.19168756902217865, -0.067714162170887, 0.05076851323246956, 0.020597076043486595, 0.39017295837402344, -0.3734395205974579, -0.37280023097991943, -0.11757205426692963, 0.029671866446733475, -0.2199006974697113, -0.12787674367427826, -0.35661280155181885, -3.909912347793579, 0.1474280059337616, -0.24990156292915344, -0.5535109043121338, 0.29233187437057495, -0.04425835236907005, -0.02061220444738865, 0.4304869472980499, 0.31025034189224243, 0.39371809363365173, -0.24142338335514069, 0.017404237762093544, -0.09191522747278214, -0.2977474331855774, 0.4586583077907562, 0.07819712162017822, 0.050049394369125366, 0.5542734265327454, 0.06228125840425491, 0.35887572169303894, -0.04096357151865959, 0.2845742106437683, -0.3214123547077179, 0.7073125243186951, -0.3832436501979828, -0.03670669347047806, 0.4397467076778412, -0.25934529304504395, -0.08269535005092621, -0.4433881640434265, -0.3745032548904419, 0.2371019870042801, -0.40638142824172974, 0.1189269870519638, -0.1383811980485916, 0.5906409621238708, 0.16793301701545715, -0.14911915361881256, 0.005770017858594656, 0.331513911485672, -0.115826815366745, 0.12609700858592987, 0.03488811105489731, 0.5533571243286133, 0.04981718584895134, 0.11647234857082367, 0.028200319036841393, 0.33604419231414795, 0.04024316743016243, -0.12442947179079056, 0.4097025990486145, 0.2657051682472229, 0.4918646514415741, 0.3792816400527954, 0.25806131958961487, -0.39763107895851135, 0.07596468180418015, -0.4587903618812561, -0.28252485394477844, -0.3254837095737457, 0.09801989793777466, -0.40204980969429016, -0.13394443690776825, -2.1445367336273193, 0.33817926049232483, -0.30031999945640564, 0.051143575459718704, -0.15871118009090424, -0.07325860112905502, 0.43768081068992615, 0.33612000942230225, 0.023604894056916237, 0.39480793476104736, -0.06530894339084625, 0.02905341424047947, 0.22071222960948944, 0.30465182662010193, -0.29548659920692444, 0.2791503965854645, -0.018684975802898407, 0.01035378035157919, 0.20292268693447113, 0.004674934782087803, 0.06943352520465851, 0.21877573430538177, 0.1575680822134018, -0.0025875407736748457, 0.03790793940424919, 0.04270085692405701, 0.05994820222258568, 0.18563060462474823, 0.08336935937404633, 0.18286195397377014, -0.2064599245786667, -0.43556109070777893, -0.13828803598880768, -2.7523889541625977, 0.15265163779258728, 0.946354866027832, -0.2291143387556076, -0.16638557612895966, -0.36268529295921326, -0.07602144032716751, 0.19291414320468903, -0.157522052526474, 0.193132683634758, 0.10975001007318497, -0.2557995319366455, -0.3776862919330597, -0.23752206563949585, -0.27581632137298584, 0.040875568985939026, 0.07719217240810394, 0.6289659142494202, -0.18132761120796204, -0.3549252450466156, 0.07056356966495514, 0.05552702397108078, -0.003091661259531975, -0.1843942403793335, 0.2414667010307312, 0.386749804019928, 0.07535912096500397, 0.23312129080295563, 0.21244585514068604, -0.16820648312568665, 0.7575407028198242, 0.5644491910934448, 0.2942656874656677, 0.20269954204559326, -0.08274959772825241, 0.0367899164557457, 0.06723354756832123, 0.3824717402458191, -0.7321056723594666, 0.40317291021347046, 0.052393246442079544, -0.1486666351556778, 0.30533745884895325, 0.19962556660175323, 0.46008387207984924, -0.2279970943927765, -0.4725387990474701, -0.13036391139030457, -0.40327489376068115, -0.40466779470443726, 0.2586505711078644, 0.15469986200332642, 0.8109539747238159, -0.23148095607757568, 0.15560130774974823, -0.3527946472167969, -0.2672618627548218, 0.3316340744495392, 0.0998680591583252, -0.22501136362552643, 0.3316219449043274, -0.3231879770755768, -0.3030894100666046, 4.156560897827148, 0.15384739637374878, -0.06684377044439316, -0.24977757036685944, 0.19272078573703766, -0.3805781304836273, -0.25405195355415344, -0.032833531498909, -0.3795096278190613, -0.08069532364606857, 0.25783005356788635, 0.5336788892745972, -0.279561311006546, -0.05411117151379585, -0.0025198233779519796, 0.03609898313879967, -0.03135789930820465, -0.6030423045158386, 0.0695546567440033, -0.42120298743247986, -0.3591378927230835, 0.2986651659011841, -0.08326086401939392, 0.19891053438186646, -1.6750575304031372, 0.002473290776833892, -0.17520321905612946, 0.12612509727478027, 0.45760688185691833, -0.33272647857666016, 0.29159125685691833, -0.001387274474836886, 0.15706820785999298, 0.06903965026140213, -0.13913194835186005, -0.11758885532617569, 0.4829826056957245, 0.15486781299114227, 0.46730685234069824, -0.10448193550109863, 0.6257362961769104, 0.34309256076812744, -0.6368098258972168, 0.2177010029554367, 0.18673944473266602, 0.22538495063781738, 0.20007778704166412, 0.055618662387132645, -0.1186804249882698, 0.1209508404135704, -0.13755379617214203, 0.08213456720113754, 0.018950477242469788, -0.19796472787857056, -0.49103543162345886, -0.3158029615879059, -0.04995568469166756, -0.1421680599451065, 0.04033030942082405, -0.13859719038009644, -0.01179975550621748, 0.5683783292770386, -0.1808914840221405, 0.023804740980267525, 0.06076328083872795, 0.4286077618598938, -0.07819776237010956, -0.1910601705312729, -2.81023907661438, -0.2051631361246109, -0.03412801772356033, 0.4723121225833893, 0.22271718084812164, 0.0069154915399849415, -0.4166979491710663, 0.3225547671318054, 0.34002459049224854, -0.26815420389175415, -0.19824545085430145, 0.47351551055908203, -0.20255355536937714, 0.5250629186630249, -0.486248254776001, 0.20329181849956512, 0.214028462767601, -0.38002631068229675, -0.0009055160917341709, -0.1980203092098236, -0.23844711482524872, 0.5009728670120239, -0.0831046923995018, 0.19408762454986572, 0.43403273820877075, -0.03601144999265671, -0.3077263832092285, -0.2676672041416168, 0.1500118225812912, 0.13283945620059967, 0.34758394956588745, -0.0897815003991127, -0.3288353383541107, 0.0038129747845232487, -0.14969460666179657, -3.9534926414489746, -0.21961365640163422, -0.028085529804229736, -0.38772842288017273, 0.17810563743114471, -0.2614399194717407, 0.04036679491400719, -0.07440714538097382, -0.411958247423172, 0.017390992492437363, 0.1017783135175705, 0.04787860065698624, -0.0105472132563591, -0.2493748515844345, 0.45631036162376404, 0.05668976902961731, 0.17593485116958618, -0.7059544920921326, 0.274318128824234, -0.19349536299705505, 0.12076642364263535, 0.28750330209732056, 0.323799192905426, 0.14622342586517334, 0.2765245735645294, 0.4974812865257263, -0.44183555245399475, -0.33987972140312195, -0.23456059396266937, -0.14808373153209686, -0.11298681795597076, -0.3107879161834717, 0.10029082000255585, -0.22953152656555176, -0.2239670306444168, 0.040017444640398026, 0.4163239598274231, -0.1961377114057541, 0.554904580116272, 0.12244497239589691, 0.38423842191696167, 0.28841888904571533, 0.3958602547645569, 0.1650855392217636, 0.164062961935997, -0.11632167547941208, 0.34683215618133545, -0.48745235800743103, 0.36942192912101746, 0.03188728168606758, -0.26727262139320374, -0.18636998534202576, 1.1876944303512573, -0.01897268183529377, -0.03465556353330612, 0.016758332028985023, 0.10130429267883301, 0.13166365027427673, -0.0984359011054039, 0.3476305902004242, 0.7220776081085205, -0.3303188681602478, 0.4944344460964203, 0.07077275216579437, -0.2460355907678604, -0.31190821528434753, 0.3388236463069916, -0.5295347571372986, -0.023712212219834328, 0.051643192768096924, 0.05428783968091011, 0.1911928355693817, -0.24655383825302124, -1.55766761302948, 0.12175644189119339, 0.038708463311195374, -0.20116381347179413, 0.24932581186294556, 0.0902978926897049, 0.26926830410957336, 0.2497730404138565, -0.10806422680616379, -0.09630421549081802, 0.34454113245010376, -0.6313672661781311, -0.3259925842285156, 0.35551562905311584, 0.33235964179039, -0.46474793553352356, 0.35524725914001465, 0.14764760434627533, 0.3994535207748413, 0.2697010040283203, 0.17363938689231873, 0.18656983971595764, 0.3702321946620941, 0.39891788363456726, -1.2047170400619507, 0.0704052597284317, -0.2693959176540375, -0.02173594757914543, -0.1375783234834671, -0.023754814639687538, -0.003432611469179392, -0.2670746147632599, -0.10340125113725662, -0.4743511974811554, 0.30812275409698486, 0.4588169753551483, -0.07122344523668289, -0.19935618340969086, 0.33257895708084106, -0.0010169362649321556, -0.03813676908612251, 0.9869416356086731, -0.050280969589948654, -0.2601895034313202, 1.0546205043792725, 0.3096286952495575, -0.21089868247509003, 0.31123030185699463, 0.20237311720848083, -0.21535320580005646, -0.36722537875175476, 0.08963920921087265, 0.0752616599202156, 0.2661539912223816, -0.333789199590683, -0.4166019856929779, -0.10752037912607193, 0.02775413542985916, -0.4684816598892212, -0.3689117431640625, -0.43920913338661194, -0.2078181803226471, -0.20279955863952637, -0.23570875823497772, 0.4047021269798279, -0.3984732925891876, -0.1376197338104248, 0.3220809996128082, -0.22022219002246857, -0.31504642963409424, 0.2545894682407379, -0.2734876275062561, 0.39292648434638977, -0.15629036724567413, 0.05413253232836723, 0.32846176624298096, 0.7328441739082336, -0.1090269535779953, 0.1932307481765747, 0.10139826685190201, -0.6348473429679871, 0.2757667899131775, 0.3194895088672638, -0.25259071588516235, 0.0746767669916153, -0.054922375828027725, 0.2328805774450302, -0.06937111914157867, -0.37939703464508057, -1.824073076248169, 0.27360132336616516, 0.22914192080497742, -0.10299285501241684, -0.03189864754676819, -0.050538450479507446, -0.41766589879989624, 0.30784764885902405, 0.011355404742062092, -0.018993619829416275, -0.3404057025909424, 0.19445882737636566, 0.02628745324909687, -0.05837366729974747, 0.2579111158847809, 0.07266028970479965, 0.4112645387649536, -0.03836076334118843, -0.02830413170158863, -0.1271129697561264, 0.1412333995103836, 0.09033237397670746, 0.3794269859790802, -0.28353142738342285, -0.2685216963291168, -0.30836451053619385, 0.13676631450653076, 0.5405058264732361, 0.12661749124526978, 0.04123290628194809, -0.22303330898284912, -0.15491673350334167, -0.4934053122997284, 0.17238503694534302, 0.5535210967063904, 0.3941323757171631, 0.03149710223078728, 0.27446308732032776, 0.7181549668312073, -0.14115330576896667, -0.4997589886188507, 0.3644901216030121, 0.32447195053100586, -0.040740739554166794, 0.30752190947532654, 0.016338471323251724, -0.4202123284339905, 0.3658522367477417, 0.39163270592689514, -0.1455833464860916, -0.43987205624580383, -0.42291489243507385, -0.31701427698135376, -0.33485668897628784, -0.0676155611872673, -0.3216080069541931, 0.03926834091544151, -0.04333139583468437, -0.2547351121902466, -0.31475770473480225, -0.34799233078956604, 0.053276848047971725, -0.11010546237230301, 0.2835954427719116, -0.6810022592544556, -0.7403154373168945, 0.3717534840106964, -0.039483048021793365, -0.38457003235816956, 0.3434942662715912, 0.41990402340888977, 0.3545319437980652, -0.23542247712612152, 0.12479609996080399, -0.003721119137480855, 0.5227444171905518, 0.01412186585366726, 0.11830709129571915, 0.20857028663158417, -0.4648851752281189, 0.21892346441745758, -0.3360830545425415, -0.1610257476568222, 0.6533229947090149, -0.2577088177204132, -0.1578863263130188, 0.01047542318701744, -0.10256253927946091, 0.1976311206817627, -0.2982437014579773, -0.3431830108165741, -0.10203444957733154, 0.03583352267742157, -0.09434929490089417, 0.12760759890079498, 0.25511205196380615, -0.02952432632446289, 0.0387863926589489, -0.4539282023906708, -0.0815381184220314, 0.11167699843645096, -0.07182896137237549, 0.2816771864891052, 0.2600880265235901, -0.27871841192245483, 0.04888661578297615, 0.4896569550037384, 0.24631237983703613, -0.6791788339614868, -0.46604597568511963, 0.20799227058887482, 0.01910236105322838, -0.20622919499874115, -0.17208199203014374, -0.13668759167194366, -0.10364606976509094, 0.49401649832725525, -0.32199370861053467, 1.8253902196884155, 0.14396709203720093, -0.06781068444252014, -0.5261773467063904, 0.5968437194824219, -0.17244020104408264, -0.15550239384174347, -0.029494130983948708, -0.37279993295669556, 0.6527836322784424, -0.1603415310382843, 0.5867739319801331, 0.03206222876906395, 0.3907310366630554, 0.3310107886791229, 0.385651558637619, -0.10150456428527832, -0.1915694773197174, -0.7995128631591797, -0.07677021622657776, -0.18861238658428192, 0.4507254660129547, 0.5285515785217285, -0.1342458873987198, -0.14557883143424988, 0.4906272292137146, -0.05385341867804527, -0.08382145315408707, 0.24456404149532318, 0.2460111826658249, -0.49011996388435364, -0.21292206645011902, 0.5110383033752441, -0.06739969551563263, -0.403169184923172, 0.27173784375190735, -0.06711295247077942, -0.19299666583538055, -0.29677242040634155, 0.27271705865859985, 0.10128727555274963, -0.31576302647590637, 0.6667463779449463, 0.5285969376564026, -0.035598933696746826, 0.37648800015449524, -0.3592410981655121, -0.11348980665206909, 0.6471429467201233, 0.509803295135498, 0.04987535625696182, 0.11328718811273575, -0.3051607310771942, 0.12936854362487793, 0.528913676738739, -0.21918781101703644, -0.022513410076498985, -0.4605673849582672, 0.07196371257305145, 0.06528982520103455, -0.21632254123687744, 0.24512135982513428, 0.44349101185798645, -0.32358819246292114, -0.0006373492651619017, 0.19838345050811768, 0.3998057544231415, -0.23034979403018951, 0.25250914692878723, 0.08775752782821655, 0.015272995457053185, 0.3593636155128479, -0.06937356293201447, 0.36074769496917725, 0.1506197452545166, 0.36549708247184753, 0.26232150197029114, 0.006581620313227177, -0.6999436616897583, -2.3025851249694824, 0.06002027168869972, 0.1275026649236679, 0.4106066823005676, -0.07550066709518433, 0.09080919623374939, 0.6930807828903198, -0.052983179688453674, 0.20370030403137207, -0.11857543885707855, 0.12536375224590302, 0.3273303508758545, 0.5235079526901245, -0.2215043008327484, 0.43545103073120117, -0.12361886352300644, 0.2462647557258606, -0.1643325239419937, -0.2007761001586914, -0.44961944222450256, -0.2447594851255417, -0.23382622003555298, 0.10254471749067307, -0.17957210540771484, -0.3325265347957611, 0.42046982049942017, -0.11329199373722076, -0.08371894806623459, 0.07399092614650726, -0.10956887900829315, -0.0338636115193367, -0.009512909688055515, -0.04796609655022621, -0.2629486620426178, 0.20242775976657867, -0.07587811350822449, 0.11515136063098907, 0.27102234959602356, -0.07170476764440536, 0.1022704541683197, 0.18745431303977966, 0.677659809589386, -0.11840825527906418, 0.44803619384765625, 0.12148842960596085, -0.36016416549682617, 0.34365400671958923, -0.02814173698425293, 0.4229799807071686, -0.34798291325569153, -0.08781958371400833, 0.05701449513435364, 0.3219151198863983, -0.10458477586507797, -0.006412987597286701, 0.18563739955425262, -0.17131727933883667, 0.18588276207447052, 0.27789467573165894, -0.3097815215587616, -0.31101036071777344, 0.11068366467952728, -0.360493928194046, -0.0678618922829628, 0.7940950393676758, -0.43750864267349243, -0.09162205457687378, 0.33935320377349854, -0.260751873254776, -0.3198701739311218, 0.22052180767059326, -0.3584687113761902, 0.5340270400047302, 0.12742841243743896, 0.13188934326171875, 0.208737313747406, 0.17929214239120483, -0.13399450480937958, -0.2906303107738495, -0.18527500331401825, -0.25849685072898865, 0.037662386894226074, 0.06552107632160187, -0.0775282233953476, 0.489376038312912, -6.289691925048828, -0.001364746829494834, -0.08387192338705063, -0.5119690299034119, -0.31703460216522217, -0.07444688677787781, -0.07742901146411896, -0.4142134487628937, 0.0365925207734108, -0.35127347707748413, -0.022499557584524155, -0.2277003973722458, -0.24864092469215393, -0.20438779890537262, 0.1761375367641449, 0.44013890624046326]</t>
+          <t>['medium', 'high', 'high', 'high', 'high', 'low']</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>[-0.5, -0.5, 0.5, 0.0, -0.5, -1.0]</t>
+          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[3, 5, 5, 5, 3, 2]</t>
+          <t>[30.0, 30.0, 35.0, 35.0, 30.0, 30.0]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
+          <t>['man', 'man', 'man', 'woman', 'man', 'man']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>[30.0, 30.0, 35.0, 30.0, 40.0, 30.0]</t>
+          <t>[1, 1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>['man', 'man', 'man', 'man', 'woman', 'man']</t>
+          <t>[3, 3, 5, 3, 5, 5]</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1, 1]</t>
+          <t>[5, 5, 5, 4, 1, 5]</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>[3, 3, 5, 4, 5, 5]</t>
+          <t>[5, 3, 5, 5, 5, 3]</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 3, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>[5, 3, 5, 4, 5, 5]</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>[1, 1, 1, 3, 1, 1]</t>
-        </is>
+          <t>[1, 1, 1, 1, 1, 1]</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>6</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 3, 1, 1]</t>
+          <t>[5, 5, 4, 5, 1, 5]</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 3, 1, 1]</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>[0.83333333 0.         0.16666667 0.         0.        ]</t>
-        </is>
-      </c>
-      <c r="T8" t="n">
-        <v>0.2</v>
+          <t>[0.16666667 0.         0.         0.16666667 0.66666667]</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>251</v>
+        <v>364</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>I've been to Italy a few times, and only saw two niggers in Venice.... some old dudes who were missing nearly all their teeth.. . I just don't go back to Venice.. problem solved.</t>
+          <t>So can we just stop saying there is no racism in this place. It's a racist country controlled by racist white people...period. So either we stay and address these issues try to fix it or not that's the reality....even they admit it...NIGGERS DONT COUNT.(their words not mine) thanks ROBERTS!</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 3, 5, 5]</t>
+          <t>[5, 4, 2, 5, 5, 4]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 5, 5, 5]</t>
+          <t>['Black american', '{}', '{}', '{}', '{}', '{}']</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>['{}', '{}', '{}', '{}', '{}', '{}']</t>
+          <t>['left', 'left', 'center', 'right', 'far left', 'far left']</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>[0.04304308444261551, 0.20432381331920624, -0.05765422433614731, -0.3930075764656067, -0.24504180252552032, -0.23116306960582733, 0.5238943099975586, 0.8017547726631165, 0.03697590529918671, -0.17205440998077393, -0.14035721123218536, 0.1932256817817688, -0.1403101682662964, 0.49633651971817017, 0.5569868087768555, 0.5762100219726562, 0.336031436920166, 0.21381013095378876, 0.1898920238018036, 0.027893664315342903, -0.08898045867681503, 0.0021757858339697123, 0.0883922353386879, -0.3138091266155243, 0.08399512618780136, -0.03202635422348976, 0.09420706331729889, -0.31671303510665894, -0.7942909598350525, 0.500475287437439, 0.01680343598127365, 0.6962363719940186, -0.6085750460624695, -0.0026229028590023518, 0.32409289479255676, -0.28865906596183777, 0.14513157308101654, -0.11391930282115936, 0.3021482825279236, -0.4169377088546753, -0.1268763244152069, 0.2703213393688202, -0.08475398272275925, -0.05486389622092247, -0.052988722920417786, -0.4173992872238159, -3.7109034061431885, 0.10497207939624786, 0.025259869173169136, -0.6152263879776001, -0.08026063442230225, -0.4966272711753845, 0.18141750991344452, 0.8142001628875732, 0.2909328043460846, 0.21653148531913757, -0.30953970551490784, -0.0728548914194107, 0.08112217485904694, -0.5838748812675476, 0.6238039135932922, 0.22198863327503204, 0.26929688453674316, 0.038391031324863434, -0.24067336320877075, 0.5073854327201843, 0.34792056679725647, 0.4762364625930786, -0.33579713106155396, 0.3398149609565735, -0.39373359084129333, -0.3683241605758667, 0.6567047238349915, -0.5283328294754028, 0.275003582239151, -0.03267202526330948, 0.1007220447063446, -0.01900390349328518, -0.5044131875038147, 0.053572557866573334, -0.08813150972127914, 0.732049822807312, 0.4718549847602844, -0.24566391110420227, 0.2552952766418457, -0.3994870185852051, -0.5655098557472229, -0.5976281762123108, 0.14499427378177643, 0.5170459747314453, -0.02037467435002327, 0.10520263016223907, -0.14344480633735657, 0.5769491791725159, 0.3472486138343811, -0.0888369008898735, 0.30380555987358093, -0.1030522957444191, 0.22600801289081573, 0.5083240270614624, 0.7518405914306641, -0.2987225353717804, 0.006659660954028368, -0.4297083020210266, -0.46759405732154846, -0.10735494643449783, -0.1895306408405304, -0.21718686819076538, 0.1326928287744522, -1.426682472229004, 0.22719532251358032, 0.13275346159934998, -0.05856781825423241, -0.5011642575263977, 0.00024416661472059786, 0.5862315893173218, 0.3538139760494232, -0.35747992992401123, 0.2505631744861603, 0.3046371340751648, 0.0063672857359051704, 0.0818067267537117, -0.12423121184110641, -0.034351032227277756, -0.07962775975465775, -0.20221516489982605, 0.3566124737262726, 0.272053986787796, -0.3493630588054657, 0.24739259481430054, 0.5528460741043091, 0.48110246658325195, 0.02721295692026615, -0.3302451968193054, 0.06259245425462723, -0.32488372921943665, 0.32047420740127563, -0.0031759587582200766, 0.022702863439917564, -0.39235496520996094, -0.43725064396858215, -0.13546122610569, -2.174748659133911, 0.4137406647205353, 0.4910530149936676, -0.10350152850151062, -0.21502143144607544, -0.27631011605262756, 0.16207729279994965, 0.1508767157793045, 0.32757487893104553, 0.39085593819618225, 0.5734806060791016, -0.1665915995836258, -0.15924707055091858, -0.010647142305970192, -0.39343059062957764, -0.1283797323703766, 0.3049187660217285, 0.9249259829521179, 0.4503515660762787, 0.046108245849609375, 0.40868687629699707, 0.26008376479148865, -0.07252145558595657, 0.7441004514694214, 0.2545176148414612, 0.40392351150512695, 0.29225748777389526, 0.11860137432813644, 0.04583372920751572, 0.0699106901884079, 0.7046883702278137, -0.15550826489925385, -0.14703823626041412, 0.36641231179237366, 0.17296405136585236, 0.5285360813140869, 0.33169037103652954, -0.29972365498542786, -0.787244439125061, 0.516955554485321, 0.23424144089221954, -0.12633077800273895, 0.13007615506649017, -0.23578350245952606, 0.8500767946243286, -0.44599252939224243, -0.37597963213920593, 0.2606808841228485, -0.49833622574806213, -0.8380783200263977, 0.35052505135536194, -0.5728949308395386, 0.486206978559494, 0.29248932003974915, 0.20263081789016724, -0.9133422374725342, -0.09125140309333801, 0.2309483140707016, 0.08906237781047821, -0.47610679268836975, 0.6567742228507996, 0.1049576923251152, -0.41549649834632874, 3.9805312156677246, 0.050721824169158936, -0.06058249622583389, 0.20867884159088135, 0.1739151030778885, -0.481355220079422, -0.16895535588264465, -0.23197364807128906, -0.34844258427619934, -0.13591048121452332, 0.0339692085981369, 0.3488842248916626, -0.5590641498565674, -0.2350730150938034, -0.09524029493331909, -0.050184156745672226, -0.09986165910959244, -0.7539427280426025, 0.3566592335700989, -0.33907800912857056, 0.07643090933561325, 0.14760233461856842, 0.15465059876441956, 0.336477130651474, -1.6468585729599, -0.1709093153476715, -0.020878048613667488, -0.2972120940685272, 0.3979933261871338, -0.03735578432679176, 0.06653568148612976, -0.3151922821998596, -0.5327886343002319, 0.09652402251958847, -0.2403710037469864, 0.0468112975358963, 0.6006752848625183, -0.15387848019599915, 0.1582799255847931, -0.21772021055221558, 0.5047177076339722, 0.308331698179245, -0.7746910452842712, -0.14044921100139618, -0.058128103613853455, 0.3044188916683197, 0.5321716070175171, 0.5255566835403442, -0.8040544390678406, 0.12331542372703552, 0.3811416029930115, -0.03521052002906799, -0.015528264455497265, -0.1267666220664978, -0.8353387713432312, -0.4465703070163727, 0.12426909059286118, -0.32404544949531555, 0.217671737074852, -1.0340017080307007, -0.26927828788757324, 0.37526965141296387, 0.2598232328891754, -0.13058169186115265, -0.06803740561008453, 0.5819441080093384, -0.09164027124643326, -0.19247719645500183, -1.5627751350402832, -0.06969879567623138, -0.005037778988480568, 0.053261883556842804, 0.3150433897972107, -0.4959993362426758, -0.3131568431854248, 0.40515267848968506, 0.17580156028270721, -0.6750890016555786, -0.05257060006260872, -0.7406834363937378, -0.003119430271908641, 0.2727511525154114, -0.43127256631851196, 0.22174091637134552, -0.05863520875573158, -0.20643210411071777, -0.0467456616461277, -0.7017465233802795, -0.09861563891172409, 0.27068743109703064, -0.04800671711564064, 0.40990158915519714, 0.32922983169555664, -0.08999165892601013, -0.26257070899009705, 0.01454133354127407, 0.04498552903532982, 0.09685827791690826, 0.2884272336959839, 0.003453467972576618, -0.32162389159202576, -0.2834815979003906, -0.48028936982154846, -4.322561740875244, -0.05236714705824852, -0.7664717435836792, -0.21265988051891327, 0.060159265995025635, -0.0062501137144863605, 0.5287639498710632, -0.21972763538360596, -0.7311346530914307, 0.10815580189228058, 0.2668359875679016, -0.04834861308336258, -0.21662652492523193, 0.03870275616645813, 0.7296079993247986, -0.242789626121521, 0.4737808108329773, -0.3202565610408783, 0.1768883615732193, 0.3393056392669678, -0.11178014427423477, 0.04160842299461365, 0.21897947788238525, -0.11072739213705063, 0.6799074411392212, 0.9532760977745056, -1.0615774393081665, 0.23202407360076904, -0.4550568759441376, -0.1099899560213089, 0.11408063769340515, -0.3044784367084503, -0.10104525089263916, -0.6931874752044678, -0.16267067193984985, -0.20526546239852905, 0.24821564555168152, -0.30800506472587585, 0.2958869934082031, -0.2634741961956024, 0.25441598892211914, 0.07478278875350952, 0.10850678384304047, 0.3272353410720825, 1.0083647966384888, -0.1597926914691925, 0.187892884016037, -0.09650648385286331, 0.09141667187213898, 0.7060730457305908, 0.01287424098700285, 0.19763389229774475, 0.9554003477096558, 0.2884734869003296, 0.4540785253047943, -0.46496835350990295, 0.4434486925601959, 0.0915057435631752, -0.038006238639354706, 0.3334052264690399, 0.9818665981292725, -0.433037668466568, 0.6486644744873047, -0.41724205017089844, -0.32328447699546814, -0.21856987476348877, -0.015565512701869011, -0.9941807389259338, -0.12175096571445465, 0.22517308592796326, 0.13046354055404663, 0.23981349170207977, -0.2020702064037323, -1.6303402185440063, 0.4094259440898895, 0.20959773659706116, -0.11226984113454819, 0.5922034382820129, -0.10641422867774963, 0.1565379649400711, 0.11188003420829773, 0.02566526085138321, -0.6272159814834595, 0.12820574641227722, -0.6882002353668213, -0.4010235667228699, -0.18106767535209656, 0.041209638118743896, -0.8488414287567139, -0.10144804418087006, 0.09353217482566833, 0.5376204252243042, 0.22600966691970825, 0.36004120111465454, 0.19055360555648804, 0.10187997668981552, 0.654904842376709, -0.8178156018257141, 0.573588490486145, -0.3326479196548462, 0.27271297574043274, -0.3444490432739258, -0.29025280475616455, 0.33574140071868896, 0.020654605701565742, 0.07815676927566528, -0.11490727961063385, 0.3966411352157593, 0.3702867329120636, -0.16040994226932526, -0.0682276263833046, -0.5186351537704468, 0.06019303575158119, 0.31636813282966614, 0.7672834396362305, -0.5750739574432373, -0.3738691210746765, 0.6347989439964294, 0.027165016159415245, 0.06744755059480667, 0.8073412179946899, -0.07218562066555023, 0.025414230301976204, -0.35014796257019043, -0.48603278398513794, 0.13255488872528076, 0.12016111612319946, -0.4238086938858032, -0.352418452501297, -0.17188164591789246, -0.07596686482429504, -0.37784016132354736, -0.7231237292289734, -0.23135435581207275, -0.254373699426651, -0.5142419934272766, -0.46877217292785645, 0.23445552587509155, 0.32778400182724, 0.18807749450206757, 0.7389506697654724, 0.16058306396007538, -0.14764347672462463, 0.08771336823701859, -0.8124276995658875, 1.1413755416870117, 0.06027912348508835, 0.26197999715805054, -0.4839901328086853, 0.7985914349555969, -0.1747911274433136, -0.05880491062998772, -0.25865691900253296, -0.5496636629104614, 0.5200570225715637, 0.2469419240951538, -0.3319861590862274, 0.05570824444293976, 0.10219883173704147, 0.08883942663669586, 0.4631136953830719, -0.3843974769115448, -1.6029294729232788, 0.8238094449043274, 0.47880613803863525, 0.07211259007453918, 0.007375417277216911, -0.08151762187480927, -0.34631600975990295, 0.3103909194469452, 0.1790350377559662, 0.17637299001216888, -0.5285935997962952, 0.4357171356678009, 0.6402763724327087, -0.09998062252998352, -0.2903948128223419, -0.05989038571715355, -0.03634137660264969, -0.4069477319717407, 0.005013429559767246, -0.49103280901908875, -0.13923242688179016, 0.28816500306129456, 0.2675749659538269, -0.19127170741558075, 0.15394702553749084, -0.604157030582428, -0.06330148130655289, 1.0562433004379272, 0.4545004963874817, 0.3111783266067505, -0.06683427840471268, -0.02150629833340645, -0.5774112343788147, -0.45085790753364563, 0.3201152980327606, -0.20268994569778442, -0.08174246549606323, -0.22268375754356384, 0.9127334952354431, 0.3611122965812683, -0.23756557703018188, 0.7317808866500854, 0.6143574714660645, 0.007638915441930294, 0.4084389805793762, 0.04039742797613144, -0.657023012638092, 0.7096072435379028, 0.3613731265068054, -0.5021209716796875, -0.39822402596473694, -0.26466965675354004, -0.6861150860786438, -0.1549989879131317, -0.027118489146232605, -0.3825959265232086, -0.28079894185066223, 0.26426994800567627, -0.6982642412185669, -0.21268950402736664, 0.016309650614857674, -0.17808985710144043, -0.731149435043335, 0.3351084589958191, -0.16312196850776672, -0.9848585724830627, -0.29604431986808777, -0.5401628613471985, -0.850760817527771, 0.42173972725868225, 0.34817707538604736, 0.17255011200904846, -0.3557488024234772, 0.5807017087936401, -0.12232131510972977, 0.45683521032333374, 0.18835334479808807, 0.34186887741088867, 0.3882147967815399, -0.13889946043491364, 0.37116488814353943, -0.2799968421459198, -0.21107245981693268, 0.130056232213974, -0.32015082240104675, 0.21619263291358948, -0.4872223436832428, -0.034365806728601456, 0.08365113288164139, -0.5099729895591736, -0.6577096581459045, -0.30088305473327637, 0.23415736854076385, -0.27227410674095154, -0.0878659039735794, 0.3440777063369751, 0.5203151106834412, -0.2796410620212555, -0.3030064105987549, -0.4602837562561035, -0.22338911890983582, 0.20720639824867249, 0.3877090811729431, -0.033706799149513245, -0.17750035226345062, 0.4347947835922241, 0.43566447496414185, 0.06474652141332626, -0.7170861959457397, -0.502000093460083, 0.7028183937072754, -0.0015503867762163281, -0.2342359721660614, -0.35250943899154663, -0.20136424899101257, -0.6996928453445435, 0.36027732491493225, -0.8889989256858826, 0.8733051419258118, 0.04820597544312477, 0.42764997482299805, -0.12654100358486176, 0.9764947891235352, -0.2174253761768341, -0.2503557503223419, 0.3022656738758087, -0.45157384872436523, 0.35066649317741394, -0.827008068561554, 0.47463229298591614, -0.25646060705184937, 0.4761938154697418, 0.44939374923706055, 0.33939269185066223, 0.1576033979654312, -0.1053173840045929, -0.7752137184143066, 0.2791140079498291, 0.018822364509105682, 0.48428741097450256, 0.29281094670295715, 0.04164557531476021, 0.07739321887493134, 0.6448164582252502, 0.2988767623901367, -0.05224688723683357, 0.8256268501281738, 0.6467883586883545, 0.09245170652866364, 0.49285072088241577, 0.1555688977241516, 0.2194221019744873, -0.9620137214660645, -0.4394597113132477, -0.07061957567930222, -0.43179208040237427, -0.20388348400592804, 0.04214005917310715, 0.6408650279045105, -0.26454344391822815, 0.5667937994003296, 0.27361950278282166, -0.4319821298122406, 0.232448011636734, -0.24650928378105164, -0.1884615570306778, 0.5554936528205872, 1.0108219385147095, 0.1542799323797226, 0.24610017240047455, -0.2636927366256714, -0.004745981656014919, -0.038492098450660706, 0.009611458517611027, -0.23504218459129333, -0.41235727071762085, -0.40052613615989685, 0.10143821686506271, -0.5200713276863098, 0.4946762025356293, -0.09949566423892975, 0.10566140711307526, 0.02765861712396145, -0.15342628955841064, 0.003231140784919262, -0.351508229970932, 0.37572386860847473, -0.48890671133995056, -0.029098838567733765, 0.46950045228004456, -0.042306140065193176, -0.05168086662888527, 0.10589770972728729, 0.21830888092517853, -0.0537383109331131, 0.024962475523352623, -0.5202732682228088, -1.1847211122512817, 0.5033631324768066, 0.2066270112991333, 0.16890399158000946, -0.07725954055786133, 0.24124307930469513, 0.5702387094497681, 0.02566664293408394, -0.05441579595208168, -0.14526744186878204, 0.2577814757823944, 0.7793075442314148, 0.41542917490005493, -0.21657803654670715, 0.5008963346481323, -0.2732027471065521, 0.27071747183799744, -0.48711368441581726, 0.5633232593536377, -0.09780620783567429, 0.438178151845932, 0.29756245017051697, -0.03654352203011513, -0.5150554180145264, -0.6296660900115967, 0.6091063618659973, -0.5619975924491882, -0.2997874915599823, 0.618526041507721, 0.2114822417497635, 0.132745623588562, 0.20336481928825378, -0.49854934215545654, -0.5087563395500183, -0.0723031759262085, 0.16408157348632812, -0.48968416452407837, 0.04401165246963501, 0.31477615237236023, 0.0574580654501915, -0.10798068344593048, 0.8397366404533386, -0.05214770883321762, 0.5953037738800049, 0.4425995349884033, -0.4803698658943176, 0.4455932080745697, 0.19087034463882446, 0.5942661166191101, -0.377025842666626, 0.38045933842658997, 0.11819293349981308, 0.5321289896965027, -0.0015720791416242719, 0.2097361534833908, -0.2883121073246002, 0.024430835619568825, 0.1232467070221901, 0.24252186715602875, -0.6560935974121094, -0.3575552999973297, 0.18355773389339447, -0.9648566246032715, -0.43841788172721863, 0.6145330667495728, -0.4121309816837311, -0.31378304958343506, 0.1748938262462616, -0.207940474152565, -0.5609054565429688, -0.04332145303487778, -0.19655855000019073, 1.0486541986465454, 0.19860325753688812, -0.20514078438282013, 0.08996637165546417, 0.33278888463974, 0.2873539328575134, 0.16899119317531586, -0.21851859986782074, 0.06128750741481781, 0.38953274488449097, -0.09754161536693573, 0.011617463082075119, 0.0847511738538742, -3.9647207260131836, -0.1955259144306183, 0.20966941118240356, -0.5438560843467712, -0.5901197791099548, -0.2084285020828247, -0.09717437624931335, -0.6648894548416138, -0.16230575740337372, -0.3649955093860626, -0.019717855378985405, 0.44492587447166443, -0.4730076193809509, -0.22072097659111023, 0.6312919855117798, 0.48417025804519653]</t>
+          <t>['high', 'medium', 'high', 'high', 'high', 'high']</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>[-0.5, 0.0, 0.0, 0.5, 0.0, -0.5]</t>
+          <t>['black', 'black', 'other', 'white', 'white', 'white']</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[4, 5, 5, 4, 5, 5]</t>
+          <t>[30.0, 30.0, 55.0, 35.0, 30.0, 45.0]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
+          <t>['man', 'woman', 'man', 'woman', 'man', 'woman']</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>[40.0, 45.0, 40.0, 40.0, 35.0, 35.0]</t>
+          <t>[1, 1, 2, 1, 3, 1]</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>['woman', 'man', 'woman', 'man', 'woman', 'woman']</t>
+          <t>[5, 4, 5, 5, 5, 5]</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 5, 3, 1]</t>
+          <t>[5, 4, 2, 5, 5, 3]</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>[4, 5, 5, 1, 4, 5]</t>
+          <t>[5, 5, 5, 5, 4, 5]</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 3, 5, 5]</t>
+          <t>[5, 1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>[2, 4, 5, 5, 3, 4]</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>[1, 1, 1, 3, 5, 1]</t>
-        </is>
+          <t>[5, 2, 2, 5, 5, 3]</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>6</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 3, 5, 5]</t>
+          <t>[5, 4, 2, 5, 5, 4]</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 3, 5, 5]</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>[0.         0.         0.16666667 0.         0.83333333]</t>
-        </is>
-      </c>
-      <c r="T9" t="n">
-        <v>0.2</v>
+          <t>[0.         0.16666667 0.         0.33333333 0.5       ]</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>328</v>
+        <v>411</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Our economy is in the fucking dark and all black people care about is black lives matter</t>
+          <t>They say that they "ride for my motherfuckin' niggas". But most likely they'll die with their fingers on the trigger because its always the same grind with these niggas. And they don't go in unless they with my niggas</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[5, 4, 1, 4, 5, 5]</t>
+          <t>[4, 2, 4, 5, 2, 3]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 5, 5, 5]</t>
+          <t>['{}', '{}', '{}', '{}', 'none', 'woman']</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>[nan, '{}', '{}', '{}', '{}', 'bisexual']</t>
+          <t>['left', 'center', 'right', 'right', 'center', 'left']</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>[0.4139760732650757, 0.22946445643901825, -0.48915085196495056, -0.36006301641464233, -0.697897732257843, -0.637546956539154, 0.7535286545753479, 0.8096444010734558, 0.15013554692268372, -0.2685016393661499, 0.42508527636528015, 0.0971808135509491, -0.5873947739601135, 0.5203596353530884, 0.06368342787027359, 0.3864530622959137, -0.06835683435201645, 0.2597598731517792, 0.006770209409296513, 0.25669753551483154, -0.43925291299819946, -0.2869648337364197, 0.2586548626422882, 0.011870209127664566, 0.010360261425375938, -0.1431533396244049, -0.0004306180344428867, -0.49004286527633667, -0.22119086980819702, 0.44386541843414307, 0.06251679360866547, 0.2244083136320114, -0.46990305185317993, -0.4870041310787201, 0.6014286279678345, -0.17522314190864563, 0.2380620837211609, 0.10090044885873795, 0.21351848542690277, 0.17072801291942596, -0.46801432967185974, 0.22598689794540405, -0.1583569198846817, -0.18361856043338776, -0.020674455910921097, -0.5063517689704895, -3.151851177215576, -0.1015196442604065, -0.051555413752794266, -0.1268061399459839, 0.10102294385433197, -0.5467013120651245, -0.39665091037750244, 0.6452994346618652, 0.3242221474647522, 0.06969262659549713, -0.7015413641929626, 0.17341606318950653, -0.19742469489574432, -0.1422329694032669, 0.6469646096229553, 0.05090034753084183, -0.3142971396446228, -0.17582979798316956, -0.03545102849602699, 0.10391926765441895, 0.24962909519672394, 0.2693880796432495, -0.8755396604537964, 0.0330631248652935, -1.0556684732437134, -0.6403983235359192, 0.25745245814323425, -0.4547317922115326, -0.07407357543706894, -0.39578697085380554, -0.07002680748701096, 0.34697940945625305, -0.33939453959465027, -0.4542026221752167, 0.3224655091762543, 0.8413585424423218, 0.1418464630842209, 0.15095655620098114, -0.36589285731315613, 0.42154765129089355, -0.4290054738521576, -0.2552171051502228, 0.13976231217384338, 0.5664716362953186, -0.06506877392530441, 0.6965669393539429, 0.29811495542526245, 0.45039132237434387, 0.31143513321876526, -0.20746766030788422, 0.30599626898765564, -0.5496639609336853, -0.017147907987236977, 0.5122835636138916, 0.7209271192550659, 0.005647947080433369, 0.7022969722747803, -0.5796861052513123, 0.013224251568317413, -0.09180323779582977, 0.09976313263177872, -0.35537347197532654, 0.7780297994613647, -2.2864365577697754, 0.3225014805793762, -0.09038140624761581, -0.4265005588531494, -0.4619450569152832, -0.21376952528953552, 0.43809473514556885, 0.09006470441818237, -0.46562281250953674, 0.8406029343605042, 0.17049473524093628, -0.08430388569831848, 0.13342852890491486, -0.48702794313430786, 0.619545042514801, -0.09952929615974426, 0.14808137714862823, -0.13284215331077576, -0.015124204568564892, -0.060440544039011, 0.5495225787162781, 0.42803674936294556, 0.6205283403396606, 0.06356062740087509, -0.1657228320837021, -0.3244912326335907, 0.298358678817749, 0.6548975110054016, 0.12682592868804932, 0.1493392288684845, -0.5645564198493958, -0.29937055706977844, -0.385890394449234, -2.15612530708313, 0.007360709831118584, 0.3611525595188141, 0.1325925588607788, -0.1639455109834671, -0.16460496187210083, 0.13882644474506378, -0.08023776859045029, 0.37270763516426086, 0.04667387902736664, 0.30152323842048645, -0.5578784942626953, -0.1433752179145813, -0.7573506832122803, -0.7397106885910034, -0.610059916973114, 0.6007003784179688, 0.8210899233818054, 0.5736815929412842, -0.4229303300380707, 0.37362027168273926, 0.06764567643404007, -0.5509541630744934, -0.008936818689107895, 0.17248083651065826, 0.8860978484153748, -0.1684376299381256, 0.12884649634361267, -0.02135656587779522, 0.5412470698356628, 0.6335741281509399, -0.03961797431111336, 0.2522992789745331, 0.5104370713233948, 0.3677806556224823, 0.2795410752296448, 0.19687528908252716, 0.07871595770120621, -0.7250805497169495, 0.38128820061683655, 0.10046727955341339, 0.3426390290260315, 0.9578812718391418, -0.19385239481925964, 0.45110219717025757, -0.04609358310699463, -0.27214810252189636, 0.14597776532173157, -0.38326209783554077, -0.7877947688102722, 0.19909149408340454, -0.08324287086725235, 0.6118779182434082, -0.37546849250793457, 0.000907664536498487, -0.4585435092449188, 0.26131802797317505, 0.2796016037464142, -0.6054849624633789, -0.47396141290664673, -0.24090565741062164, -0.23702026903629303, -0.8301059603691101, 3.709723949432373, 0.0990746021270752, 0.07279406487941742, -0.2681759297847748, 0.20548057556152344, -0.19604656100273132, -0.3758522868156433, -0.6263872981071472, 0.07698261737823486, -0.14099889993667603, -0.04578578844666481, 0.3140471279621124, -0.3234785795211792, -0.10103610903024673, -0.11560939997434616, 0.42747023701667786, -0.07000204920768738, -0.24722349643707275, 0.05565480515360832, -0.8775789141654968, -0.13595609366893768, -0.3386926054954529, 0.18193984031677246, -0.2465992122888565, -1.5697044134140015, 0.4132344126701355, 0.13927794992923737, -0.7988341450691223, 0.49844542145729065, -0.5306803584098816, 0.036179691553115845, -0.46655702590942383, -0.64450603723526, 0.25896257162094116, -0.233947291970253, 0.32660162448883057, 0.2672664225101471, 0.21259820461273193, -0.03646161034703255, -0.2707872986793518, 0.5588677525520325, 0.2797165811061859, -0.6258519887924194, 0.3816612660884857, 0.3873661756515503, 0.06203805282711983, 0.03205946087837219, -0.09799984842538834, -0.23856544494628906, 0.2656855285167694, 0.5427442789077759, -0.19008506834506989, -0.07132142037153244, -0.1609734147787094, -0.6918571591377258, -0.26045411825180054, 0.06873898953199387, 0.25826725363731384, -0.14116312563419342, -0.5029469728469849, -0.6528956890106201, 0.05912676081061363, 0.11746580898761749, 0.1005776897072792, -0.1075698733329773, 0.8925599455833435, -0.04194147512316704, -0.3037574589252472, -2.578528881072998, 0.2530228793621063, 0.13465666770935059, 0.3546353578567505, 0.6900254487991333, -0.7637665867805481, 0.044122327119112015, 0.8099732995033264, -0.009653942659497261, -0.8740940093994141, 0.26560690999031067, 0.2811099588871002, 0.32475632429122925, 0.42373764514923096, -0.28373655676841736, 0.4225345551967621, 0.2431589514017105, -0.3463297486305237, -0.5491977334022522, -0.5306172966957092, -0.11673417687416077, 0.3519759774208069, 0.2306547909975052, -0.26942020654678345, -0.06974267959594727, -0.035428937524557114, -0.030046049505472183, -0.3189007639884949, 0.4508032202720642, -0.06230815127491951, 0.15850524604320526, -0.21638427674770355, -0.17076551914215088, -0.12524782121181488, -0.39942291378974915, -3.6682302951812744, 0.5795503258705139, -0.3168666958808899, 0.027736062183976173, -0.03862568363547325, -0.10771115869283676, 0.3580901324748993, -0.09357915073633194, -0.6179212331771851, -0.06262773275375366, -0.2905016243457794, -0.21462354063987732, -0.054780274629592896, 0.3428274095058441, 0.5891951322555542, 0.22422343492507935, 0.5534130334854126, -0.9166929721832275, 0.45693063735961914, 0.3301006853580475, -0.060136016458272934, 0.04904777556657791, 0.20387417078018188, -0.12923289835453033, 0.2850652039051056, 0.4370352625846863, -0.34619027376174927, -0.20104607939720154, 0.0365428552031517, 0.09248137474060059, -0.31265702843666077, 0.018008826300501823, -0.07315845787525177, -0.2533614933490753, -0.20220792293548584, -0.7040514349937439, -0.20826323330402374, -0.14165140688419342, -0.2943766117095947, -0.10592344403266907, 0.30777040123939514, 0.4917091131210327, -0.07357323914766312, 0.41013941168785095, 1.2089942693710327, -0.025295067578554153, 0.17858299612998962, -0.7580073475837708, 0.2614137828350067, 0.2886575162410736, 0.030478572472929955, 0.44455277919769287, 1.1786397695541382, -0.10803385823965073, -0.5096390247344971, -0.42570731043815613, 0.2931402027606964, 0.2524786591529846, 0.1839340478181839, 0.18022705614566803, 1.1391419172286987, -0.4048214554786682, -0.09292447566986084, 0.5424861907958984, -0.3366338610649109, -0.4995045065879822, 0.38975366950035095, -0.7895827889442444, 0.14034676551818848, 0.15637396275997162, -0.06981093436479568, 0.17553000152111053, -0.7255166172981262, -1.1989191770553589, 0.2502594590187073, -0.20804151892662048, -0.34907570481300354, -0.020479191094636917, 0.22378601133823395, -0.01312626525759697, 0.06235092505812645, -0.021152332425117493, -0.11735480278730392, 0.5593997240066528, -0.3743712902069092, -0.46030959486961365, -0.057294685393571854, 0.1508907973766327, -0.3224993050098419, 0.3589649498462677, -0.22131189703941345, -0.25973644852638245, 0.29858464002609253, 0.20205748081207275, 0.043929919600486755, -0.2784305214881897, 0.49512746930122375, -0.46593910455703735, 0.10514310002326965, 0.260449081659317, -0.3631671965122223, -0.8493672013282776, -0.2914943993091583, -0.24807633459568024, -0.1677142083644867, -0.40057969093322754, -0.10952194780111313, 0.793646514415741, -0.3766474425792694, 0.5289693474769592, 0.13894018530845642, -0.04807428643107414, 0.2098865658044815, 0.41767993569374084, 0.7796810865402222, -0.5970857739448547, -0.09862735867500305, 0.7362468242645264, 0.3606049120426178, -0.08288086205720901, 0.6548864841461182, 0.45398980379104614, -0.14711520075798035, -0.001009280444122851, -0.39942482113838196, -0.113043874502182, 0.09181807935237885, 0.04264374077320099, -0.5054899454116821, -0.29573529958724976, 0.1328941434621811, -0.2541801929473877, -0.5759417414665222, -0.5443671345710754, -0.06711458414793015, -0.17827166616916656, -0.20132769644260406, 0.3166819214820862, -0.31431764364242554, 0.2182481735944748, 1.0771845579147339, -0.07921610027551651, 0.10339083522558212, 0.2421930432319641, -0.7373677492141724, 0.8932093381881714, -0.16409249603748322, 0.257450670003891, -0.12394864857196808, 0.7362109422683716, -0.06653054058551788, -0.0011733946157619357, -0.19492276012897491, -0.17293310165405273, 0.44611412286758423, 0.009801493026316166, 0.21056179702281952, 0.29816779494285583, 0.12441540509462357, -0.5001962780952454, -0.11603967845439911, 0.20305371284484863, -1.9260368347167969, 0.39583003520965576, 1.1571452617645264, 0.14924299716949463, 0.3061527907848358, -0.6152868270874023, -0.6521317958831787, 1.254366159439087, 0.33479535579681396, 0.3606376349925995, -0.05451243370771408, 0.06469753384590149, 0.0669320821762085, -0.14822907745838165, 0.2691132128238678, -0.25951889157295227, 0.18188612163066864, -0.2197311967611313, 0.06211087107658386, 0.26311013102531433, -0.319607138633728, -0.3295954465866089, 0.30295735597610474, -0.27558887004852295, -0.37222152948379517, -0.4907962679862976, -0.3275563418865204, 0.5146979689598083, -0.06032458692789078, 0.4877249598503113, -0.27435269951820374, -0.30957740545272827, -0.6732300519943237, 0.05364641174674034, 0.15252527594566345, 0.01962183602154255, 0.15806351602077484, 0.10821101069450378, 0.7621822953224182, 0.7879520654678345, 0.09415993094444275, 0.7132918834686279, 0.11327917873859406, 0.06577805429697037, 0.21276353299617767, 0.45141029357910156, -0.6762717366218567, 0.7996979355812073, -0.09287665039300919, -0.22324858605861664, -0.6779102683067322, -0.24112051725387573, -0.6990313529968262, -0.16032840311527252, 0.054228488355875015, -0.11192262917757034, -0.4525563418865204, -0.016262374818325043, -0.7204253077507019, -0.2630370855331421, 0.2522755265235901, 0.26067957282066345, -0.5111680626869202, -0.064933180809021, -0.7594573497772217, -0.46089813113212585, 0.1741204708814621, -0.7491576075553894, -0.5727755427360535, 0.7931103706359863, 0.48186662793159485, 0.18208420276641846, -0.16205306351184845, 0.7454856038093567, -0.12897272408008575, 0.5324684977531433, 0.2304968237876892, -0.084182508289814, 0.2011692076921463, -0.3066401183605194, -0.16501747071743011, -0.6274749636650085, -0.07000771164894104, 0.4093071520328522, 0.14410077035427094, 0.6379081606864929, -0.04638231545686722, -0.09177500009536743, -0.33726558089256287, -0.27256181836128235, -0.45422476530075073, -0.6995320320129395, 0.5412957668304443, -0.3651231825351715, -0.08263330161571503, -0.27265071868896484, 0.24616660177707672, -0.09327850490808487, -0.18496818840503693, -0.09610585868358612, -0.23400545120239258, 0.43053320050239563, 0.2096460610628128, 0.13550560176372528, -0.0330975279211998, 0.34845104813575745, 0.6924192905426025, -0.12543916702270508, -0.33178162574768066, -0.10543370991945267, -0.2103557139635086, -0.06567950546741486, -0.19814036786556244, -0.05383187159895897, 0.24825946986675262, -0.4136090874671936, 0.07430611550807953, -0.8416182994842529, 1.5676432847976685, 0.20425009727478027, 0.3139972388744354, -0.9770280718803406, 0.5805884599685669, -0.2662508487701416, 0.4057333469390869, 0.5653391480445862, -0.631015419960022, -0.11363975703716278, -0.600462019443512, -0.42744162678718567, 0.6118058562278748, 0.5671554207801819, 0.5245010852813721, 0.3833743929862976, 0.07976077497005463, -0.17632627487182617, -0.5172489285469055, -0.07992802560329437, -0.3849177956581116, 0.4174339473247528, 0.21867522597312927, 0.13484418392181396, 0.05862526223063469, 0.4616052508354187, 0.3375278115272522, 0.48748716711997986, 0.15088129043579102, 0.7747437357902527, -0.1264919489622116, -0.3146369755268097, 0.3851788640022278, 0.3895379602909088, -0.7300878763198853, 0.3516367971897125, 0.3192463219165802, -0.5108954906463623, 0.010920243337750435, 0.15932516753673553, 0.2620812952518463, -0.6023145914077759, 0.5564573407173157, 0.3277938961982727, 0.0584641695022583, 0.5764814615249634, -0.2817094027996063, 0.23581543564796448, 0.5474253296852112, 0.5465195178985596, -0.4250083863735199, 0.34432780742645264, -0.5884859561920166, 0.09399192035198212, 0.037941135466098785, 0.037403371185064316, 0.1455129235982895, -0.32833486795425415, -0.34612342715263367, 0.3496519923210144, 0.2493753731250763, 0.40221211314201355, 0.4506109058856964, -0.03316608816385269, 0.11454825848340988, 0.2696475386619568, -0.6742091178894043, 0.012001892551779747, 0.20693561434745789, -0.14541734755039215, -0.25481295585632324, 0.036627303808927536, 0.2166551798582077, 0.027792440727353096, 0.7979013919830322, 0.21299317479133606, 0.8387848734855652, 0.2487044632434845, -0.2795718014240265, -2.0983057022094727, 0.053593166172504425, -0.23454175889492035, 0.06905076652765274, 0.005603334400802851, 0.3417579233646393, 0.26211798191070557, -0.13886159658432007, -0.2631680965423584, -0.3537374436855316, -0.0034066871739923954, 0.13863277435302734, 0.19411592185497284, 0.4478381276130676, 0.28546878695487976, 0.23070062696933746, 0.3709709346294403, -0.3819258511066437, -0.44522714614868164, -0.320366770029068, 0.6446709632873535, 0.2946918308734894, -0.2170981615781784, -0.6062980890274048, 0.10224700719118118, 0.6539377570152283, -0.01441151276230812, -0.15266628563404083, 0.3827812671661377, 0.4331423342227936, 0.09593939781188965, 0.018655158579349518, 0.02556503377854824, -0.3853946328163147, 0.0714723989367485, 0.44213613867759705, -0.33444610238075256, 0.055788662284612656, 0.28126654028892517, -0.02068290300667286, 0.08033095300197601, 1.2648813724517822, -0.49652037024497986, -0.017934467643499374, 0.3969208002090454, -0.730238139629364, 0.18136237561702728, -0.1599377691745758, 0.29947397112846375, -0.37091442942619324, 0.5902212262153625, -0.28395745158195496, 0.15113113820552826, -0.09759478271007538, 0.4053942859172821, 0.10487665981054306, 0.6681742668151855, 0.3311077058315277, 0.08836376667022705, -0.2810308635234833, 0.23391735553741455, -0.09735725075006485, -0.35765591263771057, -0.4300920367240906, 0.34641021490097046, -0.37359029054641724, 0.04478132352232933, 0.606715977191925, 0.2361954152584076, -0.35008305311203003, 0.23841071128845215, -0.4371967017650604, 0.828963577747345, 0.2848496437072754, 0.13884134590625763, -0.00014925423602107912, -0.09264382719993591, 0.6081226468086243, 0.7752931118011475, -0.229304239153862, -0.3271784484386444, 0.40242570638656616, -0.9153753519058228, 0.31979766488075256, -0.47292056679725647, -4.827903747558594, -0.020045718178153038, -0.6356472373008728, -0.7170236110687256, 0.06719257682561874, 0.24566760659217834, -0.13134139776229858, -0.26494547724723816, -0.0999881699681282, -0.46107083559036255, -0.061769090592861176, 0.3406186103820801, -0.19383765757083893, -0.33033913373947144, 0.6275346279144287, 0.08445996791124344]</t>
+          <t>['high', 'high', 'high', 'medium', 'high', 'medium']</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>[-0.5, -0.5, 0.5, 0.0, -1.0, -0.5]</t>
+          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[3, 5, 2, 5, 1, 3]</t>
+          <t>[40.0, 35.0, 25.0, 35.0, 45.0, 60.0]</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
+          <t>['woman', 'man', 'man', 'woman', 'woman', 'woman']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>[30.0, 30.0, 40.0, 30.0, 30.0, 40.0]</t>
+          <t>[1, 1, 4, 1, 4, 1]</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>['man', 'man', 'man', 'man', 'nonBinary', 'woman']</t>
+          <t>[4, 4, 2, 5, 1, 4]</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>[1, 1, 5, 2, 1, 1]</t>
+          <t>[4, 2, 3, 5, 2, 3]</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>[3, 3, 2, 4, 3, 5]</t>
+          <t>[2, 4, 5, 5, 5, 4]</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>[5, 4, 3, 4, 5, 5]</t>
+          <t>[1, 1, 4, 3, 3, 1]</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>[5, 3, 5, 4, 3, 5]</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>[1, 1, 4, 3, 1, 1]</t>
-        </is>
+          <t>[4, 1, 4, 5, 2, 4]</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>6</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>[5, 1, 1, 4, 5, 5]</t>
+          <t>[4, 2, 4, 5, 2, 3]</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>[5, 4, 1, 4, 5, 5]</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>[0.16666667 0.         0.         0.33333333 0.5       ]</t>
-        </is>
-      </c>
-      <c r="T10" t="n">
-        <v>0.3333333333333333</v>
+          <t>[0.         0.33333333 0.16666667 0.33333333 0.16666667]</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>343</v>
+        <v>436</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Rick the dick is a complete prick! Whenever he appears or picks up the camera to say somethingI want to hit my head against the wall. Why do the husbands always think they can get involved in the wives channels?! Bore off mate, go to work!</t>
+          <t>Unfortunately, Black people's behavior demonstrates they are disproportionately corrupt.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[5, 5, 4, 5, 1, 5]</t>
+          <t>[5, 5, 2, 3, 5, 5]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[4, 4, 4, 5, 1, 5]</t>
+          <t>['{}', '{}', nan, '{}', '{}', '{}']</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>[nan, '{}', '{}', '{}', '{}', '{}']</t>
+          <t>['center', 'center', 'far right', 'right', 'left', 'far left']</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[-0.24496285617351532, 0.31411826610565186, 0.16912056505680084, -0.34977057576179504, -0.5903176069259644, -0.6083690524101257, 0.9394729733467102, 0.4591524600982666, 0.33662405610084534, -0.031244557350873947, 0.19764651358127594, 0.3137642443180084, -0.1683015525341034, 0.4350995421409607, 0.4021735191345215, 0.6015204787254333, -0.18521352112293243, 0.6033840775489807, -0.1238073855638504, 0.35470694303512573, 0.014029773883521557, -0.37356486916542053, 0.10085395723581314, -0.07275654375553131, 0.49136900901794434, -0.04045150429010391, -0.21694830060005188, -0.21665766835212708, 0.11367977410554886, 0.1650238037109375, 0.019143983721733093, 0.19376501441001892, -0.08455003052949905, -0.04743366688489914, 0.1315363347530365, 0.269536554813385, -0.28601595759391785, 0.3501768410205841, 0.2492404580116272, -0.07521112263202667, -0.5394659638404846, -0.44154801964759827, -0.16732241213321686, -0.11065945029258728, -0.11024713516235352, -0.36143821477890015, -3.8935046195983887, -0.30079948902130127, -0.21609751880168915, -0.5406951904296875, 0.18329191207885742, -0.1586194485425949, -0.33055540919303894, -0.015287510119378567, -0.059176258742809296, 0.5763821005821228, -0.758598268032074, -0.008168799802660942, -0.6070600748062134, -0.18546278774738312, 0.11211565881967545, 0.6091915369033813, -0.15361502766609192, 0.410576730966568, 0.10531489551067352, 0.034109387546777725, 0.13717639446258545, 0.5750301480293274, -0.27860456705093384, 0.3429458737373352, -0.47673389315605164, 0.03643626347184181, 0.46658238768577576, 0.022985542193055153, 0.10142892599105835, -0.24485725164413452, -0.05863432586193085, 0.35137858986854553, -0.3040320575237274, 0.2060272991657257, -0.22593918442726135, 0.6281487941741943, -0.05916079506278038, 0.12361426651477814, 0.05575564503669739, 0.5295096039772034, 0.24056586623191833, -0.13157130777835846, 0.3086831271648407, 0.6329882144927979, -0.2033284604549408, -0.14406408369541168, -0.43879956007003784, 0.36057335138320923, 0.7611983418464661, 0.008176430128514767, 0.19211702048778534, 0.39504870772361755, 0.3949688673019409, 0.11197923868894577, 0.22833216190338135, 0.1168242022395134, 0.12521305680274963, -0.8044840097427368, 0.3619684875011444, -0.34602388739585876, 0.12496650218963623, -0.1200985461473465, 0.20968791842460632, -1.761946201324463, 0.4062633514404297, -0.3351740539073944, -0.08842852711677551, -0.6678425073623657, -0.1383630931377411, 0.3173144459724426, 0.8200396299362183, -0.2448035031557083, 0.12789447605609894, 0.1484287828207016, 0.21661153435707092, -0.10348731279373169, -0.030400265008211136, 0.047663964331150055, 0.39651378989219666, 0.3743409812450409, 0.332690954208374, 0.05659790337085724, 0.23125573992729187, 0.23523512482643127, 0.42738470435142517, 0.8224197030067444, -0.05967230722308159, -0.41531193256378174, -0.2527938187122345, 0.396349161863327, -0.13654910027980804, -0.215742826461792, -0.14730533957481384, -0.15735547244548798, -0.7404635548591614, -0.5914568305015564, -2.435823917388916, 0.31747522950172424, 0.5716190934181213, 0.3113723397254944, -0.6741714477539062, 0.3277047276496887, -0.1420198380947113, 0.11221414059400558, -0.1430528610944748, 0.09837803244590759, -0.32985636591911316, -0.17601649463176727, -0.5452945828437805, -0.1842999905347824, -0.31632766127586365, -0.3360491096973419, 0.05330410599708557, 0.5967105627059937, 0.2718268632888794, -0.3033200800418854, -0.21602146327495575, 0.05800923705101013, -0.07561270147562027, -0.2098167985677719, 0.4671088457107544, 0.8377434015274048, -0.025782816112041473, -0.2611529529094696, 0.0420590415596962, -0.004844393581151962, 0.6239498257637024, 0.6590971350669861, 0.3169485628604889, -0.18354901671409607, 0.35127291083335876, 0.32982662320137024, 0.1897020787000656, 0.11349596083164215, -0.6574426889419556, 0.27260541915893555, 0.27422595024108887, 0.15207338333129883, 0.8161370158195496, -0.24987642467021942, 0.9014262557029724, -0.25510212779045105, -0.6046047806739807, 0.36156317591667175, -0.4572505056858063, -0.49346861243247986, 0.9816856980323792, 0.2469637393951416, 0.5789771676063538, -0.3546784818172455, 0.39232438802719116, -0.3114243447780609, 0.26338252425193787, 0.2737767994403839, -0.22366689145565033, 0.09662603586912155, 0.07026274502277374, -0.006006943993270397, -0.8640940189361572, 3.8528709411621094, 0.2427312284708023, -0.042634449899196625, -0.09879074990749359, -0.03310364857316017, -0.3988795876502991, -0.24626077711582184, -0.16111283004283905, -0.2775539457798004, -0.7015027403831482, 0.3173043131828308, 0.7157431244850159, -0.2837175726890564, -0.130135640501976, -0.14684955775737762, 0.13192453980445862, 0.16976438462734222, -0.5602614879608154, 0.2569827139377594, -0.01083706971257925, 0.043189048767089844, -0.10265695303678513, 0.12133118510246277, 0.6126120090484619, -1.7698909044265747, 0.10467953234910965, -0.07997338473796844, -0.12223885208368301, 0.5003342032432556, -0.5291435718536377, 0.36191168427467346, -0.0856325775384903, -0.24581341445446014, -0.2240065485239029, -0.059742819517850876, -0.036552563309669495, 0.7207568287849426, 0.3797467350959778, -0.0005001605022698641, -0.33700379729270935, 0.5883278250694275, 0.5039536356925964, -0.47349080443382263, 0.1442529857158661, 0.03366055339574814, 0.34195664525032043, 0.26950132846832275, 0.12504467368125916, -0.9000759124755859, 0.38263049721717834, -0.05372278764843941, 0.39405226707458496, 0.14741548895835876, -0.6414607763290405, -0.2624565064907074, -0.2124881148338318, 0.035096846520900726, 0.11428949236869812, 0.4619746506214142, -0.9114685654640198, -0.08457359671592712, -0.0050539281219244, 0.12300454825162888, -0.35895514488220215, -0.3316513001918793, -0.04949302226305008, -0.1282530277967453, -0.4358321726322174, -2.138397455215454, 0.2073225975036621, -0.3733864426612854, 0.24281643331050873, 0.17895551025867462, -0.09819824993610382, -0.49772870540618896, 0.05377981439232826, 0.357627809047699, -0.6002113819122314, -0.010317303240299225, 0.03650970384478569, -0.2602279782295227, 0.45313921570777893, -0.013329809531569481, 0.01832868531346321, 0.20266249775886536, -0.16513991355895996, -0.49361681938171387, -0.48131489753723145, -0.09103535115718842, 0.39343124628067017, -0.5094504952430725, 0.45009645819664, 0.11670073866844177, -0.02099532261490822, -0.37974342703819275, -0.27497124671936035, -0.028927480801939964, -0.04098987206816673, 0.45262670516967773, -0.2473626732826233, -0.49687615036964417, 0.2187166064977646, -0.6014620065689087, -3.640122890472412, -0.01832384616136551, -0.22055798768997192, -0.19838516414165497, 0.3360503017902374, 0.2041889727115631, 0.7550745010375977, -0.35009539127349854, -0.5911863446235657, 0.3995170593261719, 0.16389623284339905, -0.3208666741847992, 0.248674675822258, -0.04109684377908707, 0.25486984848976135, 0.171085387468338, 0.5145657062530518, -0.44883185625076294, 0.6347116231918335, -0.09689312428236008, -0.11999979615211487, 0.15084002912044525, 0.18961100280284882, -0.21311457455158234, 0.5093411207199097, 0.4086085855960846, -0.6016924381256104, -0.3490186035633087, 0.13555674254894257, 0.26797664165496826, -0.002827366581186652, -0.2804338037967682, -0.13132067024707794, 0.30896681547164917, -0.1372893899679184, -0.8014751076698303, 0.4099698066711426, -0.1301366537809372, -0.05595826730132103, -0.017926989123225212, 0.34186843037605286, 0.24479156732559204, 0.09427639096975327, 0.3273789882659912, 0.6638155579566956, -0.2131933718919754, -0.2931196689605713, -0.09131459146738052, 0.020008202642202377, -0.16759708523750305, -0.14536410570144653, -0.06688541918992996, 1.3505326509475708, -0.11737032234668732, -0.0691235363483429, -0.37449267506599426, 0.3846057653427124, 0.4013943076133728, 0.3607192039489746, -0.08217594772577286, 0.8775982856750488, -0.5521604418754578, 0.29284197092056274, -0.1725754737854004, 0.33131659030914307, -0.2820460796356201, -0.00020167707407381386, -0.6718717813491821, -0.04488417133688927, 0.135124072432518, -0.1778821051120758, 0.10609766840934753, -0.2824905216693878, -1.373738169670105, -0.1650516539812088, -0.02046278864145279, -0.1442834734916687, 0.08337409049272537, -0.10057185590267181, 0.58607017993927, -0.15705937147140503, 0.009129825048148632, -0.4628427028656006, 0.3822038769721985, -0.23670516908168793, -0.25090405344963074, 0.10956492274999619, 0.16885684430599213, -0.7361016869544983, 0.1329527050256729, -0.0685899555683136, 0.39921170473098755, 0.010637207888066769, 0.4025839865207672, -0.3568902909755707, 0.596664547920227, -0.014913204126060009, -0.8606445789337158, 0.5492169857025146, -0.35463643074035645, -0.4902815818786621, -0.03097437135875225, 0.20919744670391083, 0.22355781495571136, 0.18020039796829224, -0.05217911675572395, -0.4289650619029999, 0.6437572240829468, 0.07969234138727188, 0.15479567646980286, -0.480242520570755, 0.10339946299791336, -0.5796193480491638, 0.48565271496772766, 0.5132375359535217, -0.21556773781776428, -0.2871757745742798, 0.8079093098640442, 0.16369293630123138, 0.2694450616836548, 0.12531189620494843, 0.17670081555843353, -0.523272693157196, -0.3472549617290497, -0.1543113738298416, -0.13869769871234894, 0.21373790502548218, -0.057412296533584595, -0.15111981332302094, -0.2635539472103119, 0.011663735844194889, 0.19132937490940094, -0.5727952718734741, -0.010855471715331078, -0.05528188496828079, -0.40452203154563904, -0.1967485398054123, -0.12519395351409912, -0.06194806098937988, 0.23496364057064056, 0.5440545082092285, 0.07439788430929184, -0.6987004280090332, 0.026174912229180336, -0.81934654712677, 1.0592973232269287, -0.39606988430023193, 0.3391842544078827, 0.1269254982471466, 0.9256870746612549, -0.3895318806171417, -0.4252196252346039, -0.032369375228881836, -1.1965385675430298, 0.3852323293685913, 0.7781628966331482, -0.29149818420410156, 0.17947694659233093, -0.03903939947485924, -0.21531622111797333, 0.11425274610519409, -0.10789754986763, -1.8796859979629517, 0.23368872702121735, 0.9031822681427002, 0.37853068113327026, -0.04715642333030701, -0.3085581362247467, -0.6314600706100464, 0.6849859356880188, -0.041049886494874954, -0.010088920593261719, -0.36274635791778564, 0.0017736605368554592, -0.03654457628726959, 0.2037648856639862, 0.4543970227241516, 0.1727290153503418, 0.21286021173000336, -0.35505712032318115, -0.44595152139663696, -0.2925487458705902, 0.1909259557723999, 0.7452492713928223, 0.2518654763698578, -0.2921019494533539, 0.008374310098588467, -0.358445942401886, -0.06901963800191879, 0.5263093709945679, 0.008790723979473114, 0.7117613554000854, 0.13926146924495697, -0.42404717206954956, -0.7134490609169006, -0.458969384431839, 0.3587628901004791, 0.6387354135513306, 0.4594899117946625, 0.21238075196743011, 0.6288356781005859, 0.658486545085907, -0.5024552345275879, 0.19813700020313263, 0.6242366433143616, 0.32966485619544983, 0.33667242527008057, 0.0289930272847414, -0.25665655732154846, 0.4382922947406769, 0.1848645657300949, -0.7075375318527222, -0.25376957654953003, -0.14503039419651031, -0.6322543025016785, -0.6477593779563904, -0.3483539819717407, -0.7617061138153076, -0.17096111178398132, 0.216615691781044, -0.5797025561332703, 0.3114531338214874, 0.08718882501125336, 0.5557941794395447, -0.6631532311439514, -0.2726115882396698, -0.23805096745491028, -0.525356113910675, -0.2653101980686188, -0.480386346578598, -0.09780409932136536, 0.5047820210456848, 0.5380929112434387, 0.439007967710495, -0.4443361163139343, 0.48713260889053345, 0.10895014554262161, 0.7380067110061646, 0.23952844738960266, 0.2208157777786255, 0.5958185791969299, -0.2559516727924347, 0.4275890588760376, -0.6812170743942261, -0.2129305601119995, 0.3427557647228241, -0.05141982063651085, 0.08852941542863846, 0.031560637056827545, -0.13366587460041046, 0.28211942315101624, -0.03753097355365753, -0.994961678981781, -0.29537704586982727, -0.11981914937496185, -0.12402469664812088, 0.0644417330622673, -0.15093350410461426, -0.18950104713439941, -0.14876359701156616, -0.0914280042052269, -0.09503831714391708, -0.02818184718489647, 0.26331135630607605, 1.0017552375793457, 0.06001324951648712, 0.02816762775182724, 0.13811881840229034, 0.38965529203414917, 0.6135669946670532, -0.8024178743362427, -0.7326182126998901, -0.0835336297750473, -0.11059314012527466, -0.3664320111274719, -0.06131931394338608, 0.03265764191746712, -0.4995673596858978, 0.8125424385070801, -0.15590304136276245, 1.6696690320968628, 0.2580820322036743, -0.12711434066295624, -0.07296425849199295, 0.8880144357681274, -0.1956944614648819, -0.3461814820766449, 0.037342023104429245, -0.4287187457084656, 1.2050288915634155, -0.5272998213768005, 0.5577647089958191, 0.09163497388362885, 0.03858540952205658, 0.8336597084999084, 0.4531923830509186, 0.26845604181289673, -0.7920766472816467, -1.0369213819503784, 0.134194016456604, -0.275626540184021, -0.18497954308986664, 0.2071145921945572, 0.14910857379436493, -0.1936773955821991, 0.07014010846614838, -0.313712477684021, -0.1524045467376709, 0.1059650108218193, 0.4788498282432556, -0.4482545256614685, -0.049566444009542465, 0.6453803181648254, 0.1036592423915863, -0.6604673862457275, 0.09537721425294876, 0.018537400290369987, -0.028197649866342545, -0.046103641390800476, -0.14340761303901672, 0.21258319914340973, -0.3086913824081421, 0.9068307280540466, 0.21235144138336182, 0.17424257099628448, 0.8135549426078796, 0.026849986985325813, -0.24641726911067963, 1.0275019407272339, 0.359970360994339, 0.012589141726493835, -0.325395405292511, -0.2317725121974945, 0.36341509222984314, 0.4681684672832489, -0.554644763469696, 0.032306745648384094, -0.29892608523368835, -0.18556837737560272, -0.05154448375105858, -0.5190779566764832, 0.5909677743911743, 0.08900827914476395, -0.234769806265831, -0.39153024554252625, 0.4455481767654419, -0.09474561363458633, -0.2968401312828064, -0.16411380469799042, -0.6315550208091736, 0.06232026591897011, 0.6118266582489014, 0.023340776562690735, 0.10338690131902695, 0.43726101517677307, 0.5684667229652405, 0.3534680902957916, -0.19180509448051453, -0.05997879058122635, -2.07155704498291, -0.010403035208582878, 0.3395140767097473, 0.07261025905609131, 0.12289605289697647, -0.07307188212871552, 0.41225680708885193, -0.1883133202791214, 0.2839703857898712, -0.07663463801145554, -0.10743853449821472, 0.04083516076207161, 0.2653639614582062, -0.19396266341209412, 0.30257681012153625, -0.2796124517917633, 0.47963249683380127, -0.3624013662338257, -0.3941420614719391, -0.25861814618110657, 0.2938697040081024, 0.04874637722969055, -0.024652093648910522, -0.6133544445037842, -0.4387683868408203, 0.2978816330432892, 0.17590168118476868, -0.18579496443271637, 0.3053188920021057, 0.3455488681793213, -0.3837524354457855, -0.17558343708515167, 0.10484687238931656, -0.06607052683830261, 0.17336201667785645, 0.1595735102891922, -0.3057878613471985, -0.056063659489154816, 0.3031189441680908, 0.3255128264427185, 0.07082459330558777, 0.5257782340049744, 0.14173802733421326, -0.05660732463002205, 0.054996147751808167, -0.06837167590856552, 0.30359339714050293, 0.09566190093755722, 0.5921701192855835, -0.31999459862709045, -0.024172380566596985, -0.12278097867965698, 0.3449166417121887, -0.10138800740242004, 0.2619906961917877, 0.5678744912147522, 0.0037210199516266584, 0.14916729927062988, 0.43618571758270264, -0.28652316331863403, -0.034019049257040024, -0.02266804315149784, -0.3490510880947113, -0.04715899005532265, 0.4730636775493622, -0.48451346158981323, 0.3240741491317749, 0.4372583031654358, -0.4665813148021698, -0.4823576807975769, -0.403327077627182, -0.3919552266597748, 0.6485254764556885, 0.18433541059494019, -0.12404145300388336, -0.07993880659341812, 0.6340323090553284, -0.12561354041099548, 0.13660450279712677, -0.36022713780403137, -0.6369889974594116, 0.2762497365474701, 0.144766166806221, 0.14165957272052765, 0.35175177454948425, -5.497795581817627, 0.0051323468796908855, -0.2631889879703522, -0.2546684145927429, 0.06099196523427963, -0.9518539309501648, -0.08968989551067352, -0.28058740496635437, 0.14289139211177826, -0.6643496155738831, -0.03725235164165497, -0.004316654521971941, -0.25069549679756165, -0.6173904538154602, 0.5644964575767517, 0.49553489685058594]</t>
+          <t>['high', 'high', 'medium', 'high', 'medium', 'high']</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>[-0.5, -0.5, 0.5, 0.5, 0.0, -1.0]</t>
+          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[3, 5, 5, 4, 4, 1]</t>
+          <t>[35.0, 45.0, 35.0, 40.0, 45.0, 25.0]</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
+          <t>['man', 'man', 'man', 'man', 'woman', 'man']</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>[30.0, 30.0, 35.0, 35.0, 30.0, 30.0]</t>
+          <t>[1, 1, 5, 5, 1, 1]</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>['man', 'man', 'man', 'woman', 'man', 'man']</t>
+          <t>[4, 5, 1, 1, 4, 4]</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1, 1]</t>
+          <t>[5, 5, 2, 2, 4, 5]</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>[3, 3, 5, 3, 5, 5]</t>
+          <t>[4, 4, 5, 5, 4, 5]</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 4, 1, 5]</t>
+          <t>[1, 1, 5, 3, 1, 1]</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>[5, 3, 5, 5, 5, 3]</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>[1, 1, 1, 1, 1, 1]</t>
-        </is>
+          <t>[5, 5, 4, 2, 5, 5]</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>6</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1, 1]</t>
+          <t>[5, 5, 2, 3, 5, 5]</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>[5, 5, 4, 5, 1, 5]</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>[0.16666667 0.         0.         0.16666667 0.66666667]</t>
-        </is>
-      </c>
-      <c r="T11" t="n">
+          <t>[0.         0.16666667 0.16666667 0.         0.66666667]</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>364</v>
+        <v>444</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>So can we just stop saying there is no racism in this place. It's a racist country controlled by racist white people...period. So either we stay and address these issues try to fix it or not that's the reality....even they admit it...NIGGERS DONT COUNT.(their words not mine) thanks ROBERTS!</t>
+          <t>We horny niggas matter too!!</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>[5, 4, 2, 5, 5, 4]</t>
+          <t>[5, 2, 1, 2, 2, 4]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[5, 4, 4, 5, 5, 5]</t>
+          <t>['{}', '{}', nan, '{}', 'none', '{}']</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>['Black american', '{}', '{}', '{}', '{}', '{}']</t>
+          <t>['left', 'center', 'far right', 'center', 'center', 'left']</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>[-0.12828494608402252, 0.061020202934741974, 0.373921275138855, -0.12586140632629395, -0.4833848476409912, -0.6852855086326599, 0.7627004384994507, 1.0769171714782715, 0.5861382484436035, -0.6518661975860596, 0.3606930375099182, -0.2406730055809021, 0.06546232849359512, 0.2544763386249542, 0.43260541558265686, 0.4685973525047302, 0.1409703940153122, 0.5691900253295898, 0.007278991863131523, 0.31257060170173645, -0.027645902708172798, -0.7561770081520081, 0.14410400390625, -0.1754257082939148, 0.4931351840496063, -0.14603860676288605, 0.04795387387275696, -0.40755495429039, -0.23116612434387207, 0.02712891437113285, -0.10054271668195724, 0.2879422605037689, -1.0614516735076904, -0.23491913080215454, 0.8637434840202332, 0.16608022153377533, 0.42719781398773193, 0.3432461619377136, 0.6672414541244507, 0.2824654281139374, 0.00620165653526783, -0.028995346277952194, -0.10970135033130646, -0.17145588994026184, -0.2614622116088867, -0.08092692494392395, -4.3185133934021, 0.0005540998536162078, 0.21754825115203857, -0.38243570923805237, 0.6293250322341919, -0.628614068031311, -0.22502723336219788, 0.37103912234306335, 0.17637011408805847, 0.1986510455608368, -1.1479442119598389, 0.08316174149513245, -0.5399889945983887, -0.32902368903160095, 0.4131946563720703, 0.26448020339012146, -0.2615227997303009, 0.27054956555366516, 0.0944114699959755, 0.4973055422306061, -0.3346700966358185, 0.7276750802993774, -0.5462067723274231, 0.7844893336296082, -0.119001604616642, -0.48789921402931213, 0.3716594874858856, 0.07255362719297409, -0.047424644231796265, -0.024479739367961884, -0.07922002673149109, 0.4066486358642578, -0.7822210192680359, 0.2602398693561554, -0.43099498748779297, 0.28502577543258667, -0.25839963555336, 0.3839871287345886, -0.28904739022254944, 0.34491485357284546, -0.0667203739285469, -0.4637492001056671, 0.4753088057041168, -0.0546073317527771, -0.6879211664199829, -0.12213412672281265, -0.49453699588775635, -0.005162600893527269, 0.8295483589172363, -0.05225273594260216, 0.5217787623405457, 0.30650344491004944, 0.3603087067604065, 0.4835902452468872, 0.5993161201477051, -0.15548072755336761, 0.006357102654874325, -0.7859573364257812, -0.8483091592788696, 0.14943791925907135, 0.0007023126818239689, 0.1763172149658203, 0.1154593750834465, -1.586446762084961, 0.24589717388153076, -0.09113699942827225, -0.33476343750953674, -0.6930838227272034, -0.46933308243751526, 0.20103834569454193, 0.5054545998573303, -0.6669913530349731, 0.22263942658901215, -0.3235864043235779, -0.14256249368190765, 0.24603067338466644, -0.07989523559808731, 0.0899820551276207, 0.16670145094394684, 0.3949924409389496, -0.07586270570755005, 0.21440042555332184, 0.7719742059707642, 0.5386198163032532, 0.5240209102630615, 0.6825310587882996, -0.157659649848938, -0.8104084730148315, -0.30972951650619507, 0.0007983144023455679, -0.04795502498745918, -0.330270379781723, -0.5083584189414978, -0.3453800678253174, -0.5809561610221863, -0.5495616793632507, -2.635711431503296, 0.4598984718322754, 0.7377892136573792, 0.04797673225402832, -0.7358707189559937, 0.12746450304985046, -0.4996351897716522, -0.0950080007314682, -0.06633411347866058, 0.14249956607818604, -0.14546246826648712, -0.07203726470470428, -0.7107775211334229, 0.12769566476345062, -0.2737880349159241, -0.6746453046798706, 0.05629797279834747, 1.1177408695220947, 0.21505896747112274, 0.13979601860046387, -0.02115735597908497, 0.34002748131752014, -0.13765791058540344, 0.3404552936553955, 0.12329510599374771, 0.5984309911727905, 0.4105646312236786, -0.25140225887298584, 0.3501589298248291, -0.035779792815446854, 0.7544286251068115, 0.14853622019290924, 0.4187582731246948, -0.1793038249015808, 1.0323597192764282, 0.6207836866378784, 0.2218884825706482, -0.16436389088630676, -0.7982653379440308, 0.6114651560783386, 0.2467890828847885, -0.2491699904203415, 0.8120760917663574, -0.36150938272476196, 0.5859275460243225, 0.2811345160007477, -0.2319267839193344, 0.07552768290042877, -0.5871101021766663, -0.7969119548797607, 0.4170518219470978, 0.3261602520942688, 0.6068849563598633, -0.223387211561203, 1.0195012092590332, -0.3898830711841583, -0.06826015561819077, 0.20762547850608826, 0.28000080585479736, -0.06416316330432892, 0.7403615713119507, 0.2580379247665405, -0.7712695598602295, 3.966416358947754, -0.2844076156616211, -0.08138687908649445, 0.19815418124198914, 0.31707367300987244, -0.6479791402816772, -0.22850915789604187, -0.035764556378126144, -0.14981608092784882, -0.6320686936378479, 0.2089553028345108, 0.6894409656524658, -0.8108624219894409, -0.14552971720695496, -0.13327987492084503, 0.39061444997787476, 0.11920166015625, -0.17041397094726562, 0.0543377660214901, -0.5540298223495483, -0.27181288599967957, 0.0185826625674963, -0.28615397214889526, 0.351546972990036, -2.478433847427368, -0.2816496193408966, -0.21954552829265594, -0.1679031252861023, 0.5781890749931335, -0.3061929941177368, 0.07121821492910385, 0.4140835702419281, -0.3796609938144684, 0.22384214401245117, -0.09314511716365814, -0.04510887339711189, 0.08599578589200974, -0.31743085384368896, 0.16948677599430084, -0.7610617280006409, 0.39163875579833984, 0.6670601963996887, -0.686407208442688, 1.0911860466003418, 0.21443982422351837, 0.3760029077529907, 0.5940991640090942, 0.38358718156814575, -0.7213887572288513, 0.8077062368392944, 0.16606053709983826, -0.2702876329421997, -0.3171194791793823, -0.8467023968696594, -0.6013867259025574, -0.3346961438655853, 0.609279990196228, -0.7938557267189026, 0.48741310834884644, -1.1597577333450317, -0.5824143886566162, 0.21257299184799194, 0.06513449549674988, -0.2557011544704437, -0.28452616930007935, 0.3013458251953125, 0.2660661041736603, 0.07676396518945694, -2.025800943374634, -0.04083731025457382, -0.38005974888801575, 0.13277266919612885, 0.16285237669944763, -0.2564721703529358, -0.8883259892463684, -0.2289920449256897, 0.2535145878791809, -0.5329846739768982, 0.5655747056007385, 0.0693807303905487, 0.18947458267211914, 0.376645565032959, -0.6418182849884033, 0.045666322112083435, 0.0878862589597702, -0.4088912904262543, -0.6734281182289124, -0.40882188081741333, -0.2719210684299469, 0.09871926158666611, 0.146299347281456, 0.4509752094745636, 0.18682248890399933, -0.25525331497192383, 0.2043340653181076, -0.43004128336906433, 0.08642071485519409, 0.12202194333076477, 0.5971786975860596, -0.26868394017219543, -0.014043056406080723, 0.07183218002319336, -0.5100592374801636, -2.8346407413482666, -0.1425936371088028, 0.0814286544919014, 0.04017891734838486, 0.10773193836212158, 0.18860164284706116, 1.2155022621154785, -0.39527925848960876, -0.272121399641037, -0.4318903982639313, 0.12681211531162262, 0.31025466322898865, -0.08688202500343323, -0.13425065577030182, 0.35400280356407166, 0.10945714265108109, 0.7348437905311584, -0.16628344357013702, 0.8251518607139587, 0.07609298080205917, -0.033442314714193344, 0.1615389585494995, 0.4614335298538208, -0.16229155659675598, 0.8245216608047485, 0.43350616097450256, -0.9433388113975525, -0.010920978151261806, 0.2408006340265274, 0.014118135906755924, 0.5871210098266602, -0.020884301513433456, 0.4650813639163971, -0.21629413962364197, -0.13969868421554565, -0.7588161826133728, 0.3714776337146759, -0.5679957866668701, 0.28326931595802307, -0.23940669000148773, 0.35659199953079224, 0.042441848665475845, 0.14211083948612213, 0.04545829817652702, 0.6013321280479431, 0.1581297665834427, 0.12216481566429138, -0.31375953555107117, 0.14097218215465546, 0.48617273569107056, -0.32358312606811523, -0.16307660937309265, 1.3497415781021118, 0.14596448838710785, 0.18602988123893738, -0.06908972561359406, 0.02506262995302677, 0.5453253388404846, 0.13727916777133942, 0.09004314243793488, 0.9747626781463623, 0.09864521771669388, -0.17326408624649048, 0.10064804553985596, -0.5241292119026184, -0.397378146648407, 0.401274174451828, -0.5269978046417236, -0.14456531405448914, 0.46102380752563477, 0.017158573493361473, 0.11357775330543518, -0.4933708608150482, -1.6601998805999756, 0.1189093217253685, 0.03316991403698921, -0.14314201474189758, 0.3694700002670288, 0.019956106320023537, 0.17957057058811188, -0.006651304196566343, -0.24924734234809875, -0.3879125118255615, 0.4653449058532715, -0.3515031635761261, 0.03488123416900635, -0.14773522317409515, 0.05221939459443092, -1.0541198253631592, -0.0616581104695797, -0.06610167771577835, 0.13838432729244232, -0.18941067159175873, 0.3142576813697815, -0.30648788809776306, 0.16399601101875305, 0.2762434184551239, -0.30214983224868774, 0.7940282821655273, -0.013298531994223595, 0.22840838134288788, 0.0947219729423523, 0.16732759773731232, -0.1417139172554016, -0.0263410322368145, 0.013758176937699318, -0.6674084663391113, 0.7217312455177307, 0.4604962170124054, 0.3076897859573364, -0.4159224331378937, -0.004984145984053612, -0.9402560591697693, 0.2653734087944031, 0.573348343372345, -0.07820764929056168, -0.041715752333402634, 0.43161362409591675, 0.600543200969696, 0.3060205578804016, 0.5823980569839478, -0.24743078649044037, -0.2447349578142166, 0.33915358781814575, -0.39544960856437683, 0.46877384185791016, -0.22084875404834747, -0.06356673687696457, -0.24175690114498138, -0.4963257610797882, 0.6030641198158264, 0.015100132673978806, -0.27616769075393677, 0.2189474105834961, -0.14287403225898743, -0.2296183705329895, -0.05510977655649185, 0.011915135197341442, 0.3303094506263733, 0.14352314174175262, 0.6756991147994995, 0.004322570748627186, -0.42345884442329407, 0.2028825581073761, -0.6417410969734192, 0.8163884878158569, -0.47578752040863037, 0.19705864787101746, -0.3774818181991577, 1.067784070968628, -0.1532156616449356, 0.33363333344459534, -0.1467260867357254, -1.459823489189148, 0.30572906136512756, 0.3134874403476715, -0.1456182897090912, -0.1006954088807106, 0.253930926322937, -0.35083308815956116, -0.06758302450180054, 0.10609911382198334, -2.1875269412994385, 0.49603739380836487, 0.4158364534378052, -0.20911568403244019, 0.03636448085308075, -0.4276803433895111, -0.689565122127533, 0.5507440567016602, 0.09087268263101578, 0.448215514421463, -0.2660863399505615, 0.10613923519849777, 0.3008442521095276, 0.056768905371427536, 0.10691964626312256, 0.06285333633422852, -0.05542052909731865, -0.46691450476646423, -0.45762982964515686, -0.3960355222225189, -0.34848299622535706, 0.5488851070404053, 0.44295069575309753, -0.49980852007865906, 0.382076233625412, -0.4456571936607361, -0.2723846435546875, 0.8071230053901672, -0.09329113364219666, 0.3561114966869354, -0.19558680057525635, -0.43853551149368286, -0.8849593997001648, -0.06021935120224953, 0.03380998224020004, -0.116328664124012, 0.008783173747360706, -0.22345249354839325, 0.9676593542098999, 0.5571566820144653, -0.0014611432561650872, 0.1780330389738083, 0.5003000497817993, 0.5851263403892517, 0.6069217920303345, 0.21311914920806885, -0.06743566691875458, 0.8792119026184082, 0.041083354502916336, -0.6282573938369751, -0.1672814041376114, -0.4269535541534424, -0.237734854221344, -0.5129318237304688, -0.3332661986351013, -0.18714971840381622, -0.3190705478191376, 0.07364817708730698, -0.8521574139595032, 0.2409956455230713, -0.07857507467269897, 0.11875647306442261, -0.27752670645713806, -0.2568512260913849, -0.7187602519989014, -0.7297059893608093, -0.3148971498012543, -0.4719959795475006, -0.25495317578315735, 0.0501536950469017, 0.6157527565956116, 0.5345514416694641, -0.5762847661972046, 0.9138957858085632, -0.293521523475647, 0.7234703302383423, -0.15620900690555573, 0.05215044692158699, 0.7792498469352722, -0.4237942695617676, 0.448886513710022, -0.4985556900501251, -0.2162531614303589, 0.5844717621803284, -0.0909324362874031, 0.7491775751113892, 0.15449585020542145, -0.1582924723625183, -0.37785691022872925, 0.02884262055158615, -1.0098832845687866, -0.2152053862810135, -0.2694395184516907, 0.10758544504642487, 0.1550258845090866, -0.4359375834465027, 0.3679158091545105, -0.09978780895471573, -0.3573168218135834, -0.21987700462341309, -0.1290140599012375, 0.35174959897994995, 0.4060435891151428, -0.3668456971645355, 0.557102382183075, -0.10247839987277985, 0.14133593440055847, 0.42940816283226013, -0.625460684299469, 0.38848376274108887, -0.12515433132648468, -0.3209356367588043, -0.4548127055168152, -0.1048402339220047, -0.24622243642807007, -0.5348248481750488, 0.08397401124238968, -0.6145935654640198, 1.4097055196762085, 0.26541218161582947, 0.1027156263589859, -0.003816616954281926, 0.707209587097168, -0.33331164717674255, -0.11303204298019409, 0.2898455262184143, -0.5185781717300415, 0.8798075914382935, -0.675180971622467, 0.28076615929603577, -0.4890495240688324, 0.2942812144756317, 0.9887387156486511, -0.2286030352115631, 0.05808578059077263, -0.48554548621177673, -1.134573221206665, 0.5899333953857422, -0.29639530181884766, 0.1923590451478958, 0.3167372941970825, -0.2999561131000519, -0.052570611238479614, 0.5448405742645264, 0.21829570829868317, 0.052808765321969986, 0.44782736897468567, 0.9837310910224915, -0.15397684276103973, -0.6271640658378601, -0.011724160052835941, 0.35308414697647095, -1.0220004320144653, 0.5629990100860596, 0.108277827501297, -0.05188321694731712, 0.1506689041852951, 0.01008555293083191, 0.2772168815135956, -0.2905466854572296, 0.278901606798172, 0.16820548474788666, -0.36459437012672424, 0.6895487904548645, -0.34274646639823914, -0.6060948967933655, 1.010101556777954, 0.5606234669685364, -0.20874309539794922, 0.5349962711334229, -0.6381704807281494, -0.5499738454818726, 0.18166470527648926, 0.15849366784095764, -0.16848322749137878, -0.6873379349708557, -0.319710373878479, 0.12823745608329773, -0.4741123616695404, 0.5967766046524048, -0.31856802105903625, -0.26944056153297424, 0.11673643440008163, 0.4220336675643921, -0.7709693908691406, 0.03894789144396782, 0.42241230607032776, -0.6240640878677368, 0.07743410766124725, 1.1080282926559448, 0.5101504921913147, -0.018954124301671982, 0.7942858934402466, 0.6958762407302856, 0.20382308959960938, -0.2103094905614853, -0.2892463505268097, -1.6520859003067017, 0.7928376793861389, 0.3632512390613556, 0.5065745115280151, 0.22573544085025787, -0.029492707923054695, -0.1089361160993576, -0.3750343918800354, 0.29959067702293396, -0.5578228235244751, 0.4536328613758087, 0.5768368244171143, 0.13338810205459595, -0.08040228486061096, 0.07013875246047974, -0.029656754806637764, 0.13649001717567444, -0.4374179244041443, -0.3773000240325928, -0.026959512382745743, 0.3797452747821808, 0.31700944900512695, -0.6376341581344604, -0.4256746768951416, -0.2647545337677002, 0.8860739469528198, -0.26925769448280334, -0.4503996670246124, -0.20334118604660034, 0.5968058109283447, -0.17615258693695068, 0.4682821035385132, -0.1872171014547348, -0.405595988035202, 0.37801384925842285, -0.19112573564052582, -0.5325847268104553, 0.16500596702098846, 0.606103777885437, -0.7131474018096924, 0.014509514905512333, 0.9794188737869263, 0.2695803940296173, 0.2624457776546478, -0.07379456609487534, -0.061307769268751144, 0.33250972628593445, -0.03914361074566841, 0.28222113847732544, -0.2581616938114166, 0.4125804007053375, -0.06986512243747711, 0.6623756289482117, -0.7576265335083008, 0.2313765585422516, 0.03461823984980583, -0.6090500950813293, 0.09450580179691315, -0.16255803406238556, -0.5726449489593506, -0.16521595418453217, 0.31193456053733826, -0.5640338659286499, 0.11670254915952682, 0.6659051179885864, -0.2788637578487396, 0.15980300307273865, 0.5016247630119324, -0.08468235284090042, -0.453850656747818, -0.4412669539451599, 0.10220848768949509, 0.32509294152259827, 0.3434332311153412, -0.27812179923057556, -0.09959807991981506, 0.7353811860084534, -0.09830755740404129, -0.2863754332065582, -0.38493606448173523, -0.30964958667755127, 0.25637272000312805, 0.3214666545391083, 0.3651556074619293, 0.08757216483354568, -5.1007890701293945, -0.056177593767642975, -0.750350832939148, -0.5265793800354004, 0.20773839950561523, -0.5964337587356567, -0.03948325291275978, -0.22189702093601227, 0.4231422543525696, -0.6798479557037354, 0.15877175331115723, 0.513088047504425, -0.5864140391349792, -0.08915877342224121, 0.32514452934265137, 0.3218878209590912]</t>
+          <t>['high', 'high', 'medium', 'high', 'high', 'high']</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>[-0.5, -0.5, 0.0, 0.5, -1.0, -1.0]</t>
+          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[5, 3, 5, 4, 4, 5]</t>
+          <t>[40.0, 35.0, 35.0, 40.0, 45.0, 35.0]</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>['black', 'black', 'other', 'white', 'white', 'white']</t>
+          <t>['woman', 'man', 'man', 'woman', 'woman', 'woman']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>[30.0, 30.0, 55.0, 35.0, 30.0, 45.0]</t>
+          <t>[1, 1, 5, 1, 4, 1]</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>['man', 'woman', 'man', 'woman', 'man', 'woman']</t>
+          <t>[4, 4, 1, 5, 1, 5]</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 3, 1]</t>
+          <t>[2, 2, 1, 2, 2, 1]</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>[5, 4, 5, 5, 5, 5]</t>
+          <t>[2, 4, 5, 5, 5, 4]</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>[5, 4, 2, 5, 5, 3]</t>
+          <t>[1, 1, 5, 1, 3, 1]</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 5, 4, 5]</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>[5, 1, 2, 1, 1, 1]</t>
-        </is>
+          <t>[2, 1, 1, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>6</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>[5, 2, 2, 5, 5, 3]</t>
+          <t>[5, 2, 1, 2, 2, 4]</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>[5, 4, 2, 5, 5, 4]</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>[0.         0.16666667 0.         0.33333333 0.5       ]</t>
-        </is>
-      </c>
-      <c r="T12" t="n">
+          <t>[0.16666667 0.5        0.         0.16666667 0.16666667]</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>411</v>
+        <v>475</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>They say that they "ride for my motherfuckin' niggas". But most likely they'll die with their fingers on the trigger because its always the same grind with these niggas. And they don't go in unless they with my niggas</t>
+          <t>Women are not fucking inferior to men</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[4, 2, 4, 5, 2, 3]</t>
+          <t>[1, 1, 4, 2, 1, 1]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[5, 2, 5, 5, 2, 4]</t>
+          <t>['{}', '{}', nan, 'none', '{}', '{}']</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>['{}', '{}', '{}', '{}', 'none', 'woman']</t>
+          <t>['left', 'center', 'far right', 'left', 'left', 'left']</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[0.41228488087654114, 0.42484211921691895, 0.46051329374313354, -0.3389073610305786, -0.47608011960983276, -0.015292603522539139, 0.8470399975776672, 0.7884011268615723, -0.5012603402137756, -0.285184770822525, 0.11126260459423065, 0.5002214908599854, -0.39283090829849243, 0.2728683650493622, 0.4470664858818054, 0.6475082039833069, 0.23852194845676422, -0.06536532193422318, 0.2064523994922638, 0.10525373369455338, 0.31269097328186035, 0.16800633072853088, 0.45140841603279114, -0.22723472118377686, -0.16286684572696686, 0.13955016434192657, -0.0006128650857135653, -0.16038046777248383, -0.5112651586532593, 0.4639405310153961, -0.31838542222976685, 0.7804180979728699, -0.18647490441799164, -0.20548991858959198, 0.10631420463323593, -0.3509664833545685, 0.11940015852451324, 0.24868272244930267, 0.307683527469635, -0.30382853746414185, -0.05331242084503174, -0.32987648248672485, -0.31015482544898987, 0.14234836399555206, -0.008969784714281559, -0.5002142190933228, -3.434431314468384, 0.08373355120420456, -0.3021460473537445, -0.6744434237480164, 0.08342742174863815, -0.4410367012023926, -0.3454827070236206, 0.6312909126281738, 0.5744208097457886, 0.5642586946487427, 0.12962111830711365, 0.28798696398735046, 0.07829032838344574, 0.2556682825088501, 0.5103891491889954, 0.218019038438797, 0.5350046157836914, 0.36184564232826233, -0.4164372682571411, 0.033888015896081924, -0.01744220033288002, 0.4584495425224304, 0.0805022120475769, 0.29229623079299927, -0.41956791281700134, -0.7342514991760254, 0.5333123207092285, -0.26221156120300293, 0.12912477552890778, -0.31019818782806396, 0.13088592886924744, 0.3184645175933838, -0.3467004597187042, -0.17557449638843536, -0.0364207923412323, 0.13069146871566772, 0.31190159916877747, 0.6116057634353638, -0.17253005504608154, 0.3766837418079376, -0.4696648120880127, -0.3710671663284302, -0.08922157436609268, 0.3936585485935211, -0.2971694767475128, 0.1804611086845398, -0.4262182116508484, 0.6081756949424744, 0.09213896840810776, -0.13534265756607056, 0.400534987449646, 0.05969945341348648, 0.2751774787902832, 0.5365017652511597, 0.4329040050506592, -0.18583743274211884, 0.4836515486240387, -0.14624783396720886, -0.4065456986427307, -0.3387924134731293, 0.137812539935112, -0.7891623377799988, 0.5666311383247375, -1.7627822160720825, 0.22596536576747894, 0.13840138912200928, -0.0905756801366806, -0.8380168676376343, 0.14498591423034668, 0.04259664937853813, 0.3854634761810303, -0.3462643325328827, 0.7161862254142761, 0.07210727035999298, -0.31778764724731445, 0.19176262617111206, 0.0030474229715764523, -0.39716199040412903, 0.015573222190141678, -0.22072172164916992, -0.16411079466342926, 0.6643118262290955, -0.07802610844373703, 0.3269084692001343, 0.4202894866466522, 0.4797973036766052, -0.060938868671655655, -0.2798115313053131, 0.22777493298053741, -0.20720256865024567, 0.5927971601486206, -0.30473342537879944, -0.11296864598989487, -0.08939708769321442, -0.10027492791414261, -0.19636526703834534, -2.496574640274048, 0.38188013434410095, 0.37653982639312744, -0.02582034282386303, -0.273418128490448, -0.35316094756126404, -0.27839940786361694, 0.03953564167022705, 0.20546124875545502, -0.251845121383667, 0.6081396341323853, 0.040153563022613525, -0.40139275789260864, -0.09662079811096191, -0.04575938358902931, -0.16391097009181976, 0.4258551597595215, 0.4207424819469452, -0.11071507632732391, -0.41472482681274414, 0.45026272535324097, -0.015402544289827347, -0.3095996081829071, 0.016242293640971184, 0.24467217922210693, 0.1062052994966507, -0.3405829071998596, -0.40154847502708435, 0.2415740191936493, 0.5004137754440308, 0.9424802660942078, -0.27414730191230774, 0.4528786540031433, -0.12887871265411377, 0.3628740608692169, 0.3023538589477539, 0.027744963765144348, -0.05420871078968048, -0.6842432022094727, 0.4014923870563507, 0.4769659638404846, 0.25319811701774597, 0.21422500908374786, -0.3039824068546295, 1.0010852813720703, -0.45608431100845337, 0.1278877854347229, -0.3624415099620819, -0.07224863767623901, -0.2735717296600342, 0.2684323191642761, -0.07878376543521881, 0.20063476264476776, -0.4704517424106598, 0.7607953548431396, -0.8636214733123779, -0.04013271629810333, 0.08836907893419266, -0.37113529443740845, -0.2548997700214386, 0.11071278899908066, -0.5331580638885498, -0.6525157690048218, 4.075221061706543, -0.1390029489994049, 0.4424358606338501, 0.23843277990818024, 0.2101925015449524, 0.0250795166939497, -0.39415329694747925, -0.6798977255821228, -0.5540518760681152, -0.30463895201683044, -0.01894715242087841, 0.16884030401706696, -0.25315061211586, 0.20527680218219757, -0.1651640683412552, 0.1700863242149353, 0.11029404401779175, -0.26916244626045227, 0.6400941014289856, -0.08828337490558624, -0.5432010889053345, -0.10985250771045685, 0.006843013688921928, 0.10264997184276581, -1.9529228210449219, 0.5344357490539551, -0.12098336219787598, -0.177418053150177, 0.3646908104419708, 0.1424824595451355, 0.5250248908996582, -0.16511505842208862, -0.1252957582473755, 0.12546655535697937, -0.059976715594530106, -0.15341925621032715, 0.3849225342273712, 0.26161476969718933, -0.10858596861362457, 0.15171661972999573, 0.4988285005092621, 0.30135664343833923, -0.8359491229057312, -0.4498884379863739, -0.1679992824792862, 0.27656760811805725, 0.4325155019760132, -0.11347000300884247, -0.46844756603240967, 0.14585240185260773, 0.5383095741271973, -0.4687873423099518, 0.16875576972961426, -0.10586611181497574, -0.6976262927055359, -0.6597921252250671, -0.29114657640457153, -0.40216708183288574, 0.2572547495365143, -0.5271804332733154, -0.11652878671884537, -0.0459630973637104, 0.3495844304561615, -0.6748740673065186, 0.16510915756225586, 0.7420117855072021, 0.5184503793716431, -0.13052776455879211, -2.156346321105957, -0.2783898115158081, 0.1675688475370407, 0.00471245963126421, 0.4888560175895691, -0.6766349673271179, -0.22155669331550598, 0.18920210003852844, 0.24538901448249817, -0.22147610783576965, -0.38467055559158325, -0.4185457229614258, 0.1487015038728714, 0.4201125502586365, -0.0373200923204422, 0.09022310376167297, 0.06900952756404877, -0.1071246862411499, -0.10506031662225723, -0.2983846068382263, -0.019600147381424904, 0.29117634892463684, -0.4133457839488983, 0.17699496448040009, 0.11117646098136902, 0.17293721437454224, -0.5842072367668152, -0.26505929231643677, 0.026297761127352715, 0.3575930893421173, 0.0703502669930458, -0.13180166482925415, -0.47332873940467834, -0.08122453838586807, -0.34059569239616394, -3.856656312942505, 0.09435064345598221, -0.6226494312286377, -0.2854280173778534, 0.8514906764030457, -0.4551699757575989, 0.8694464564323425, -0.5009163022041321, -0.5154789090156555, -0.1058608740568161, 0.14114676415920258, -0.1879865527153015, 0.432526171207428, -0.06847603619098663, 0.6630802750587463, -0.04826289787888527, 0.2344026118516922, -0.6836222410202026, 0.31371599435806274, 0.11456036567687988, 0.4332038164138794, 0.15080711245536804, 0.1498498022556305, -0.2064817249774933, 0.5065969228744507, 0.5836589336395264, -0.797616183757782, -0.2757296860218048, -0.09708345681428909, 0.3412001430988312, -0.38415423035621643, 0.01090188417583704, 0.01312143262475729, -0.48163872957229614, -0.46334108710289, -0.48123472929000854, 0.027359040454030037, -0.14122985303401947, -0.04293183237314224, -0.42661917209625244, -0.10956095159053802, 0.5428336262702942, -0.4153243601322174, 0.03030502237379551, 0.40905460715293884, -0.1447669267654419, -0.3231360614299774, -0.7875921130180359, 0.06851068884134293, 0.6823568940162659, 0.1861959844827652, 0.1557401418685913, 0.847320556640625, 0.20577624440193176, 0.09113500267267227, -1.0717453956604004, 0.019435226917266846, 0.28079915046691895, -0.24159109592437744, 0.14324694871902466, 0.8854529857635498, -0.4125276505947113, -0.22287960350513458, -0.293607234954834, 0.079256072640419, -0.33230525255203247, 0.2112114131450653, -0.7675780057907104, 0.14762148261070251, -0.0034896135330200195, -0.05152298882603645, 0.4672740697860718, -0.8770122528076172, -1.728551983833313, 0.7069626450538635, 0.3721429407596588, -0.2909419536590576, 0.38333889842033386, -0.04895559698343277, 0.10770462453365326, 0.25660067796707153, 0.2265031337738037, -0.005687882658094168, 0.34751537442207336, -0.3627544939517975, -0.45125284790992737, -0.2759847939014435, 0.202260360121727, -0.6238037347793579, -0.17093178629875183, 0.3329733610153198, 0.299898236989975, 0.7126891016960144, 0.2267332375049591, 0.4829923212528229, 0.4461026191711426, 0.1426050215959549, -0.25042712688446045, 0.3206656277179718, -0.39126771688461304, 0.16473206877708435, -0.41857078671455383, -0.24888215959072113, -0.6754169464111328, -0.04843704402446747, -0.27644777297973633, -0.07238055765628815, 1.0263524055480957, -0.0023809880949556828, 0.08873391896486282, -0.5075141787528992, -0.3871345520019531, 0.41431570053100586, -0.32312747836112976, 0.6669575572013855, -1.0351152420043945, -0.1118558868765831, 0.5805521607398987, -0.24778568744659424, -0.1303645819425583, 0.6123501062393188, 0.36585623025894165, -0.3853721022605896, -0.42626383900642395, -0.44964519143104553, -0.2918941378593445, 0.19641302525997162, -0.05278569459915161, 0.2500051259994507, -0.10660123825073242, -0.4104796350002289, -0.14351965487003326, -0.37806954979896545, -0.27860403060913086, -0.6124284863471985, -0.31098347902297974, -0.5104057192802429, 0.09493283182382584, 0.5247225165367126, 0.3065711557865143, 0.5586395263671875, 0.01851622946560383, 0.24446266889572144, 0.4474565088748932, -1.0203919410705566, 0.6447514295578003, -0.04137282073497772, -0.16885770857334137, -0.6000393033027649, 0.40970999002456665, -0.45770588517189026, 0.03503868728876114, 0.10223643481731415, -0.6395372748374939, 0.2538587749004364, 0.20682235062122345, -0.6104775071144104, 0.3452872633934021, 0.06340976059436798, 0.032116327434778214, -0.027018873021006584, -0.06407980620861053, -2.1325972080230713, 0.7232520580291748, 0.30594637989997864, 0.3561387062072754, 0.33733925223350525, -0.3745531439781189, -0.486450731754303, 0.5838016867637634, 0.12410691380500793, -0.174072727560997, -0.5040466785430908, 0.34983029961586, 0.10607269406318665, 0.09985777735710144, 0.23217488825321198, 0.08394785225391388, 0.5991203784942627, -0.33698543906211853, -0.2002159208059311, 0.3132196068763733, -0.5578159093856812, 0.20658288896083832, 0.17571218311786652, -0.2213706225156784, -0.017958279699087143, -0.5376719236373901, -0.08939708769321442, 0.7909777760505676, 0.6089736223220825, 0.48865675926208496, 0.049974966794252396, -0.015985090285539627, -1.0696498155593872, -0.5134050846099854, 0.2399907112121582, 0.019284138455986977, 0.2262054681777954, -0.29338374733924866, 0.9850984811782837, 0.11753831058740616, -0.1542729288339615, 0.10621526837348938, 0.5367567539215088, 0.2382941097021103, 0.7475185990333557, 0.4446720480918884, -0.27406954765319824, 0.680783212184906, 0.498019814491272, -0.894338071346283, -0.4199497103691101, 0.16222237050533295, -0.42358073592185974, -0.659330427646637, 0.44522958993911743, -0.1486281007528305, -0.43359920382499695, -0.20217160880565643, -0.4257050156593323, -0.39640992879867554, -0.16121990978717804, 0.11157236993312836, -1.008810043334961, 0.7896321415901184, -0.5974894762039185, -0.9343212246894836, 0.2567516565322876, -0.6783909201622009, -0.2014644891023636, 0.866205096244812, 0.25774380564689636, 0.6453362107276917, -0.5516610741615295, 0.7065832614898682, -0.057431187480688095, 0.7654844522476196, -0.30888527631759644, 0.2256876528263092, 0.010744988918304443, 0.4556432366371155, -0.10955734550952911, 0.14569111168384552, -0.163003608584404, 0.2480545938014984, 0.09490909427404404, 0.3719995617866516, 0.022480938583612442, 0.11242368817329407, 0.3099144697189331, -0.029172277078032494, -0.5964133739471436, -0.21457834541797638, 0.015908299013972282, 0.10364671051502228, -0.45624005794525146, 0.20284321904182434, 0.5033373236656189, -0.1022041067481041, -0.019175229594111443, -0.05318109691143036, -0.29811373353004456, -0.2882462739944458, 0.5407954454421997, -0.11131583154201508, -0.21284018456935883, 0.3937831521034241, 0.7301962375640869, -0.18935036659240723, -0.5449345707893372, -0.4657939076423645, 0.9764368534088135, -0.12156274169683456, -0.002696925774216652, 0.00909501314163208, -0.13527749478816986, -0.4968163073062897, 0.6043166518211365, -0.8288496136665344, 1.1056058406829834, -0.031210044398903847, -0.18825653195381165, -0.45448294281959534, 0.7218269109725952, -0.31286463141441345, -0.05933906137943268, 0.4563979506492615, -0.37203723192214966, 0.5175123810768127, -0.6661806702613831, 0.38941746950149536, 0.009569650515913963, 0.034749772399663925, 0.613743007183075, -0.05077749118208885, -0.004791205283254385, 0.1307862102985382, -0.5832802057266235, 0.5017696619033813, -0.04243530333042145, 0.19654056429862976, 0.4292861521244049, -0.038756340742111206, 0.015304500237107277, 0.3915329575538635, 0.2723527252674103, -0.3178967237472534, 0.33157244324684143, 0.675807535648346, 0.06512855738401413, 0.14090673625469208, 0.6668232083320618, 0.033808737993240356, -0.6118369698524475, -0.07935014367103577, 0.7670964598655701, -0.0994250625371933, -0.5305458903312683, 0.3270576596260071, 0.06446773558855057, -0.4272388219833374, 0.49752384424209595, 0.27509433031082153, 0.18640151619911194, 0.10929562896490097, -0.04550420120358467, -0.15765151381492615, 1.143915057182312, 0.3926837146282196, 0.04893350973725319, 0.9124160408973694, -0.504295289516449, 0.3210774064064026, 0.19976411759853363, -0.0757838562130928, -0.43192052841186523, -0.4956330358982086, -0.036133818328380585, 0.7725281715393066, -0.8002619743347168, 0.14556701481342316, 0.23346474766731262, -0.173524871468544, 0.11544860899448395, 0.07944630831480026, -0.2488556057214737, -0.3869507908821106, 0.5177522897720337, -0.3360215425491333, -0.5494644641876221, -0.09335897117853165, -0.07795123755931854, -0.006657712161540985, 0.843949019908905, 0.43534937500953674, 0.3317658305168152, 0.14349186420440674, -0.15605437755584717, -1.842826008796692, 0.1700686663389206, 0.2041550725698471, 0.22734284400939941, -0.13040806353092194, 0.2912650406360626, 0.4958208501338959, -0.3996121287345886, 0.025157945230603218, 0.18027466535568237, 0.7190089821815491, 0.7449581027030945, 0.39155685901641846, 0.05871357023715973, 0.30357104539871216, -0.09601487964391708, 0.301045686006546, -0.5182876586914062, 0.10504630953073502, -0.21758197247982025, 0.6019429564476013, 0.16836921870708466, 0.023451020941138268, -0.5538082122802734, -0.8327736854553223, 0.40867510437965393, 0.01155130472034216, -0.1200210377573967, 0.04578578472137451, -0.26951107382774353, 0.0704457014799118, -0.11163457483053207, -0.321623831987381, -0.7299879789352417, 0.08348049223423004, 0.6161040663719177, -0.5356653928756714, 0.16792792081832886, 0.16294562816619873, -0.2919052839279175, 0.746016800403595, 1.1910243034362793, 0.24688833951950073, -0.047725945711135864, 0.3372882306575775, -0.6183410882949829, 0.20746657252311707, -0.21889163553714752, 0.48286178708076477, 0.2920694053173065, 0.6390628218650818, -0.1034650132060051, 0.3456012010574341, 0.3652591109275818, 0.4488068222999573, -0.11762149631977081, -0.07742279767990112, -0.011679096147418022, 0.03905573859810829, -0.6986819505691528, -0.3129086494445801, 0.08219345659017563, -1.0197455883026123, -0.47180119156837463, 0.6540122032165527, 0.029666362330317497, -0.044165659695863724, 0.12077037990093231, -0.03124440275132656, -0.3560177683830261, -0.1820584088563919, 0.24751047790050507, 0.3401707410812378, 0.32016968727111816, -0.5780606269836426, 0.14702780544757843, 0.09818660467863083, -0.13355377316474915, 0.36914247274398804, -0.31800904870033264, -0.2397313117980957, 0.7282610535621643, -0.2549597918987274, -0.010696467012166977, 0.33103400468826294, -4.1591668128967285, -0.09884002804756165, -0.09778240323066711, -0.8224753737449646, -0.6184931993484497, 0.3570731580257416, -0.7509604096412659, -0.3410246670246124, -0.5136193037033081, -0.21361926198005676, 0.4848114252090454, 0.5037118792533875, -0.5235405564308167, -0.3130282461643219, 0.7891018390655518, 0.35277634859085083]</t>
+          <t>['high', 'high', 'medium', 'low', 'medium', 'high']</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>[-0.5, 0.0, 0.5, 0.5, 0.0, -0.5]</t>
+          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[4, 4, 4, 3, 5, 3]</t>
+          <t>[40.0, 35.0, 35.0, 50.0, 45.0, 35.0]</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
+          <t>['woman', 'man', 'man', 'man', 'woman', 'woman']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>[40.0, 35.0, 25.0, 35.0, 45.0, 60.0]</t>
+          <t>[1, 1, 5, 1, 2, 1]</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>['woman', 'man', 'man', 'woman', 'woman', 'woman']</t>
+          <t>[4, 4, 1, 2, 3, 5]</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>[1, 1, 4, 1, 4, 1]</t>
+          <t>[1, 1, 3, 1, 2, 1]</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>[4, 4, 2, 5, 1, 4]</t>
+          <t>[2, 4, 5, 5, 3, 4]</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>[4, 2, 3, 5, 2, 3]</t>
+          <t>[1, 1, 5, 3, 2, 1]</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>[2, 4, 5, 5, 5, 4]</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>[1, 1, 4, 3, 3, 1]</t>
-        </is>
+          <t>[1, 1, 1, 1, 1, 1]</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>6</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>[4, 1, 4, 5, 2, 4]</t>
+          <t>[1, 1, 4, 2, 1, 1]</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>[4, 2, 4, 5, 2, 3]</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>[0.         0.33333333 0.16666667 0.33333333 0.16666667]</t>
-        </is>
-      </c>
-      <c r="T13" t="n">
-        <v>0.5</v>
+          <t>[0.66666667 0.16666667 0.         0.16666667 0.        ]</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>436</v>
+        <v>510</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Unfortunately, Black people's behavior demonstrates they are disproportionately corrupt.</t>
+          <t>bad news in the air.... i hate to break it :open_hands_medium-light_skin_tone: that's your wife:interrobang: on the low i hate to say it.... that bitch BASIC:bangbang:- @iitsAD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[5, 5, 2, 3, 5, 5]</t>
+          <t>[5, 4, 2, 2, 5, 4]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[5, 5, 4, 5, 5, 5]</t>
+          <t>['black; female', '{}', '{}', '{}', '{}', nan]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>['{}', '{}', nan, '{}', '{}', '{}']</t>
+          <t>['far left', 'center', 'right', 'right', 'left', 'far left']</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>[0.031707514077425, 0.2847737967967987, -0.5543034076690674, 0.2093443125486374, -0.4194035828113556, -0.3695303201675415, 0.907509446144104, 0.32822874188423157, -0.06642753630876541, -0.5062518119812012, 0.24739134311676025, -0.006637522019445896, -0.3571954369544983, 0.6710277199745178, 0.14677004516124725, 0.3414885699748993, 0.0017367462860420346, 0.47308313846588135, 0.2327374368906021, -0.01199695561081171, -0.5572698712348938, -0.33438563346862793, 0.20265807211399078, 0.319793701171875, 0.20786486566066742, -0.031938180327415466, 0.39481446146965027, -0.4076729416847229, -0.012292216531932354, 0.06139978766441345, -0.1133381798863411, 0.11826863139867783, -0.26808810234069824, -0.37281879782676697, 0.2753088176250458, 0.029760580509901047, -0.23637713491916656, -0.22457554936408997, 0.4332253038883209, 0.44181928038597107, -0.22392655909061432, -0.19778744876384735, -0.06278547644615173, 0.2824154496192932, -0.17791134119033813, -0.28221625089645386, -3.696467399597168, 0.09930497407913208, -0.020224137231707573, -0.16470521688461304, 0.051399994641542435, 0.015241389162838459, 0.24704845249652863, 0.5489212870597839, 0.23210439085960388, 0.2920982837677002, -0.39115941524505615, 0.5940644145011902, 0.14547671377658844, -0.0793590396642685, 0.4241495728492737, 0.3795756995677948, -0.14699657261371613, -0.3002566397190094, -0.37505701184272766, 0.11543502658605576, 0.06334741413593292, 0.33299675583839417, -0.3384149372577667, 0.0250714011490345, -0.9351797103881836, -0.5134004950523376, 0.2764834761619568, -0.45260998606681824, -0.38459038734436035, -0.15402311086654663, -0.3558543622493744, 0.172806978225708, -0.20219311118125916, -0.46690088510513306, -0.10168567299842834, 0.6971023082733154, 0.4462471902370453, -0.05173887312412262, 0.4743482768535614, 0.2140624225139618, 0.2110394686460495, 0.384102463722229, 0.10987616330385208, 0.47687962651252747, -0.2804393470287323, 0.43962404131889343, 0.34882503747940063, 0.6389044523239136, 0.47820618748664856, -0.1792471557855606, 0.56997150182724, -0.631828248500824, -0.017589520663022995, 0.613401472568512, 0.38694730401039124, -0.5259261727333069, 0.36121314764022827, -0.3741993010044098, 0.49370256066322327, -0.2572889029979706, 0.06305202096700668, -0.30745798349380493, 0.04347725212574005, -2.4074347019195557, 0.0882459208369255, 0.38753271102905273, -0.3620782196521759, -0.4044937789440155, -0.086432084441185, 0.35269641876220703, 0.39713236689567566, 0.07927412539720535, -0.12006058543920517, -0.25681737065315247, 0.2857944369316101, 0.41112685203552246, -0.3112160861492157, -0.3308778703212738, -0.28395599126815796, -0.1388440728187561, -0.11285842955112457, 0.42780426144599915, 0.1563323736190796, 0.2823012173175812, 0.27183815836906433, 0.07669630646705627, -0.3841134011745453, 0.004862531553953886, -0.12286245077848434, 0.06831440329551697, 0.544411301612854, 0.058034393936395645, -0.2718632221221924, -0.20909354090690613, -0.3635324537754059, -0.5932034254074097, -2.5325310230255127, -0.0030824716668576, 0.8312853574752808, 0.12743036448955536, 0.32375624775886536, 0.25943511724472046, 0.1523914784193039, 0.03399832919239998, 0.5035567879676819, 0.22979222238063812, -0.027896519750356674, -0.09236684441566467, -0.006763062439858913, -0.19765719771385193, -0.2903412878513336, -0.0861407220363617, -0.09362542629241943, 0.9374549984931946, 0.0734238550066948, -0.25667014718055725, -0.0667235255241394, -0.31604257225990295, -0.6730676293373108, 0.06589431315660477, 0.2754463255405426, 0.4521466791629791, -0.08652812987565994, 0.4363481104373932, 0.13948841392993927, 0.4207761883735657, -0.0018414967926219106, -0.11634870618581772, 0.5757362246513367, 0.4971311390399933, -0.27161526679992676, 0.31680622696876526, 0.0190989151597023, 0.24930469691753387, -0.5877533555030823, 0.4603472352027893, 0.14958424866199493, 0.0681670755147934, 0.4968147873878479, -0.47369909286499023, 0.3876188099384308, -0.12148706614971161, -0.30362468957901, 0.1318628489971161, -0.22058644890785217, -0.5055091381072998, 0.008032363839447498, -0.11335457861423492, 0.7467382550239563, -0.10647514462471008, 0.27153465151786804, -0.04909215867519379, 0.18612231314182281, -0.15034453570842743, -0.5143165588378906, -0.36570367217063904, -0.6257877349853516, -0.08871167153120041, -0.8129240274429321, 3.673008918762207, 0.1763017624616623, 0.11227796226739883, 0.12820006906986237, -0.18974155187606812, -0.11153152585029602, -0.5561449527740479, -0.3794626295566559, -0.18178348243236542, -0.1312021017074585, 0.05325375497341156, 0.3944082260131836, 0.011455285362899303, -0.316251665353775, -0.10950294882059097, 0.0019636943470686674, -0.05015924200415611, -0.0629233568906784, 0.3487214148044586, -0.13478562235832214, 0.29861709475517273, 0.10145348310470581, 0.5848790407180786, 0.3587322235107422, -1.5059393644332886, 0.2214469462633133, 0.15175007283687592, -0.3839396834373474, 0.14650294184684753, -0.5797526240348816, 0.04128348454833031, -0.19505436718463898, -0.2961989939212799, 0.04734743759036064, -0.2055554986000061, 0.03723827376961708, 0.1372828483581543, -0.41395631432533264, 0.19415950775146484, -0.15246200561523438, 0.14697137475013733, 0.10289189964532852, -0.002194708678871393, 0.055345434695482254, -0.18448488414287567, 0.20427380502223969, 0.32492223381996155, 0.085167296230793, -0.06968428194522858, 0.15424124896526337, 0.19784048199653625, 0.060779307037591934, 0.19837512075901031, -0.3274737000465393, -0.6548078060150146, -0.5333268642425537, 0.13945350050926208, -0.1042582243680954, -0.008325903676450253, -0.7836369872093201, -0.3624768853187561, -0.13272856175899506, 0.10060890018939972, -0.205177903175354, -0.08060408383607864, 0.1398048847913742, -0.20647786557674408, -0.41628938913345337, -3.3893353939056396, -0.3018982410430908, -0.2414402961730957, 0.7955111861228943, 0.48067644238471985, -0.23767124116420746, -0.03038065880537033, 0.22075451910495758, 0.12400282174348831, -0.594622790813446, 0.1395275592803955, 0.11348983645439148, -0.0975085198879242, 0.2524268329143524, -0.48128828406333923, 0.391159325838089, 0.3625582158565521, -0.6541886925697327, 0.12622030079364777, -0.27692002058029175, -0.47813546657562256, 0.17561115324497223, 0.1833016276359558, -0.012350286357104778, 0.01354921329766512, 0.15701574087142944, -0.14294478297233582, -0.18920695781707764, -0.061555638909339905, -0.17943954467773438, 0.04458359628915787, -0.2067996710538864, 0.0641891285777092, 0.07446994632482529, -0.1008085235953331, -3.1992855072021484, 0.272607684135437, -0.2763613164424896, -0.023357149213552475, 0.07308025658130646, -0.24741558730602264, 0.5851549506187439, -0.03361668437719345, -0.4530161917209625, 0.16449818015098572, -0.3350229561328888, -0.24157916009426117, -0.021109331399202347, 0.3132995367050171, 0.2593965530395508, 0.2499079555273056, 0.9010518193244934, -0.5046136975288391, 0.02547954022884369, 0.28282374143600464, -0.0163206085562706, -0.1936105340719223, -0.4061729311943054, 0.011261433362960815, 0.11910688132047653, -0.009831966832280159, -0.9060623049736023, -0.22339889407157898, -0.25462430715560913, 0.11714929342269897, 0.16696181893348694, -0.5750560164451599, 0.06263349205255508, -0.6470127701759338, -0.42767468094825745, -0.25672438740730286, -0.24050574004650116, 0.2424718141555786, -0.23735585808753967, -0.1185084730386734, -0.4869176149368286, 0.7928051948547363, -0.09018710255622864, 0.4362715184688568, 0.6208149790763855, 0.8504171371459961, -0.017634455114603043, -0.3060264587402344, 0.20576581358909607, 0.13028675317764282, -0.042876940220594406, 0.21613910794258118, 1.3655304908752441, 0.1300966888666153, -0.19671384990215302, -0.02582373470067978, 0.5027866363525391, -0.06653540581464767, -0.09642459452152252, 0.07619372755289078, 0.8615004420280457, -0.12754857540130615, -0.016102446243166924, 0.2099974900484085, 0.3678458034992218, -0.7997581958770752, 0.09119483083486557, -0.4648267328739166, 0.10828909277915955, -0.012330853380262852, -0.12777355313301086, 0.795565664768219, -0.3831164538860321, -1.054460048675537, -0.01835162565112114, -0.23369865119457245, -0.1905151903629303, 0.005647051148116589, 0.2655761241912842, 0.12324148416519165, -0.31063029170036316, 0.11920303851366043, -0.19938340783119202, 0.31033772230148315, -0.3294163644313812, -0.566673219203949, 0.19992470741271973, 0.8395111560821533, -0.9055247902870178, 0.009609801694750786, 0.08611392974853516, 0.1997000277042389, 0.10000529885292053, -0.01419799029827118, 0.18233230710029602, -0.19902990758419037, 0.2880786657333374, -0.5660990476608276, 0.35698458552360535, 0.0024891335051506758, -0.21776163578033447, -0.46925732493400574, -0.5318843126296997, -0.13970081508159637, -0.203237384557724, -0.08382008969783783, 0.12083049863576889, 0.7889566421508789, 0.2005004584789276, 0.16089417040348053, -0.10365988314151764, -0.03783624991774559, -0.17084552347660065, 0.4103759825229645, 1.475965976715088, 0.0009635772439651191, 0.03913524001836777, 0.7930187582969666, 0.4511229395866394, -0.11315815150737762, 0.5832633376121521, 0.5744290947914124, 0.009431323036551476, -0.10753864049911499, -0.663423478603363, 0.43029075860977173, 0.2565060257911682, 0.212882399559021, -0.7285080552101135, -0.354900062084198, 0.20551571249961853, -0.27998021245002747, -0.2919561266899109, -0.5453024506568909, -0.3249351978302002, -0.4148962199687958, 0.06490852683782578, 0.6329025030136108, -0.22006122767925262, -0.26968714594841003, 0.4252629578113556, -0.025134647265076637, -0.07884590327739716, -0.13681535422801971, -0.11183390021324158, 0.16403967142105103, -0.06005838140845299, 0.17589589953422546, -0.04997941106557846, 0.07099418342113495, 0.16786623001098633, 0.010234322398900986, 0.15275710821151733, -0.3239723742008209, 0.2112845480442047, -0.039319660514593124, 0.11027312278747559, 0.08541732281446457, -0.05609297752380371, -0.4210382103919983, 0.13660351932048798, 0.24491214752197266, -2.219417095184326, 0.23231633007526398, 0.8863052725791931, 0.18479664623737335, 0.14952538907527924, -0.4593181014060974, -0.20030958950519562, 0.8153230547904968, 0.00446052523329854, 0.16535808145999908, -0.5127701759338379, -0.07470846176147461, -0.02860805206000805, -0.34120050072669983, 0.16828881204128265, -0.3787230849266052, 0.11571339517831802, -0.27152177691459656, -0.15100513398647308, 0.1625632345676422, -0.06199382618069649, 0.22042053937911987, 0.0311698280274868, -0.16059555113315582, 0.012640452943742275, -0.14930661022663116, -0.34811750054359436, 0.13606904447078705, 0.04766314476728439, 0.38973891735076904, -0.16828037798404694, -0.3740536868572235, -0.7766481041908264, 0.43303096294403076, -0.15905526280403137, -0.03401380032300949, 0.15901847183704376, -0.07785799354314804, -0.055965717881917953, 0.56531822681427, -0.20526693761348724, 0.18942710757255554, 0.501143217086792, -0.2307361662387848, 0.22818772494792938, 0.32656329870224, -0.7319201231002808, 0.576629102230072, -0.21656343340873718, -0.1863958239555359, -0.4669986069202423, 0.027265232056379318, -0.4048710763454437, -0.5287598967552185, 0.10828272998332977, -0.3647140860557556, -0.17329643666744232, 0.44133105874061584, -0.1940883994102478, -0.19335545599460602, 0.18238478899002075, 0.003585120663046837, -0.047170720994472504, -0.1275133341550827, -0.4184320271015167, -0.7598668336868286, -0.01278669573366642, -0.2941482663154602, -0.42020097374916077, 0.31877845525741577, 0.570563554763794, 0.2659410238265991, -0.8291407823562622, 0.5322614312171936, -0.2022923231124878, 0.49849000573158264, -0.22524163126945496, -0.26747968792915344, 0.20835380256175995, -0.32061105966567993, -0.2352929711341858, -0.14368270337581635, 0.4589315950870514, 0.532183825969696, -0.15232780575752258, 0.1810203641653061, -0.3576136529445648, -0.27472442388534546, -0.4720928370952606, -0.021249545738101006, -0.5275289416313171, -0.10177208483219147, 0.29514607787132263, 0.35741591453552246, 0.18668995797634125, -0.4232368767261505, -0.19718137383460999, -0.10930082201957703, -0.11375024914741516, -0.3414000868797302, 0.2220793068408966, 0.18260160088539124, 0.3379100263118744, -0.003380382200703025, 0.015099301934242249, 0.44186997413635254, 0.7246592044830322, -0.36664918065071106, -0.06265102326869965, -0.03836483880877495, 0.1541697084903717, -0.28639480471611023, -0.09615515172481537, -0.05599270761013031, 0.20962214469909668, -0.1154228150844574, 0.3236592411994934, -0.30802470445632935, 2.2225186824798584, 0.03873731195926666, 0.044289905577898026, -0.24392443895339966, 0.5354986786842346, 0.17621682584285736, 0.4749871492385864, 0.2584134638309479, -0.09314362704753876, -0.16892372071743011, -0.7208344340324402, -0.18166965246200562, 0.37277981638908386, 0.2137727439403534, 0.5482630133628845, 0.6568142175674438, 0.3354342579841614, -0.1975754350423813, -0.18879418075084686, 0.08812780678272247, -0.21680162847042084, 0.4968719482421875, 0.22064290940761566, 0.13438118994235992, 0.11443959921598434, 0.15704511106014252, 0.06657269597053528, 0.3099276125431061, 0.0719817653298378, 0.43433836102485657, -0.2825601100921631, 0.05073036998510361, 0.3266025483608246, 0.2232370376586914, -0.2582411766052246, 0.13091963529586792, 0.12089617550373077, -0.269685834646225, 0.15269602835178375, -0.030418530106544495, -0.2334624081850052, -0.20775221288204193, 0.29403334856033325, 0.09687276184558868, -0.028538363054394722, 0.6211109757423401, -0.05764901265501976, -0.21066372096538544, 0.29420384764671326, 0.4262631833553314, -0.09438266605138779, 0.6090142130851746, -0.33086079359054565, 0.027625491842627525, 0.03131698817014694, -0.294237345457077, 0.06065214052796364, -0.058599408715963364, 0.13114824891090393, 0.7189412713050842, -0.1344851404428482, 0.22545847296714783, 0.30877867341041565, -0.40160927176475525, -0.047693103551864624, 0.010270528495311737, -0.7249788641929626, 0.4471171200275421, -0.27925413846969604, -0.16218657791614532, 0.05678965151309967, -0.02148982509970665, 0.4212009012699127, 0.6093279719352722, 0.5422093272209167, -0.22395282983779907, 0.7373961806297302, 0.09964161366224289, -0.4602838456630707, -2.687702178955078, 0.07978160679340363, -0.3192049562931061, 0.5629061460494995, 0.022757673636078835, 0.7379239797592163, 0.3091801702976227, -0.036802586168050766, -0.07012411952018738, 0.09006116539239883, 0.3335999548435211, 0.3707146942615509, 0.31818389892578125, 0.3150925636291504, 0.010741278529167175, 0.4883314073085785, 0.28737813234329224, -0.19577668607234955, -0.1916123777627945, -0.04244783893227577, 0.056658852845430374, -0.0012057751882821321, 0.0557929165661335, -0.15553048253059387, -0.5195225477218628, -0.00843470823019743, 0.396884024143219, -0.12409604340791702, 0.2242678701877594, 0.39628085494041443, -0.07304814457893372, 0.306580513715744, 0.11318905651569366, 0.2223013937473297, 0.2760148346424103, -0.1805783212184906, 0.17438679933547974, -0.07212711870670319, 0.15469785034656525, 0.01249408908188343, -0.30213838815689087, 0.6432240605354309, -0.004431987181305885, -0.043395694345235825, 0.024972669780254364, -0.41915205121040344, 0.022293372079730034, 0.044443223625421524, 0.3298669457435608, -0.2582758367061615, -0.11445178836584091, 0.026392413303256035, -0.40626099705696106, 0.5113366842269897, 0.5698051452636719, 0.155767560005188, 0.6789791584014893, 0.3114379346370697, 0.1236715018749237, -0.4538944363594055, 0.3969848155975342, 0.14517126977443695, -0.2121189534664154, -0.11214695125818253, 0.2137015163898468, -0.4672533869743347, -0.2686099708080292, 0.48774024844169617, -0.35976558923721313, -0.4016030728816986, 0.04023532569408417, -0.3007107377052307, 0.5288698673248291, 0.42736533284187317, 0.3238085210323334, 0.27000588178634644, -0.06233211234211922, 0.4110391139984131, 0.6692153215408325, 0.01043714489787817, -0.24757681787014008, -0.051102958619594574, -0.1775573045015335, 0.25110870599746704, 0.47663363814353943, -6.563918113708496, -0.14744117856025696, -0.33199557662010193, -0.10524290800094604, 0.16988436877727509, 0.09174960106611252, -0.5185513496398926, -0.026354284957051277, -0.3944922685623169, -0.2504107356071472, 0.0012664999812841415, 0.29851746559143066, 0.2072037309408188, -0.4543539881706238, 0.22656023502349854, 0.36570286750793457]</t>
+          <t>['high', 'high', 'medium', 'medium', 'high', 'high']</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 1.0, 0.5, -0.5, -1.0]</t>
+          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[4, 5, 3, 4, 3, 4]</t>
+          <t>[40.0, 45.0, 30.0, 35.0, 35.0, 45.0]</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
+          <t>['woman', 'man', 'man', 'woman', 'woman', 'woman']</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>[35.0, 45.0, 35.0, 40.0, 45.0, 25.0]</t>
+          <t>[1, 1, 4, 1, 1, 1]</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>['man', 'man', 'man', 'man', 'woman', 'man']</t>
+          <t>[5, 5, 1, 5, 5, 5]</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>[1, 1, 5, 5, 1, 1]</t>
+          <t>[5, 4, 4, 5, 5, 3]</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>[4, 5, 1, 1, 4, 4]</t>
+          <t>[4, 4, 5, 5, 4, 3]</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>[5, 5, 2, 2, 4, 5]</t>
+          <t>[1, 1, 5, 3, 1, 1]</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>[4, 4, 5, 5, 4, 5]</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>[1, 1, 5, 3, 1, 1]</t>
-        </is>
+          <t>[1, 1, 1, 1, 4, 1]</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>6</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>[5, 5, 4, 2, 5, 5]</t>
+          <t>[5, 4, 2, 2, 5, 4]</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>[5, 5, 2, 3, 5, 5]</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>[0.         0.16666667 0.16666667 0.         0.66666667]</t>
-        </is>
-      </c>
-      <c r="T14" t="n">
-        <v>0.25</v>
+          <t>[0.         0.33333333 0.         0.33333333 0.33333333]</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>444</v>
+        <v>521</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>We horny niggas matter too!!</t>
+          <t>doesnt matter if straights r oppressed or not sayin u hate all of them even if you dont mean it is as bad as homophobes sayin they hate gays</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[5, 2, 1, 2, 2, 4]</t>
+          <t>[2, 1, 4, 2, 2, 2]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[4, 2, 2, 2, 2, 4]</t>
+          <t>[nan, '{}', '{}', 'none', '{}', '{}']</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>['{}', '{}', nan, '{}', 'none', '{}']</t>
+          <t>['left', 'left', 'center', 'right', 'left', 'far left']</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>[0.2703861892223358, 0.38602450489997864, 0.14386431872844696, -0.3571215271949768, -0.5761386752128601, -0.24539677798748016, 0.7371736764907837, 0.601039469242096, 0.11333305388689041, -0.2087414562702179, 0.025113938376307487, 0.3950401544570923, -0.22132301330566406, 0.3234716057777405, 0.2086249738931656, 0.15746723115444183, -0.06873895972967148, 0.14266180992126465, 0.27739739418029785, 0.16800802946090698, 0.10292147099971771, 0.025911513715982437, 0.15653440356254578, -0.14961440861225128, -0.039633918553590775, -0.12924441695213318, 0.40467318892478943, -0.2940288186073303, -0.1807904839515686, 0.5419406294822693, -0.01095113530755043, 0.4774540960788727, -0.17790305614471436, -0.013648281805217266, -0.06760445237159729, 0.2735709846019745, -0.025326881557703018, 0.270145446062088, 0.38664913177490234, -0.000425580918090418, -0.32873010635375977, -0.18037712574005127, -0.025117143988609314, -0.01938767544925213, -0.15868955850601196, -0.73309326171875, -2.9600822925567627, -0.09845585376024246, -0.3902573585510254, -0.11118452250957489, 0.30642858147621155, -0.1429290920495987, -0.06171834468841553, 0.21904821693897247, 0.05265960469841957, 0.09038268774747849, -0.7172331809997559, 0.3056493103504181, -0.10548882186412811, -0.10542245209217072, 0.5042223334312439, 0.1478179544210434, 0.011913444846868515, 0.41443929076194763, 0.074620820581913, -0.11626338213682175, 0.16665875911712646, 0.7330201268196106, -0.4026815891265869, 0.5137374401092529, -0.4791446030139923, -0.14992502331733704, 0.35837119817733765, 0.1706274449825287, -0.22688478231430054, -0.04403672367334366, 0.01658414676785469, 0.3154717683792114, -0.3959670066833496, -0.14525222778320312, 0.037865445017814636, 0.20354719460010529, 0.2180696576833725, 0.12278120964765549, -0.2935590445995331, 0.1565813571214676, -0.12873566150665283, -0.2640469968318939, 0.05920058861374855, 0.29474613070487976, -0.2625013291835785, 0.151821106672287, 0.17360322177410126, 0.29676395654678345, 0.7192999720573425, -0.050297193229198456, 0.35987234115600586, -0.07665054500102997, 0.09890513867139816, 0.3369695544242859, 0.6286364197731018, -0.15798641741275787, 0.2698814868927002, -0.8984432816505432, 0.11112416535615921, -0.06446568667888641, 0.18022793531417847, -0.17659306526184082, 0.3021729588508606, -2.617293357849121, 0.07660701125860214, 0.06287913024425507, -0.29668283462524414, -0.3931269645690918, -0.035551656037569046, 0.4028995931148529, 0.44843730330467224, 0.029489021748304367, 0.5072569251060486, -0.06029808148741722, -0.025243792682886124, 0.5950233340263367, 0.26745519042015076, 0.25212493538856506, -0.08650220185518265, 0.5295935869216919, -0.2603590190410614, 0.10577157139778137, 0.20554199814796448, 0.3883713483810425, 0.35262763500213623, 0.4690898060798645, 0.130853071808815, -0.7178743481636047, -0.15283572673797607, -0.014696028083562851, 0.24274615943431854, -0.03985977545380592, 0.14824838936328888, -0.3539113402366638, -0.4060618579387665, -0.4838709533214569, -2.911996364593506, 0.2382703721523285, 0.4663756191730499, -0.07472607493400574, -0.7070890069007874, -0.16377782821655273, -0.2683568298816681, -0.1267419010400772, -0.13262805342674255, -0.3600592613220215, 0.1663849651813507, -0.25046005845069885, 0.010087085887789726, -0.14995110034942627, -0.5259946584701538, -0.28343477845191956, 0.19579921662807465, 0.8973196744918823, 0.2703540027141571, -0.35874035954475403, -0.18485087156295776, -0.3250437080860138, -0.5008929371833801, -0.45494192838668823, 0.12335017323493958, 0.27354899048805237, -0.018396778032183647, -0.06485994905233383, 0.03683583065867424, -0.10030780732631683, 0.8436181545257568, 0.43802347779273987, 0.5045539140701294, 0.014681435190141201, 0.3254319727420807, -0.10584001243114471, -0.2769887447357178, 0.2161606103181839, -0.6090186238288879, 0.6227737069129944, 0.21014849841594696, 0.0730847418308258, 0.6345540881156921, -0.18673621118068695, 0.6903137564659119, -0.3778967559337616, 0.11077222228050232, 0.2230573147535324, -0.03683730587363243, -0.6226933598518372, 0.5399707555770874, -0.09233147650957108, 0.40745046734809875, -0.2697887420654297, -0.12024789303541183, -0.31593385338783264, 0.34416234493255615, 0.09363605082035065, 0.16834311187267303, -0.25730615854263306, 0.224240243434906, 0.06605954468250275, -0.7492491006851196, 4.158207416534424, 0.37448087334632874, 0.20344775915145874, -0.01560549158602953, -0.0038406290113925934, -0.366127073764801, 0.09530851989984512, -0.03793010860681534, -0.27494335174560547, -0.3345944881439209, 0.36568525433540344, 0.5203796029090881, 0.05249159410595894, 0.06038890779018402, -0.04708322137594223, 0.4832433760166168, -0.08765289932489395, -0.4144390821456909, -0.10404640436172485, -0.14187350869178772, -0.05636485293507576, 0.12246251851320267, 0.12586812674999237, 0.38736289739608765, -1.6816627979278564, 0.1189403384923935, -0.15189704298973083, -0.2217377871274948, 0.638088047504425, -0.3919687569141388, 0.33256858587265015, 0.005288140848278999, 0.07702583074569702, -0.0849180743098259, 0.1054740771651268, 0.21758119761943817, 0.37276145815849304, 0.24112994968891144, 0.33963415026664734, -0.3591594099998474, 0.2366473525762558, 0.417080819606781, -0.3768501877784729, -0.007947152480483055, 0.07404062151908875, 0.14568203687667847, 0.0019365146290510893, -0.03780009225010872, -0.6629248857498169, 0.2369903028011322, -0.002038580598309636, 0.10126841068267822, 0.16160154342651367, -0.014064719900488853, -0.28913015127182007, -0.2032046914100647, -0.3987119793891907, -0.013982150703668594, 0.1359647661447525, -0.5073038935661316, -0.4858466684818268, 0.3165426552295685, 0.17308871448040009, -0.29002898931503296, -0.20145942270755768, 0.15524733066558838, 0.2673306167125702, -0.17122100293636322, -3.3724281787872314, 0.242027148604393, 0.14683985710144043, 0.6019139289855957, 0.08841946721076965, -0.5425468683242798, -0.24112610518932343, -0.004333406686782837, 0.4136855900287628, -0.21119946241378784, -0.04604480415582657, 0.24593324959278107, 0.2066216766834259, 0.5690956115722656, 0.15773005783557892, 0.3733106553554535, 0.3935825824737549, -0.2797715365886688, -0.2308458834886551, -0.35463565587997437, -0.05884106084704399, 0.2904087007045746, -0.06135464832186699, 0.21703793108463287, 0.3423326909542084, -0.13688994944095612, -0.15828441083431244, -0.08833036571741104, 0.2515401542186737, -0.3624122440814972, 0.06904710084199905, 0.05379074439406395, -0.10627340525388718, -0.08706336468458176, -0.003483978332951665, -3.156571865081787, 0.171918123960495, -0.39731281995773315, -0.0725681483745575, -0.2173452228307724, -0.13219410181045532, 0.06582903116941452, -0.2025788128376007, -0.6402440071105957, 0.03376078978180885, -0.10478676855564117, 0.09928712993860245, 0.26148754358291626, 0.32450443506240845, 0.2258642166852951, -0.176371768116951, 0.6863348484039307, -0.37615740299224854, 0.5599316954612732, -0.10257450491189957, 0.05524706095457077, -0.1056532934308052, -0.014924481511116028, 0.09140576422214508, 0.20525002479553223, 0.5023828744888306, -0.19948948919773102, -0.2093942016363144, -0.11912873387336731, -0.1017782986164093, -0.17626504600048065, -0.18175475299358368, 0.07681785523891449, 0.1641446202993393, -0.3412761092185974, -0.344188928604126, -0.01954837143421173, -0.08366164565086365, 0.15270479023456573, -0.17247374355793, 0.31170785427093506, 0.31444063782691956, 0.4526441693305969, 0.266028493642807, 0.5207197070121765, -0.1274784505367279, -0.23878861963748932, -0.40695565938949585, 0.019741559401154518, 0.039165742695331573, -0.14836351573467255, -0.4886574447154999, 1.1239277124404907, -0.21570469439029694, -0.03051530197262764, -0.34497812390327454, 0.35818880796432495, 0.4432235062122345, 0.6174136996269226, -0.0007744397735223174, 0.9210309982299805, 0.02181912399828434, 0.321490615606308, 0.02695736661553383, -0.4019032418727875, -0.20786556601524353, 0.1433037966489792, -0.5968317985534668, 0.029958561062812805, 0.1465313881635666, -0.06280003488063812, 0.3893885016441345, -0.6327255964279175, -0.7180533409118652, -0.02202899008989334, 0.2980465292930603, -0.22641690075397491, 0.03838282451033592, -0.14194148778915405, 0.39033761620521545, 0.08840125799179077, -0.027014359831809998, -0.581342875957489, 0.45936018228530884, -0.5232411623001099, -0.3933405876159668, 0.06684162467718124, -0.004168698098510504, -0.36705711483955383, 0.30951055884361267, -0.1682242751121521, 0.041580747812986374, -0.27930381894111633, 0.25852125883102417, 0.043258585035800934, 0.20987661182880402, 0.31361618638038635, -0.6454787850379944, 0.3783837556838989, -0.3348671495914459, -0.4790610373020172, -0.11525975167751312, 0.173796609044075, 0.0035063314717262983, -0.34484001994132996, -0.2204204648733139, -0.193144753575325, 0.5648218393325806, 0.018501969054341316, 0.23114308714866638, 0.13533295691013336, 0.00779162859544158, -0.036451950669288635, 0.2869262397289276, 0.7547851800918579, -0.033201370388269424, 0.16980130970478058, 0.5411356091499329, 0.126584991812706, -0.014670013450086117, 0.10049104690551758, 0.2789362967014313, -0.41725996136665344, -0.2397182732820511, 0.1698319911956787, -0.07180742174386978, 0.24269506335258484, -0.22793594002723694, -0.1290903240442276, -0.34525829553604126, 0.11008131504058838, -0.45444804430007935, -0.08898355066776276, -0.5065240859985352, -0.2937858998775482, -0.34112030267715454, -0.23040388524532318, 0.3350762128829956, -0.010704531334340572, 0.061111755669116974, 0.7194722890853882, 0.09683936089277267, 0.022159628570079803, 0.48047882318496704, -0.514967143535614, 0.5247077941894531, -0.4029597342014313, 0.1505192369222641, -0.18883758783340454, 0.8878018260002136, -0.27157503366470337, -0.2618495523929596, 0.05806220695376396, -0.37118980288505554, 0.141016885638237, 0.2642214298248291, 0.06374849379062653, 0.24096158146858215, 0.04244537279009819, -0.3858363628387451, -0.11558655649423599, -0.07335290312767029, -1.6753062009811401, 0.6211515665054321, 0.5789393782615662, 0.016929028555750847, 0.3537445664405823, -0.29610344767570496, -0.8624245524406433, 0.5980072021484375, -0.07037920504808426, -0.15050897002220154, -0.36480996012687683, 0.43178585171699524, 0.1515064835548401, -0.37390708923339844, 0.24335765838623047, -0.012245372869074345, 0.22130174934864044, -0.3862023651599884, -0.04023263603448868, 0.18863627314567566, -0.11850251257419586, 0.18150123953819275, 0.11983376741409302, -0.10440357029438019, -0.2795829772949219, -0.5246668457984924, 0.04942721873521805, 0.6773599982261658, -0.11035159230232239, 0.5463586449623108, 0.11849918961524963, -0.5583316683769226, -0.5307141542434692, -0.2898993194103241, 0.458506315946579, 0.033161841332912445, 0.09214658290147781, 0.44101443886756897, 0.7569868564605713, 0.29156190156936646, 0.1311047375202179, 0.03672156110405922, 0.16769888997077942, 0.02031705528497696, 0.3307800889015198, 0.18909622728824615, -0.4931144118309021, 0.4282836616039276, 0.17212969064712524, -0.5908036828041077, -0.37996238470077515, 0.12072480469942093, -0.39140236377716064, -0.3508935868740082, 0.036457981914281845, -0.09594620764255524, -0.08387411385774612, -0.19127482175827026, -0.39344078302383423, -0.20712192356586456, -0.045604005455970764, 0.32801342010498047, -0.7823301553726196, -0.07768093794584274, -0.7564622759819031, -0.4598240256309509, 0.2195192277431488, -0.5204946994781494, 0.08529595285654068, 0.43372929096221924, 0.5092770457267761, 0.5694820880889893, -0.37642404437065125, 0.3316726088523865, -0.33817264437675476, 0.5070784687995911, 0.13490840792655945, 0.308908075094223, 0.23646359145641327, -0.502354621887207, 0.24007906019687653, -0.1815994679927826, -0.28773343563079834, 0.20120929181575775, -0.08341706544160843, 0.1528986394405365, -0.03395857289433479, -0.03947848081588745, 0.0703536868095398, -0.03872715309262276, -0.6202741861343384, -0.4521092474460602, 0.25660648941993713, -0.11316271126270294, -0.14442141354084015, 0.1512974500656128, 0.09000636637210846, 0.00023498208611272275, -0.2528752088546753, 0.322682648897171, -0.3142909109592438, 0.11249230802059174, 0.44092512130737305, 0.16306179761886597, 0.22219687700271606, 0.24283865094184875, 0.35557693243026733, 0.7415138483047485, -0.8176921606063843, -0.27890345454216003, -0.2638511657714844, 0.3283248841762543, 0.03944462537765503, -0.004560477565973997, 0.1387237012386322, -0.5911491513252258, 0.30744868516921997, -0.3310900032520294, 2.3247034549713135, 0.6538443565368652, 0.3477884531021118, -0.15887939929962158, 0.5320207476615906, -0.025065921247005463, -0.17359429597854614, -0.23983627557754517, -0.2689885199069977, 0.5706744194030762, -0.1587410420179367, -0.007946575991809368, 0.32313987612724304, 0.3839522898197174, 0.42004236578941345, 0.35326051712036133, 0.14751742780208588, -0.5830652713775635, -1.175637125968933, -0.20000766217708588, -0.32068100571632385, -0.26150280237197876, 0.44223305583000183, -0.057110145688056946, -0.0976821631193161, -0.14719773828983307, -0.03914819285273552, 0.2883463203907013, 0.20543617010116577, 0.6169496774673462, -0.14611950516700745, -0.4050041139125824, 0.3628854751586914, 0.17466479539871216, -0.25077977776527405, 0.4058045744895935, 0.08558737486600876, -0.3184027373790741, -0.15084505081176758, 0.06729770451784134, 0.5550144910812378, -0.25782543420791626, 0.6537365913391113, 0.3975425660610199, 0.4201667308807373, 0.46557366847991943, 0.11597089469432831, -0.22403539717197418, 0.7934178113937378, 0.5592066049575806, -0.37396925687789917, -0.06606115400791168, -0.24465033411979675, 0.2947409749031067, 0.08412808179855347, -0.4662749469280243, 0.04846911132335663, -0.36906811594963074, -0.4289205074310303, 0.38618800044059753, 0.047873593866825104, 0.08592633157968521, 0.20586293935775757, -0.2031582146883011, -0.08045044541358948, 0.19769346714019775, -0.40907394886016846, -0.14017362892627716, 0.2224290668964386, -0.5737417340278625, -0.3307346701622009, 0.41140368580818176, -0.00614906707778573, -0.13350149989128113, 1.1088517904281616, 0.14151595532894135, -0.013095051981508732, -0.06922703981399536, -0.25575947761535645, -2.82375168800354, 0.32266896963119507, 0.26470351219177246, 0.16612021625041962, -0.09131370484828949, 0.37647897005081177, 0.17650975286960602, -0.26419442892074585, 0.09909451752901077, -0.5256055593490601, 0.24603168666362762, 0.6135826706886292, 0.2284911572933197, 0.3228275179862976, 0.05447806417942047, -0.2445993274450302, 0.29458147287368774, -0.44357916712760925, -0.40021634101867676, -0.26783785223960876, -0.16074706614017487, 0.023142218589782715, -0.2275691032409668, -0.5704769492149353, 0.0006373431533575058, 0.5724309682846069, -0.028656240552663803, -0.4307388663291931, 0.2336197793483734, 0.05846089869737625, 0.05642017349600792, -0.03220620006322861, -0.16889943182468414, -0.5406980514526367, -0.15881390869617462, 0.39534205198287964, -0.3245457410812378, 0.013079141266644001, 0.4062722623348236, -0.1520046442747116, 0.05466736480593681, 0.8457476496696472, -0.02541254088282585, 0.29798027873039246, -0.11918839812278748, -0.4002818763256073, -0.0010972341988235712, -0.21958699822425842, 0.21010296046733856, -0.13962286710739136, 0.44941040873527527, 0.05930712819099426, 0.23596857488155365, -0.23219415545463562, 0.639024019241333, 0.18085581064224243, -0.13532108068466187, 0.10579728335142136, 0.10892248898744583, -0.3817426562309265, -0.4205513000488281, -0.22942863404750824, -0.2107570767402649, -0.15589581429958344, -0.07837095856666565, -0.5324995517730713, 0.292819619178772, 0.12334021180868149, -0.24838382005691528, -0.160284623503685, 0.20530186593532562, -0.16368435323238373, 0.6904869079589844, 0.527715265750885, -0.16201016306877136, -0.1111883670091629, 0.2442317008972168, 0.20691558718681335, -0.05488637834787369, -0.24257467687129974, -0.11010152846574783, 0.46040982007980347, -0.08746062219142914, 0.292173832654953, -0.01850995421409607, -6.839569091796875, -0.5703526735305786, -0.2438323199748993, -0.08140864223241806, -0.16292639076709747, -0.11431260406970978, -0.09377098828554153, -0.3155216574668884, -0.14053989946842194, -0.50955730676651, 0.18254590034484863, -0.03490336611866951, -0.2968553304672241, -0.3649541139602661, 0.3515074849128723, 0.11844953894615173]</t>
+          <t>['medium', 'high', 'high', 'high', 'medium', 'low']</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>[-0.5, 0.0, 1.0, 0.0, 0.0, -0.5]</t>
+          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[4, 4, 3, 5, 5, 5]</t>
+          <t>[30.0, 30.0, 30.0, 60.0, 45.0, 30.0]</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
+          <t>['man', 'man', 'man', 'woman', 'woman', 'man']</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>[40.0, 35.0, 35.0, 40.0, 45.0, 35.0]</t>
+          <t>[1, 1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>['woman', 'man', 'man', 'woman', 'woman', 'woman']</t>
+          <t>[3, 3, 4, 5, 4, 5]</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>[1, 1, 5, 1, 4, 1]</t>
+          <t>[1, 1, 4, 2, 1, 3]</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>[4, 4, 1, 5, 1, 5]</t>
+          <t>[5, 3, 4, 5, 4, 3]</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>[2, 2, 1, 2, 2, 1]</t>
+          <t>[1, 1, 3, 1, 1, 1]</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>[2, 4, 5, 5, 5, 4]</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>[1, 1, 5, 1, 3, 1]</t>
-        </is>
+          <t>[1, 1, 4, 2, 1, 1]</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>6</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 2, 3]</t>
+          <t>[2, 1, 4, 2, 2, 2]</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>[5, 2, 1, 2, 2, 4]</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>[0.16666667 0.5        0.         0.16666667 0.16666667]</t>
-        </is>
-      </c>
-      <c r="T15" t="n">
-        <v>0.3333333333333333</v>
+          <t>[0.16666667 0.66666667 0.         0.16666667 0.        ]</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>475</v>
+        <v>524</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Women are not fucking inferior to men</t>
+          <t>fuck black culture and its shitty ass values</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[1, 1, 4, 2, 1, 1]</t>
+          <t>[5, 5, 1, 5, 5, 5]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[2, 1, 4, 2, 1, 1]</t>
+          <t>['{}', '{}', nan, '{}', '{}', '{}']</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>['{}', '{}', nan, 'none', '{}', '{}']</t>
+          <t>['left', 'center', 'far right', 'center', 'far left', 'left']</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>[0.14752458035945892, 0.41403263807296753, -0.1459645926952362, 0.05109398812055588, -0.7411067485809326, -0.44831761717796326, 0.8362647294998169, 0.7996543645858765, -0.19007781147956848, -0.27704912424087524, 0.22516335546970367, 0.03815362602472305, -0.21686697006225586, 0.19015876948833466, 0.2782444655895233, 0.26355332136154175, -0.033347632735967636, 0.5373479723930359, 0.25757670402526855, 0.06388741731643677, -0.30573442578315735, -0.13608141243457794, -0.15212954580783844, 0.03574568033218384, 0.17960837483406067, 0.008200415410101414, 0.240830197930336, -0.3848094940185547, 0.06511449813842773, -0.22454293072223663, -0.012470065616071224, 0.4508902430534363, -0.22241359949111938, -0.27179214358329773, 0.34984228014945984, -0.06141919270157814, 0.2506597638130188, -0.036148786544799805, 0.36524438858032227, -0.045175425708293915, -0.06045079231262207, -0.16194242238998413, 0.12831534445285797, 0.1694827824831009, 0.02798093855381012, -0.23543760180473328, -2.593045711517334, -0.17884290218353271, 0.14270547032356262, -0.244166299700737, 0.22828097641468048, -0.09822092950344086, -0.07270509004592896, 0.5339207649230957, 0.2932871878147125, 0.3639346957206726, -0.5048637986183167, 0.44485440850257874, -0.14374804496765137, 0.3688129484653473, 0.4217480719089508, 0.14646616578102112, 0.005468596238642931, 0.022670980542898178, -0.10688214004039764, 0.11164774000644684, -0.1440117061138153, 0.38854363560676575, -0.5073153376579285, 0.45705536007881165, -0.8785630464553833, -0.43351083993911743, 0.6120684742927551, -0.31540897488594055, -0.2059265375137329, -0.20795467495918274, -0.21715493500232697, -0.10109014809131622, -0.23345986008644104, -0.4247363209724426, 0.008804742246866226, 0.6806690096855164, 0.1252410113811493, 0.008381394669413567, 0.08793095499277115, 0.5723599195480347, 0.2303880900144577, -0.21043966710567474, 0.26491281390190125, 0.4191892743110657, -0.17062252759933472, 0.48565229773521423, 0.35938552021980286, 0.43043574690818787, 0.513422429561615, -0.16890475153923035, 0.39884936809539795, -0.13579823076725006, 0.2584112286567688, 0.18720021843910217, 0.42194753885269165, -0.01834963448345661, 0.3928300142288208, -0.9062390327453613, 0.30784595012664795, -0.3553493022918701, 0.021619321778416634, -0.23911483585834503, 0.5582186579704285, -2.7657477855682373, 0.542418360710144, 0.1545345038175583, -0.15306346118450165, -0.018669333308935165, 0.0449366457760334, 0.6384401321411133, 0.257923424243927, -0.1922255903482437, 0.2762168049812317, 0.05170661211013794, -0.4086475074291229, 0.48647668957710266, -0.19565314054489136, 0.20805707573890686, -0.11375875771045685, 0.1440495103597641, 0.07415343075990677, 0.24261128902435303, 0.2765595316886902, 0.4647245705127716, 0.009582101367413998, 0.1160316988825798, 0.14222434163093567, -0.16644397377967834, 0.024781038984656334, -0.20889344811439514, 0.44158050417900085, -0.22147247195243835, -0.1878580003976822, -0.09701726585626602, -0.5461068749427795, -0.2761339545249939, -2.9693703651428223, -0.15338775515556335, 0.7159193754196167, 0.08707698434591293, 0.04307271167635918, -0.05634470283985138, 0.15360933542251587, 0.17284755408763885, 0.19259721040725708, 0.10234682261943817, 0.16171588003635406, -0.029188478365540504, -0.04546808823943138, -0.4173688590526581, -0.4959249496459961, -0.08528795838356018, 0.4566583037376404, 0.5939031839370728, -0.09932811558246613, -0.29432639479637146, 0.008498015813529491, -0.18387523293495178, -0.4907720685005188, -0.19576717913150787, 0.19204552471637726, 0.07215950638055801, 0.15475253760814667, -0.1424238085746765, 0.06123068928718567, 0.1383945196866989, 0.5459343194961548, 0.07317741215229034, 0.8427122235298157, -0.07940836995840073, -0.15060701966285706, 0.3705422282218933, -0.28166085481643677, 0.27359479665756226, -0.2137022763490677, 0.6270740628242493, 0.0021890103816986084, 0.05425407737493515, 0.47020694613456726, -0.35111409425735474, 0.12893283367156982, -0.2744652032852173, -0.30508580803871155, 0.5556841492652893, -0.05671653896570206, -0.46156933903694153, 0.31247004866600037, 0.2376909703016281, 0.5649405121803284, -0.22934387624263763, 0.17648428678512573, -0.7559360861778259, -0.31758520007133484, 0.2376292645931244, -0.5373263955116272, -0.33421874046325684, -0.6017025709152222, -0.07250510156154633, -0.6411972045898438, 4.040211200714111, 0.12392497807741165, -0.2533789575099945, 0.13413456082344055, 0.34771493077278137, 0.024260757490992546, -0.010931605473160744, -0.3653988242149353, -0.3945314288139343, -0.14682872593402863, -0.08512633293867111, 0.30753588676452637, 0.13751426339149475, -0.25425776839256287, -0.2819511890411377, 0.25284263491630554, 0.22959856688976288, 0.11457878351211548, 0.29154735803604126, -0.17075760662555695, 0.11162035912275314, -0.13586650788784027, 0.15771836042404175, -0.31022533774375916, -1.0496431589126587, 0.47259408235549927, 0.23901423811912537, -0.3626216948032379, 0.3862689137458801, -0.26447442173957825, 0.2774428725242615, -0.13932210206985474, -0.3364943563938141, -0.018062004819512367, 0.07648609578609467, -0.08661547303199768, 0.09076708555221558, 0.04202118515968323, 0.20423053205013275, -0.4015344977378845, 0.021718554198741913, 0.2336747944355011, -0.20381630957126617, 0.15775670111179352, 0.4850788116455078, 0.20938290655612946, -0.1361127346754074, -0.04559972137212753, -0.2464834749698639, 0.04984124004840851, 0.08826879411935806, -0.10582337528467178, 0.3795472979545593, -0.2079404890537262, -0.36024725437164307, -0.3111273944377899, -0.19775015115737915, 0.13269288837909698, 0.17258557677268982, -0.308442622423172, -0.390338271856308, -0.0658382847905159, -0.2920359671115875, -0.11048397421836853, 0.1481514573097229, 0.25042232871055603, -0.08418770879507065, -0.40656089782714844, -3.7604820728302, -0.2036798745393753, 0.10243677347898483, 0.24976599216461182, 0.3479989171028137, -0.13183344900608063, -0.17242933809757233, 0.6086272597312927, 0.36164870858192444, -0.29676175117492676, 0.19896991550922394, 0.2409052848815918, 0.1580222100019455, 0.507914662361145, -0.2501758635044098, 0.5174644589424133, 0.10786110907793045, -0.17888237535953522, 0.14616131782531738, -0.29020243883132935, -0.05406514182686806, 0.7247180342674255, 0.183406263589859, -0.23564080893993378, 0.27926164865493774, 0.11247539520263672, -0.34562721848487854, -0.25765153765678406, 0.10279560089111328, -0.3801827132701874, -0.07649599760770798, -0.19543130695819855, 0.03606284037232399, 0.007155915256589651, -0.22295163571834564, -2.8426778316497803, 0.47073090076446533, -0.369645893573761, -0.22180330753326416, -0.09377270936965942, -0.3936787545681, 0.5520045161247253, -0.25262242555618286, -0.5170846581459045, 0.40374407172203064, -0.22053878009319305, 0.013222170993685722, -0.14598961174488068, 0.23742160201072693, 0.18428583443164825, 0.1833551824092865, 0.7231417298316956, -0.31099212169647217, -0.017029086127877235, 0.3340853750705719, 0.11616048216819763, 0.25507351756095886, -0.23459894955158234, -0.214207261800766, 0.1397234946489334, 0.2558099329471588, -0.3812471926212311, 0.15867488086223602, -0.07035310566425323, 0.11974714696407318, -0.09332465380430222, 0.17100925743579865, -0.11126254498958588, -0.2918879985809326, -0.34292927384376526, -0.4621528387069702, 0.09483819454908371, 0.34314194321632385, 0.08228512853384018, 0.1323402225971222, -0.1847754865884781, 0.679452657699585, -0.1543661504983902, 0.4318309426307678, 0.5963549613952637, 0.12231026589870453, -0.19049108028411865, -0.32204756140708923, 0.30927518010139465, -0.019190017133951187, 0.04969466105103493, 0.21455952525138855, 1.266433596611023, -0.028497692197561264, -0.304671049118042, -0.32612431049346924, 0.5824958682060242, 0.10025918483734131, 0.356421560049057, -0.2632738947868347, 0.7013089060783386, -0.15674814581871033, 0.5959071516990662, 0.14899396896362305, -0.04697118699550629, -0.17611289024353027, 0.18188397586345673, -0.5350545644760132, -0.17511457204818726, 0.25163760781288147, 0.10668158531188965, 0.43353602290153503, -0.6787120699882507, -0.911670446395874, 0.13459527492523193, -0.024312183260917664, -0.3384380638599396, 0.10338296741247177, 0.1379208117723465, 0.1447339951992035, -0.13052615523338318, 0.0439484603703022, -0.4629231095314026, 0.3267897963523865, -0.16327029466629028, -0.13897329568862915, 0.2955610156059265, 0.5368101000785828, -0.7238446474075317, 0.04414523392915726, -0.27464061975479126, 0.45223602652549744, 0.21944622695446014, 0.20197449624538422, -0.10113651305437088, 0.05974113568663597, 0.3346000015735626, -0.724143385887146, 0.10745692253112793, -0.27466869354248047, -0.18327006697654724, -0.33278682827949524, -0.3020589053630829, -0.05681294947862625, -0.37613242864608765, 0.0741497129201889, -0.12840832769870758, 0.5473049283027649, -7.743702008156106e-05, 0.1165313571691513, 0.018840260803699493, 0.0011164210736751556, -0.04552159085869789, 0.3825061619281769, 1.0572283267974854, -0.08742639422416687, -0.15783216059207916, 0.7994888424873352, 0.34564411640167236, 0.20070292055606842, 0.5840145349502563, 0.17264366149902344, -0.04350544139742851, -0.09331351518630981, -0.38937339186668396, -0.049226537346839905, 0.19359363615512848, -0.045678671449422836, -0.547558069229126, -0.1396341323852539, 0.06136142462491989, -0.39928847551345825, -0.47361236810684204, -0.4486250877380371, -0.20051658153533936, -0.21238338947296143, -0.24190977215766907, 0.45424914360046387, 0.11108261346817017, 0.041646379977464676, 0.42477983236312866, 0.261623352766037, -0.14451566338539124, 0.2591439187526703, -0.49399593472480774, 0.5494371652603149, -0.08781593292951584, -0.049636248499155045, -0.16063973307609558, 0.42313528060913086, -0.035972900688648224, -0.30014678835868835, 0.10205478221178055, -0.4988580644130707, 0.3509284555912018, -0.09163473546504974, 0.02268395759165287, 0.1676490753889084, -0.12827931344509125, -0.4262014627456665, -0.14825206995010376, 0.1706705242395401, -1.806214451789856, 0.2469118982553482, 0.8639327883720398, -0.02230674773454666, 0.2978920340538025, -0.32635384798049927, -0.749553918838501, 0.4658277630805969, 0.2931510806083679, 0.30758771300315857, -0.09316246211528778, -0.13975059986114502, 0.03015584871172905, -0.07199543714523315, 0.3181436061859131, 0.08106037229299545, 0.13294246792793274, -0.4295181930065155, -0.21992193162441254, 0.04137323796749115, -0.1961546242237091, 0.23818285763263702, -0.3608015179634094, 0.1653718203306198, -0.2740185856819153, -0.3669109046459198, -0.25177162885665894, 0.4160734713077545, -0.320795476436615, 0.1462063193321228, -0.05977432057261467, -0.5263361930847168, -0.5923031568527222, 0.223189577460289, 0.3259010314941406, -0.20117279887199402, 0.018501078709959984, -0.1075294092297554, 0.5008914470672607, 0.5813836455345154, -0.2719357907772064, 0.3780449330806732, -0.05702221021056175, -0.08282840996980667, 0.2736021876335144, 0.17792662978172302, -0.6445788741111755, 0.42025327682495117, 0.12036962062120438, -0.19336816668510437, -0.5239923000335693, 0.17975348234176636, -0.34302473068237305, -0.3309507668018341, 0.11123429983854294, 0.013821256347000599, -0.14354318380355835, -0.07669975608587265, -0.0536896176636219, -0.14812064170837402, -0.08428725600242615, 0.1154363751411438, -0.3132556676864624, 0.16200485825538635, -0.4855682849884033, -0.6299196481704712, 0.2628142237663269, -0.3517998158931732, -0.3023808002471924, 0.4743030071258545, 0.4762348234653473, 0.39817747473716736, -0.07375337183475494, 0.08257441222667694, -0.21860039234161377, 0.40259435772895813, -0.12091144919395447, -0.15457259118556976, -0.12760914862155914, -0.09383910149335861, -0.2846967577934265, -0.5477538704872131, -0.20493917167186737, 0.2427751123905182, -0.09558276832103729, 0.29116830229759216, -0.3586600422859192, -0.15287353098392487, -0.1762656420469284, -0.3782440423965454, -0.589515209197998, -0.4222671687602997, 0.23544076085090637, 0.26912766695022583, 0.1572408676147461, 0.01089917030185461, 0.16069883108139038, 0.08495573699474335, 0.10546237975358963, -0.0800851583480835, -0.1723850667476654, 0.2342487871646881, 0.12953805923461914, 0.3279438018798828, 0.41546282172203064, 0.41587162017822266, 0.11981892585754395, 0.39378270506858826, -0.40748149156570435, -0.08265527337789536, 0.15161651372909546, -0.1508512645959854, -0.2092992067337036, 0.0036205200012773275, 0.008273801766335964, -0.07039573788642883, 0.4285236895084381, -0.5173697471618652, 1.9517555236816406, 0.1867092251777649, 0.3407094478607178, -0.2990741729736328, 0.41099295020103455, -0.06452417373657227, 0.1324562281370163, 0.2833867073059082, -0.5883856415748596, 0.2519853413105011, -0.13423578441143036, -0.2387596070766449, 0.1755772829055786, 0.3186618685722351, 0.5032967925071716, 0.4617061913013458, -0.08549106121063232, -0.27220845222473145, -0.3132493495941162, -0.03318827599287033, -0.3209003210067749, 0.4083949327468872, 0.23441864550113678, -0.1330847293138504, 0.2108968049287796, 0.14167578518390656, -0.034470248967409134, 0.053792260587215424, 0.20146837830543518, 0.2311057299375534, -0.506533682346344, -0.08947891741991043, 0.2490389347076416, 0.27195045351982117, -0.3143630027770996, 0.27712926268577576, 0.3172128200531006, -0.5829175114631653, -0.07166966050863266, 0.12576690316200256, -0.1974227875471115, -0.5336465239524841, 0.8744670152664185, 0.20520050823688507, 0.1736450046300888, 0.4840240478515625, -0.4597693681716919, -0.08623004704713821, 0.5142685174942017, 0.38103634119033813, -0.271908700466156, 0.18278835713863373, -0.281257301568985, 0.10849206149578094, -0.08173179626464844, -0.25521183013916016, -0.009877988137304783, -0.20233169198036194, -0.2710997462272644, 0.6088957190513611, -0.09380174428224564, 0.277680367231369, 0.2019871175289154, 0.13732512295246124, -0.08519216626882553, 0.06710097193717957, -0.5372422933578491, 0.2583199143409729, 0.14506858587265015, -0.47173574566841125, -0.08229336887598038, 0.1523161232471466, 0.21943779289722443, 0.017117958515882492, 0.4603025019168854, -0.04043814167380333, 0.6549714207649231, 0.04609151929616928, -0.2874009311199188, -3.0685887336730957, -0.060571905225515366, -0.26286429166793823, 0.06220870465040207, -0.331233412027359, 0.5716676115989685, 0.07926635444164276, -0.0008579751010984182, 0.0974634662270546, -0.2956711947917938, 0.25896742939949036, 0.10705964267253876, 0.3241439163684845, -0.06683962047100067, 0.03474488854408264, 0.21772542595863342, 0.11962311714887619, -0.22790592908859253, -0.5562617182731628, -0.1343054473400116, 0.07002755999565125, 0.027264850214123726, -0.2707548141479492, -0.20757871866226196, -0.3622201681137085, 0.13641272485256195, 0.2579585015773773, -0.1524696797132492, 0.4067534804344177, 0.38420093059539795, -0.038362279534339905, -0.01561181154102087, 0.1680821180343628, -0.09241947531700134, -0.17970269918441772, -0.12979337573051453, -0.18205934762954712, -0.09988313168287277, 0.1907232701778412, 0.09538688510656357, -0.12018435448408127, 0.4032272398471832, 0.003306398866698146, 0.03428894653916359, 0.20026631653308868, -0.32365718483924866, 0.00855656061321497, -0.33365586400032043, 0.5332062840461731, -0.17875413596630096, -0.004998568911105394, -0.012226242572069168, -0.04765764996409416, -0.19574806094169617, 0.3197147250175476, 0.19055262207984924, 0.4671759009361267, 0.043321188539266586, -0.01157782506197691, -0.03500358760356903, 0.4951452612876892, -0.15990310907363892, -0.40488097071647644, -0.10846776515245438, 0.40830427408218384, -0.3080751597881317, 0.04026762768626213, -0.01968693919479847, -0.1214146539568901, -0.21439316868782043, -0.19443204998970032, -0.12589006125926971, 0.5673751831054688, 0.14140912890434265, 0.11636856198310852, 0.44311970472335815, -0.038000743836164474, 0.3002474308013916, 0.3929488956928253, 0.037897054105997086, 0.13631576299667358, 0.23481124639511108, -0.2629503309726715, 0.23619365692138672, 0.10013790428638458, -7.67518949508667, -0.16325481235980988, -0.3987599015235901, -0.3634212017059326, 0.21273161470890045, -0.026457611471414566, -0.0032272683456540108, -0.18665219843387604, 0.02041047438979149, -0.2594093382358551, -0.022025035694241524, 0.059042710810899734, -0.014660152606666088, -0.4672327935695648, 0.37039846181869507, 0.32228514552116394]</t>
+          <t>['high', 'high', 'medium', 'high', 'high', 'medium']</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>[-0.5, 0.0, 1.0, -0.5, -0.5, -0.5]</t>
+          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[4, 4, 3, 2, 3, 5]</t>
+          <t>[40.0, 35.0, 35.0, 40.0, 35.0, 45.0]</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
+          <t>['woman', 'man', 'man', 'woman', 'woman', 'woman']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>[40.0, 35.0, 35.0, 50.0, 45.0, 35.0]</t>
+          <t>[1, 1, 5, 1, 1, 2]</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>['woman', 'man', 'man', 'man', 'woman', 'woman']</t>
+          <t>[4, 4, 1, 5, 5, 3]</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>[1, 1, 5, 1, 2, 1]</t>
+          <t>[5, 5, 3, 5, 5, 5]</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>[4, 4, 1, 2, 3, 5]</t>
+          <t>[2, 4, 5, 5, 5, 3]</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>[1, 1, 3, 1, 2, 1]</t>
+          <t>[1, 1, 5, 1, 1, 2]</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>[2, 4, 5, 5, 3, 4]</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>[1, 1, 5, 3, 2, 1]</t>
-        </is>
+          <t>[5, 5, 4, 5, 5, 5]</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>6</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1, 1]</t>
+          <t>[5, 5, 1, 5, 5, 5]</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>[1, 1, 4, 2, 1, 1]</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>[0.66666667 0.16666667 0.         0.16666667 0.        ]</t>
-        </is>
-      </c>
-      <c r="T16" t="n">
-        <v>0.25</v>
+          <t>[0.16666667 0.         0.         0.         0.83333333]</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>510</v>
+        <v>532</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>bad news in the air.... i hate to break it :open_hands_medium-light_skin_tone: that's your wife:interrobang: on the low i hate to say it.... that bitch BASIC:bangbang:- @iitsAD</t>
+          <t>i don't care what people say, blacks have ugly eyelashes!</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[5, 4, 2, 2, 5, 4]</t>
+          <t>[5, 4, 2, 5, 4, 5]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[5, 5, 2, 3, 5, 5]</t>
+          <t>['{}', '{}', nan, '{}', '{}', '{}']</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>['black; female', '{}', '{}', '{}', '{}', nan]</t>
+          <t>['left', 'center', 'far right', 'center', 'center', 'far left']</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>[0.052012424916028976, 0.02669532597064972, 0.0778852105140686, -0.1427941769361496, -0.21687285602092743, -0.22660353779792786, 0.4155513346195221, 0.3650507628917694, -0.08145210146903992, -0.22167722880840302, -0.051966242492198944, 0.10483100265264511, -0.12242062389850616, 0.22682248055934906, 0.6454288959503174, 0.3237689733505249, -0.32411351799964905, 0.32601848244667053, 0.22137117385864258, -0.13388429582118988, -0.3060635030269623, -0.50645512342453, 0.21594180166721344, -0.11706932634115219, 0.13541296124458313, -0.07577725499868393, -0.07878611981868744, -0.2553565204143524, -0.23110726475715637, 0.34499242901802063, -0.05938452109694481, 0.022234532982110977, -0.23036953806877136, -0.20272965729236603, 0.34768790006637573, -0.20365431904792786, -0.20432162284851074, 0.01614190638065338, 0.3173127770423889, 0.20800770819187164, -0.06575090438127518, -0.15258125960826874, 0.2362312227487564, 0.06365113705396652, -0.23410183191299438, -0.26263895630836487, -3.2680041790008545, 0.13376182317733765, -0.24743804335594177, -0.47005605697631836, 0.39083170890808105, -0.10858194530010223, -0.03316620737314224, 0.17723943293094635, 0.057350676506757736, 0.35721057653427124, -0.11890765279531479, 0.17216701805591583, 0.002306526992470026, 0.11719924956560135, -0.01690588891506195, 0.06108017638325691, -0.01985740289092064, 0.3149473965167999, -0.23229654133319855, 0.09909026324748993, -0.0675831288099289, 0.6776948571205139, -0.4882813096046448, 0.6809253692626953, -0.0093348678201437, -0.08733469992876053, 0.3069581389427185, -0.23235058784484863, 0.19852124154567719, -0.2693033218383789, 0.023842813447117805, 0.40673166513442993, -0.02631925605237484, 0.3384890854358673, -0.056189488619565964, 0.28620603680610657, 0.40334928035736084, -0.037675995379686356, 0.24757522344589233, 0.2381347119808197, 0.07670716941356659, -0.41384410858154297, 0.2650517225265503, 0.2448303997516632, -0.08269868046045303, -0.20201557874679565, -0.0032639307901263237, -0.014181108213961124, 0.7281692624092102, -0.10682285577058792, -0.04169956222176552, 0.33940061926841736, 0.1743701845407486, 0.2645738422870636, -0.024648917838931084, 0.2165326029062271, -0.24607287347316742, -0.37245678901672363, -0.3175283372402191, 0.12761946022510529, -0.16723668575286865, -0.27570876479148865, 0.07032700628042221, -1.9314842224121094, 0.450880229473114, 0.14131566882133484, -0.42948704957962036, -0.4769434630870819, 0.28436946868896484, 0.2933551073074341, 0.24441437423229218, -0.06594016402959824, 0.4613056182861328, 0.16788247227668762, -0.09761948138475418, 0.402283638715744, -0.010900668799877167, -0.30974239110946655, 0.3554062843322754, 0.32508525252342224, 0.384639710187912, -0.08981264382600784, 0.4222654700279236, 0.20242813229560852, 0.15966317057609558, 0.3442910313606262, -0.13258853554725647, -0.13034765422344208, 0.021684259176254272, -0.20226308703422546, 0.22203946113586426, -0.21996499598026276, -0.2044965624809265, -0.09251609444618225, -0.6993118524551392, -0.280447781085968, -3.002340078353882, 0.2729179859161377, 0.2605880796909332, 0.1918834149837494, -0.1233542338013649, 0.014789684675633907, -0.18442051112651825, 0.15562258660793304, -0.22522999346256256, 0.017427096143364906, -0.10344500839710236, 0.04370024800300598, -0.33744174242019653, 0.15922319889068604, -0.08638955652713776, -0.08879552036523819, 0.051689863204956055, 0.7031733989715576, 0.2719942629337311, 0.3990333378314972, -0.0018386855954304338, 0.05105400085449219, 0.36860209703445435, -0.26815083622932434, -0.0031731000635772943, -0.055970024317502975, -0.18537411093711853, -0.4181586503982544, 0.16682758927345276, -0.24090676009655, 0.3390747308731079, 0.11134492605924606, 0.1893826723098755, 0.0711541622877121, 0.2248670607805252, 0.26047730445861816, 0.04853987693786621, -0.11504348367452621, -0.34066781401634216, 0.19863301515579224, -0.12222599238157272, 0.1289975792169571, 0.4007178246974945, -0.1374148428440094, 0.6014636754989624, -0.12897467613220215, 0.024731146171689034, 0.4302206337451935, -0.2851271331310272, -0.057184357196092606, 0.56303870677948, 0.4696770906448364, 0.3206650912761688, -0.15864472091197968, -0.10143529623746872, 0.050012871623039246, 0.3674793839454651, 0.0834849402308464, 0.1885421872138977, -0.16066278517246246, 0.5513676404953003, -0.12120962888002396, -0.33654487133026123, 3.87506365776062, -0.19724494218826294, -0.13032661378383636, -0.08557265251874924, 0.2878943383693695, -0.3565181493759155, 0.16463392972946167, -0.14747405052185059, -0.2682752013206482, -0.06664382666349411, -0.014875983819365501, 0.3945038616657257, -0.30354490876197815, -0.028144596144557, 0.11578332632780075, 0.1637134701013565, 0.4084399342536926, 0.11903190612792969, 0.3292396068572998, -0.3552694320678711, 0.22975505888462067, 0.22011975944042206, 0.11428835242986679, 0.3409394323825836, -1.4490156173706055, -0.16495099663734436, 0.19076862931251526, -0.40025824308395386, 0.260026752948761, 0.22179904580116272, 0.24862508475780487, -0.10393604636192322, -0.2370857298374176, 0.13307863473892212, 0.06049088016152382, 0.19415268301963806, 0.29950660467147827, -0.07830314338207245, 0.07773319631814957, -0.4174904227256775, 0.2666681408882141, 0.47113388776779175, -0.28235241770744324, 0.46249282360076904, 0.04644279181957245, 0.33438417315483093, 0.0486549511551857, 0.03130340203642845, -0.22174172103405, 0.26656240224838257, 0.09683845192193985, -0.34287896752357483, -0.09660633653402328, -0.7846315503120422, -0.34904026985168457, -0.5965295433998108, -0.04540438577532768, -0.0029760764446109533, -0.035186320543289185, -0.24713236093521118, -0.2508605122566223, -0.07631677389144897, -0.0957728773355484, 0.14510329067707062, -0.17782635986804962, -0.10563239455223083, 0.012201032601296902, -0.21128368377685547, -3.098161220550537, 0.15349680185317993, -0.10395641624927521, 0.033166754990816116, 0.16283029317855835, 0.1840209662914276, -0.3305416405200958, 0.08549167960882187, -0.2708260118961334, -0.009015635587275028, 0.05075141414999962, 0.4410066306591034, -0.25142040848731995, 0.435431569814682, -0.3840179443359375, -0.09887809306383133, 0.13202150166034698, -0.5002495646476746, -0.526587188243866, -0.2399998903274536, 0.20114216208457947, 0.4285370707511902, -0.3976234793663025, 0.36118650436401367, 0.18332305550575256, -0.2721570134162903, 0.16967305541038513, -0.2299777716398239, 0.3389764726161957, -0.2891274094581604, 0.07036501914262772, -0.2950436472892761, -0.2238030582666397, -0.045425157994031906, -0.39302343130111694, -4.1631317138671875, -0.002670587971806526, 0.05601697042584419, -0.5478232502937317, 0.1652761697769165, -0.12714801728725433, 0.43881016969680786, 0.1861468255519867, 0.03037099353969097, 0.037512242794036865, 0.07591184973716736, 0.0596398264169693, 0.1987515240907669, -0.2962847650051117, 0.19146274030208588, 0.3918624222278595, 0.20049436390399933, -0.11676197499036789, -0.11276382952928543, -0.023486308753490448, -0.2418244630098343, 0.30751124024391174, 0.13091717660427094, 0.1624671071767807, 0.2720475494861603, 0.47751060128211975, -0.2330399751663208, 0.11385755985975266, 0.13810545206069946, 0.2720170021057129, 0.404776394367218, 0.14502298831939697, -0.22828687727451324, -0.2014782577753067, -0.4383682906627655, -0.17817829549312592, 0.4803474247455597, 0.10174702107906342, 0.2535228729248047, -0.07466711103916168, 0.28708377480506897, 0.3118225038051605, -0.1281656175851822, -0.13479971885681152, 0.6046921014785767, -0.21761593222618103, -0.011867448687553406, -0.008455597795546055, 0.14573413133621216, -0.07811248302459717, -0.46398723125457764, -0.272245317697525, 1.217198133468628, 0.042481228709220886, 0.4844052791595459, -0.3330395221710205, -0.22567959129810333, 0.49803048372268677, 0.15220823884010315, 0.37791040539741516, 0.8592122197151184, 0.1354333907365799, 0.2530544698238373, -0.17982618510723114, 0.19243700802326202, -0.1232447624206543, 0.22512921690940857, -0.534936785697937, -0.06280871480703354, 0.15711823105812073, -0.10760770738124847, 0.17244715988636017, 0.17420093715190887, -1.1530503034591675, 0.08519139140844345, -0.09668536484241486, -0.3639993667602539, 0.21409344673156738, -0.18583737313747406, 0.3958492875099182, -0.10239383578300476, 0.05225810408592224, -0.024651478976011276, 0.46835362911224365, -0.5673896074295044, -0.3985489010810852, -0.06657585501670837, 0.16266536712646484, -0.47663137316703796, 0.594417154788971, -0.09150363504886627, 0.022334199398756027, -0.02913622185587883, -0.036032017320394516, -0.024658484384417534, 0.13324978947639465, 0.4438681900501251, -0.8435363173484802, 0.31211766600608826, -0.041152697056531906, 0.7291695475578308, -0.2134876549243927, 0.03134046122431755, -0.35827693343162537, -0.16311249136924744, -0.042845167219638824, -0.15125441551208496, 0.2663794755935669, 0.12577448785305023, -0.09867258369922638, -0.14974647760391235, 0.042294785380363464, -0.6878067851066589, 0.3144327402114868, 0.6940581202507019, -0.04971510171890259, -0.3318614661693573, 0.3956095278263092, 0.37024953961372375, -0.052269693464040756, 0.1387472152709961, 0.1351083368062973, 0.11301541328430176, 0.2610851526260376, -0.3464319109916687, 0.10364554077386856, 0.06157561019062996, -0.1438005268573761, -0.21944187581539154, -0.2929295599460602, -0.0732610672712326, -0.28941819071769714, -0.3384212255477905, -0.40688374638557434, -0.028638822957873344, -0.2779880464076996, 0.13188208639621735, 0.27668318152427673, 0.3597404658794403, 0.00563559727743268, 0.3450377881526947, -0.08754443377256393, 0.049145542085170746, 0.1961255818605423, -0.37733739614486694, 0.46932363510131836, -0.24988001585006714, 0.05255431681871414, -0.027439454570412636, 0.2378593236207962, 0.0532037653028965, -0.4632129967212677, 0.2669706344604492, -0.41855311393737793, 0.1858881115913391, -0.007073004264384508, -0.08443339169025421, 0.24409298598766327, -0.4967970550060272, 0.03295780345797539, 0.30927836894989014, -0.217188760638237, -1.3678621053695679, 0.3779049813747406, 0.29440706968307495, -0.05004756152629852, 0.037953492254018784, -0.23763489723205566, -0.1727183610200882, 0.010756248608231544, -0.1660476177930832, 0.1414179503917694, -0.27083027362823486, 0.14371594786643982, 0.14921772480010986, 0.20242278277873993, 0.2670265734195709, -0.1055554524064064, 0.24565450847148895, 0.0069920956157147884, -0.10247209668159485, -0.11859725415706635, 0.09440655261278152, 0.47535157203674316, 0.4075722098350525, -0.14888347685337067, 0.229527086019516, -0.06840591877698898, -0.30733436346054077, 0.5932637453079224, -0.02523389272391796, -0.09951353818178177, -0.08682149648666382, -0.3512091636657715, -0.09665807336568832, -0.17567096650600433, 0.46795299649238586, 0.4991639256477356, 0.1779603511095047, 0.286784827709198, 0.40984657406806946, 0.6837192177772522, -0.6522536873817444, 0.26272162795066833, 0.20206902921199799, 0.5381622314453125, 0.764644205570221, 0.14122970402240753, 0.019311711192131042, 0.17101484537124634, 0.4251879155635834, -0.42321187257766724, -0.07193171977996826, -0.5121769905090332, -0.3074619174003601, -0.21895742416381836, -0.4066363573074341, -0.40918871760368347, 0.14172330498695374, -0.28309857845306396, -0.5314006805419922, -0.010578078217804432, -0.19853226840496063, 0.24462459981441498, -0.2495630830526352, 0.2923286259174347, -0.3670773208141327, -0.6083260178565979, 0.1717025339603424, -0.10312390327453613, -0.06339601427316666, 0.3342234790325165, 0.4255126714706421, 0.3181573450565338, -0.5907321572303772, 0.0336855985224247, -0.41778600215911865, 0.41473662853240967, -0.27119147777557373, 0.09204951673746109, 0.12422966212034225, -0.3195018470287323, 0.2514393627643585, -0.4264538586139679, -0.18507304787635803, 0.6417801976203918, -0.47352319955825806, 0.08953847736120224, -0.00026009746943600476, -0.0662270113825798, 0.2766592502593994, 0.22251200675964355, -0.5704636573791504, -0.28219977021217346, 0.16683833301067352, 0.24599511921405792, 0.25611868500709534, 0.06434854120016098, -0.3747296929359436, 0.01268813293427229, -0.10461490601301193, -0.03587929531931877, -0.06414540112018585, 0.18343481421470642, 0.23579323291778564, 0.1720954179763794, 0.29780954122543335, -0.003046864876523614, 0.31053677201271057, 0.16370227932929993, -0.15135207772254944, 0.022680489346385002, 0.3128277659416199, 0.21128451824188232, -0.13543881475925446, -0.20497749745845795, -0.15368278324604034, -0.11327659338712692, 0.059190358966588974, -0.17530104517936707, 1.757836103439331, 0.10959374159574509, 0.11731281131505966, -0.04703739285469055, 0.6320485472679138, -0.025484466925263405, 0.06407750397920609, 0.05897793918848038, -0.1941802203655243, 0.619958758354187, -0.33969083428382874, 0.5742165446281433, -0.4308081567287445, -0.02060522325336933, 0.41368886828422546, 0.40618905425071716, -0.06773894280195236, -0.5131767988204956, -0.2528468668460846, 0.018362099304795265, -0.005422312766313553, 0.03436014801263809, 0.4726473093032837, 0.1433878242969513, -0.1907418817281723, 0.2912476360797882, 0.054429616779088974, -0.41531649231910706, 0.042803969234228134, 0.12849070131778717, -0.39033743739128113, -0.18633602559566498, -0.04117624834179878, 0.07666923850774765, -0.5602442026138306, 0.022292183712124825, 0.30549028515815735, -0.009327736683189869, -0.38639283180236816, -0.21544066071510315, 0.08488963544368744, -0.3028383255004883, 0.5019558668136597, 0.019559605047106743, -0.1801537573337555, 0.2791110873222351, -0.09950960427522659, -0.20536582171916962, 0.4351232051849365, 0.19454538822174072, 0.0714939534664154, -0.06446640938520432, -0.492492139339447, 0.11708196997642517, 0.16654899716377258, -0.4994438886642456, 0.14786957204341888, -0.19778776168823242, -0.3100259602069855, 0.47082310914993286, -0.3343144357204437, 0.5119056105613708, 0.2099185436964035, -0.25704851746559143, -0.054806146770715714, 0.025952372699975967, -0.19119033217430115, 0.040823228657245636, 0.31186363101005554, -0.22895874083042145, -0.2082514464855194, 0.4341948330402374, 0.0028812233358621597, 0.05045603588223457, 0.07555439323186874, 0.04249449074268341, -0.013721414841711521, -0.24186936020851135, -0.1696660965681076, -2.531970262527466, 0.21524624526500702, 0.24112969636917114, -0.032455965876579285, 0.0445631667971611, 0.03224591910839081, -0.028955431655049324, 0.3511715233325958, 0.2279433310031891, -0.1647733598947525, -0.16363026201725006, 0.020979614928364754, 0.3508692979812622, 0.05401597544550896, 0.07838626950979233, -0.3694060444831848, 0.06705991178750992, 0.0812005028128624, 0.04633921757340431, -0.07639399915933609, -0.13634376227855682, 0.25621214509010315, -0.3891761302947998, -0.2224191278219223, -0.030331365764141083, 0.2847152054309845, 0.1878243088722229, -0.1572410613298416, 0.4103415012359619, -0.0793221965432167, -0.19382382929325104, 0.1996578425168991, -0.27695566415786743, -0.517183244228363, 0.10119514912366867, -0.22358731925487518, -0.23053953051567078, 0.13050127029418945, 0.07744640856981277, 0.3139105439186096, 0.5407171249389648, 0.42009633779525757, 0.038290709257125854, 0.12553706765174866, -0.13347963988780975, -0.12676149606704712, 0.3894016444683075, -0.16259640455245972, 0.4335824251174927, -0.17357110977172852, 0.20673899352550507, 0.12207154184579849, 0.2807975113391876, -0.1668836772441864, 0.18784968554973602, 0.2552742063999176, 0.2498745173215866, 0.292341023683548, -0.005326542071998119, -0.2380416989326477, -0.11132270842790604, 0.00035791273694485426, -0.2994704246520996, -0.24993498623371124, 0.4006589651107788, 0.13247746229171753, 0.08894757926464081, 0.050589073449373245, -0.1039232686161995, -0.30847540497779846, 0.01841776818037033, 0.09561129659414291, 0.024409500882029533, 0.4584128260612488, -0.017012357711791992, -0.16027119755744934, 0.5569205284118652, -0.15153641998767853, 0.4084171652793884, 0.04620564356446266, 0.0708402469754219, -0.4490683376789093, -0.19218294322490692, -0.12056508660316467, 0.209365114569664, -6.693418025970459, -0.2639264464378357, -0.35170575976371765, -0.44647032022476196, -0.3467884063720703, -0.64693284034729, 0.17518632113933563, -0.3581460416316986, -0.03420974314212799, -0.21175706386566162, 0.284219890832901, 0.1787467747926712, -0.25898298621177673, -0.21443374454975128, 0.1242169588804245, 0.4652353525161743]</t>
+          <t>['high', 'high', 'medium', 'high', 'high', 'high']</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>[-1.0, 0.0, 0.5, 0.5, -0.5, -1.0]</t>
+          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[4, 5, 3, 3, 5, 5]</t>
+          <t>[40.0, 35.0, 35.0, 40.0, 35.0, 25.0]</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
+          <t>['woman', 'man', 'man', 'woman', 'woman', 'man']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>[40.0, 45.0, 30.0, 35.0, 35.0, 45.0]</t>
+          <t>[1, 1, 5, 1, 3, 1]</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>['woman', 'man', 'man', 'woman', 'woman', 'woman']</t>
+          <t>[4, 4, 1, 5, 4, 4]</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>[1, 1, 4, 1, 1, 1]</t>
+          <t>[5, 4, 3, 5, 4, 5]</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>[5, 5, 1, 5, 5, 5]</t>
+          <t>[2, 4, 5, 5, 3, 5]</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>[5, 4, 4, 5, 5, 3]</t>
+          <t>[1, 1, 5, 1, 1, 1]</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>[4, 4, 5, 5, 4, 3]</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>[1, 1, 5, 3, 1, 1]</t>
-        </is>
+          <t>[5, 4, 3, 5, 4, 5]</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>6</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 4, 1]</t>
+          <t>[5, 4, 2, 5, 4, 5]</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>[5, 4, 2, 2, 5, 4]</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>[0.         0.33333333 0.         0.33333333 0.33333333]</t>
-        </is>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
+          <t>[0.         0.16666667 0.         0.33333333 0.5       ]</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>521</v>
+        <v>548</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>doesnt matter if straights r oppressed or not sayin u hate all of them even if you dont mean it is as bad as homophobes sayin they hate gays</t>
+          <t>in this park we do not tolerate blacks</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[2, 1, 4, 2, 2, 2]</t>
+          <t>[3, 5, 5, 3, 5, 5]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[3, 1, 4, 2, 2, 4]</t>
+          <t>['NONE', 'immigrant, black,', '{}', '{}', '{}', 'none']</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>[nan, '{}', '{}', 'none', '{}', '{}']</t>
+          <t>['far right', 'center', 'center', 'right', 'left', 'left']</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>[-0.20119306445121765, 0.7069498896598816, -0.14992761611938477, -0.2390473186969757, -0.710702657699585, -0.3061859905719757, 1.006700873374939, 0.6239320039749146, 0.09754796326160431, 0.08842302113771439, 0.19398395717144012, -0.4560011327266693, -0.31830447912216187, -0.08364543318748474, 0.45174747705459595, 0.3539140820503235, -0.31902995705604553, 0.4128640294075012, -0.1481868028640747, 0.4053802788257599, -0.0968509390950203, -0.5046557784080505, 0.11493239551782608, -0.2565808594226837, 0.2296999841928482, 0.2230871170759201, 0.5698683857917786, -0.27109378576278687, -0.12540845572948456, 0.09024601429700851, 0.11268797516822815, 0.363669216632843, -0.3919260799884796, -0.2568528950214386, 0.5745081901550293, -0.161943256855011, 0.2186536341905594, 0.5625247955322266, 0.22876670956611633, 0.06382982432842255, -0.48008549213409424, -0.14424842596054077, -0.39104795455932617, -0.6374729871749878, 0.26365044713020325, -0.1878271996974945, -3.3843536376953125, 0.1464170515537262, 0.15040463209152222, -0.4378623068332672, 0.21018396317958832, -0.5735017657279968, -0.19397270679473877, 0.6382496356964111, -0.18749208748340607, 0.33619576692581177, -0.38500502705574036, 0.17781440913677216, -0.11119295656681061, 0.2182609587907791, 0.3503209352493286, 0.2909812927246094, -0.07685969769954681, 0.12100038677453995, 0.017478786408901215, 0.21382680535316467, -0.36871957778930664, 1.1786905527114868, -1.1651955842971802, 0.3663087487220764, -1.1302274465560913, -0.4098149240016937, 0.7342451810836792, 0.10123308002948761, 0.42076897621154785, -0.1364542543888092, -0.321563184261322, 0.17371954023838043, -0.5159904360771179, 0.06668813526630402, -0.13192741572856903, 0.6099758148193359, -0.21824239194393158, 0.0862840861082077, 0.10896576195955276, 0.5909700393676758, 0.4489505887031555, -0.024755436927080154, 0.1365533173084259, -0.10007325559854507, 0.042974699288606644, -0.07627198100090027, 0.2629469037055969, -0.2726023495197296, 0.6422498226165771, 0.3355269432067871, 0.4503345191478729, 0.19054244458675385, 0.3246922194957733, 0.4052791893482208, 0.338159441947937, -0.042119164019823074, 0.0898967906832695, -0.9830190539360046, -0.21842634677886963, -0.7124437093734741, 0.08059367537498474, -0.18112227320671082, 0.5519651770591736, -1.9196815490722656, 0.10854872316122055, -0.2542738616466522, -0.37145906686782837, -0.47189122438430786, -0.5651751160621643, 0.2941398024559021, 0.5398911833763123, -0.44401219487190247, 0.32524389028549194, 0.38775190711021423, -0.25725001096725464, 0.24636369943618774, 0.11903656274080276, -0.17521557211875916, 0.17279353737831116, 0.0973818302154541, 0.08935706317424774, 0.14177252352237701, 0.3532978296279907, 0.37236228585243225, 0.27349749207496643, 0.49452653527259827, -0.08297659456729889, -0.5261712670326233, -0.25661495327949524, 0.02023560181260109, -0.033148251473903656, -0.16151642799377441, -0.13743895292282104, -0.4726980924606323, -0.4838416278362274, -0.6328606009483337, -2.3436856269836426, 0.24447061121463776, 0.40532660484313965, 0.1854228526353836, -0.023845594376325607, -0.15013864636421204, -0.5044358372688293, 0.21542225778102875, 0.36462172865867615, -0.06945759803056717, 0.07332602143287659, -0.15161703526973724, -0.03057503141462803, 0.14564591646194458, -0.37226012349128723, -0.6093884110450745, 0.033656392246484756, 0.7608596682548523, 0.234386146068573, -0.344454288482666, -0.18413423001766205, 0.4518618881702423, 0.3236267864704132, -0.0869581401348114, -0.3492872416973114, 0.01768798567354679, -0.16578662395477295, -0.31336498260498047, 0.2664797604084015, -0.27501368522644043, 0.9898118376731873, 0.07425454258918762, 0.36245131492614746, -0.4010026454925537, 0.7020726203918457, 0.2129538357257843, -0.1040748655796051, -0.161748006939888, -0.5822168588638306, 0.391133576631546, 0.24425964057445526, 0.15366053581237793, 0.8300114274024963, -0.0422898605465889, 0.3064334988594055, 0.03148074448108673, -0.1519697904586792, 0.11658252030611038, -0.443525493144989, -0.2037365585565567, 0.35698452591896057, 0.6219399571418762, 1.0139267444610596, -0.6546695828437805, 0.31993237137794495, -0.5676867961883545, -0.175556942820549, 0.08897273242473602, -0.33117082715034485, -0.5206104516983032, 0.34299248456954956, 0.7218098044395447, -0.686491072177887, 3.6419899463653564, 0.20676389336585999, -0.024342581629753113, -0.02144230529665947, 0.6557943224906921, -0.49798715114593506, 0.2163388729095459, 0.17599211633205414, -0.2176455557346344, -0.10101994127035141, 0.16147015988826752, 0.2685641646385193, -0.2706187963485718, -0.13179241120815277, 0.053457897156476974, 0.4550239145755768, 0.14440865814685822, -0.2893301844596863, 0.16024330258369446, -0.011565225198864937, 0.0654277503490448, 0.03923289477825165, -0.45687538385391235, -0.05109936371445656, -1.6279010772705078, 0.31625479459762573, -0.13901953399181366, 0.37190812826156616, 0.38005754351615906, -0.5900141596794128, 0.09505335241556168, -0.007472809869796038, 0.04417596757411957, 0.13256235420703888, -0.07711058855056763, 0.26746049523353577, 0.36035290360450745, -0.3376239836215973, 0.15037409961223602, -0.37784597277641296, 0.7898373603820801, 0.41335994005203247, -0.8204149007797241, 0.36007586121559143, 0.4936956763267517, 0.07969839125871658, -0.19140596687793732, -0.07458402216434479, -0.3145483434200287, 0.5162557363510132, 0.08443398028612137, 0.13919638097286224, 0.05513964593410492, -0.8199800252914429, -0.8138044476509094, -0.11392314732074738, 0.03806213289499283, 0.08154289424419403, 0.23759566247463226, -0.9113376140594482, -0.0030225978698581457, 0.26798099279403687, -0.07016292959451675, -0.5082078576087952, 0.110806904733181, 0.14056403934955597, -0.0895267203450203, -0.06034209579229355, -2.601764678955078, -0.3811553120613098, 0.3919942080974579, 0.05693802982568741, 0.4897003769874573, -0.03519381210207939, -0.1639135479927063, 0.2192361056804657, 0.5555791854858398, -1.014899492263794, 0.325961709022522, 0.22028224170207977, 0.17947755753993988, 0.025891324505209923, -0.15128783881664276, 0.11684098839759827, -0.3528851866722107, 0.2187957614660263, -0.33237937092781067, 0.033047866076231, 0.4127071499824524, 0.0375792570412159, -0.03398517891764641, 0.2083456665277481, 0.06998925656080246, -0.3092997074127197, 0.1228385791182518, -0.25662803649902344, -0.36220210790634155, 0.12458575516939163, 0.5318529605865479, -0.0641210675239563, 0.3052407503128052, 0.06832572817802429, -0.3418859839439392, -3.3882200717926025, -0.22236581146717072, 0.025288334116339684, -0.4455123841762543, -0.16396133601665497, -0.3135482668876648, 0.8956264853477478, -0.33410024642944336, -0.6765615344047546, 0.21219073235988617, -0.2500687837600708, -0.23564769327640533, 0.051712967455387115, -0.019130073487758636, 0.578228235244751, 0.6237029433250427, 0.493315726518631, -0.5719930529594421, -0.10140319913625717, 0.3259361684322357, 0.5829592943191528, 0.6568438410758972, -0.10841967910528183, -0.042093995958566666, 0.8798391819000244, 0.3623300790786743, -0.741913914680481, -0.06805393844842911, 0.012061482295393944, 0.1766473352909088, 0.3588327467441559, 0.4253496825695038, 0.036814168095588684, -0.2936829626560211, -0.23967227339744568, -0.4228048622608185, 0.40927398204803467, 0.19411882758140564, -0.07603124529123306, 0.21218301355838776, 0.04854588955640793, 0.30416059494018555, -0.17489394545555115, -0.352018266916275, 0.7003332376480103, -0.1512921303510666, 0.2117815762758255, -0.2888047695159912, 0.039425864815711975, 0.20229564607143402, 0.10636208206415176, 0.23665322363376617, 0.871735155582428, 0.5964003205299377, -0.18349601328372955, -0.5013353228569031, -0.10351330786943436, -0.01776912249624729, -0.18509067595005035, -0.33960285782814026, 0.5287793874740601, -0.27410703897476196, 0.10110326111316681, 0.2162664830684662, 0.14580470323562622, -0.569769561290741, -0.16607092320919037, -0.24143701791763306, 0.0642777532339096, 0.5059319734573364, 0.07412424683570862, 0.4931287467479706, -0.06714989989995956, -1.5356357097625732, -0.046047937124967575, 0.26492026448249817, -0.5995647311210632, 0.07560979574918747, -0.21071989834308624, 0.20075403153896332, -0.4280504882335663, -0.13070544600486755, -0.7862858772277832, 0.15437684953212738, -0.6751205921173096, -0.07604838907718658, 0.12063547968864441, 0.326989084482193, -0.7527142763137817, -0.3935358226299286, 0.2077464461326599, 0.4573085308074951, -0.0025578418280929327, 0.6908137202262878, -0.41126012802124023, -0.16480550169944763, 0.7480928301811218, -0.36446598172187805, 0.5512701272964478, -0.42389383912086487, 0.5741594433784485, -0.10223446041345596, 0.03518903627991676, -0.3437066376209259, -0.0013750094221904874, 0.07066048681735992, -0.16733819246292114, 1.198677897453308, 0.09116223454475403, 0.384813517332077, -0.5507059693336487, -0.21702827513217926, -0.37080851197242737, 0.3493654131889343, 0.6674025058746338, -0.4216257333755493, -0.09670524299144745, 1.0923100709915161, 0.402406245470047, 0.0783817321062088, 0.27979063987731934, 0.29554301500320435, -0.38782620429992676, -0.2954285740852356, -0.852482259273529, 0.3830050230026245, -0.8059127330780029, 0.04599280282855034, -0.2342776656150818, -0.0718374103307724, 0.32574543356895447, 0.08327607065439224, -0.31221628189086914, -0.24891625344753265, 0.20689967274665833, -0.13341106474399567, 0.3066374361515045, 0.32926875352859497, 0.2367272526025772, -0.14935073256492615, 0.2372320145368576, -0.21587885916233063, -0.4308064877986908, 0.15764378011226654, -0.3571188747882843, 0.6259762644767761, -0.5059119462966919, 0.041738804429769516, -0.33560287952423096, 0.8232225775718689, -0.7308654189109802, -0.22547820210456848, -0.12903502583503723, -0.7880582809448242, 0.6319864988327026, 0.07184873521327972, -0.2845706045627594, 0.08216959983110428, -0.12568111717700958, -0.3983474671840668, -0.114390067756176, -0.12205586582422256, -2.3713579177856445, 0.33075886964797974, 0.9847793579101562, -0.0395829938352108, 0.2693890929222107, 0.0608806237578392, -0.7333070635795593, 0.5712278485298157, 0.28467848896980286, 0.05126000568270683, -0.47525501251220703, -0.07929634302854538, 0.0800233706831932, -0.08833163231611252, 0.1415577381849289, 0.14599627256393433, -0.23721228539943695, -0.6451687812805176, -0.6461386680603027, -0.26009395718574524, -0.3310966193675995, 0.3267298936843872, 0.22734561562538147, -0.38932839035987854, -0.039441682398319244, -0.41692230105400085, -0.09425034373998642, 0.4161118268966675, -0.1503455638885498, -0.027887044474482536, -0.3311794400215149, -0.1519625335931778, -0.5581225752830505, 0.05656328424811363, 0.21741878986358643, -0.32471445202827454, 0.2855183184146881, -0.06827627122402191, 0.8143616318702698, 0.7687851786613464, -0.1196972131729126, 0.42203807830810547, 0.3128100633621216, 0.3033187687397003, 0.6832960844039917, 0.2055487185716629, -0.07375699281692505, 0.6340646743774414, 0.08067990839481354, -0.49489736557006836, -0.7493049502372742, -0.0630515068769455, 0.026039639487862587, -0.3012762665748596, 0.005891139153391123, -0.20188428461551666, -0.18614432215690613, 0.06879696995019913, -0.5209110379219055, 0.08259204775094986, -0.44948452711105347, 0.005463351495563984, -0.40311476588249207, -0.15745100378990173, -0.7938171029090881, -0.5101956129074097, -0.006327990908175707, -0.7744059562683105, -0.19677460193634033, 0.2858528196811676, 0.5596116185188293, 0.3649687170982361, -0.5883057117462158, 0.46705740690231323, 0.15579165518283844, 0.560147225856781, -0.27859172224998474, -0.06379809975624084, 0.06129001826047897, -0.2546755373477936, -0.2366354614496231, -0.9184345602989197, -0.3413490056991577, 0.6346269845962524, -0.03250258043408394, 0.2879641652107239, -0.36563384532928467, 0.23173323273658752, -0.16247425973415375, -0.6811977624893188, -0.658053457736969, -0.4091063439846039, 0.055471088737249374, 0.7057278156280518, -0.27309274673461914, -0.4286412000656128, 0.2886340916156769, 0.1630581170320511, 0.07720249146223068, 0.3400328457355499, -0.36513444781303406, 0.12507714331150055, 0.1549694985151291, 0.18397024273872375, 0.8303784132003784, 0.6109749674797058, 0.4120577871799469, 0.03958522155880928, -0.8686316013336182, -0.053860459476709366, 0.17801834642887115, 0.02613944560289383, -0.6628819108009338, -0.23573781549930573, -0.5942159295082092, -0.12530392408370972, 0.2277049422264099, -0.3976792097091675, 1.4450265169143677, 0.11962782591581345, -0.011352992616593838, -0.28631237149238586, 0.6872963309288025, -0.19620323181152344, 0.5144879221916199, 0.5818504691123962, -0.6254531145095825, 0.22884953022003174, -0.5009803771972656, 0.3145942986011505, -0.2860679030418396, -0.05595133826136589, 1.0449841022491455, 0.010698707774281502, -0.1222226545214653, -0.7531038522720337, -0.5032710433006287, -0.10928524285554886, 0.13201230764389038, 0.1578795611858368, 0.9162445664405823, 0.0036392617039382458, 0.41165247559547424, 0.6642419695854187, 0.17092524468898773, -0.43601325154304504, 0.5502778887748718, 0.7019280791282654, -0.6510776877403259, -0.21624456346035004, 0.14473767578601837, 0.7246900796890259, -0.89271479845047, 0.28724175691604614, 0.2873438596725464, 0.20372645556926727, -0.2621360421180725, 0.08908002823591232, 0.3115270137786865, -0.46605542302131653, 0.5144928693771362, -0.05361611396074295, -0.37816452980041504, 0.24936220049858093, -0.25535067915916443, -0.5467643737792969, 0.8907882571220398, 0.543053388595581, 0.08300336450338364, -0.008378816768527031, -0.5629078149795532, -0.07834821194410324, 0.05003201588988304, -0.11352808028459549, -0.5734981894493103, -0.32679882645606995, -0.0439654216170311, 0.3551671504974365, 0.3951454162597656, 0.9053782224655151, -0.20558694005012512, -0.28024545311927795, -0.08849956840276718, 0.39517465233802795, -0.5088270306587219, -0.2523898482322693, 0.2659788131713867, -0.2198033630847931, 0.25042110681533813, 0.7808077335357666, -0.3530254364013672, 0.5067251920700073, 0.1808379739522934, 1.0310512781143188, 0.7711237072944641, -0.17671415209770203, -0.3187863230705261, -2.0455617904663086, 0.7322452068328857, 0.08264461159706116, -0.012442823499441147, -0.14395827054977417, 0.2866179049015045, 0.34318897128105164, -0.00832295324653387, 0.3786383271217346, -0.6690447330474854, 0.4211524426937103, 0.0022459584288299084, 0.3574274480342865, -0.00783796701580286, 0.1823907196521759, 0.17532795667648315, 0.41425415873527527, -0.4134805202484131, -0.17258119583129883, -1.082025408744812, -0.1172749474644661, 0.3316648006439209, -0.538201630115509, -0.9871743321418762, -0.3778163492679596, 0.4081255793571472, 0.032346971333026886, -0.2343883514404297, 0.31831762194633484, 0.43049749732017517, 0.046488743275403976, 0.3765175938606262, 0.25258195400238037, -0.17542579770088196, 0.17597125470638275, -0.22738239169120789, -0.128386989235878, 0.38068288564682007, 0.30140772461891174, -0.1962948888540268, -0.013175011612474918, 0.8297450542449951, -0.01981859840452671, -0.2532227635383606, 0.3258879780769348, -0.1396588385105133, 0.597024142742157, 0.3359094560146332, 0.5004715323448181, -0.026264525949954987, -0.13022708892822266, -0.22275246679782867, -0.041957393288612366, -0.29446038603782654, 0.01590629294514656, 0.6742022037506104, 0.33339935541152954, -0.33994272351264954, -0.29297909140586853, -0.8612285852432251, 0.25693845748901367, 0.18330124020576477, -0.382478803396225, -0.0217266995459795, 0.5983209609985352, -0.4108423590660095, 0.14602437615394592, 0.2968698740005493, 0.5523532629013062, -0.19680151343345642, -0.382252961397171, -0.2957623302936554, 0.27340811491012573, 0.3983306884765625, 0.1435021013021469, 0.1268370896577835, 0.6780037879943848, -0.041033294051885605, 0.46964964270591736, -0.2681453227996826, -0.3503507375717163, -0.007155228406190872, -0.2787597179412842, 0.28897175192832947, 0.8301249146461487, -5.458395004272461, 0.17187079787254333, -0.6209625601768494, -0.330730676651001, 0.057267215102910995, -0.7226327657699585, 0.13138820230960846, -0.27789080142974854, 0.038894567638635635, -0.2801416218280792, 0.09414400160312653, 0.6199294924736023, 0.1018252745270729, -0.7341530323028564, 0.3996795117855072, 0.590160071849823]</t>
+          <t>['medium', 'medium', 'high', 'low', 'high', 'medium']</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>[-0.5, -0.5, 0.0, 0.5, -0.5, -1.0]</t>
+          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[3, 5, 5, 5, 3, 1]</t>
+          <t>[45.0, 35.0, 40.0, 35.0, 40.0, 50.0]</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
+          <t>['man', 'woman', 'man', 'man', 'woman', 'man']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>[30.0, 30.0, 30.0, 60.0, 45.0, 30.0]</t>
+          <t>[5, 1, 2, 2, 1, 1]</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>['man', 'man', 'man', 'woman', 'woman', 'man']</t>
+          <t>[4, 4, 5, 2, 3, 5]</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1, 1]</t>
+          <t>[5, 5, 5, 3, 5, 5]</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>[3, 3, 4, 5, 4, 5]</t>
+          <t>[3, 4, 4, 2, 5, 4]</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>[1, 1, 4, 2, 1, 3]</t>
+          <t>[3, 1, 2, 3, 2, 1]</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>[5, 3, 4, 5, 4, 3]</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>[1, 1, 3, 1, 1, 1]</t>
-        </is>
+          <t>[3, 5, 5, 5, 5, 5]</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>6</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>[1, 1, 4, 2, 1, 1]</t>
+          <t>[3, 5, 5, 3, 5, 5]</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>[2, 1, 4, 2, 2, 2]</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>[0.16666667 0.66666667 0.         0.16666667 0.        ]</t>
-        </is>
-      </c>
-      <c r="T18" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>524</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>fuck black culture and its shitty ass values</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>[5, 5, 1, 5, 5, 5]</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>[5, 5, 4, 5, 5, 5]</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>['{}', '{}', nan, '{}', '{}', '{}']</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>[-0.09207677841186523, 0.5539317727088928, -0.4886804521083832, -0.08987221866846085, -0.7303043007850647, -0.42936405539512634, 0.549062967300415, 1.0861015319824219, 0.09388432651758194, -0.4257853925228119, 0.32209524512290955, 0.05537068843841553, -0.538631021976471, 0.4653983414173126, 0.3331025540828705, 0.2594566345214844, -0.2206936776638031, 0.24038486182689667, 0.2943410277366638, 0.5947030186653137, -0.24107839167118073, -0.24798277020454407, -0.12001525610685349, 0.0808521956205368, 0.20502535998821259, 0.2667677700519562, -0.013346388936042786, -0.14876782894134521, -0.374642014503479, 0.19202101230621338, -0.11935878545045853, 0.029771557077765465, -0.1841069757938385, -0.3551378548145294, 0.6492818593978882, -0.2960340082645416, 0.163191020488739, -0.014789605513215065, -0.31052854657173157, 0.2211834043264389, 0.06355831772089005, 0.2135901153087616, 0.12824231386184692, 0.13043522834777832, 0.1252267062664032, -0.6160646677017212, -2.5478925704956055, 0.011571772396564484, 0.3227500319480896, -0.35011178255081177, 0.2207452356815338, -0.44986772537231445, -0.2637580633163452, 0.3011975586414337, 0.5456625819206238, 0.09795729070901871, -0.6157270073890686, 0.42673659324645996, 0.1170223131775856, 0.2023949921131134, 0.2784780263900757, 0.43986618518829346, -0.3914400637149811, -0.34568363428115845, 0.07382489740848541, 0.01869605854153633, 0.06694886088371277, 0.40731537342071533, -0.910248339176178, -0.12885141372680664, -0.7273026704788208, -0.7105759382247925, 0.5377011895179749, -0.747650146484375, -0.24328771233558655, -0.4069191515445709, -0.23240898549556732, 0.5393906831741333, -0.43431299924850464, -0.4218793511390686, 0.3519969582557678, 0.1380547136068344, 0.06916447728872299, -0.04717686027288437, 0.1311807632446289, 0.7394717931747437, 0.14727509021759033, -0.031088991090655327, 0.3411461412906647, 0.5634101629257202, -0.31931033730506897, 0.3932741582393646, 0.5512082576751709, 0.7299264073371887, 0.34969833493232727, -0.549348771572113, 0.6373559236526489, -0.3717312216758728, -0.36452677845954895, 0.3652024269104004, -0.007381012663245201, 0.0071009686216712, 0.5332419276237488, -0.5249122977256775, 0.010551206767559052, -0.14858520030975342, -0.02542111463844776, 0.010466034524142742, 0.09864615648984909, -2.5844757556915283, 0.5957626700401306, 0.49298295378685, -0.4574260115623474, -0.24008813500404358, 0.03229048475623131, 0.23308996856212616, 0.34263941645622253, -0.5754170417785645, 0.6079723834991455, 0.1813964694738388, -0.0835920050740242, 0.22241312265396118, -0.25063055753707886, 0.7518185973167419, 0.17977356910705566, 0.25477010011672974, -0.17117460072040558, 0.034474682062864304, 0.2806079685688019, 0.04084733501076698, 0.1618807017803192, 0.6793881058692932, -0.16968891024589539, -0.18974271416664124, -0.18863709270954132, 0.16355210542678833, 0.5284349918365479, 0.07106860727071762, 0.3540315628051758, -0.5478783845901489, -0.48659148812294006, -0.5783679485321045, -2.5122835636138916, 0.17896239459514618, 0.6994249820709229, -0.3638940453529358, -0.06668264418840408, 0.10276265442371368, 0.13510897755622864, 0.12448087334632874, -0.027252910658717155, 0.4102465510368347, -0.16034221649169922, -0.2960588037967682, -0.03994911536574364, -0.5458240509033203, -0.4447164833545685, -0.17434059083461761, 0.5135950446128845, 0.8092958927154541, 0.33364418148994446, -0.8504906296730042, -0.06832923740148544, 0.3287340998649597, -0.14475297927856445, -0.1829390972852707, 0.249649316072464, 0.2783643901348114, 0.10864487290382385, -0.4147399663925171, 0.006863148882985115, 0.4914395809173584, 0.7543002367019653, 0.06995577365159988, 0.7124042510986328, 0.09960583597421646, 0.3718360960483551, 0.339571475982666, -0.14929218590259552, 0.368806391954422, -0.6446895003318787, 0.499041348695755, -0.21510621905326843, 0.25346633791923523, 0.5231924653053284, -0.10181517153978348, 0.342827707529068, -0.27508994936943054, -0.01652923971414566, 0.20221316814422607, -0.3397148549556732, -0.7520100474357605, 0.31133824586868286, 0.20573382079601288, 0.31987839937210083, -0.9730750918388367, 0.11000809818506241, -0.34870272874832153, 0.14858520030975342, 0.4916045665740967, -0.12705481052398682, -0.41594573855400085, -0.32635924220085144, 0.19583165645599365, -0.8514360785484314, 4.1680827140808105, -0.1567930281162262, 0.06395255029201508, 0.14894871413707733, 0.4778017997741699, -0.07492635399103165, 0.29590854048728943, -0.30433082580566406, 0.07246287167072296, -0.09269487112760544, -0.2251143455505371, 0.3862561583518982, -0.16236549615859985, -0.6746241450309753, -0.5237709283828735, 0.5832239985466003, 0.010493003763258457, -0.14614541828632355, -0.08170080184936523, -0.18639996647834778, -0.18982850015163422, -0.40353769063949585, 0.2772730588912964, -0.06390834599733353, -1.7066925764083862, 0.5405821204185486, -0.09584751725196838, -0.5521435737609863, 0.28571370244026184, -0.3042885661125183, 0.10628591477870941, -0.47180676460266113, -0.8746636509895325, 0.00018141411419492215, 0.20008215308189392, -0.0398048534989357, -0.07511990517377853, 0.35434281826019287, -0.022100379690527916, -0.5965569019317627, 0.014809150248765945, 0.3447464406490326, -0.49647441506385803, 0.27355217933654785, 0.5063520073890686, 0.4680997431278229, -0.18610842525959015, 0.1293112188577652, -0.3339255154132843, -0.06053396314382553, 0.18454252183437347, -0.30415305495262146, -0.03068888932466507, -0.6223512887954712, -0.33299726247787476, -0.3643702566623688, -0.015125938691198826, 0.31728994846343994, -0.6487419605255127, 0.011192457750439644, -0.3263208866119385, 0.029797010123729706, -0.016509495675563812, 0.19265414774417877, -0.17807669937610626, 0.1962457299232483, -0.1479242891073227, -0.42499566078186035, -3.3424293994903564, -0.3559502363204956, 0.31661614775657654, 0.048279739916324615, 0.5386810898780823, -0.3296792209148407, -0.1755537986755371, 0.1333986520767212, 0.34125345945358276, -0.7773465514183044, 0.9090882539749146, 0.2044602483510971, 0.1900741457939148, 0.51543790102005, -0.4401746988296509, 0.09055879712104797, 0.2958219051361084, 0.11608336865901947, 0.2846194803714752, -0.4692726731300354, -0.28046977519989014, 0.583588719367981, 0.016504108905792236, -0.3644702136516571, -0.07574041187763214, -0.25097280740737915, -0.45417001843452454, -0.2462976574897766, 0.35139596462249756, -0.38490602374076843, 0.1688939929008484, -0.2588595151901245, 0.11939457058906555, -0.013730970211327076, -0.6069274544715881, -2.4709713459014893, 0.3095685541629791, -0.2445523589849472, -0.48537886142730713, 0.01804128661751747, -0.046417467296123505, 0.2820318937301636, -0.20782054960727692, -0.6743133068084717, 0.15807431936264038, -0.31644630432128906, 0.1174711138010025, -0.15961015224456787, 0.20043623447418213, 0.20853325724601746, 0.40425974130630493, 0.4681450128555298, -0.3480047285556793, 0.2023211270570755, 0.5459083318710327, 0.3547308146953583, 0.04023173823952675, 0.07678532600402832, -0.01747230812907219, 0.2743847966194153, 0.35917380452156067, -0.30477073788642883, 0.14759401977062225, -0.3299095034599304, 0.135416641831398, -0.17066165804862976, -0.044049281626939774, 0.05444551259279251, -0.10539961606264114, -0.04602956026792526, -0.7823596596717834, -0.0635848343372345, 0.28917330503463745, 0.2120012491941452, 0.2390878051519394, 0.173731729388237, 1.1767899990081787, -0.36648982763290405, 0.4243791699409485, 1.0135968923568726, 0.2940554618835449, 0.19250896573066711, -0.12075533717870712, 0.15977096557617188, 0.28874292969703674, -0.06283555179834366, 0.23691365122795105, 1.087823510169983, -0.048763975501060486, -0.36300715804100037, -0.4849970042705536, 0.6058593988418579, -0.20301686227321625, 0.19624607264995575, -0.08118022233247757, 0.9088242650032043, -0.17884697020053864, 0.2160388082265854, 0.5456274151802063, -0.3608822822570801, -0.43160301446914673, 0.12823577225208282, -1.4352213144302368, 0.02881244570016861, 0.37336820363998413, -0.06887849420309067, 0.09494596719741821, -0.7659080028533936, -1.0928784608840942, 0.20051229000091553, 0.22853553295135498, -0.4576658606529236, 0.03824125602841377, -0.2376573383808136, -0.17314377427101135, 0.15006625652313232, -0.41263148188591003, -0.2063905894756317, 0.5912903547286987, -0.5205686688423157, -0.3616064786911011, -0.17427867650985718, 0.28798237442970276, -0.6449794173240662, 0.2671812176704407, -0.14338219165802002, 0.6046658158302307, 0.10020236670970917, -0.05563952401280403, -0.22820042073726654, 0.4195074737071991, 0.7972059845924377, -0.8060388565063477, -0.009726583026349545, -0.12668943405151367, -0.4058283269405365, -0.3938961625099182, 0.054679084569215775, 0.20110070705413818, -0.2772071361541748, -0.16128064692020416, -0.38009724020957947, 0.5028891563415527, -0.07351915538311005, 0.5581080317497253, 0.44431135058403015, 0.35239076614379883, 0.2035188525915146, 0.8254641890525818, 0.26341238617897034, -0.5591574907302856, -0.4759039580821991, 0.74257892370224, 0.3702283501625061, -0.21946901082992554, 0.2737635672092438, 0.16560854017734528, -0.7905882000923157, 0.24851089715957642, -0.0589740164577961, -0.0461900420486927, 0.46442711353302, 0.17496271431446075, -0.6255959868431091, -0.4634131193161011, 0.5644592642784119, -0.15463058650493622, -0.4266025125980377, -0.7792283296585083, 0.11166127026081085, -0.4217284619808197, -0.2913893461227417, -0.038558125495910645, 0.061392832547426224, 0.07422591745853424, 0.434150367975235, 0.20743025839328766, 0.13575300574302673, 0.2637503743171692, -0.7551833391189575, 0.826948881149292, -0.10734287649393082, 0.35445454716682434, -0.15849389135837555, 0.3431642949581146, -0.23081976175308228, 0.19653788208961487, -0.4822312593460083, -0.21341876685619354, 0.48487699031829834, -0.21474821865558624, -0.39544016122817993, -0.10586947202682495, 0.4227314591407776, -0.4985336363315582, -0.09525493532419205, 0.4201083481311798, -1.6072624921798706, 0.03666336089372635, 0.8273382186889648, 0.22248657047748566, 0.557503879070282, -0.5070488452911377, -0.8853811025619507, 0.8415718674659729, 0.5639176964759827, 0.5279306769371033, 0.16489334404468536, -0.2843417525291443, -3.962049959227443e-05, 0.14196135103702545, -0.017094366252422333, -0.07389742881059647, 0.47343772649765015, 0.09034526348114014, -0.3247661292552948, 0.021987294778227806, -0.293020635843277, -0.16449913382530212, 0.23000742495059967, -0.15710067749023438, -0.9928672909736633, -0.16098423302173615, -0.19460631906986237, 0.7701150178909302, 0.11376292258501053, 0.21696917712688446, 0.0488344207406044, -0.37253913283348083, -0.6386109590530396, 0.00528811477124691, 0.4687045216560364, -0.46181821823120117, 0.12507419288158417, 0.1579909473657608, 0.5137956738471985, 0.6279675960540771, -0.023112209513783455, 0.26418593525886536, -0.14896781742572784, -0.03987634927034378, 0.4914180636405945, 0.7087992429733276, -0.7759749889373779, 0.33331990242004395, 0.25608178973197937, -0.27848172187805176, -0.7183810472488403, -0.0005446933209896088, -0.19949786365032196, -0.23753294348716736, 0.6614310145378113, -0.20435920357704163, 0.1923881322145462, -0.13755856454372406, -0.43821001052856445, -0.11256707459688187, -0.03701166808605194, -0.15768486261367798, -0.5506129860877991, 0.06120973080396652, -0.5397984981536865, -0.557702898979187, 0.2510114014148712, -0.3796926438808441, -0.44065773487091064, 0.6802731156349182, 0.47371867299079895, 0.24797722697257996, 0.07110874354839325, 0.6258254051208496, -0.395213782787323, 0.3484465181827545, 0.5305983424186707, 0.06957253068685532, 0.33865833282470703, -0.6432678699493408, -0.5415211915969849, -0.5886648893356323, 0.04734060540795326, 0.19695274531841278, -0.16611269116401672, 0.593993067741394, -0.1252448856830597, -0.11627296358346939, -0.8576013445854187, -0.4136153757572174, -0.36311134696006775, -0.7096134424209595, 0.569659948348999, -0.11452741175889969, -0.3580434024333954, -0.2177836149930954, 0.15919771790504456, 0.18412357568740845, -0.10904648900032043, 0.21980758011341095, 0.05704150348901749, 0.23178412020206451, 0.521470308303833, -0.012184835970401764, 0.36096951365470886, 0.2729816138744354, 0.22770506143569946, 0.4666837453842163, -0.2972758412361145, 0.2699989676475525, -0.04185992479324341, -0.28374776244163513, -0.6257646679878235, -0.3691985309123993, 0.0842546671628952, -0.48336660861968994, 0.12822379171848297, -0.514180064201355, 1.7095327377319336, 0.20137310028076172, 0.6364034414291382, -0.4813658893108368, 0.7379443049430847, -0.5042692422866821, 0.07073167711496353, 0.04894202575087547, -0.4413892924785614, 0.33211880922317505, -0.4123273193836212, 0.05890338867902756, 0.3170408606529236, 0.4581742584705353, 0.6045815348625183, 0.44893744587898254, -0.22881171107292175, -0.3988211452960968, -0.8537609577178955, 0.3891943693161011, -0.06442642956972122, 0.39945605397224426, 0.2520159184932709, -0.15215907990932465, 0.6923807263374329, 0.33629894256591797, 0.04254663735628128, 0.16987118124961853, 0.388701856136322, 0.2408447265625, -0.5716602206230164, -0.5591132640838623, 0.2075619399547577, 0.43637171387672424, -0.2696622610092163, 0.4365426301956177, 0.35346922278404236, -0.4008263945579529, 0.16505315899848938, 0.11622165143489838, -0.18499049544334412, -0.6107390522956848, 1.0024456977844238, 0.28315597772598267, 0.20146802067756653, 0.6804682016372681, -0.8200511336326599, -0.23142440617084503, 1.175907850265503, 0.7521394491195679, -0.6652565598487854, 0.06321346759796143, -0.5548615455627441, -0.09087187051773071, 0.13653773069381714, 0.09585954993963242, 0.010004794225096703, -0.5833569765090942, -0.3149902820587158, 0.06056264787912369, 0.20227913558483124, 0.2968130111694336, 0.3591706156730652, -0.19437460601329803, 0.22458451986312866, -0.0634840801358223, -0.6736383438110352, -0.02218119613826275, 0.28413522243499756, -0.32437559962272644, 0.008789950050413609, -0.07214021682739258, 0.18845094740390778, -0.4359627068042755, 0.5010125637054443, 0.23743371665477753, 0.6929628252983093, 0.15146404504776, -0.7642250061035156, -2.3710098266601562, 0.25063052773475647, 0.14517530798912048, -0.07108946889638901, 0.04672630503773689, 0.1263846904039383, 0.20986749231815338, -0.1147163063287735, -0.2936842441558838, 0.04603290185332298, -0.03225461021065712, 0.29102057218551636, 0.3810156285762787, 0.45333290100097656, 0.14487051963806152, 0.6118153929710388, 0.30757948756217957, -0.06785126030445099, -0.35640496015548706, -0.3326326906681061, 0.30319181084632874, 0.02549830451607704, -0.6762422919273376, -0.731005847454071, -0.2142500877380371, 0.6122284531593323, -0.0016781872836872935, -0.19250956177711487, 0.15654325485229492, 0.705274224281311, -0.14427916705608368, -0.16859959065914154, 0.19713294506072998, 0.26809239387512207, 0.10105668008327484, -0.14779871702194214, 0.016822248697280884, 0.5296590328216553, 0.1997978687286377, -0.2663187086582184, 0.006517838686704636, 1.0160839557647705, -0.0555637888610363, 0.07585783302783966, 0.2706303596496582, -0.4549630582332611, 0.5511307716369629, -0.3373400568962097, 0.4532742202281952, -0.3545864224433899, -0.04384354501962662, -0.09594037383794785, 0.8698383569717407, -0.05178259313106537, 0.33258676528930664, 0.47031715512275696, 0.6598560214042664, 0.11546538770198822, 0.06749016791582108, -0.253324031829834, 0.4647524058818817, 0.057770535349845886, -0.5708246231079102, 0.06464727222919464, 0.6626228094100952, -0.7353842258453369, -0.09237957000732422, 0.03428593650460243, 0.2586599290370941, -0.3709583878517151, -0.5366361141204834, -0.08051017671823502, 0.1135953739285469, -0.015008542686700821, 0.2558586299419403, 0.3183533847332001, -0.14542274177074432, 0.11241333186626434, -0.05065510794520378, -0.0980234369635582, -0.0671328604221344, 0.40798136591911316, -0.510352373123169, 0.6232460141181946, 0.0832802951335907, -6.705783843994141, 0.1445479542016983, -0.689847469329834, -0.4087517559528351, -0.060350630432367325, 0.35945701599121094, 0.5040393471717834, -0.11690885573625565, -0.011995993554592133, -0.18605490028858185, -0.11548792570829391, -0.14097164571285248, -0.7841743230819702, -0.2946627736091614, 0.5305153727531433, -0.04631921276450157]</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>[-0.5, 0.0, 1.0, 0.0, -1.0, -0.5]</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>[4, 4, 3, 5, 4, 3]</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>[40.0, 35.0, 35.0, 40.0, 35.0, 45.0]</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>['woman', 'man', 'man', 'woman', 'woman', 'woman']</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>[1, 1, 5, 1, 1, 2]</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>[4, 4, 1, 5, 5, 3]</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>[5, 5, 3, 5, 5, 5]</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>[2, 4, 5, 5, 5, 3]</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>[1, 1, 5, 1, 1, 2]</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>[5, 5, 4, 5, 5, 5]</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>[5, 5, 1, 5, 5, 5]</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>[0.16666667 0.         0.         0.         0.83333333]</t>
-        </is>
-      </c>
-      <c r="T19" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>532</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>i don't care what people say, blacks have ugly eyelashes!</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>[5, 4, 2, 5, 4, 5]</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>[5, 4, 3, 5, 5, 5]</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>['{}', '{}', nan, '{}', '{}', '{}']</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>[0.3178290128707886, 0.10239183902740479, -0.11476724594831467, -0.36375901103019714, -0.36237186193466187, -0.41822826862335205, 0.8114929795265198, 0.8226035833358765, 0.015632908791303635, -0.02184436284005642, 0.3810977041721344, 0.07789675146341324, -0.23651397228240967, 0.6637969613075256, 0.34074077010154724, 0.21933189034461975, -0.1088080182671547, 0.6738126873970032, 0.14059105515480042, 0.27983593940734863, 0.06379428505897522, 0.054791759699583054, 0.14457303285598755, -0.22016137838363647, 0.2701249420642853, 0.05367879197001457, 0.15531150996685028, 0.09729461371898651, -0.2680453956127167, 0.38965362310409546, 0.0255469661206007, 0.2759043872356415, -0.21872280538082123, -0.09607071429491043, 0.34788602590560913, 0.1032172441482544, -0.19383643567562103, 0.23799005150794983, 0.3081347346305847, -0.08856489509344101, -0.3680383265018463, -0.008165808394551277, 0.05631920322775841, 0.3257201015949249, -0.025120623409748077, -0.7171140313148499, -3.697481632232666, 0.030419575050473213, -0.05621812120079994, -0.21742181479930878, 0.3587227463722229, -0.055416692048311234, -0.10288751870393753, 0.2767459750175476, 0.4768860340118408, 0.24538254737854004, -0.7688122987747192, 0.3975811004638672, 0.05128214508295059, -0.11075896769762039, 0.4630963206291199, 0.31846335530281067, -0.2371349334716797, 0.1418432593345642, 0.07651340216398239, -0.06399254500865936, -0.33069223165512085, 0.4392860531806946, -0.5617997646331787, 0.327305406332016, -0.4372338354587555, -0.4273378252983093, 0.5820342898368835, -0.17024697363376617, 0.0066853356547653675, 0.22184494137763977, -0.2538670301437378, 0.20100060105323792, -0.03629477322101593, -0.01644526980817318, 0.20905143022537231, 0.23847690224647522, 0.19586864113807678, 0.5681434869766235, -0.0628216341137886, 0.4179542064666748, -0.2806306779384613, -0.1879318505525589, 0.3311823606491089, 0.11373984068632126, -0.5474014282226562, 0.5985790491104126, 0.28691375255584717, 0.7240774035453796, 0.5711860656738281, 0.11142688244581223, 0.25095927715301514, -0.32087624073028564, 0.24886628985404968, 0.48312270641326904, 0.33089393377304077, -0.05113549157977104, 0.19944733381271362, -0.5722564458847046, 0.1838422566652298, 0.022338157519698143, 0.16338063776493073, -0.0030694101005792618, 0.07884974032640457, -2.0721664428710938, -0.015036610886454582, 0.04997970163822174, -0.2607838809490204, -0.5626741051673889, -0.18570996820926666, 0.6480815410614014, 0.9943816661834717, -0.14401407539844513, 0.2748371958732605, -0.03653500974178314, -0.20427599549293518, 0.214805006980896, -0.0003503956540953368, 0.1118980422616005, -0.000880928011611104, 0.2857811748981476, -0.009128241799771786, 0.13659217953681946, 0.07612977921962738, 0.5355508327484131, 0.42376551032066345, 0.6106972694396973, 0.14373356103897095, -0.6812952756881714, -0.25014743208885193, -0.26924389600753784, 0.0725250169634819, -0.05188699811697006, 0.2956802248954773, -0.702297568321228, -0.6648094058036804, -0.3556015193462372, -3.171976327896118, -0.16649021208286285, 0.36025020480155945, -0.11256016045808792, -0.17645633220672607, 0.20427873730659485, -0.2681315839290619, 0.050901029258966446, -0.039721034467220306, 0.04984547197818756, 0.1513742059469223, -0.1160421371459961, -0.40699702501296997, -0.19959257543087006, -0.5362390279769897, -0.6461457014083862, 0.4425687789916992, 0.8744749426841736, 0.46416622400283813, -0.42880091071128845, 0.09208685904741287, -0.13576056063175201, -0.6159741878509521, 0.006246821954846382, -0.012874806299805641, 0.5242388248443604, -0.07190714031457901, 0.18002425134181976, 0.12760958075523376, 0.2915216386318207, 0.5698289275169373, 0.5354433655738831, 0.3741929531097412, -0.09688294678926468, 0.40825629234313965, 0.22084283828735352, -0.013420681469142437, 0.15149706602096558, -0.5481065511703491, 0.4304220974445343, 0.49689963459968567, 0.37205496430397034, 0.6509963274002075, -0.23185811936855316, 0.6323235034942627, -0.12313517928123474, -0.40808552503585815, 0.07589013874530792, -0.30722445249557495, -0.43197187781333923, 0.5265432000160217, 0.28396832942962646, 0.5526182651519775, -0.301524817943573, -0.010343475267291069, -0.675250768661499, 0.13405895233154297, 0.3530687987804413, -0.2234785556793213, -0.17826460301876068, -0.023949459195137024, 0.11615504324436188, -0.8593055605888367, 4.0816779136657715, 0.38256481289863586, 0.506350040435791, -0.17642618715763092, -0.030151478946208954, -0.25705447793006897, -0.21991893649101257, -0.19466450810432434, -0.08364331722259521, -0.5324355959892273, -0.06204473227262497, 0.18522165715694427, -0.1943001002073288, -0.05798938497900963, -0.1412401646375656, 0.41235655546188354, 0.1926671266555786, -0.81796795129776, -0.18015016615390778, -0.27012649178504944, -0.2830410599708557, -0.4524245858192444, 0.15923626720905304, 0.47140100598335266, -1.6662919521331787, -0.19039961695671082, -0.11349762976169586, -0.622284471988678, 0.1604740470647812, -0.35672590136528015, 0.25981709361076355, 0.03358006849884987, -0.30627140402793884, 0.2004551887512207, 0.2902931272983551, 0.02713005058467388, 0.25503918528556824, -0.021845756098628044, -0.15893229842185974, -0.5003278255462646, 0.3588217496871948, 0.2749781608581543, -0.5514739751815796, 0.12394151091575623, 0.1468334197998047, 0.3860962986946106, 0.10803407430648804, 0.050527509301900864, -0.2731114327907562, 0.5762656331062317, 0.2551869750022888, 0.06531742960214615, 0.1965276598930359, -0.44029682874679565, -0.5220707654953003, -0.3185743987560272, 0.18917140364646912, -0.02108854614198208, 0.49037256836891174, -0.7395579814910889, 0.025739816948771477, 0.533722460269928, -0.1292879730463028, -0.1983276605606079, -0.0432647280395031, 0.2409040480852127, -0.035341229289770126, -0.3541575074195862, -2.9297053813934326, -0.08479741960763931, 0.021079175174236298, 0.2860349416732788, 0.38344720005989075, -0.6833804845809937, -0.08141251653432846, 0.30410897731781006, 0.20582348108291626, -0.7580112814903259, 0.2756516635417938, 0.06699526309967041, 0.07445107400417328, 0.6172996163368225, -0.17588016390800476, 0.000624565058387816, 0.13952888548374176, -0.11202564090490341, -0.1833079755306244, -0.38377317786216736, -0.004958410281687975, -0.06973333656787872, -0.41195443272590637, 0.37922513484954834, 0.18800000846385956, -0.15920796990394592, -0.1602652370929718, 0.006327876355499029, 0.2832682430744171, -0.05514715984463692, 0.22836129367351532, -0.08670590072870255, 0.13243547081947327, -0.1733023226261139, -0.3345315754413605, -3.01965594291687, 0.4222930073738098, -0.8078866004943848, -0.1128508672118187, -0.18127180635929108, -0.23230208456516266, 0.2636905014514923, -0.4050457179546356, -0.4651086628437042, -0.1807374209165573, -0.07088081538677216, 0.05146618187427521, -0.40740126371383667, 0.1772375851869583, 0.06352062523365021, 0.14165939390659332, 0.5618035793304443, -0.44658002257347107, 0.42768368124961853, 0.25497007369995117, 0.19803869724273682, 0.353390097618103, -0.05107853561639786, -0.11288909614086151, 0.4059546887874603, 0.6097323298454285, -0.0691559836268425, -0.32643991708755493, -0.06257450580596924, 0.11599870026111603, 0.042409319430589676, -0.11751864850521088, 0.014958227053284645, 0.08047997951507568, -0.46279415488243103, -0.615379273891449, 0.016986368224024773, -0.15076854825019836, -0.08685240149497986, -0.0912666767835617, 0.15628284215927124, 0.179706409573555, -0.2489253133535385, 0.5835107564926147, 0.5514633059501648, -0.37599968910217285, -0.23888236284255981, -0.39467012882232666, 0.18706075847148895, 0.10529324412345886, -0.10886818170547485, 0.05332183837890625, 1.2599209547042847, 0.22694937884807587, 0.02924051135778427, -0.36978262662887573, 0.5089397430419922, 0.3125283122062683, 0.16938962042331696, 0.007531516253948212, 0.8146932125091553, -0.521347165107727, 0.45961061120033264, -0.44753149151802063, -0.30125996470451355, -0.5636686086654663, 0.1429644376039505, -0.7877346873283386, 0.10312972962856293, -0.06809363514184952, 0.3004058003425598, -0.03891661763191223, -0.5368148684501648, -1.2549655437469482, 0.2277093529701233, 0.5465510487556458, -0.4619835317134857, 0.07783440500497818, -0.15816718339920044, 0.25796911120414734, 0.1753653734922409, 0.13074277341365814, -0.16768798232078552, 0.2754327952861786, -0.9065729379653931, -0.7740568518638611, -0.13421224057674408, 0.4488590955734253, -0.7264787554740906, -0.14593349397182465, 0.22523514926433563, 0.22471266984939575, -0.1057622879743576, 0.5115225911140442, -0.023077676072716713, 0.3679957985877991, 0.2808476984500885, -0.7109429240226746, 0.2377968728542328, -0.11369037628173828, -0.636688232421875, 0.011828661896288395, -0.22300094366073608, 0.058919504284858704, 0.19698579609394073, -0.041727203875780106, -0.3986758291721344, 0.6360142230987549, 0.3149747848510742, 0.2726794183254242, 0.1880592405796051, -0.22031806409358978, 0.17020444571971893, 0.1336197853088379, 0.8650107383728027, -0.4129146933555603, 0.13352249562740326, 0.689819872379303, 0.3317730724811554, -0.13477714359760284, 0.4351412355899811, 0.22699934244155884, -0.5261520147323608, -0.252032071352005, -0.4594962000846863, 0.21584567427635193, 0.06116924807429314, 0.1596737504005432, -0.32284748554229736, -0.2410893440246582, 0.17741866409778595, -0.19955284893512726, -0.4295524060726166, -0.13255363702774048, -0.04817747324705124, -0.4331332743167877, -0.5517920851707458, -0.11285775154829025, 0.1155739426612854, 0.16166500747203827, 0.7808359265327454, 0.06180420517921448, -0.266052782535553, 0.14467792212963104, -0.6349380016326904, 0.6865395903587341, -0.16453486680984497, 0.24350227415561676, -0.3068883419036865, 0.6657521724700928, -0.45100465416908264, -0.33533960580825806, 0.1006559431552887, -0.722244381904602, 0.028571253642439842, 0.2917702794075012, 0.18320608139038086, 0.24310755729675293, 0.015671702101826668, -0.3208126425743103, 0.3846209943294525, 0.22857631742954254, -1.9528627395629883, 0.5012966990470886, 0.9084088802337646, -0.08533928543329239, 0.05154767259955406, -0.013666770420968533, -0.4861103594303131, 0.6887986063957214, 0.23679949343204498, 0.1553003042936325, -0.45157042145729065, 0.3714326024055481, -0.08172550797462463, -0.062164969742298126, 0.2986617386341095, 0.0022061646450310946, 0.12585614621639252, -0.40211084485054016, -0.09953337907791138, -0.32677894830703735, -0.013727682642638683, 0.04074687883257866, -0.003061263356357813, 0.2130429595708847, 0.11286765336990356, -0.25941458344459534, -0.10247025638818741, 0.5157378315925598, 0.041849441826343536, 0.3375122845172882, -0.30114805698394775, -0.51937335729599, -1.035048007965088, -0.2220967411994934, 0.38335567712783813, -0.0707942470908165, 0.11698025465011597, -0.02834555320441723, 0.1169268935918808, 0.6203681230545044, -0.3981836438179016, 0.24443642795085907, 0.36320415139198303, -0.034797146916389465, 0.16525602340698242, 0.28812357783317566, -0.33845919370651245, 0.7256311178207397, 0.41673406958580017, -0.4662820100784302, -0.050794102251529694, -0.3079737424850464, -0.518174409866333, -0.2851100564002991, -0.1614101529121399, -0.12463169544935226, -0.26805752515792847, -0.06680461764335632, -0.527797281742096, -0.30554795265197754, 0.16832223534584045, 0.1055736094713211, -0.6987255215644836, -0.09530651569366455, -0.420940101146698, -0.4368963837623596, -0.13748814165592194, -0.49693793058395386, -0.4304982125759125, 0.5964179635047913, 0.41087958216667175, 0.5130544304847717, -0.36287999153137207, 0.6467273831367493, -0.23141054809093475, 0.47616568207740784, 0.38674426078796387, 0.6591209769248962, 0.7304102778434753, -0.24590998888015747, -0.3116670548915863, -0.2682085633277893, 0.049408920109272, 0.14404767751693726, -0.1910923421382904, 0.18940436840057373, -0.36761435866355896, -0.4496142864227295, -0.01180657185614109, -0.16459856927394867, -0.8409638404846191, -0.4400877058506012, 0.41922080516815186, -0.16013425588607788, -0.23263578116893768, -0.029039261862635612, 0.29853183031082153, -0.02489907294511795, -0.27976560592651367, 0.1367831975221634, -0.25684019923210144, 0.2044648826122284, 0.7107626795768738, -0.0253220796585083, 0.2849123477935791, 0.539524495601654, 0.6193115711212158, 0.44126051664352417, -0.43868157267570496, -0.5356076955795288, 0.22818973660469055, 0.05499788373708725, -0.43889692425727844, 0.01826854795217514, -0.12598079442977905, -0.3851776123046875, 0.6365671753883362, -0.5234556794166565, 1.7954857349395752, 0.17044395208358765, 0.19688577950000763, -0.5938403606414795, 0.766260027885437, 0.0266216229647398, 0.009084911085665226, 0.4070001244544983, -0.564960777759552, 0.6384594440460205, -0.29173001646995544, 0.18685133755207062, 0.32141754031181335, -0.20222462713718414, 0.6612817645072937, 0.07573270052671432, 0.20782363414764404, -0.21493597328662872, -0.8244983553886414, 0.07976940274238586, -0.35827571153640747, 0.005567710846662521, 0.4103812873363495, -0.3335261940956116, 0.3947809338569641, -0.08709628880023956, 0.19580988585948944, 0.4658792316913605, 0.5411419868469238, 0.40445709228515625, -0.28611642122268677, 0.0011573572410270572, 0.040768589824438095, 0.3506779074668884, -0.7072327733039856, 0.19739621877670288, 0.17927265167236328, -0.14105170965194702, -0.08905243873596191, -0.14587201178073883, 0.014287149533629417, -0.36493411660194397, 0.5249089002609253, 0.4155149459838867, -0.25347691774368286, 0.6343210339546204, 0.18844017386436462, 0.022665685042738914, 0.8267415761947632, 0.6401751041412354, -0.07753286510705948, 0.1586126685142517, 0.04739563539624214, -0.03973737731575966, 0.3120069205760956, -0.6261382102966309, -0.12330929934978485, -0.36402928829193115, -0.3237949311733246, 0.3672733008861542, -0.3001103103160858, 0.5377870202064514, -0.10330035537481308, -0.05779179185628891, -0.2205026000738144, 0.276619553565979, -0.5923020243644714, 0.026666752994060516, 0.4371810555458069, -0.4832971692085266, -0.09147767722606659, 0.5475842356681824, 0.2304360419511795, 0.21169742941856384, 0.6075694561004639, 0.40696874260902405, 0.5113222599029541, -0.3288068473339081, -0.3397929072380066, -2.692147731781006, 0.2222317010164261, 0.03578074648976326, -0.35610431432724, 0.007962488569319248, 0.03735833615064621, 0.451713502407074, -0.5335475206375122, 0.15730077028274536, -0.3083885908126831, 0.20037321746349335, 0.26826179027557373, 0.6502943634986877, -0.1777511090040207, 0.43551963567733765, 0.17934951186180115, 0.4104495644569397, -0.7759630680084229, -0.23554158210754395, -0.16214756667613983, 0.3669126629829407, -0.048725228756666183, -0.3797934353351593, -0.5388696789741516, -0.15991052985191345, 0.39365890622138977, 0.36786317825317383, -0.29767605662345886, 0.2500801682472229, 0.2785571217536926, -0.20446781814098358, 0.03701528161764145, -0.3479590117931366, -0.09338356554508209, 0.026182884350419044, 0.20700770616531372, -0.41867637634277344, -0.2345036119222641, 0.09002657979726791, -0.1296250969171524, 0.05358113721013069, 0.8617005348205566, 0.1505686193704605, 0.3604157865047455, 0.21959498524665833, -0.5554285645484924, 0.35931360721588135, -0.15595899522304535, 0.5334513783454895, -0.5534942150115967, 0.3308084011077881, -0.09824980050325394, 0.4121018648147583, -0.15363092720508575, 0.1612711399793625, 0.5054649710655212, 0.15062491595745087, 0.12625688314437866, 0.6255545616149902, -0.41161537170410156, -0.15873116254806519, 0.021237412467598915, -0.7597692608833313, -0.4906468391418457, 0.1361885517835617, -0.23200711607933044, 0.0914301648736, 0.23062466084957123, 0.09575571864843369, -0.37169191241264343, -0.39582139253616333, -0.01463584415614605, 0.6340214014053345, 0.41077250242233276, 0.2476183921098709, -0.1906171441078186, 0.5966098308563232, 0.3448713421821594, 0.041410740464925766, -0.3336430490016937, -0.2897225320339203, 0.46667343378067017, -0.2016831338405609, 0.1746119260787964, 0.08616087585687637, -6.443469524383545, -0.015813056379556656, -0.030953986570239067, -0.3500092327594757, -0.04499375820159912, -0.2934625446796417, -0.36923083662986755, -0.4219139814376831, 0.2635336220264435, -0.21958096325397491, 0.14683985710144043, 0.17002972960472107, -0.26208263635635376, -0.36339879035949707, 0.3144693672657013, 0.0725860670208931]</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>[-0.5, 0.0, 1.0, 0.0, 0.0, -1.0]</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>[4, 4, 3, 5, 5, 4]</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>[40.0, 35.0, 35.0, 40.0, 35.0, 25.0]</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>['woman', 'man', 'man', 'woman', 'woman', 'man']</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>[1, 1, 5, 1, 3, 1]</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>[4, 4, 1, 5, 4, 4]</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>[5, 4, 3, 5, 4, 5]</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>[2, 4, 5, 5, 3, 5]</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>[1, 1, 5, 1, 1, 1]</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>[5, 4, 3, 5, 4, 5]</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>[5, 4, 2, 5, 4, 5]</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>[0.         0.16666667 0.         0.33333333 0.5       ]</t>
-        </is>
-      </c>
-      <c r="T20" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>548</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>in this park we do not tolerate blacks</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>[3, 5, 5, 3, 5, 5]</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>[2, 5, 5, 3, 5, 5]</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>['NONE', 'immigrant, black,', '{}', '{}', '{}', 'none']</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>[0.06542951613664627, 0.2752820551395416, -0.2803797423839569, -0.366268515586853, 0.05562972649931908, -0.519413411617279, 0.6720623970031738, 0.5900916457176208, -0.1716737002134323, -0.3192693293094635, -0.07483824342489243, -0.003215445438399911, -0.4281359314918518, 0.5166827440261841, -0.088563933968544, 0.34768766164779663, -0.2528613805770874, 0.35923194885253906, 0.3392036557197571, 0.045056361705064774, 0.07619444280862808, -0.6390796899795532, 0.04614903777837753, -0.04403029382228851, 0.17528334259986877, 0.14079222083091736, 0.47185635566711426, 0.04644393548369408, -0.2118707001209259, 0.06145154684782028, 0.014198154211044312, 0.7264453768730164, -0.34078449010849, -0.01236241590231657, 0.32796913385391235, -0.14168980717658997, 0.4656215310096741, -0.09081058949232101, 0.41443443298339844, 0.34052619338035583, -0.019505953416228294, 0.4002962112426758, 0.2679675817489624, -0.18182975053787231, 0.3001735210418701, -0.1238376572728157, -2.340409278869629, -0.08848140388727188, 0.06558354198932648, -0.11751441657543182, 0.09589787572622299, 0.06016072258353233, 0.13836857676506042, 0.6089949011802673, 0.2728179097175598, 0.20456023514270782, -1.0769975185394287, 0.4687470495700836, -0.112444669008255, -0.2570725083351135, 0.4820742905139923, -0.09354456514120102, 0.24511533975601196, 0.1115189716219902, -0.040647249668836594, 0.30476129055023193, -0.0971221774816513, 0.1808919757604599, -0.20280013978481293, 0.49869242310523987, -0.19988283514976501, -0.04561638832092285, -0.015296922996640205, -0.359256386756897, 0.13645435869693756, -0.42705386877059937, -0.06144292652606964, 0.19754964113235474, -0.21248558163642883, 0.25242745876312256, 0.4833492338657379, 0.48231688141822815, 0.23671069741249084, 0.15401162207126617, -0.2778342664241791, 0.6144955158233643, -0.17438779771327972, -0.1640305370092392, 0.39431843161582947, 0.5255261659622192, -0.3347185552120209, 0.6879211068153381, -0.053765956312417984, -0.016842199489474297, 0.25952932238578796, 0.006228066980838776, 0.25852489471435547, -0.23611032962799072, 0.18522855639457703, 0.42658770084381104, 0.004914236720651388, 0.07811927795410156, 0.25725987553596497, -0.481618195772171, -0.22430402040481567, -0.25407159328460693, 0.21069994568824768, -0.24982990324497223, 0.5174286961555481, -2.374084949493408, 0.4912332594394684, 0.43870702385902405, -0.1231810450553894, -0.5540099740028381, -0.2935381531715393, 0.49966225028038025, 0.46331751346588135, -0.23870889842510223, 0.21653889119625092, 0.253555029630661, -0.22819289565086365, 0.5253382325172424, -0.2695360481739044, 0.20262503623962402, -0.032063767313957214, 0.49477705359458923, 0.3519546091556549, 0.07438965886831284, -0.04099863022565842, 0.38522833585739136, 0.25994405150413513, 0.7131580114364624, 0.0609976090490818, -0.2156645953655243, 0.06564763933420181, -0.16983146965503693, 0.38094931840896606, -0.35930517315864563, -0.18682116270065308, -0.23709191381931305, -0.16966839134693146, -0.22022730112075806, -2.857715368270874, 0.32602712512016296, 0.7434707283973694, -0.06335563957691193, -0.18642088770866394, -0.21578840911388397, -0.07115736603736877, 0.16610324382781982, 0.11719558387994766, 0.15278135240077972, -0.07640992105007172, 0.16065873205661774, -0.18850205838680267, -0.26771214604377747, -0.5130138397216797, -0.2908531129360199, -0.08771564066410065, 0.6268574595451355, 0.23305700719356537, -0.2847402095794678, 0.30332151055336, -0.12301035970449448, -0.4919525682926178, 0.18760015070438385, -0.10345747321844101, 0.32238927483558655, 0.30008095502853394, -0.0013318908168002963, -0.020034611225128174, -0.24134448170661926, 0.2216472029685974, -0.03258974477648735, 0.20941472053527832, -0.26795515418052673, -0.11076788604259491, 0.3224753439426422, -0.163328617811203, -0.2244458645582199, -0.4870402216911316, 0.31048133969306946, -0.15384294092655182, 0.46308931708335876, 0.42015549540519714, -0.1545983850955963, 0.10707101970911026, -0.037063367664813995, -0.011218355037271976, 0.004642909858375788, 0.13995517790317535, -0.42978912591934204, 0.22713802754878998, 0.11765456199645996, 0.9966655969619751, 0.07487355172634125, 0.03376685455441475, -0.858711838722229, 0.2566445469856262, 0.3236630856990814, -0.2966313362121582, 0.022997207939624786, -0.10165958851575851, 0.021653514355421066, -0.664036214351654, 3.791908025741577, -0.2165302038192749, -0.057661838829517365, -0.06867098808288574, -0.06964997947216034, -0.23182344436645508, -0.010603826493024826, -0.059202875941991806, -0.0681241974234581, 0.0208883173763752, -0.130255326628685, 0.5005201101303101, -0.3648514449596405, -0.02715982310473919, -0.21289485692977905, -0.07861272990703583, 0.004165711812674999, -0.20742622017860413, 0.26811671257019043, -0.4642944633960724, -0.30871227383613586, 0.10498519241809845, 0.6497268676757812, -0.18394531309604645, -1.3015373945236206, 0.2934492528438568, -0.1078108549118042, -0.058901600539684296, 0.6075884103775024, -0.23802801966667175, 0.10556783527135849, 0.17353671789169312, -0.36670947074890137, 0.33055898547172546, 0.08335018157958984, 0.2559818923473358, -0.019354604184627533, 0.06284598261117935, 0.4363253116607666, -0.19460628926753998, 0.3102932870388031, 0.5118298530578613, -0.30123987793922424, -0.17565226554870605, -0.2508263885974884, 0.5513836145401001, 0.039101969450712204, 0.09573893994092941, -0.38651883602142334, 0.35400840640068054, 0.07265511155128479, 0.4903225898742676, -0.10552472621202469, -0.007976824417710304, -0.4716736674308777, -0.25732216238975525, 0.14745421707630157, -0.28284889459609985, -0.16726019978523254, -0.3909052014350891, -0.5069007873535156, -0.05330459401011467, -0.07633145898580551, -0.2581637501716614, -0.1268012523651123, 0.22000274062156677, 7.823620762792416e-06, -0.11684514582157135, -3.6138668060302734, -0.2328820377588272, 0.36421507596969604, 0.12829890847206116, 0.5319105982780457, -0.19345387816429138, 0.07712158560752869, 0.17443689703941345, 0.010844092816114426, -0.37118279933929443, 0.398647665977478, 0.2663410007953644, 0.39245253801345825, 0.45056581497192383, -0.24597565829753876, 0.20253755152225494, -0.06381038576364517, -0.07929246127605438, -0.11407162994146347, -0.00533336354419589, -0.21120353043079376, 0.2282213419675827, 0.4283309876918793, -0.07126649469137192, 0.053447723388671875, 0.07883564382791519, -0.18997403979301453, 0.06051689013838768, 0.10616321861743927, -0.28053751587867737, -0.060602884739637375, -0.1846550703048706, 0.11146088689565659, -0.14383207261562347, -0.13156424462795258, -3.6613433361053467, 0.075385183095932, -0.4343496263027191, 0.3091271221637726, -0.14939476549625397, -0.016685808077454567, 0.3031253218650818, -0.054301969707012177, -0.7727558612823486, -0.06857039034366608, -0.32759279012680054, -0.023837203159928322, 0.04454948753118515, 0.487642377614975, 0.5667736530303955, 0.01459045521914959, 0.21316394209861755, -0.2219974249601364, 0.25060898065567017, 0.2907245457172394, -0.19705308973789215, 0.23863419890403748, -0.2715792953968048, -0.1849154829978943, 0.04512789845466614, 0.3472994565963745, 0.32692474126815796, -0.39586779475212097, -0.2792796194553375, -0.2750850319862366, -0.08866844326257706, -0.29556185007095337, 0.019782820716500282, -0.47928380966186523, -0.32047203183174133, -0.009952963329851627, 0.009643759578466415, -0.02120574750006199, -0.08168069273233414, -0.23497451841831207, 0.035894934087991714, 0.22056975960731506, 0.2447870522737503, 0.5469666719436646, 0.38382527232170105, 0.14666056632995605, -0.07708615809679031, -0.4718410074710846, 0.0932588055729866, 0.5013386607170105, -0.020257405936717987, 0.2518567442893982, 0.9862360954284668, -0.1258668601512909, -0.32930248975753784, -0.11320123076438904, 0.5533416867256165, -0.002805395284667611, 0.11337792873382568, -0.19019170105457306, 0.523865818977356, -0.33615565299987793, 0.01451100967824459, 0.17639391124248505, 0.10807938128709793, -0.007838274352252483, 0.8168046474456787, -0.5217655897140503, -0.38323524594306946, -0.21575459837913513, 0.10833781212568283, 0.5331732034683228, -0.17052222788333893, -0.9311783313751221, -0.32274261116981506, 0.060797858983278275, -0.8237393498420715, -0.11915884912014008, 0.2952396273612976, -0.3736104667186737, -0.038626983761787415, -0.1940736621618271, -0.01667632721364498, 0.5824722051620483, -0.3150504231452942, -0.41340523958206177, 0.24886205792427063, 0.08709277957677841, -0.42236652970314026, -0.02044542320072651, -0.2636040151119232, 0.13958194851875305, -0.18028277158737183, 0.14607606828212738, -0.01557077094912529, 0.14682528376579285, 0.38269177079200745, -0.8633493185043335, 0.14412708580493927, 0.187173530459404, 0.1593504399061203, -0.14910367131233215, -0.14707359671592712, -0.16732418537139893, -0.003572130110114813, -0.1893690675497055, 0.29818665981292725, 0.4453355073928833, -0.3019447326660156, 0.34646934270858765, 0.1847735047340393, -0.22417829930782318, 0.3462854325771332, 0.4087770879268646, 0.8422523140907288, -0.19372540712356567, 0.42301222681999207, 0.15728798508644104, 0.27401652932167053, -0.06862451881170273, 0.475763738155365, -0.13260647654533386, 0.016726352274417877, -0.03498304635286331, -0.4377710521221161, 0.1290552169084549, 0.3647311329841614, -0.2576809227466583, -0.5333080887794495, -0.22753946483135223, -0.17135272920131683, -0.47567978501319885, 0.0084040816873312, -0.7645049095153809, -0.1954449564218521, -0.04009755700826645, -0.19097696244716644, 0.16838400065898895, 0.2876010537147522, 0.0610639713704586, 0.25657153129577637, 0.11606813222169876, -0.34084808826446533, 0.5706855654716492, -0.36468881368637085, 0.5212602019309998, 0.2630261778831482, -0.284606397151947, -0.43960586190223694, 0.6699817776679993, 0.0019840870518237352, -0.3743111789226532, 0.06146860495209694, 0.07210598140954971, 0.705437958240509, -0.20436535775661469, 0.27575987577438354, 0.17167571187019348, 0.08440222591161728, -0.11205282807350159, -0.34222546219825745, 0.5665172338485718, -1.7539664506912231, 0.23422352969646454, 0.4806429147720337, 0.20467016100883484, 0.3329566419124603, -0.2411932498216629, -0.6098619103431702, 0.827480137348175, -0.011815933510661125, 0.15714895725250244, -0.36778491735458374, 0.45756641030311584, -0.15764187276363373, -0.6137815713882446, 0.0010934253223240376, 0.300637811422348, 0.23053330183029175, -0.21886318922042847, -0.17479832470417023, 0.3022359311580658, -0.06598839908838272, 0.3194499611854553, 0.02913070283830166, -0.40702828764915466, -0.4012545049190521, -0.5335376858711243, 0.12548023462295532, 0.4095432162284851, 0.006551775615662336, 0.19784681499004364, 0.1143823191523552, -0.20229768753051758, -0.26399946212768555, 0.03760896995663643, 0.01603955775499344, -0.21332010626792908, 0.09599433094263077, 0.08978354185819626, 0.4031115770339966, 0.3550644814968109, -0.22150066494941711, 0.5095629692077637, -0.029683662578463554, -0.07872558385133743, 0.3176214098930359, 0.14919519424438477, -0.4995405673980713, 0.5696553587913513, -0.04519068822264671, -0.034602608531713486, -0.45484301447868347, -0.22550088167190552, -0.36013734340667725, -0.31040722131729126, 0.1499396562576294, -0.11968621611595154, -0.05094432085752487, 0.15807077288627625, 0.0028889761306345463, -0.2332758605480194, 0.2507484257221222, -0.11539354175329208, -0.32144400477409363, -0.025625750422477722, -0.3760386109352112, -0.6561665534973145, 0.22208364307880402, -0.3335438072681427, -0.5893524289131165, 0.4576795697212219, 0.7468323111534119, 0.1013479083776474, -0.37245973944664, 0.3754979074001312, -0.3144984543323517, 0.3091440200805664, -0.27985647320747375, 0.247010737657547, 0.24373774230480194, -0.234327033162117, -0.20659887790679932, -0.400088906288147, -0.5254981517791748, 0.32225051522254944, -0.30145835876464844, 0.14879585802555084, -0.5564079880714417, 0.022115685045719147, -0.4395817518234253, -0.38132601976394653, -0.1307106912136078, -0.6458512544631958, 0.22276107966899872, 0.05792204290628433, 0.3096204996109009, 0.20322799682617188, 0.5600916743278503, 0.24699924886226654, 0.3997212052345276, -0.29368123412132263, -0.38225293159484863, 0.3412907123565674, -0.011757437139749527, 0.2099413126707077, 0.32495108246803284, 0.20721624791622162, 0.6310094594955444, 0.013107993640005589, -0.596835196018219, -0.39014187455177307, -0.0456426627933979, -0.005724747199565172, -0.2630394697189331, -0.31611019372940063, 0.11373727023601532, -0.10042542219161987, 0.08883348852396011, -0.6009144186973572, 2.2276694774627686, 0.23975661396980286, 0.16557428240776062, -0.18201781809329987, 0.19744804501533508, -0.10714031010866165, -0.07597666233778, 0.39446717500686646, -0.37181565165519714, 0.07301065325737, -0.19584734737873077, -0.0391942597925663, 0.28371956944465637, 0.4580077528953552, 0.24766619503498077, 0.11595679074525833, -0.15810394287109375, -0.5239324569702148, -0.5993211269378662, -0.20434719324111938, -0.7009155750274658, 0.19666187465190887, -0.039676275104284286, -0.19118376076221466, -0.07683668285608292, 0.16857463121414185, 0.5181828141212463, -0.031017331406474113, 0.021712061017751694, 0.5085563659667969, -0.020770160481333733, 0.1875363290309906, 0.14169757068157196, 0.5168802738189697, -0.4161372482776642, 0.4914158880710602, 0.07778336107730865, -0.5382490754127502, 0.10357583314180374, -0.35405483841896057, -0.10710477828979492, -0.6492437720298767, 0.3004443943500519, 0.33964455127716064, -0.06920159608125687, 0.47783035039901733, -0.08792142570018768, -0.03201102092862129, 0.3911445438861847, 0.09924548864364624, -0.5022037625312805, 0.0177434291690588, -0.24560122191905975, 0.223948672413826, -0.11860399693250656, 0.4119398593902588, -0.010076001286506653, -0.4504479765892029, -0.4594578742980957, 0.02230376936495304, 0.07768727838993073, -0.050251930952072144, 0.2017861008644104, -0.37010806798934937, 0.3348786532878876, -0.13163146376609802, -0.39257094264030457, 0.22410929203033447, -0.029745599254965782, -0.2532830834388733, -0.12143703550100327, 0.32496359944343567, 0.2333916276693344, 0.6755471229553223, 0.32276609539985657, 0.1733461320400238, 0.25204265117645264, 0.07586497813463211, -0.4377205967903137, -2.769529104232788, 0.4544432759284973, 0.32838186621665955, 0.012190384790301323, 0.07497188448905945, 0.4708220660686493, 0.26103878021240234, -0.20546205341815948, -0.1535782366991043, -0.19048072397708893, 0.2941330671310425, 0.4011881649494171, 0.051886945962905884, 0.08231234550476074, -0.2881695628166199, 0.07403260469436646, -0.09745030850172043, -0.33881762623786926, -0.05550231784582138, -0.17498858273029327, 0.2098562866449356, 0.30321502685546875, 0.24708902835845947, -0.06023227795958519, -0.53069007396698, 0.64193195104599, -0.5958493947982788, 0.11685013771057129, 0.29999005794525146, 0.12501682341098785, -0.20759350061416626, 0.11076117306947708, 0.1373077929019928, -0.1458287090063095, -0.2108181118965149, 0.3835816979408264, -0.15117162466049194, 0.06272338330745697, 0.5402176380157471, -0.24905996024608612, 0.015160761773586273, 0.6394910216331482, -0.0019378141732886434, -0.05720418319106102, -0.2579450011253357, -0.25866368412971497, 0.21396522223949432, -0.5536196827888489, 0.32484281063079834, -0.46896740794181824, 0.28713247179985046, 0.15851736068725586, -0.02966875024139881, 0.08493069559335709, 0.6980795860290527, 0.19657225906848907, 0.4430253803730011, 0.13061928749084473, -0.35202357172966003, -0.5647071003913879, 0.10068339854478836, -0.15559795498847961, -0.6227151155471802, -0.14564599096775055, 0.6397282481193542, -0.038581185042858124, -0.20854376256465912, 0.13810189068317413, -0.2783685028553009, 0.21334274113178253, 0.17344914376735687, 0.1984989494085312, 0.2661448121070862, 0.35895854234695435, -0.10478536039590836, -0.039204079657793045, 0.23021215200424194, 0.24259357154369354, 0.32659101486206055, 0.13926874101161957, -0.1586274802684784, 0.027912447229027748, -0.3082644045352936, 0.4820719361305237, 0.1008857935667038, -6.5540924072265625, -0.14088046550750732, -0.3160800337791443, -0.18826383352279663, -0.029223885387182236, 0.11609763652086258, -0.06840953230857849, -0.1552404910326004, 0.02514498680830002, -0.09281843900680542, 0.04231104254722595, -0.060469258576631546, 0.07564813643693924, -0.27128538489341736, -0.04974394664168358, 0.27303576469421387]</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>[1.0, 0.0, 0.0, 0.5, -0.5, -0.5]</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>[3, 3, 4, 2, 4, 3]</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>[45.0, 35.0, 40.0, 35.0, 40.0, 50.0]</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>['man', 'woman', 'man', 'man', 'woman', 'man']</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>[5, 1, 2, 2, 1, 1]</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>[4, 4, 5, 2, 3, 5]</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>[5, 5, 5, 3, 5, 5]</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>[3, 4, 4, 2, 5, 4]</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>[3, 1, 2, 3, 2, 1]</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>[3, 5, 5, 5, 5, 5]</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>[3, 5, 5, 3, 5, 5]</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
           <t>[0.         0.         0.33333333 0.         0.66666667]</t>
         </is>
       </c>
-      <c r="T21" t="n">
+      <c r="S18" t="n">
         <v>0.5</v>
       </c>
     </row>
